--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB67DC1B-D15B-4D83-A3F3-59B9BACE62E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B313983-DFC3-4787-A45F-0113885F868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="890" yWindow="1430" windowWidth="28800" windowHeight="15370" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="452">
   <si>
     <t>id</t>
   </si>
@@ -767,21 +767,6 @@
     <t>近战吸魔</t>
   </si>
   <si>
-    <t>降低物理抗性</t>
-  </si>
-  <si>
-    <t>降低火焰抗性</t>
-  </si>
-  <si>
-    <t>降低风雷抗性</t>
-  </si>
-  <si>
-    <t>降低神圣抗性</t>
-  </si>
-  <si>
-    <t>降低毒素抗性</t>
-  </si>
-  <si>
     <t>火球术</t>
   </si>
   <si>
@@ -1399,6 +1384,30 @@
   </si>
   <si>
     <t>(d) =&gt; (d.setStat("rtpres", {value:Math.min(75 + d.getStat("mxpres").value, d.getStat("pres").value)}))</t>
+  </si>
+  <si>
+    <t>降低目标物理抗性</t>
+  </si>
+  <si>
+    <t>降低目标火焰抗性</t>
+  </si>
+  <si>
+    <t>降低目标风雷抗性</t>
+  </si>
+  <si>
+    <t>降低目标神圣抗性</t>
+  </si>
+  <si>
+    <t>降低目标毒素抗性</t>
+  </si>
+  <si>
+    <t>prockill</t>
+  </si>
+  <si>
+    <t>击杀触发</t>
+  </si>
+  <si>
+    <t>杀死敌人时，有{0}%概率施展等级{1}的{2}</t>
   </si>
 </sst>
 </file>
@@ -1802,7 +1811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" style="1" customWidth="1"/>
@@ -1833,7 +1842,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -1859,7 +1868,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>5</v>
@@ -1875,7 +1884,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>169</v>
@@ -1904,13 +1913,13 @@
         <v>153</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1924,13 +1933,13 @@
         <v>153</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1944,7 +1953,7 @@
         <v>153</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1958,7 +1967,7 @@
         <v>153</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1972,13 +1981,13 @@
         <v>153</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1992,13 +2001,13 @@
         <v>153</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>160</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -2012,7 +2021,7 @@
         <v>153</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2026,7 +2035,7 @@
         <v>153</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -2040,7 +2049,7 @@
         <v>153</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -2054,7 +2063,7 @@
         <v>153</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -2068,7 +2077,7 @@
         <v>153</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -2082,7 +2091,7 @@
         <v>154</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -2096,7 +2105,7 @@
         <v>154</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -2110,7 +2119,7 @@
         <v>154</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -2124,7 +2133,7 @@
         <v>154</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -2138,7 +2147,7 @@
         <v>154</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -2152,7 +2161,7 @@
         <v>153</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -2166,7 +2175,7 @@
         <v>153</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -2180,7 +2189,7 @@
         <v>153</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -2194,7 +2203,7 @@
         <v>153</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -2208,7 +2217,7 @@
         <v>153</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -2222,7 +2231,7 @@
         <v>153</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -2236,7 +2245,7 @@
         <v>153</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -2250,7 +2259,7 @@
         <v>153</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -2264,7 +2273,7 @@
         <v>153</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -2278,7 +2287,7 @@
         <v>153</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -2292,13 +2301,13 @@
         <v>153</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>161</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -2312,13 +2321,13 @@
         <v>153</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>162</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -2332,13 +2341,13 @@
         <v>153</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>163</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -2352,13 +2361,13 @@
         <v>153</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>164</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -2372,13 +2381,13 @@
         <v>153</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>165</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -2395,7 +2404,7 @@
         <v>157</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -2412,7 +2421,7 @@
         <v>157</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -2429,72 +2438,72 @@
         <v>158</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -2508,7 +2517,7 @@
         <v>153</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -2522,7 +2531,7 @@
         <v>153</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -2536,7 +2545,7 @@
         <v>153</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -2550,7 +2559,7 @@
         <v>153</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -2561,24 +2570,24 @@
         <v>209</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -2592,7 +2601,7 @@
         <v>153</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -2606,7 +2615,7 @@
         <v>153</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -2620,203 +2629,203 @@
         <v>153</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>215</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>154</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>154</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>154</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>154</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>154</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -2830,7 +2839,7 @@
         <v>153</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -2844,7 +2853,7 @@
         <v>153</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -2858,7 +2867,7 @@
         <v>153</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -2872,7 +2881,7 @@
         <v>153</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -2886,7 +2895,7 @@
         <v>153</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -2900,7 +2909,7 @@
         <v>153</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -2914,7 +2923,7 @@
         <v>153</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -2928,7 +2937,7 @@
         <v>153</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -2942,7 +2951,7 @@
         <v>153</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -2956,49 +2965,49 @@
         <v>153</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -3009,10 +3018,10 @@
         <v>226</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -3023,38 +3032,38 @@
         <v>227</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>226</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>227</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -3065,10 +3074,10 @@
         <v>228</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -3079,10 +3088,10 @@
         <v>229</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -3093,38 +3102,38 @@
         <v>230</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>229</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -3135,10 +3144,10 @@
         <v>231</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -3149,10 +3158,10 @@
         <v>232</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -3163,38 +3172,38 @@
         <v>233</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>232</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>233</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -3205,10 +3214,10 @@
         <v>234</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
@@ -3219,10 +3228,10 @@
         <v>235</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -3233,10 +3242,10 @@
         <v>236</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
@@ -3247,10 +3256,10 @@
         <v>237</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -3264,7 +3273,7 @@
         <v>155</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
@@ -3278,91 +3287,91 @@
         <v>153</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -3376,7 +3385,7 @@
         <v>153</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -3390,35 +3399,35 @@
         <v>153</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>242</v>
+        <v>444</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -3426,13 +3435,13 @@
         <v>75</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>243</v>
+        <v>445</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -3440,13 +3449,13 @@
         <v>76</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>244</v>
+        <v>446</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -3454,13 +3463,13 @@
         <v>77</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>245</v>
+        <v>447</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
@@ -3468,13 +3477,13 @@
         <v>78</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>246</v>
+        <v>448</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -3482,13 +3491,13 @@
         <v>79</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
@@ -3496,13 +3505,13 @@
         <v>80</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
@@ -3510,13 +3519,13 @@
         <v>81</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
@@ -3524,13 +3533,13 @@
         <v>82</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
@@ -3538,13 +3547,13 @@
         <v>83</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
@@ -3552,13 +3561,13 @@
         <v>84</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -3566,13 +3575,13 @@
         <v>85</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
@@ -3580,13 +3589,13 @@
         <v>86</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
@@ -3594,13 +3603,13 @@
         <v>87</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
@@ -3608,13 +3617,13 @@
         <v>88</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -3622,13 +3631,13 @@
         <v>89</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -3636,13 +3645,13 @@
         <v>90</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -3650,13 +3659,13 @@
         <v>91</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
@@ -3664,13 +3673,13 @@
         <v>92</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -3678,13 +3687,13 @@
         <v>93</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -3692,13 +3701,13 @@
         <v>94</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -3706,13 +3715,13 @@
         <v>95</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
@@ -3720,13 +3729,13 @@
         <v>96</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -3734,13 +3743,13 @@
         <v>97</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
@@ -3748,13 +3757,13 @@
         <v>98</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
@@ -3762,13 +3771,13 @@
         <v>99</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
@@ -3776,13 +3785,13 @@
         <v>100</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
@@ -3790,13 +3799,13 @@
         <v>101</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
@@ -3804,13 +3813,13 @@
         <v>102</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
@@ -3818,13 +3827,13 @@
         <v>103</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
@@ -3832,13 +3841,13 @@
         <v>104</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
@@ -3846,13 +3855,13 @@
         <v>105</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
@@ -3860,13 +3869,13 @@
         <v>106</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
@@ -3874,13 +3883,13 @@
         <v>107</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
@@ -3888,13 +3897,13 @@
         <v>108</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
@@ -3902,13 +3911,13 @@
         <v>109</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
@@ -3916,13 +3925,13 @@
         <v>110</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
@@ -3930,13 +3939,13 @@
         <v>111</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
@@ -3944,13 +3953,13 @@
         <v>112</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
@@ -3958,13 +3967,13 @@
         <v>113</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
@@ -3972,13 +3981,13 @@
         <v>114</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
@@ -3986,13 +3995,13 @@
         <v>115</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
@@ -4000,13 +4009,13 @@
         <v>116</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
@@ -4014,13 +4023,13 @@
         <v>117</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
@@ -4028,13 +4037,13 @@
         <v>118</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
@@ -4042,13 +4051,13 @@
         <v>119</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
@@ -4056,13 +4065,13 @@
         <v>120</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
@@ -4070,13 +4079,13 @@
         <v>121</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
@@ -4084,13 +4093,13 @@
         <v>122</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
@@ -4098,13 +4107,13 @@
         <v>123</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
@@ -4112,13 +4121,13 @@
         <v>124</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
@@ -4126,13 +4135,13 @@
         <v>125</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
@@ -4140,13 +4149,13 @@
         <v>126</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
@@ -4154,13 +4163,13 @@
         <v>127</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
@@ -4168,13 +4177,13 @@
         <v>128</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
@@ -4182,13 +4191,13 @@
         <v>129</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
@@ -4196,13 +4205,13 @@
         <v>130</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
@@ -4210,13 +4219,13 @@
         <v>131</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
@@ -4224,13 +4233,13 @@
         <v>132</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
@@ -4238,13 +4247,13 @@
         <v>133</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
@@ -4252,13 +4261,13 @@
         <v>134</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
@@ -4266,13 +4275,13 @@
         <v>135</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
@@ -4280,13 +4289,13 @@
         <v>136</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
@@ -4294,13 +4303,13 @@
         <v>137</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
@@ -4308,13 +4317,13 @@
         <v>138</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
@@ -4322,13 +4331,13 @@
         <v>139</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
@@ -4336,13 +4345,13 @@
         <v>140</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
@@ -4350,13 +4359,13 @@
         <v>141</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
@@ -4364,13 +4373,13 @@
         <v>142</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
@@ -4378,13 +4387,13 @@
         <v>143</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.35">
@@ -4392,13 +4401,13 @@
         <v>144</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
@@ -4406,13 +4415,13 @@
         <v>145</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.35">
@@ -4420,13 +4429,13 @@
         <v>146</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
@@ -4434,13 +4443,13 @@
         <v>147</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.35">
@@ -4448,13 +4457,13 @@
         <v>148</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
@@ -4462,13 +4471,13 @@
         <v>149</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.35">
@@ -4476,369 +4485,386 @@
         <v>150</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>153</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>400</v>
+        <v>430</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>451</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A210" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B313983-DFC3-4787-A45F-0113885F868A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC32807-0701-4153-B4FF-80BA75FAAB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="453">
   <si>
     <t>id</t>
   </si>
@@ -1408,6 +1408,9 @@
   </si>
   <si>
     <t>杀死敌人时，有{0}%概率施展等级{1}的{2}</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -4505,7 +4508,7 @@
         <v>153</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
@@ -4519,7 +4522,7 @@
         <v>153</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
@@ -4533,7 +4536,7 @@
         <v>153</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
@@ -4547,7 +4550,7 @@
         <v>153</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
@@ -4561,7 +4564,7 @@
         <v>153</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
@@ -4575,7 +4578,7 @@
         <v>153</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
@@ -4589,7 +4592,7 @@
         <v>153</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
@@ -4603,7 +4606,7 @@
         <v>153</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
@@ -4617,7 +4620,7 @@
         <v>153</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
@@ -4631,7 +4634,7 @@
         <v>153</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
@@ -4645,7 +4648,7 @@
         <v>153</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
@@ -4659,7 +4662,7 @@
         <v>153</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
@@ -4673,7 +4676,7 @@
         <v>153</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
@@ -4687,7 +4690,7 @@
         <v>153</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
@@ -4701,7 +4704,7 @@
         <v>153</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
@@ -4715,7 +4718,7 @@
         <v>153</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
@@ -4729,7 +4732,7 @@
         <v>153</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
@@ -4743,7 +4746,7 @@
         <v>153</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
@@ -4757,7 +4760,7 @@
         <v>395</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
@@ -4771,7 +4774,7 @@
         <v>395</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC32807-0701-4153-B4FF-80BA75FAAB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16856BAD-9DA4-46B5-ACC3-97F7A487F691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BEDE17-D92E-4A75-9F08-D8A6E28964BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A35849E-4E02-46B1-B7D2-A9776EF8D8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="660">
   <si>
     <t>id</t>
   </si>
@@ -2014,6 +2014,24 @@
   </si>
   <si>
     <t>杀死敌人时，有{0.2}%概率施展等级{1}的{2}</t>
+  </si>
+  <si>
+    <t>法师技能等级+{0}（限法师）</t>
+  </si>
+  <si>
+    <t>magelvlmage</t>
+  </si>
+  <si>
+    <t>warrlvlwarr</t>
+  </si>
+  <si>
+    <t>战士技能等级+{0}（限战士）</t>
+  </si>
+  <si>
+    <t>wlklvlwlk</t>
+  </si>
+  <si>
+    <t>道士技能等级+{0}（限道士）</t>
   </si>
 </sst>
 </file>
@@ -2417,7 +2435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:G222"/>
+  <dimension ref="A1:G225"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" style="1" customWidth="1"/>
@@ -3762,147 +3780,147 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>421</v>
+        <v>61</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>61</v>
+        <v>422</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>62</v>
+        <v>655</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>548</v>
+        <v>654</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>423</v>
+        <v>63</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>424</v>
+        <v>64</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>64</v>
+        <v>423</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>65</v>
+        <v>424</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>66</v>
+        <v>656</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>551</v>
+        <v>657</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>425</v>
+        <v>65</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>232</v>
@@ -3911,12 +3929,12 @@
         <v>395</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>426</v>
+        <v>66</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>233</v>
@@ -3925,7 +3943,7 @@
         <v>395</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
@@ -3944,1314 +3962,1323 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>68</v>
+        <v>425</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>69</v>
+        <v>426</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>70</v>
+        <v>658</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>555</v>
+        <v>659</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>155</v>
+        <v>395</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>408</v>
+        <v>70</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>409</v>
+        <v>237</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>310</v>
+        <v>71</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>566</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>311</v>
+        <v>72</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>316</v>
+        <v>239</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>312</v>
+        <v>408</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>317</v>
+        <v>409</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>240</v>
+        <v>317</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>74</v>
+        <v>313</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>241</v>
+        <v>318</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>410</v>
+        <v>314</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>411</v>
+        <v>319</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>393</v>
+        <v>73</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>439</v>
+        <v>240</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>440</v>
+        <v>241</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>77</v>
+        <v>393</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>322</v>
+        <v>441</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>323</v>
+        <v>442</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>324</v>
+        <v>443</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>242</v>
+        <v>325</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>243</v>
+        <v>326</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>244</v>
+        <v>327</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>250</v>
+        <v>303</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>304</v>
+        <v>251</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>256</v>
+        <v>309</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>328</v>
+        <v>257</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>329</v>
+        <v>258</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>262</v>
+        <v>333</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>334</v>
+        <v>263</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>335</v>
+        <v>264</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>336</v>
+        <v>265</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>267</v>
+        <v>338</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>340</v>
+        <v>269</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>341</v>
+        <v>270</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>342</v>
+        <v>271</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>274</v>
+        <v>345</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
-        <v>320</v>
+        <v>148</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>346</v>
+        <v>275</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
-        <v>347</v>
+        <v>149</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>348</v>
+        <v>276</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
-        <v>349</v>
+        <v>150</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>153</v>
@@ -5259,10 +5286,10 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>153</v>
@@ -5270,10 +5297,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>153</v>
@@ -5281,10 +5308,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>153</v>
@@ -5292,10 +5319,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>153</v>
@@ -5303,10 +5330,10 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>153</v>
@@ -5314,10 +5341,10 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>153</v>
@@ -5325,10 +5352,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>153</v>
@@ -5336,10 +5363,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>153</v>
@@ -5347,10 +5374,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>153</v>
@@ -5358,10 +5385,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>153</v>
@@ -5369,10 +5396,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>153</v>
@@ -5380,10 +5407,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>153</v>
@@ -5391,10 +5418,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>153</v>
@@ -5402,10 +5429,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>153</v>
@@ -5413,43 +5440,43 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>395</v>
@@ -5457,68 +5484,101 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>651</v>
+        <v>395</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>652</v>
+        <v>395</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
-        <v>444</v>
+        <v>387</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>445</v>
+        <v>388</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>653</v>
+        <v>395</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>429</v>
+        <v>391</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>395</v>
+        <v>427</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A223" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A225" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="B225" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E222" s="1" t="s">
+      <c r="C225" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E225" s="1" t="s">
         <v>468</v>
       </c>
     </row>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A35849E-4E02-46B1-B7D2-A9776EF8D8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D146E65-B167-4856-830B-111F77E61CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="661">
   <si>
     <t>id</t>
   </si>
@@ -2032,6 +2032,9 @@
   </si>
   <si>
     <t>道士技能等级+{0}（限道士）</t>
+  </si>
+  <si>
+    <t>{0}</t>
   </si>
 </sst>
 </file>
@@ -2528,6 +2531,9 @@
       <c r="C5" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2545,6 +2551,9 @@
       <c r="C6" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E6" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>159</v>
       </c>
@@ -2590,6 +2599,9 @@
       <c r="C9" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>12</v>
       </c>
@@ -2607,6 +2619,9 @@
       <c r="C10" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E10" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>160</v>
       </c>
@@ -2915,6 +2930,9 @@
       <c r="C32" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E32" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="F32" s="1" t="s">
         <v>161</v>
       </c>
@@ -2932,6 +2950,9 @@
       <c r="C33" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E33" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="F33" s="1" t="s">
         <v>162</v>
       </c>
@@ -2949,6 +2970,9 @@
       <c r="C34" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E34" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="F34" s="1" t="s">
         <v>163</v>
       </c>
@@ -2966,6 +2990,9 @@
       <c r="C35" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E35" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="F35" s="1" t="s">
         <v>164</v>
       </c>
@@ -2982,6 +3009,9 @@
       </c>
       <c r="C36" s="1" t="s">
         <v>153</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>165</v>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D146E65-B167-4856-830B-111F77E61CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7059665-3048-4C91-AEB0-E085789585C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="679">
   <si>
     <t>id</t>
   </si>
@@ -2035,6 +2035,60 @@
   </si>
   <si>
     <t>{0}</t>
+  </si>
+  <si>
+    <t>d2m</t>
+  </si>
+  <si>
+    <t>反馈</t>
+  </si>
+  <si>
+    <t>从受损的生命中恢复{0.2}%的魔法值</t>
+  </si>
+  <si>
+    <t>killhp</t>
+  </si>
+  <si>
+    <t>killmp</t>
+  </si>
+  <si>
+    <t>击杀回血</t>
+  </si>
+  <si>
+    <t>击杀回蓝</t>
+  </si>
+  <si>
+    <t>杀死敌人后，恢复{0}点生命值</t>
+  </si>
+  <si>
+    <t>杀死敌人后，恢复{0}点魔法值</t>
+  </si>
+  <si>
+    <t>debuffrd</t>
+  </si>
+  <si>
+    <t>净化</t>
+  </si>
+  <si>
+    <t>负面效果持续时间-{0}回合</t>
+  </si>
+  <si>
+    <t>resil</t>
+  </si>
+  <si>
+    <t>韧性</t>
+  </si>
+  <si>
+    <t>受到暴击几率降低{0.2}%</t>
+  </si>
+  <si>
+    <t>barg</t>
+  </si>
+  <si>
+    <t>商谈</t>
+  </si>
+  <si>
+    <t>商人物品售价降低{0.2}%</t>
   </si>
 </sst>
 </file>
@@ -2438,20 +2492,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:G225"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G231"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.54296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.1796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2474,7 +2528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -2497,12 +2551,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>321</v>
       </c>
@@ -2521,7 +2575,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2541,7 +2595,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2561,7 +2615,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -2575,7 +2629,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -2589,7 +2643,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -2609,7 +2663,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -2629,7 +2683,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -2643,7 +2697,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -2657,7 +2711,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -2671,7 +2725,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -2685,7 +2739,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -2696,7 +2750,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>473</v>
       </c>
@@ -2710,7 +2764,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -2724,7 +2778,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -2738,7 +2792,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -2752,7 +2806,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -2766,7 +2820,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -2780,7 +2834,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -2794,7 +2848,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -2808,7 +2862,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -2822,7 +2876,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -2836,7 +2890,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -2850,7 +2904,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -2864,7 +2918,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -2878,7 +2932,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -2892,7 +2946,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -2906,7 +2960,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -2920,7 +2974,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -2940,7 +2994,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -2960,7 +3014,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,7 +3034,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -3000,7 +3054,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -3020,7 +3074,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -3037,7 +3091,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -3054,7 +3108,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -3071,7 +3125,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>399</v>
       </c>
@@ -3088,7 +3142,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>400</v>
       </c>
@@ -3105,7 +3159,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>406</v>
       </c>
@@ -3122,7 +3176,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>404</v>
       </c>
@@ -3136,7 +3190,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>41</v>
       </c>
@@ -3150,7 +3204,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>42</v>
       </c>
@@ -3164,7 +3218,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>43</v>
       </c>
@@ -3178,7 +3232,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>44</v>
       </c>
@@ -3192,7 +3246,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>45</v>
       </c>
@@ -3206,7 +3260,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>420</v>
       </c>
@@ -3220,7 +3274,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>46</v>
       </c>
@@ -3234,7 +3288,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>47</v>
       </c>
@@ -3248,7 +3302,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>48</v>
       </c>
@@ -3262,7 +3316,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>278</v>
       </c>
@@ -3276,7 +3330,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>294</v>
       </c>
@@ -3290,7 +3344,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>295</v>
       </c>
@@ -3304,7 +3358,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>296</v>
       </c>
@@ -3318,7 +3372,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>297</v>
       </c>
@@ -3332,2284 +3386,2368 @@
         <v>506</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B59" s="1" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E71" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E72" s="1" t="s">
+      <c r="C73" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="1" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" s="1" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E75" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" s="1" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" s="1" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A78" s="1" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E78" s="1" t="s">
+      <c r="C79" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E80" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E82" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" s="1" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E83" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="1" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="1" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E85" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E86" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="C88" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" s="1" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E89" s="1" t="s">
+      <c r="C90" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E90" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="1" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E91" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" s="1" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E92" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" s="1" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E93" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="1" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E94" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" s="1" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E95" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" s="1" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E96" s="1" t="s">
+      <c r="C97" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" s="1" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E97" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A98" s="1" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E98" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A99" s="1" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" s="1" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E100" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" s="1" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E101" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A102" s="1" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A103" s="1" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E103" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A104" s="1" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A105" s="1" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E105" s="1" t="s">
+      <c r="C106" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E106" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A107" s="1" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E107" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A108" s="1" t="s">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E108" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A109" s="1" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E109" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E110" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A111" s="1" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" s="1" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A113" s="1" t="s">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A114" s="1" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E114" s="1" t="s">
+      <c r="C115" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A115" s="1" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E115" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A116" s="1" t="s">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E116" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A117" s="1" t="s">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E117" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A118" s="1" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E118" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A119" s="1" t="s">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E119" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A120" s="1" t="s">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E120" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A121" s="1" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B122" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E121" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A122" s="1" t="s">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B123" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E122" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A123" s="1" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B124" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E123" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A124" s="1" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B125" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E124" s="1" t="s">
+      <c r="C125" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A125" s="1" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B126" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E125" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A126" s="1" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B127" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A127" s="1" t="s">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E127" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A128" s="1" t="s">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E128" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A129" s="1" t="s">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E129" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" s="1" t="s">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E130" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A131" s="1" t="s">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E131" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A132" s="1" t="s">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E132" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A133" s="1" t="s">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E133" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A134" s="1" t="s">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E134" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A135" s="1" t="s">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B136" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E135" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A136" s="1" t="s">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B137" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E136" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A137" s="1" t="s">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B138" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A138" s="1" t="s">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E138" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A139" s="1" t="s">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E139" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A140" s="1" t="s">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A141" s="1" t="s">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E141" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A142" s="1" t="s">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B143" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E142" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A143" s="1" t="s">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B144" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E143" s="1" t="s">
+      <c r="C144" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A144" s="1" t="s">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B145" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E144" s="1" t="s">
+      <c r="C145" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E145" s="1" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A145" s="1" t="s">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B146" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E145" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A146" s="1" t="s">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E146" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A147" s="1" t="s">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B148" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E147" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A148" s="1" t="s">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E148" s="1" t="s">
+      <c r="C149" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A149" s="1" t="s">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B150" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E149" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A150" s="1" t="s">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B151" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E150" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A151" s="1" t="s">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E151" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A152" s="1" t="s">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B153" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E152" s="1" t="s">
+      <c r="C153" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A153" s="1" t="s">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B154" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E153" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A154" s="1" t="s">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B155" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E154" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A155" s="1" t="s">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B156" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E155" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A156" s="1" t="s">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B157" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E156" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A157" s="1" t="s">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B158" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E157" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A158" s="1" t="s">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B159" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E158" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A159" s="1" t="s">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B160" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E159" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A160" s="1" t="s">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B161" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E160" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A161" s="1" t="s">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B162" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E161" s="1" t="s">
+      <c r="C162" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A162" s="1" t="s">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B163" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E162" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A163" s="1" t="s">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B164" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E163" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A164" s="1" t="s">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B165" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E164" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A165" s="1" t="s">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B166" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E165" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A166" s="1" t="s">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B167" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E166" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A167" s="1" t="s">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B168" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E167" s="1" t="s">
+      <c r="C168" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A168" s="1" t="s">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B169" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E168" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A169" s="1" t="s">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="B170" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E169" s="1" t="s">
+      <c r="C170" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A170" s="1" t="s">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="B171" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A171" s="1" t="s">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="B172" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E171" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A172" s="1" t="s">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B173" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E172" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A173" s="1" t="s">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="B174" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E173" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A174" s="1" t="s">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="B175" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E174" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A175" s="1" t="s">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B176" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E175" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A176" s="1" t="s">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="B177" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E176" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A177" s="1" t="s">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B178" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E177" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A178" s="1" t="s">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B179" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E179" s="1" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A179" s="1" t="s">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="B180" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E179" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A180" s="1" t="s">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B181" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E180" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A181" s="1" t="s">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E181" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A182" s="1" t="s">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B183" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A183" s="1" t="s">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B184" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A184" s="1" t="s">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="B185" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E184" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A185" s="1" t="s">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="B186" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E185" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A186" s="1" t="s">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="B187" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E186" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A187" s="1" t="s">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B188" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E187" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A188" s="1" t="s">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="B189" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E188" s="1" t="s">
+      <c r="C189" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A189" s="1" t="s">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="B190" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E189" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A190" s="1" t="s">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="B191" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E190" s="1" t="s">
+      <c r="C191" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A191" s="1" t="s">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="B192" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E191" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A192" s="1" t="s">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B193" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C192" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E192" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A193" s="1" t="s">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="B194" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E193" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A194" s="1" t="s">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="B195" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E194" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A195" s="1" t="s">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B196" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E195" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A196" s="1" t="s">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="B197" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E196" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A197" s="1" t="s">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="B198" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E197" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A198" s="1" t="s">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="B199" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E198" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A199" s="1" t="s">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="B200" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="B201" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A201" s="1" t="s">
+      <c r="C201" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="B202" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A202" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="B203" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="B204" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A204" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="B205" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="B206" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="B207" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A207" s="1" t="s">
+      <c r="C207" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="B208" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="B209" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A209" s="1" t="s">
+      <c r="C209" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="B210" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A210" s="1" t="s">
+      <c r="C210" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="B211" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A211" s="1" t="s">
+      <c r="C211" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="B212" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="B213" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="B214" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A214" s="1" t="s">
+      <c r="C214" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="B215" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="B216" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A216" s="1" t="s">
+      <c r="C216" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="B217" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A217" s="1" t="s">
+      <c r="C217" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="B218" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C217" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A218" s="1" t="s">
+      <c r="C218" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="B219" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A219" s="1" t="s">
+      <c r="C219" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="B220" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A220" s="1" t="s">
+      <c r="C220" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="B221" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A221" s="1" t="s">
+      <c r="C221" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="B222" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A222" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>427</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>444</v>
+        <v>390</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>445</v>
+        <v>392</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>427</v>
       </c>
       <c r="E223" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E224" s="1" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A224" s="1" t="s">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B224" s="1" t="s">
+      <c r="B227" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A225" s="1" t="s">
+      <c r="C227" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="B230" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E225" s="1" t="s">
+      <c r="C230" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E230" s="1" t="s">
         <v>468</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>678</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7059665-3048-4C91-AEB0-E085789585C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06558918-F4B9-400B-B4E3-DAF17A74315B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="682">
   <si>
     <t>id</t>
   </si>
@@ -2089,6 +2089,15 @@
   </si>
   <si>
     <t>商人物品售价降低{0.2}%</t>
+  </si>
+  <si>
+    <t>ucb</t>
+  </si>
+  <si>
+    <t>圣言</t>
+  </si>
+  <si>
+    <t>圣言几率+{0.2}%</t>
   </si>
 </sst>
 </file>
@@ -2117,7 +2126,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2127,6 +2136,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2143,10 +2176,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2492,7 +2529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G232"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="1" customWidth="1"/>
@@ -2577,2960 +2614,2987 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>173</v>
+        <v>394</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>430</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>174</v>
+        <v>395</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>431</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>175</v>
+        <v>396</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>469</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>174</v>
+        <v>397</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>398</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>176</v>
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>177</v>
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>178</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>470</v>
+        <v>660</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>177</v>
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>472</v>
+        <v>660</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>179</v>
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>180</v>
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>181</v>
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>153</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>474</v>
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>499</v>
+        <v>537</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>420</v>
+        <v>54</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>419</v>
+        <v>221</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>500</v>
+        <v>538</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>501</v>
+        <v>541</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>278</v>
+        <v>58</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>502</v>
+        <v>545</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>294</v>
+        <v>412</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>295</v>
+        <v>413</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>291</v>
+        <v>416</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>296</v>
+        <v>414</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>292</v>
+        <v>417</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>293</v>
+        <v>187</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>506</v>
+        <v>478</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>661</v>
+        <v>24</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>662</v>
+        <v>188</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>663</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>394</v>
+        <v>25</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>395</v>
+        <v>26</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>396</v>
+        <v>27</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>397</v>
+        <v>38</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>398</v>
+        <v>202</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>280</v>
+        <v>39</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>285</v>
+        <v>203</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>281</v>
+        <v>40</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>286</v>
+        <v>204</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>282</v>
+        <v>399</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>289</v>
+        <v>401</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>283</v>
+        <v>400</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>287</v>
+        <v>402</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>284</v>
+        <v>406</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>288</v>
+        <v>418</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>456</v>
+        <v>405</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>457</v>
+        <v>192</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>448</v>
+        <v>29</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>458</v>
+        <v>193</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>449</v>
+        <v>30</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>459</v>
+        <v>194</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>450</v>
+        <v>31</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>460</v>
+        <v>195</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>451</v>
+        <v>32</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>461</v>
+        <v>196</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>452</v>
+        <v>33</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>462</v>
+        <v>197</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>453</v>
+        <v>34</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>463</v>
+        <v>198</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>454</v>
+        <v>35</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>464</v>
+        <v>199</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>455</v>
+        <v>36</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>465</v>
+        <v>200</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>50</v>
+        <v>393</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>217</v>
+        <v>439</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>218</v>
+        <v>440</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>535</v>
+        <v>575</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>219</v>
+        <v>441</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>536</v>
+        <v>576</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>220</v>
+        <v>442</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>537</v>
+        <v>577</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>221</v>
+        <v>443</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>55</v>
+        <v>310</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>222</v>
+        <v>315</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>539</v>
+        <v>566</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>56</v>
+        <v>311</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>223</v>
+        <v>316</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>540</v>
+        <v>567</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>57</v>
+        <v>312</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>224</v>
+        <v>317</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>541</v>
+        <v>568</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>58</v>
+        <v>313</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>225</v>
+        <v>318</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>545</v>
+        <v>569</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>412</v>
+        <v>314</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>415</v>
+        <v>319</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>416</v>
+        <v>41</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>543</v>
+        <v>495</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>417</v>
+        <v>42</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>544</v>
+        <v>496</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>226</v>
+        <v>43</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>546</v>
+        <v>497</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>227</v>
+        <v>44</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>547</v>
+        <v>498</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>228</v>
+        <v>45</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>558</v>
+        <v>499</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>226</v>
+        <v>420</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>419</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>556</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>227</v>
+        <v>661</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>662</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>557</v>
+        <v>663</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>228</v>
+        <v>17</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>654</v>
+        <v>153</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>229</v>
+        <v>473</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>474</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>548</v>
+        <v>475</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>63</v>
+        <v>676</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>230</v>
+        <v>677</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>549</v>
+        <v>678</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>64</v>
+        <v>408</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>231</v>
+        <v>409</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>423</v>
+        <v>381</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>229</v>
+        <v>382</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>230</v>
+        <v>384</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>231</v>
+        <v>46</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>657</v>
+        <v>507</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>232</v>
+        <v>47</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>550</v>
+        <v>508</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>233</v>
+        <v>48</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>551</v>
+        <v>501</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>234</v>
+        <v>278</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>279</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>552</v>
+        <v>502</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>232</v>
+        <v>294</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>290</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>562</v>
+        <v>503</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>295</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>291</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>563</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>296</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>659</v>
+        <v>505</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>235</v>
+        <v>297</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>293</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>553</v>
+        <v>506</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>70</v>
+        <v>679</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>237</v>
+        <v>680</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>555</v>
+        <v>681</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>71</v>
+        <v>670</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>238</v>
+        <v>671</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>155</v>
+        <v>395</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>72</v>
+        <v>673</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>239</v>
+        <v>674</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>564</v>
+        <v>675</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>153</v>
+        <v>427</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>565</v>
+        <v>651</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>153</v>
+        <v>427</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>566</v>
+        <v>652</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>311</v>
+        <v>444</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>316</v>
+        <v>445</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>153</v>
+        <v>427</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>317</v>
+        <v>59</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>318</v>
+        <v>60</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>319</v>
+        <v>61</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>240</v>
+        <v>421</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>241</v>
+        <v>422</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>411</v>
+        <v>655</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>573</v>
+        <v>654</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>439</v>
+        <v>62</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>440</v>
+        <v>63</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>441</v>
+        <v>64</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>442</v>
+        <v>423</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>443</v>
+        <v>424</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>322</v>
+        <v>656</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>579</v>
+        <v>657</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>323</v>
+        <v>65</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>324</v>
+        <v>66</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>325</v>
+        <v>67</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>582</v>
+        <v>552</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>326</v>
+        <v>425</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>583</v>
+        <v>562</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>327</v>
+        <v>426</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>242</v>
+        <v>658</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>585</v>
+        <v>659</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>243</v>
+        <v>68</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>586</v>
+        <v>553</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>244</v>
+        <v>69</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>236</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>587</v>
+        <v>554</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>245</v>
+        <v>70</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>588</v>
+        <v>555</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>589</v>
+        <v>155</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>247</v>
+        <v>79</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>322</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>298</v>
+        <v>80</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>323</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>299</v>
+        <v>81</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>324</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>300</v>
+        <v>82</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>325</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>301</v>
+        <v>83</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>326</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>302</v>
+        <v>84</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>303</v>
+        <v>85</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>248</v>
+        <v>86</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>243</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>249</v>
+        <v>87</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>244</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>250</v>
+        <v>88</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>245</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>251</v>
+        <v>89</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>252</v>
+        <v>90</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>247</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>253</v>
+        <v>91</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>304</v>
+        <v>92</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>299</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>305</v>
+        <v>93</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>300</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>306</v>
+        <v>94</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>301</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>307</v>
+        <v>95</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>302</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>308</v>
+        <v>96</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>303</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>309</v>
+        <v>97</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>254</v>
+        <v>98</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>249</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>255</v>
+        <v>99</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>250</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>256</v>
+        <v>100</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>257</v>
+        <v>101</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>258</v>
+        <v>102</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>259</v>
+        <v>103</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>304</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>328</v>
+        <v>104</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>305</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>329</v>
+        <v>105</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>306</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>330</v>
+        <v>106</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>307</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>331</v>
+        <v>107</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>332</v>
+        <v>108</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>309</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>333</v>
+        <v>109</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>260</v>
+        <v>110</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>261</v>
+        <v>111</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>262</v>
+        <v>112</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>257</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>263</v>
+        <v>113</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>258</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>264</v>
+        <v>114</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>265</v>
+        <v>115</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>328</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>334</v>
+        <v>116</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>329</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>335</v>
+        <v>117</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>330</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>336</v>
+        <v>118</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>331</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>337</v>
+        <v>119</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>332</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>338</v>
+        <v>120</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>339</v>
+        <v>121</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>266</v>
+        <v>122</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>267</v>
+        <v>123</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>262</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>268</v>
+        <v>124</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>263</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>269</v>
+        <v>125</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>264</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>270</v>
+        <v>126</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>265</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>271</v>
+        <v>127</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>334</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>340</v>
+        <v>128</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>335</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>341</v>
+        <v>129</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>336</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>342</v>
+        <v>130</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>337</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>343</v>
+        <v>131</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>344</v>
+        <v>132</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>339</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>345</v>
+        <v>133</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>266</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>272</v>
+        <v>134</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>273</v>
+        <v>135</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>268</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>274</v>
+        <v>136</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>269</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>275</v>
+        <v>137</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>276</v>
+        <v>138</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>277</v>
+        <v>139</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>340</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>346</v>
+        <v>140</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>341</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>348</v>
+        <v>141</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>342</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>350</v>
+        <v>142</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>343</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>354</v>
+        <v>143</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>344</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>355</v>
+        <v>144</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>356</v>
+        <v>145</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>272</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>360</v>
+        <v>146</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>273</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>361</v>
+        <v>147</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>362</v>
+        <v>148</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>364</v>
+        <v>149</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>276</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>367</v>
+        <v>150</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>153</v>
+        <v>395</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>371</v>
+        <v>320</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>153</v>
@@ -5538,10 +5602,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>153</v>
@@ -5549,10 +5613,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>153</v>
@@ -5560,10 +5624,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>153</v>
@@ -5571,183 +5635,170 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>651</v>
+        <v>153</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>652</v>
+        <v>153</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>444</v>
+        <v>365</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>445</v>
+        <v>367</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>653</v>
+        <v>153</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>664</v>
+        <v>366</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>666</v>
+        <v>368</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>665</v>
+        <v>369</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>667</v>
+        <v>373</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>428</v>
+        <v>370</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>429</v>
+        <v>374</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>670</v>
+        <v>371</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>671</v>
+        <v>375</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>672</v>
+        <v>153</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>673</v>
+        <v>372</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>674</v>
+        <v>376</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E229" s="1" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>466</v>
+        <v>377</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>467</v>
+        <v>378</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E230" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>676</v>
+        <v>379</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>677</v>
+        <v>380</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E231" s="1" t="s">
-        <v>678</v>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06558918-F4B9-400B-B4E3-DAF17A74315B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2FB213-F150-4A8B-B213-5184D882603D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="688">
   <si>
     <t>id</t>
   </si>
@@ -2098,17 +2098,41 @@
   </si>
   <si>
     <t>圣言几率+{0.2}%</t>
+  </si>
+  <si>
+    <t>setheavy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重型套装</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>setsoul</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵魂套装</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>setmagic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法套装</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2120,10 +2144,17 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2176,7 +2207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2184,9 +2215,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2213,7 +2245,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2529,16 +2561,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:G232"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.375" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5591,10 +5623,10 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>346</v>
+        <v>682</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>683</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>153</v>
@@ -5602,10 +5634,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>153</v>
@@ -5613,10 +5645,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>153</v>
@@ -5624,10 +5656,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>153</v>
@@ -5635,10 +5667,10 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>355</v>
+        <v>684</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>685</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>153</v>
@@ -5646,10 +5678,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>153</v>
@@ -5657,10 +5689,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>153</v>
@@ -5668,10 +5700,10 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>153</v>
@@ -5679,10 +5711,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>362</v>
+        <v>686</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>687</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>153</v>
@@ -5690,10 +5722,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>153</v>
@@ -5701,10 +5733,10 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>153</v>
@@ -5712,10 +5744,10 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>153</v>
@@ -5723,10 +5755,10 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>153</v>
@@ -5734,10 +5766,10 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>153</v>
@@ -5745,10 +5777,10 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>153</v>
@@ -5756,10 +5788,10 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>153</v>
@@ -5767,10 +5799,10 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>153</v>
@@ -5778,10 +5810,10 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>153</v>
@@ -5789,15 +5821,48 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="B235" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E232" s="1" t="s">
+      <c r="C235" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E235" s="1" t="s">
         <v>468</v>
       </c>
     </row>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2FB213-F150-4A8B-B213-5184D882603D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFD95F4-F818-4FE4-B364-A2DB82C12A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="786">
   <si>
     <t>id</t>
   </si>
@@ -2122,6 +2122,300 @@
   <si>
     <t>魔法套装</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>skfbltm1</t>
+  </si>
+  <si>
+    <t>skfrngm1</t>
+  </si>
+  <si>
+    <t>skfinfm1</t>
+  </si>
+  <si>
+    <t>skfbalm1</t>
+  </si>
+  <si>
+    <t>skfblsm1</t>
+  </si>
+  <si>
+    <t>skfwalm1</t>
+  </si>
+  <si>
+    <t>sktchmm1</t>
+  </si>
+  <si>
+    <t>sktbltm1</t>
+  </si>
+  <si>
+    <t>sktltnm1</t>
+  </si>
+  <si>
+    <t>sktnovm1</t>
+  </si>
+  <si>
+    <t>sktshdm1</t>
+  </si>
+  <si>
+    <t>sktblzm1</t>
+  </si>
+  <si>
+    <t>skbbasm1</t>
+  </si>
+  <si>
+    <t>skbcrtm1</t>
+  </si>
+  <si>
+    <t>skbthrm1</t>
+  </si>
+  <si>
+    <t>skbclvm1</t>
+  </si>
+  <si>
+    <t>skbcrzm1</t>
+  </si>
+  <si>
+    <t>skbfblm1</t>
+  </si>
+  <si>
+    <t>skxdefm1</t>
+  </si>
+  <si>
+    <t>skxdogm1</t>
+  </si>
+  <si>
+    <t>skxctam1</t>
+  </si>
+  <si>
+    <t>skxwmsm1</t>
+  </si>
+  <si>
+    <t>skxchgm1</t>
+  </si>
+  <si>
+    <t>skxtstm1</t>
+  </si>
+  <si>
+    <t>skhhelm1</t>
+  </si>
+  <si>
+    <t>skhgsdm1</t>
+  </si>
+  <si>
+    <t>skhinvm1</t>
+  </si>
+  <si>
+    <t>skhhsdm1</t>
+  </si>
+  <si>
+    <t>skhlokm1</t>
+  </si>
+  <si>
+    <t>skhmhlm1</t>
+  </si>
+  <si>
+    <t>skpbasm1</t>
+  </si>
+  <si>
+    <t>skppoim1</t>
+  </si>
+  <si>
+    <t>skpsklm1</t>
+  </si>
+  <si>
+    <t>skprunm1</t>
+  </si>
+  <si>
+    <t>skpcblm1</t>
+  </si>
+  <si>
+    <t>skpsdmm1</t>
+  </si>
+  <si>
+    <t>火球术可以点燃目标并造成{0.2}%的额外伤害</t>
+  </si>
+  <si>
+    <t>施放抗拒火环后，不消耗本回合。</t>
+  </si>
+  <si>
+    <t>地狱火的引燃数量+{0}</t>
+  </si>
+  <si>
+    <t>大火球的波及数量+{0}</t>
+  </si>
+  <si>
+    <t>使目标身上的点燃效果立即造成全额伤害</t>
+  </si>
+  <si>
+    <t>skfblsm2</t>
+  </si>
+  <si>
+    <t>每个未命中的目标使你有{0.2}%的几率立即再次施放爆裂火焰</t>
+  </si>
+  <si>
+    <t>火墙术的范围提升为3x3</t>
+  </si>
+  <si>
+    <t>skfwalm2</t>
+  </si>
+  <si>
+    <t>火墙范围内的目标造成的物理伤害降低{0.2}%</t>
+  </si>
+  <si>
+    <t>诱惑之光可以对精英敌人使用</t>
+  </si>
+  <si>
+    <t>对目标及其相邻的1个敌人造成{0.2}%的粉碎性打击</t>
+  </si>
+  <si>
+    <t>疾光电影的命中提升20%，但是伤害降低{0.2}%，同时，疾光电影不再对一条直线的敌人造成伤害，而是转化为闪电链，最多伤害4个目标</t>
+  </si>
+  <si>
+    <t>sktltnm2</t>
+  </si>
+  <si>
+    <t>疾光电影可以攻击2排目标</t>
+  </si>
+  <si>
+    <t>受影响的目标降低{0.2}%风雷抗性，最多叠加3层</t>
+  </si>
+  <si>
+    <t>可以吸收你的生命上限{0.2}%的物理伤害</t>
+  </si>
+  <si>
+    <t>sktshdm2</t>
+  </si>
+  <si>
+    <t>持续期间，你的反弹伤害效果提升{0.2}%</t>
+  </si>
+  <si>
+    <t>可直接杀死生命值低于{0.2}%的小怪</t>
+  </si>
+  <si>
+    <t>sktblzm2</t>
+  </si>
+  <si>
+    <t>每命中一个目标，冰咆哮的伤害提升{0.2}%</t>
+  </si>
+  <si>
+    <t>使用斧类武器时，提升{0.2}%的暴击几率</t>
+  </si>
+  <si>
+    <t>你的非物理伤害也能造成暴击</t>
+  </si>
+  <si>
+    <t>受影响的目标将受到额外{0.2}%的刺杀剑术伤害</t>
+  </si>
+  <si>
+    <t>受影响的目标遭受流血效果，每回合受到{0.2}%的物理伤害</t>
+  </si>
+  <si>
+    <t>施放十字斩后，你的刺杀剑术或者半月弯刀的冷却时间-1回合</t>
+  </si>
+  <si>
+    <t>skbcrzm2</t>
+  </si>
+  <si>
+    <t>你的十字斩攻击范围+1</t>
+  </si>
+  <si>
+    <t>烈火剑法附带等额的神圣伤害，烈火剑法现在也是神圣系技能</t>
+  </si>
+  <si>
+    <t>skbfblm2</t>
+  </si>
+  <si>
+    <t>汲取火焰伤害的{0.2}%的生命值，烈火剑法现在也是道术系技能</t>
+  </si>
+  <si>
+    <t>被击中后恢复物理减伤{0.2}%的生命值</t>
+  </si>
+  <si>
+    <t>提升等额的魔法闪避</t>
+  </si>
+  <si>
+    <t>开启后，提升{0.2}%的最大生命值</t>
+  </si>
+  <si>
+    <t>提升等额的火焰反弹</t>
+  </si>
+  <si>
+    <t>施展野蛮冲撞后，你立即普通攻击一次</t>
+  </si>
+  <si>
+    <t>受影响的目标的物理抗性降低{0.2}%</t>
+  </si>
+  <si>
+    <t>skxtstm2</t>
+  </si>
+  <si>
+    <t>再次被霜冻踏地击中时，会昏迷1回合</t>
+  </si>
+  <si>
+    <t>skhhelm2</t>
+  </si>
+  <si>
+    <t>治愈术会附加持续治疗效果，数值为治疗量的{0.2}%</t>
+  </si>
+  <si>
+    <t>治愈术现在会治疗你的整个队伍</t>
+  </si>
+  <si>
+    <t>可以吸收你的生命上限{0.2}%的非物理伤害</t>
+  </si>
+  <si>
+    <t>隐身状态的攻击造成{0.2}%的额外伤害</t>
+  </si>
+  <si>
+    <t>神圣战甲同时提供等额的非物理减伤</t>
+  </si>
+  <si>
+    <t>受影响的目标将被定义为妖魔</t>
+  </si>
+  <si>
+    <t>skhlokm2</t>
+  </si>
+  <si>
+    <t>可对精英敌人和首领敌人施展，持续时间减半</t>
+  </si>
+  <si>
+    <t>skhmhlm2</t>
+  </si>
+  <si>
+    <t>被神圣责罚杀死的敌人会为你恢复伤害的{0.2}%的生命值</t>
+  </si>
+  <si>
+    <t>每个受神圣责罚影响的目标为你提供{0.2}%的减伤</t>
+  </si>
+  <si>
+    <t>提升等额的暴击几率</t>
+  </si>
+  <si>
+    <t>伤害类毒药的持续时间减半，伤害+100%</t>
+  </si>
+  <si>
+    <t>骷髅的生命值-90%，骷髅死亡时爆炸，造成火焰伤害，召唤骷髅现在也是火焰系技能</t>
+  </si>
+  <si>
+    <t>对不死生物的伤害提升{0.2}%</t>
+  </si>
+  <si>
+    <t>击杀妖魔以后，造成的所有伤害提升{0.2}%</t>
+  </si>
+  <si>
+    <t>skpcblm2</t>
+  </si>
+  <si>
+    <t>对被灵魂火符命中的不死生物的伤害提升{0.2}%</t>
+  </si>
+  <si>
+    <t>神兽现在攻击扇形范围内的敌人，伤害类型变为毒素系，召唤神兽现在也是毒素系技能</t>
+  </si>
+  <si>
+    <t>skpsdmm2</t>
+  </si>
+  <si>
+    <t>神兽攻击时有概率战吼，整个队伍的物理伤害提升{0.2}%</t>
   </si>
 </sst>
 </file>
@@ -2132,7 +2426,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2144,7 +2438,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2218,9 +2512,79 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2245,7 +2609,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2561,20 +2925,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:G235"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G284"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2597,7 +2961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -2620,12 +2984,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>321</v>
       </c>
@@ -2644,7 +3008,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -2658,7 +3022,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>395</v>
       </c>
@@ -2672,7 +3036,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>396</v>
       </c>
@@ -2686,7 +3050,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>397</v>
       </c>
@@ -2700,7 +3064,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -2714,7 +3078,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -2728,7 +3092,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -2748,7 +3112,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -2768,7 +3132,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -2782,7 +3146,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -2796,7 +3160,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -2816,7 +3180,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -2836,7 +3200,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2850,7 +3214,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -2864,7 +3228,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -2878,7 +3242,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -2892,7 +3256,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>410</v>
       </c>
@@ -2906,7 +3270,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>664</v>
       </c>
@@ -2920,7 +3284,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>665</v>
       </c>
@@ -2934,7 +3298,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>280</v>
       </c>
@@ -2948,7 +3312,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>281</v>
       </c>
@@ -2962,7 +3326,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>282</v>
       </c>
@@ -2976,7 +3340,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>283</v>
       </c>
@@ -2990,7 +3354,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>284</v>
       </c>
@@ -3004,7 +3368,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>446</v>
       </c>
@@ -3018,7 +3382,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>447</v>
       </c>
@@ -3032,7 +3396,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>448</v>
       </c>
@@ -3046,7 +3410,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>449</v>
       </c>
@@ -3060,7 +3424,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>450</v>
       </c>
@@ -3074,7 +3438,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>451</v>
       </c>
@@ -3088,7 +3452,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>452</v>
       </c>
@@ -3102,7 +3466,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>453</v>
       </c>
@@ -3116,7 +3480,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>454</v>
       </c>
@@ -3130,7 +3494,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>455</v>
       </c>
@@ -3144,7 +3508,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -3158,7 +3522,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -3172,7 +3536,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -3186,7 +3550,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -3200,7 +3564,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -3214,7 +3578,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -3228,7 +3592,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -3242,7 +3606,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -3256,7 +3620,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -3270,7 +3634,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -3284,7 +3648,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
@@ -3298,7 +3662,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
@@ -3312,7 +3676,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -3326,7 +3690,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
@@ -3340,7 +3704,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
@@ -3354,7 +3718,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>412</v>
       </c>
@@ -3368,7 +3732,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>413</v>
       </c>
@@ -3382,7 +3746,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>414</v>
       </c>
@@ -3396,7 +3760,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -3410,7 +3774,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -3424,7 +3788,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -3438,7 +3802,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -3452,7 +3816,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -3466,7 +3830,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -3483,7 +3847,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
@@ -3500,7 +3864,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
@@ -3517,7 +3881,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>399</v>
       </c>
@@ -3534,7 +3898,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>400</v>
       </c>
@@ -3551,7 +3915,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>406</v>
       </c>
@@ -3568,7 +3932,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>404</v>
       </c>
@@ -3582,7 +3946,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -3596,7 +3960,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
@@ -3610,7 +3974,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -3624,7 +3988,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -3638,7 +4002,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -3652,7 +4016,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
@@ -3672,7 +4036,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -3692,7 +4056,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -3712,7 +4076,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -3732,7 +4096,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
@@ -3752,7 +4116,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>393</v>
       </c>
@@ -3766,7 +4130,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -3780,7 +4144,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -3794,7 +4158,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -3808,7 +4172,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -3822,7 +4186,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>310</v>
       </c>
@@ -3836,7 +4200,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>311</v>
       </c>
@@ -3850,7 +4214,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>312</v>
       </c>
@@ -3864,7 +4228,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>313</v>
       </c>
@@ -3878,7 +4242,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>314</v>
       </c>
@@ -3892,7 +4256,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -3906,7 +4270,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -3920,7 +4284,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -3934,7 +4298,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -3948,7 +4312,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -3962,7 +4326,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>420</v>
       </c>
@@ -3976,7 +4340,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>661</v>
       </c>
@@ -3990,7 +4354,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -4001,7 +4365,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>473</v>
       </c>
@@ -4015,7 +4379,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>676</v>
       </c>
@@ -4029,7 +4393,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>408</v>
       </c>
@@ -4043,7 +4407,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>381</v>
       </c>
@@ -4054,7 +4418,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>383</v>
       </c>
@@ -4065,7 +4429,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>46</v>
       </c>
@@ -4079,7 +4443,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>47</v>
       </c>
@@ -4093,7 +4457,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>48</v>
       </c>
@@ -4107,7 +4471,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>278</v>
       </c>
@@ -4121,7 +4485,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>294</v>
       </c>
@@ -4135,7 +4499,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>295</v>
       </c>
@@ -4149,7 +4513,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>296</v>
       </c>
@@ -4163,7 +4527,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>297</v>
       </c>
@@ -4177,7 +4541,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>72</v>
       </c>
@@ -4191,7 +4555,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>679</v>
       </c>
@@ -4205,7 +4569,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>670</v>
       </c>
@@ -4219,7 +4583,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>673</v>
       </c>
@@ -4233,7 +4597,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>389</v>
       </c>
@@ -4247,7 +4611,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>390</v>
       </c>
@@ -4261,7 +4625,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>444</v>
       </c>
@@ -4275,7 +4639,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>59</v>
       </c>
@@ -4289,7 +4653,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>60</v>
       </c>
@@ -4303,7 +4667,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>61</v>
       </c>
@@ -4317,7 +4681,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>421</v>
       </c>
@@ -4331,7 +4695,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>422</v>
       </c>
@@ -4345,7 +4709,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>655</v>
       </c>
@@ -4359,7 +4723,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>62</v>
       </c>
@@ -4373,7 +4737,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>63</v>
       </c>
@@ -4387,7 +4751,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>64</v>
       </c>
@@ -4401,7 +4765,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>423</v>
       </c>
@@ -4415,7 +4779,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>424</v>
       </c>
@@ -4429,7 +4793,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>656</v>
       </c>
@@ -4443,7 +4807,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>65</v>
       </c>
@@ -4457,7 +4821,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>66</v>
       </c>
@@ -4471,7 +4835,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>67</v>
       </c>
@@ -4485,7 +4849,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>425</v>
       </c>
@@ -4499,7 +4863,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>426</v>
       </c>
@@ -4513,7 +4877,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>658</v>
       </c>
@@ -4527,7 +4891,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>68</v>
       </c>
@@ -4541,7 +4905,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>69</v>
       </c>
@@ -4555,7 +4919,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>70</v>
       </c>
@@ -4569,7 +4933,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>71</v>
       </c>
@@ -4580,7 +4944,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>79</v>
       </c>
@@ -4594,7 +4958,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>80</v>
       </c>
@@ -4608,7 +4972,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>81</v>
       </c>
@@ -4622,7 +4986,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>82</v>
       </c>
@@ -4636,7 +5000,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>83</v>
       </c>
@@ -4650,7 +5014,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>84</v>
       </c>
@@ -4664,7 +5028,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>85</v>
       </c>
@@ -4678,7 +5042,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>86</v>
       </c>
@@ -4692,7 +5056,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>87</v>
       </c>
@@ -4706,7 +5070,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>88</v>
       </c>
@@ -4720,7 +5084,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>89</v>
       </c>
@@ -4734,7 +5098,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>90</v>
       </c>
@@ -4748,7 +5112,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>91</v>
       </c>
@@ -4762,7 +5126,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>92</v>
       </c>
@@ -4776,7 +5140,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>93</v>
       </c>
@@ -4790,7 +5154,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>94</v>
       </c>
@@ -4804,7 +5168,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>95</v>
       </c>
@@ -4818,7 +5182,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>96</v>
       </c>
@@ -4832,7 +5196,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>97</v>
       </c>
@@ -4846,7 +5210,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>98</v>
       </c>
@@ -4860,7 +5224,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>99</v>
       </c>
@@ -4874,7 +5238,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>100</v>
       </c>
@@ -4888,7 +5252,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>101</v>
       </c>
@@ -4902,7 +5266,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>102</v>
       </c>
@@ -4916,7 +5280,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>103</v>
       </c>
@@ -4930,7 +5294,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>104</v>
       </c>
@@ -4944,7 +5308,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>105</v>
       </c>
@@ -4958,7 +5322,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>106</v>
       </c>
@@ -4972,7 +5336,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>107</v>
       </c>
@@ -4986,7 +5350,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>108</v>
       </c>
@@ -5000,7 +5364,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>109</v>
       </c>
@@ -5014,7 +5378,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>110</v>
       </c>
@@ -5028,7 +5392,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>111</v>
       </c>
@@ -5042,7 +5406,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>112</v>
       </c>
@@ -5056,7 +5420,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>113</v>
       </c>
@@ -5070,7 +5434,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>114</v>
       </c>
@@ -5084,7 +5448,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>115</v>
       </c>
@@ -5098,7 +5462,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>116</v>
       </c>
@@ -5112,7 +5476,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>117</v>
       </c>
@@ -5126,7 +5490,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>118</v>
       </c>
@@ -5140,7 +5504,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>119</v>
       </c>
@@ -5154,7 +5518,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>120</v>
       </c>
@@ -5168,7 +5532,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>121</v>
       </c>
@@ -5182,7 +5546,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>122</v>
       </c>
@@ -5196,7 +5560,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>123</v>
       </c>
@@ -5210,7 +5574,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>124</v>
       </c>
@@ -5224,7 +5588,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>125</v>
       </c>
@@ -5238,7 +5602,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>126</v>
       </c>
@@ -5252,7 +5616,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>127</v>
       </c>
@@ -5266,7 +5630,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>128</v>
       </c>
@@ -5280,7 +5644,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>129</v>
       </c>
@@ -5294,7 +5658,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>130</v>
       </c>
@@ -5308,7 +5672,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>131</v>
       </c>
@@ -5322,7 +5686,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>132</v>
       </c>
@@ -5336,7 +5700,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>133</v>
       </c>
@@ -5350,7 +5714,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>134</v>
       </c>
@@ -5364,7 +5728,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>135</v>
       </c>
@@ -5378,7 +5742,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>136</v>
       </c>
@@ -5392,7 +5756,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>137</v>
       </c>
@@ -5406,7 +5770,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>138</v>
       </c>
@@ -5420,7 +5784,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>139</v>
       </c>
@@ -5434,7 +5798,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>140</v>
       </c>
@@ -5448,7 +5812,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>141</v>
       </c>
@@ -5462,7 +5826,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>142</v>
       </c>
@@ -5476,7 +5840,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>143</v>
       </c>
@@ -5490,7 +5854,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>144</v>
       </c>
@@ -5504,7 +5868,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>145</v>
       </c>
@@ -5518,7 +5882,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>146</v>
       </c>
@@ -5532,7 +5896,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>147</v>
       </c>
@@ -5546,7 +5910,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>148</v>
       </c>
@@ -5560,7 +5924,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>149</v>
       </c>
@@ -5574,7 +5938,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>150</v>
       </c>
@@ -5588,7 +5952,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>385</v>
       </c>
@@ -5599,7 +5963,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>387</v>
       </c>
@@ -5610,7 +5974,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>428</v>
       </c>
@@ -5621,7 +5985,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>682</v>
       </c>
@@ -5632,7 +5996,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>320</v>
       </c>
@@ -5643,7 +6007,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>347</v>
       </c>
@@ -5654,7 +6018,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>349</v>
       </c>
@@ -5665,7 +6029,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>684</v>
       </c>
@@ -5676,7 +6040,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>351</v>
       </c>
@@ -5687,7 +6051,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>352</v>
       </c>
@@ -5698,7 +6062,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>353</v>
       </c>
@@ -5709,7 +6073,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>686</v>
       </c>
@@ -5720,7 +6084,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>357</v>
       </c>
@@ -5731,7 +6095,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>358</v>
       </c>
@@ -5742,7 +6106,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>359</v>
       </c>
@@ -5753,7 +6117,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>363</v>
       </c>
@@ -5764,7 +6128,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>365</v>
       </c>
@@ -5775,7 +6139,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>366</v>
       </c>
@@ -5786,7 +6150,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>369</v>
       </c>
@@ -5797,7 +6161,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>370</v>
       </c>
@@ -5808,7 +6172,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>371</v>
       </c>
@@ -5819,7 +6183,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>372</v>
       </c>
@@ -5830,7 +6194,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>377</v>
       </c>
@@ -5841,7 +6205,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>379</v>
       </c>
@@ -5852,7 +6216,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>466</v>
       </c>
@@ -5864,11 +6228,718 @@
       </c>
       <c r="E235" s="1" t="s">
         <v>468</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A236" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A237" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A238" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A239" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A240" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A241" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A242" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A243" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A244" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A245" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A246" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A247" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A248" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A249" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A250" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A251" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A252" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A253" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A254" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A255" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A256" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A257" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A258" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A259" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A260" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A261" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A262" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A263" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A264" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A265" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A266" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A267" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A268" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A269" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A270" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A271" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A272" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A273" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A274" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A275" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A276" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A277" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A278" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A279" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A280" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A281" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A282" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A283" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A284" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B236">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B237">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B238">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B239:B240 B242 B244:B246 B248:B284">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B241">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B243">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B247">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFD95F4-F818-4FE4-B364-A2DB82C12A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA50CEDE-9821-458E-90E3-132CAF283AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="780" yWindow="450" windowWidth="32160" windowHeight="20430" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="792">
   <si>
     <t>id</t>
   </si>
@@ -2416,6 +2416,30 @@
   </si>
   <si>
     <t>神兽攻击时有概率战吼，整个队伍的物理伤害提升{0.2}%</t>
+  </si>
+  <si>
+    <t>sktblzm1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>number</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>依赖函数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>排序</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2426,7 +2450,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2438,7 +2462,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2501,7 +2525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2510,9 +2534,10 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -2609,7 +2634,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2925,20 +2950,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:G284"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H284"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.36328125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2955,13 +2981,16 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -2978,18 +3007,21 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>321</v>
       </c>
@@ -3005,10 +3037,17 @@
       <c r="E4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -3021,8 +3060,11 @@
       <c r="E5" s="1" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F5" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>395</v>
       </c>
@@ -3035,8 +3077,11 @@
       <c r="E6" s="1" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F6" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>396</v>
       </c>
@@ -3049,8 +3094,11 @@
       <c r="E7" s="1" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F7" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>397</v>
       </c>
@@ -3063,8 +3111,11 @@
       <c r="E8" s="1" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F8" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3077,8 +3128,11 @@
       <c r="E9" s="1" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F9" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3091,8 +3145,11 @@
       <c r="E10" s="1" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F10" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3105,14 +3162,17 @@
       <c r="E11" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="1">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3125,14 +3185,17 @@
       <c r="E12" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="1">
+        <v>44</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3145,8 +3208,11 @@
       <c r="E13" s="1" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F13" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3159,8 +3225,11 @@
       <c r="E14" s="1" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F14" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3173,14 +3242,17 @@
       <c r="E15" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="1">
+        <v>53</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -3193,14 +3265,17 @@
       <c r="E16" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="1">
+        <v>54</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3213,8 +3288,11 @@
       <c r="E17" s="1" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -3227,8 +3305,11 @@
       <c r="E18" s="1" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -3241,8 +3322,11 @@
       <c r="E19" s="1" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19" s="1">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -3255,8 +3339,11 @@
       <c r="E20" s="1" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20" s="1">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>410</v>
       </c>
@@ -3269,8 +3356,11 @@
       <c r="E21" s="1" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>664</v>
       </c>
@@ -3283,8 +3373,11 @@
       <c r="E22" s="1" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22" s="1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>665</v>
       </c>
@@ -3297,8 +3390,11 @@
       <c r="E23" s="1" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23" s="1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>280</v>
       </c>
@@ -3311,8 +3407,11 @@
       <c r="E24" s="1" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>281</v>
       </c>
@@ -3325,8 +3424,11 @@
       <c r="E25" s="1" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>282</v>
       </c>
@@ -3339,8 +3441,11 @@
       <c r="E26" s="1" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>283</v>
       </c>
@@ -3353,8 +3458,11 @@
       <c r="E27" s="1" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>284</v>
       </c>
@@ -3367,8 +3475,11 @@
       <c r="E28" s="1" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>446</v>
       </c>
@@ -3381,8 +3492,11 @@
       <c r="E29" s="1" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F29" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>447</v>
       </c>
@@ -3395,8 +3509,11 @@
       <c r="E30" s="1" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F30" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>448</v>
       </c>
@@ -3409,8 +3526,11 @@
       <c r="E31" s="1" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F31" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>449</v>
       </c>
@@ -3423,8 +3543,11 @@
       <c r="E32" s="1" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F32" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>450</v>
       </c>
@@ -3437,8 +3560,11 @@
       <c r="E33" s="1" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>451</v>
       </c>
@@ -3451,8 +3577,11 @@
       <c r="E34" s="1" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F34" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>452</v>
       </c>
@@ -3465,8 +3594,11 @@
       <c r="E35" s="1" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F35" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>453</v>
       </c>
@@ -3479,8 +3611,11 @@
       <c r="E36" s="1" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F36" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>454</v>
       </c>
@@ -3493,8 +3628,11 @@
       <c r="E37" s="1" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F37" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>455</v>
       </c>
@@ -3507,8 +3645,11 @@
       <c r="E38" s="1" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F38" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -3521,8 +3662,11 @@
       <c r="E39" s="1" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F39" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -3535,8 +3679,11 @@
       <c r="E40" s="1" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F40" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -3549,8 +3696,11 @@
       <c r="E41" s="1" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41" s="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -3563,8 +3713,11 @@
       <c r="E42" s="1" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -3577,8 +3730,11 @@
       <c r="E43" s="1" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F43" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -3591,8 +3747,11 @@
       <c r="E44" s="1" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F44" s="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -3605,8 +3764,11 @@
       <c r="E45" s="1" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F45" s="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -3619,8 +3781,11 @@
       <c r="E46" s="1" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F46" s="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -3633,8 +3798,11 @@
       <c r="E47" s="1" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47" s="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -3647,8 +3815,11 @@
       <c r="E48" s="1" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F48" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
@@ -3661,8 +3832,11 @@
       <c r="E49" s="1" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F49" s="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
@@ -3675,8 +3849,11 @@
       <c r="E50" s="1" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F50" s="1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -3689,8 +3866,11 @@
       <c r="E51" s="1" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F51" s="1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
@@ -3703,8 +3883,11 @@
       <c r="E52" s="1" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F52" s="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
@@ -3717,8 +3900,11 @@
       <c r="E53" s="1" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F53" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>412</v>
       </c>
@@ -3731,8 +3917,11 @@
       <c r="E54" s="1" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F54" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>413</v>
       </c>
@@ -3745,8 +3934,11 @@
       <c r="E55" s="1" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F55" s="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>414</v>
       </c>
@@ -3759,8 +3951,11 @@
       <c r="E56" s="1" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F56" s="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -3773,8 +3968,11 @@
       <c r="E57" s="1" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F57" s="1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -3787,8 +3985,11 @@
       <c r="E58" s="1" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F58" s="1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -3801,8 +4002,11 @@
       <c r="E59" s="1" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F59" s="1">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -3815,8 +4019,11 @@
       <c r="E60" s="1" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F60" s="1">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -3829,8 +4036,11 @@
       <c r="E61" s="1" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F61" s="1">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -3846,8 +4056,11 @@
       <c r="E62" s="1" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F62" s="1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
@@ -3863,8 +4076,11 @@
       <c r="E63" s="1" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F63" s="1">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
@@ -3880,8 +4096,11 @@
       <c r="E64" s="1" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F64" s="1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>399</v>
       </c>
@@ -3897,8 +4116,11 @@
       <c r="E65" s="1" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F65" s="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>400</v>
       </c>
@@ -3914,8 +4136,11 @@
       <c r="E66" s="1" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F66" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>406</v>
       </c>
@@ -3931,8 +4156,11 @@
       <c r="E67" s="1" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F67" s="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>404</v>
       </c>
@@ -3945,8 +4173,11 @@
       <c r="E68" s="1" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F68" s="1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -3959,8 +4190,11 @@
       <c r="E69" s="1" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F69" s="1">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
@@ -3973,8 +4207,11 @@
       <c r="E70" s="1" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F70" s="1">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -3987,8 +4224,11 @@
       <c r="E71" s="1" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F71" s="1">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -4001,8 +4241,11 @@
       <c r="E72" s="1" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F72" s="1">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -4015,8 +4258,11 @@
       <c r="E73" s="1" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F73" s="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
@@ -4029,14 +4275,17 @@
       <c r="E74" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="1">
+        <v>251</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -4049,14 +4298,17 @@
       <c r="E75" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="1">
+        <v>252</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -4069,14 +4321,17 @@
       <c r="E76" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="1">
+        <v>253</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -4089,14 +4344,17 @@
       <c r="E77" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="1">
+        <v>254</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
@@ -4109,14 +4367,17 @@
       <c r="E78" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="1">
+        <v>255</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>393</v>
       </c>
@@ -4129,8 +4390,11 @@
       <c r="E79" s="1" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F79" s="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -4143,8 +4407,11 @@
       <c r="E80" s="1" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F80" s="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -4157,8 +4424,11 @@
       <c r="E81" s="1" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F81" s="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -4171,8 +4441,11 @@
       <c r="E82" s="1" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F82" s="1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -4185,8 +4458,11 @@
       <c r="E83" s="1" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F83" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>310</v>
       </c>
@@ -4199,8 +4475,11 @@
       <c r="E84" s="1" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F84" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>311</v>
       </c>
@@ -4213,8 +4492,11 @@
       <c r="E85" s="1" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F85" s="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>312</v>
       </c>
@@ -4227,8 +4509,11 @@
       <c r="E86" s="1" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F86" s="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>313</v>
       </c>
@@ -4241,8 +4526,11 @@
       <c r="E87" s="1" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F87" s="1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>314</v>
       </c>
@@ -4255,8 +4543,11 @@
       <c r="E88" s="1" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F88" s="1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -4269,8 +4560,11 @@
       <c r="E89" s="1" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F89" s="1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -4283,8 +4577,11 @@
       <c r="E90" s="1" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F90" s="1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -4297,8 +4594,11 @@
       <c r="E91" s="1" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F91" s="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -4311,8 +4611,11 @@
       <c r="E92" s="1" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F92" s="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -4325,8 +4628,11 @@
       <c r="E93" s="1" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F93" s="1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>420</v>
       </c>
@@ -4339,8 +4645,11 @@
       <c r="E94" s="1" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F94" s="1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>661</v>
       </c>
@@ -4353,8 +4662,11 @@
       <c r="E95" s="1" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F95" s="1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -4364,8 +4676,11 @@
       <c r="C96" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F96" s="1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>473</v>
       </c>
@@ -4378,8 +4693,11 @@
       <c r="E97" s="1" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F97" s="1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>676</v>
       </c>
@@ -4392,8 +4710,11 @@
       <c r="E98" s="1" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F98" s="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>408</v>
       </c>
@@ -4406,8 +4727,11 @@
       <c r="E99" s="1" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F99" s="1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>381</v>
       </c>
@@ -4417,8 +4741,11 @@
       <c r="C100" s="1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F100" s="1">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>383</v>
       </c>
@@ -4428,8 +4755,11 @@
       <c r="C101" s="1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F101" s="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>46</v>
       </c>
@@ -4442,8 +4772,11 @@
       <c r="E102" s="1" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F102" s="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>47</v>
       </c>
@@ -4456,8 +4789,11 @@
       <c r="E103" s="1" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F103" s="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>48</v>
       </c>
@@ -4470,8 +4806,11 @@
       <c r="E104" s="1" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F104" s="1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>278</v>
       </c>
@@ -4484,8 +4823,11 @@
       <c r="E105" s="1" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F105" s="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>294</v>
       </c>
@@ -4498,8 +4840,11 @@
       <c r="E106" s="1" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F106" s="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>295</v>
       </c>
@@ -4512,8 +4857,11 @@
       <c r="E107" s="1" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F107" s="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>296</v>
       </c>
@@ -4526,8 +4874,11 @@
       <c r="E108" s="1" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F108" s="1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>297</v>
       </c>
@@ -4540,8 +4891,11 @@
       <c r="E109" s="1" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F109" s="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>72</v>
       </c>
@@ -4554,8 +4908,11 @@
       <c r="E110" s="1" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F110" s="1">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>679</v>
       </c>
@@ -4568,8 +4925,11 @@
       <c r="E111" s="1" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F111" s="1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>670</v>
       </c>
@@ -4582,8 +4942,11 @@
       <c r="E112" s="1" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F112" s="1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>673</v>
       </c>
@@ -4596,8 +4959,11 @@
       <c r="E113" s="1" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F113" s="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>389</v>
       </c>
@@ -4610,8 +4976,11 @@
       <c r="E114" s="1" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F114" s="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>390</v>
       </c>
@@ -4624,8 +4993,11 @@
       <c r="E115" s="1" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F115" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>444</v>
       </c>
@@ -4638,8 +5010,11 @@
       <c r="E116" s="1" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F116" s="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>59</v>
       </c>
@@ -4652,8 +5027,11 @@
       <c r="E117" s="1" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F117" s="1">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>60</v>
       </c>
@@ -4666,8 +5044,11 @@
       <c r="E118" s="1" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F118" s="1">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>61</v>
       </c>
@@ -4680,8 +5061,11 @@
       <c r="E119" s="1" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F119" s="1">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>421</v>
       </c>
@@ -4694,8 +5078,11 @@
       <c r="E120" s="1" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F120" s="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>422</v>
       </c>
@@ -4708,8 +5095,11 @@
       <c r="E121" s="1" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F121" s="1">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>655</v>
       </c>
@@ -4722,8 +5112,11 @@
       <c r="E122" s="1" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F122" s="1">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>62</v>
       </c>
@@ -4736,8 +5129,11 @@
       <c r="E123" s="1" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F123" s="1">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>63</v>
       </c>
@@ -4750,8 +5146,11 @@
       <c r="E124" s="1" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F124" s="1">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>64</v>
       </c>
@@ -4764,8 +5163,11 @@
       <c r="E125" s="1" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F125" s="1">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>423</v>
       </c>
@@ -4778,8 +5180,11 @@
       <c r="E126" s="1" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F126" s="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>424</v>
       </c>
@@ -4792,8 +5197,11 @@
       <c r="E127" s="1" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F127" s="1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>656</v>
       </c>
@@ -4806,8 +5214,11 @@
       <c r="E128" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F128" s="1">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>65</v>
       </c>
@@ -4820,8 +5231,11 @@
       <c r="E129" s="1" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F129" s="1">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>66</v>
       </c>
@@ -4834,8 +5248,11 @@
       <c r="E130" s="1" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F130" s="1">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>67</v>
       </c>
@@ -4848,8 +5265,11 @@
       <c r="E131" s="1" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F131" s="1">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>425</v>
       </c>
@@ -4862,8 +5282,11 @@
       <c r="E132" s="1" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F132" s="1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>426</v>
       </c>
@@ -4876,8 +5299,11 @@
       <c r="E133" s="1" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F133" s="1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>658</v>
       </c>
@@ -4890,8 +5316,11 @@
       <c r="E134" s="1" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F134" s="1">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>68</v>
       </c>
@@ -4904,8 +5333,11 @@
       <c r="E135" s="1" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F135" s="1">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>69</v>
       </c>
@@ -4918,8 +5350,11 @@
       <c r="E136" s="1" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F136" s="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>70</v>
       </c>
@@ -4932,8 +5367,11 @@
       <c r="E137" s="1" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F137" s="1">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>71</v>
       </c>
@@ -4943,8 +5381,11 @@
       <c r="C138" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F138" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>79</v>
       </c>
@@ -4957,8 +5398,11 @@
       <c r="E139" s="1" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F139" s="1">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>80</v>
       </c>
@@ -4971,8 +5415,11 @@
       <c r="E140" s="1" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F140" s="1">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>81</v>
       </c>
@@ -4985,8 +5432,11 @@
       <c r="E141" s="1" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F141" s="1">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>82</v>
       </c>
@@ -4999,8 +5449,11 @@
       <c r="E142" s="1" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F142" s="1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>83</v>
       </c>
@@ -5013,8 +5466,11 @@
       <c r="E143" s="1" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F143" s="1">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>84</v>
       </c>
@@ -5027,8 +5483,11 @@
       <c r="E144" s="1" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F144" s="1">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>85</v>
       </c>
@@ -5041,8 +5500,11 @@
       <c r="E145" s="1" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F145" s="1">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>86</v>
       </c>
@@ -5055,8 +5517,11 @@
       <c r="E146" s="1" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F146" s="1">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>87</v>
       </c>
@@ -5069,8 +5534,11 @@
       <c r="E147" s="1" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F147" s="1">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>88</v>
       </c>
@@ -5083,8 +5551,11 @@
       <c r="E148" s="1" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F148" s="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>89</v>
       </c>
@@ -5097,8 +5568,11 @@
       <c r="E149" s="1" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F149" s="1">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>90</v>
       </c>
@@ -5111,8 +5585,11 @@
       <c r="E150" s="1" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F150" s="1">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>91</v>
       </c>
@@ -5125,8 +5602,11 @@
       <c r="E151" s="1" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F151" s="1">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>92</v>
       </c>
@@ -5139,8 +5619,11 @@
       <c r="E152" s="1" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F152" s="1">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>93</v>
       </c>
@@ -5153,8 +5636,11 @@
       <c r="E153" s="1" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F153" s="1">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>94</v>
       </c>
@@ -5167,8 +5653,11 @@
       <c r="E154" s="1" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F154" s="1">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>95</v>
       </c>
@@ -5181,8 +5670,11 @@
       <c r="E155" s="1" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F155" s="1">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>96</v>
       </c>
@@ -5195,8 +5687,11 @@
       <c r="E156" s="1" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F156" s="1">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>97</v>
       </c>
@@ -5209,8 +5704,11 @@
       <c r="E157" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F157" s="1">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>98</v>
       </c>
@@ -5223,8 +5721,11 @@
       <c r="E158" s="1" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F158" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>99</v>
       </c>
@@ -5237,8 +5738,11 @@
       <c r="E159" s="1" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F159" s="1">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>100</v>
       </c>
@@ -5251,8 +5755,11 @@
       <c r="E160" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F160" s="1">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>101</v>
       </c>
@@ -5265,8 +5772,11 @@
       <c r="E161" s="1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F161" s="1">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>102</v>
       </c>
@@ -5279,8 +5789,11 @@
       <c r="E162" s="1" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F162" s="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>103</v>
       </c>
@@ -5293,8 +5806,11 @@
       <c r="E163" s="1" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F163" s="1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>104</v>
       </c>
@@ -5307,8 +5823,11 @@
       <c r="E164" s="1" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F164" s="1">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>105</v>
       </c>
@@ -5321,8 +5840,11 @@
       <c r="E165" s="1" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F165" s="1">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>106</v>
       </c>
@@ -5335,8 +5857,11 @@
       <c r="E166" s="1" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F166" s="1">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>107</v>
       </c>
@@ -5349,8 +5874,11 @@
       <c r="E167" s="1" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F167" s="1">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>108</v>
       </c>
@@ -5363,8 +5891,11 @@
       <c r="E168" s="1" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F168" s="1">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>109</v>
       </c>
@@ -5377,8 +5908,11 @@
       <c r="E169" s="1" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F169" s="1">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>110</v>
       </c>
@@ -5391,8 +5925,11 @@
       <c r="E170" s="1" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F170" s="1">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>111</v>
       </c>
@@ -5405,8 +5942,11 @@
       <c r="E171" s="1" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F171" s="1">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>112</v>
       </c>
@@ -5419,8 +5959,11 @@
       <c r="E172" s="1" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F172" s="1">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>113</v>
       </c>
@@ -5433,8 +5976,11 @@
       <c r="E173" s="1" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F173" s="1">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>114</v>
       </c>
@@ -5447,8 +5993,11 @@
       <c r="E174" s="1" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F174" s="1">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>115</v>
       </c>
@@ -5461,8 +6010,11 @@
       <c r="E175" s="1" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F175" s="1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>116</v>
       </c>
@@ -5475,8 +6027,11 @@
       <c r="E176" s="1" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F176" s="1">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>117</v>
       </c>
@@ -5489,8 +6044,11 @@
       <c r="E177" s="1" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F177" s="1">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>118</v>
       </c>
@@ -5503,8 +6061,11 @@
       <c r="E178" s="1" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F178" s="1">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>119</v>
       </c>
@@ -5517,8 +6078,11 @@
       <c r="E179" s="1" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F179" s="1">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>120</v>
       </c>
@@ -5531,8 +6095,11 @@
       <c r="E180" s="1" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F180" s="1">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>121</v>
       </c>
@@ -5545,8 +6112,11 @@
       <c r="E181" s="1" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F181" s="1">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>122</v>
       </c>
@@ -5559,8 +6129,11 @@
       <c r="E182" s="1" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F182" s="1">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>123</v>
       </c>
@@ -5573,8 +6146,11 @@
       <c r="E183" s="1" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F183" s="1">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>124</v>
       </c>
@@ -5587,8 +6163,11 @@
       <c r="E184" s="1" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F184" s="1">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>125</v>
       </c>
@@ -5601,8 +6180,11 @@
       <c r="E185" s="1" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F185" s="1">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>126</v>
       </c>
@@ -5615,8 +6197,11 @@
       <c r="E186" s="1" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F186" s="1">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>127</v>
       </c>
@@ -5629,8 +6214,11 @@
       <c r="E187" s="1" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F187" s="1">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>128</v>
       </c>
@@ -5643,8 +6231,11 @@
       <c r="E188" s="1" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F188" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>129</v>
       </c>
@@ -5657,8 +6248,11 @@
       <c r="E189" s="1" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F189" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>130</v>
       </c>
@@ -5671,8 +6265,11 @@
       <c r="E190" s="1" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F190" s="1">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>131</v>
       </c>
@@ -5685,8 +6282,11 @@
       <c r="E191" s="1" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F191" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>132</v>
       </c>
@@ -5699,8 +6299,11 @@
       <c r="E192" s="1" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F192" s="1">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>133</v>
       </c>
@@ -5713,8 +6316,11 @@
       <c r="E193" s="1" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F193" s="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>134</v>
       </c>
@@ -5727,8 +6333,11 @@
       <c r="E194" s="1" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F194" s="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>135</v>
       </c>
@@ -5741,8 +6350,11 @@
       <c r="E195" s="1" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F195" s="1">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>136</v>
       </c>
@@ -5755,8 +6367,11 @@
       <c r="E196" s="1" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F196" s="1">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>137</v>
       </c>
@@ -5769,8 +6384,11 @@
       <c r="E197" s="1" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F197" s="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>138</v>
       </c>
@@ -5783,8 +6401,11 @@
       <c r="E198" s="1" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F198" s="1">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>139</v>
       </c>
@@ -5797,8 +6418,11 @@
       <c r="E199" s="1" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F199" s="1">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>140</v>
       </c>
@@ -5811,8 +6435,11 @@
       <c r="E200" s="1" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F200" s="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>141</v>
       </c>
@@ -5825,8 +6452,11 @@
       <c r="E201" s="1" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F201" s="1">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>142</v>
       </c>
@@ -5839,8 +6469,11 @@
       <c r="E202" s="1" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F202" s="1">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>143</v>
       </c>
@@ -5853,8 +6486,11 @@
       <c r="E203" s="1" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F203" s="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>144</v>
       </c>
@@ -5867,8 +6503,11 @@
       <c r="E204" s="1" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F204" s="1">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>145</v>
       </c>
@@ -5881,8 +6520,11 @@
       <c r="E205" s="1" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F205" s="1">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>146</v>
       </c>
@@ -5895,8 +6537,11 @@
       <c r="E206" s="1" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F206" s="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>147</v>
       </c>
@@ -5909,8 +6554,11 @@
       <c r="E207" s="1" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F207" s="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>148</v>
       </c>
@@ -5923,8 +6571,11 @@
       <c r="E208" s="1" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F208" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>149</v>
       </c>
@@ -5937,8 +6588,11 @@
       <c r="E209" s="1" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F209" s="1">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>150</v>
       </c>
@@ -5951,8 +6605,11 @@
       <c r="E210" s="1" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F210" s="1">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>385</v>
       </c>
@@ -5962,8 +6619,11 @@
       <c r="C211" s="1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F211" s="1">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>387</v>
       </c>
@@ -5973,8 +6633,11 @@
       <c r="C212" s="1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F212" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>428</v>
       </c>
@@ -5984,8 +6647,11 @@
       <c r="C213" s="1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" ht="15" x14ac:dyDescent="0.35">
+      <c r="F213" s="1">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>682</v>
       </c>
@@ -5995,8 +6661,11 @@
       <c r="C214" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F214" s="1">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>320</v>
       </c>
@@ -6006,8 +6675,11 @@
       <c r="C215" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F215" s="1">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>347</v>
       </c>
@@ -6017,8 +6689,11 @@
       <c r="C216" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F216" s="1">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>349</v>
       </c>
@@ -6028,8 +6703,11 @@
       <c r="C217" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" ht="15" x14ac:dyDescent="0.35">
+      <c r="F217" s="1">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>684</v>
       </c>
@@ -6039,8 +6717,11 @@
       <c r="C218" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F218" s="1">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>351</v>
       </c>
@@ -6050,8 +6731,11 @@
       <c r="C219" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F219" s="1">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>352</v>
       </c>
@@ -6061,8 +6745,11 @@
       <c r="C220" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F220" s="1">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>353</v>
       </c>
@@ -6072,8 +6759,11 @@
       <c r="C221" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" ht="15" x14ac:dyDescent="0.35">
+      <c r="F221" s="1">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>686</v>
       </c>
@@ -6083,8 +6773,11 @@
       <c r="C222" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F222" s="1">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>357</v>
       </c>
@@ -6094,8 +6787,11 @@
       <c r="C223" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F223" s="1">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>358</v>
       </c>
@@ -6105,8 +6801,11 @@
       <c r="C224" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F224" s="1">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>359</v>
       </c>
@@ -6116,8 +6815,11 @@
       <c r="C225" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F225" s="1">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>363</v>
       </c>
@@ -6127,8 +6829,11 @@
       <c r="C226" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F226" s="1">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>365</v>
       </c>
@@ -6138,8 +6843,11 @@
       <c r="C227" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F227" s="1">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>366</v>
       </c>
@@ -6149,8 +6857,11 @@
       <c r="C228" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F228" s="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>369</v>
       </c>
@@ -6160,8 +6871,11 @@
       <c r="C229" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F229" s="1">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>370</v>
       </c>
@@ -6171,8 +6885,11 @@
       <c r="C230" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F230" s="1">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>371</v>
       </c>
@@ -6182,8 +6899,11 @@
       <c r="C231" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F231" s="1">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>372</v>
       </c>
@@ -6193,8 +6913,11 @@
       <c r="C232" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F232" s="1">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>377</v>
       </c>
@@ -6204,8 +6927,11 @@
       <c r="C233" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F233" s="1">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>379</v>
       </c>
@@ -6215,8 +6941,11 @@
       <c r="C234" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F234" s="1">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>466</v>
       </c>
@@ -6229,8 +6958,11 @@
       <c r="E235" s="1" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F235" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>688</v>
       </c>
@@ -6243,8 +6975,11 @@
       <c r="E236" s="1" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F236" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>689</v>
       </c>
@@ -6257,8 +6992,11 @@
       <c r="E237" s="1" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F237" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>690</v>
       </c>
@@ -6271,8 +7009,11 @@
       <c r="E238" s="1" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F238" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>691</v>
       </c>
@@ -6285,8 +7026,11 @@
       <c r="E239" s="1" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F239" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>692</v>
       </c>
@@ -6299,8 +7043,11 @@
       <c r="E240" s="1" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F240" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>729</v>
       </c>
@@ -6313,8 +7060,11 @@
       <c r="E241" s="1" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F241" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>693</v>
       </c>
@@ -6327,8 +7077,11 @@
       <c r="E242" s="1" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F242" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>732</v>
       </c>
@@ -6341,8 +7094,11 @@
       <c r="E243" s="1" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F243" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>694</v>
       </c>
@@ -6355,8 +7111,11 @@
       <c r="E244" s="1" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F244" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>695</v>
       </c>
@@ -6369,8 +7128,11 @@
       <c r="E245" s="1" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F245" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>696</v>
       </c>
@@ -6383,8 +7145,11 @@
       <c r="E246" s="1" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F246" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>737</v>
       </c>
@@ -6397,8 +7162,11 @@
       <c r="E247" s="1" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F247" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>697</v>
       </c>
@@ -6411,8 +7179,11 @@
       <c r="E248" s="1" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F248" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>698</v>
       </c>
@@ -6425,8 +7196,11 @@
       <c r="E249" s="1" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F249" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>741</v>
       </c>
@@ -6439,13 +7213,16 @@
       <c r="E250" s="1" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F250" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>699</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>699</v>
+        <v>786</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>153</v>
@@ -6453,8 +7230,11 @@
       <c r="E251" s="1" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F251" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>744</v>
       </c>
@@ -6467,8 +7247,11 @@
       <c r="E252" s="1" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F252" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>700</v>
       </c>
@@ -6481,8 +7264,11 @@
       <c r="E253" s="1" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F253" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>701</v>
       </c>
@@ -6495,8 +7281,11 @@
       <c r="E254" s="1" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F254" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>702</v>
       </c>
@@ -6509,8 +7298,11 @@
       <c r="E255" s="1" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F255" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>703</v>
       </c>
@@ -6523,8 +7315,11 @@
       <c r="E256" s="1" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F256" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>704</v>
       </c>
@@ -6537,8 +7332,11 @@
       <c r="E257" s="1" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F257" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>751</v>
       </c>
@@ -6551,8 +7349,11 @@
       <c r="E258" s="1" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F258" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>705</v>
       </c>
@@ -6565,8 +7366,11 @@
       <c r="E259" s="1" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F259" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>754</v>
       </c>
@@ -6579,8 +7383,11 @@
       <c r="E260" s="1" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F260" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>706</v>
       </c>
@@ -6593,8 +7400,11 @@
       <c r="E261" s="1" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F261" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>707</v>
       </c>
@@ -6607,8 +7417,11 @@
       <c r="E262" s="1" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F262" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>708</v>
       </c>
@@ -6621,8 +7434,11 @@
       <c r="E263" s="1" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F263" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>709</v>
       </c>
@@ -6635,8 +7451,11 @@
       <c r="E264" s="1" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F264" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>710</v>
       </c>
@@ -6649,8 +7468,11 @@
       <c r="E265" s="1" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F265" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>711</v>
       </c>
@@ -6663,8 +7485,11 @@
       <c r="E266" s="1" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F266" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>762</v>
       </c>
@@ -6677,8 +7502,11 @@
       <c r="E267" s="1" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F267" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>712</v>
       </c>
@@ -6691,8 +7519,11 @@
       <c r="E268" s="1" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F268" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>764</v>
       </c>
@@ -6705,8 +7536,11 @@
       <c r="E269" s="1" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F269" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>713</v>
       </c>
@@ -6719,8 +7553,11 @@
       <c r="E270" s="1" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F270" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>714</v>
       </c>
@@ -6733,8 +7570,11 @@
       <c r="E271" s="1" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F271" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>715</v>
       </c>
@@ -6747,8 +7587,11 @@
       <c r="E272" s="1" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F272" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>716</v>
       </c>
@@ -6761,8 +7604,11 @@
       <c r="E273" s="1" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F273" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>771</v>
       </c>
@@ -6775,8 +7621,11 @@
       <c r="E274" s="1" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F274" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>717</v>
       </c>
@@ -6789,8 +7638,11 @@
       <c r="E275" s="1" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F275" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>773</v>
       </c>
@@ -6803,8 +7655,11 @@
       <c r="E276" s="1" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F276" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>718</v>
       </c>
@@ -6817,8 +7672,11 @@
       <c r="E277" s="1" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F277" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>719</v>
       </c>
@@ -6831,8 +7689,11 @@
       <c r="E278" s="1" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F278" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>720</v>
       </c>
@@ -6845,8 +7706,11 @@
       <c r="E279" s="1" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F279" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>721</v>
       </c>
@@ -6859,8 +7723,11 @@
       <c r="E280" s="1" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F280" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>722</v>
       </c>
@@ -6873,8 +7740,11 @@
       <c r="E281" s="1" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F281" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>781</v>
       </c>
@@ -6887,8 +7757,11 @@
       <c r="E282" s="1" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F282" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>723</v>
       </c>
@@ -6901,8 +7774,11 @@
       <c r="E283" s="1" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F283" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>784</v>
       </c>
@@ -6914,6 +7790,9 @@
       </c>
       <c r="E284" s="1" t="s">
         <v>785</v>
+      </c>
+      <c r="F284" s="1">
+        <v>999</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA50CEDE-9821-458E-90E3-132CAF283AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1801A4-B694-4629-B0FB-BFE93D24CE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="450" windowWidth="32160" windowHeight="20430" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="795">
   <si>
     <t>id</t>
   </si>
@@ -2440,6 +2440,15 @@
   <si>
     <t>排序</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rwt</t>
+  </si>
+  <si>
+    <t>允许符文之语-显示</t>
+  </si>
+  <si>
+    <t>可制作五行符</t>
   </si>
 </sst>
 </file>
@@ -2450,7 +2459,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2462,7 +2471,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2475,7 +2484,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2512,6 +2521,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2525,7 +2558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2535,9 +2568,13 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -2622,6 +2659,12 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCC99"/>
+      <color rgb="FFFF9999"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2634,7 +2677,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2950,21 +2993,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:H284"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H285"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2990,7 +3033,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -3016,12 +3059,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>321</v>
       </c>
@@ -3047,7 +3090,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -3064,7 +3107,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>395</v>
       </c>
@@ -3081,7 +3124,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>396</v>
       </c>
@@ -3098,7 +3141,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>397</v>
       </c>
@@ -3115,7 +3158,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3132,7 +3175,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3149,7 +3192,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3172,7 +3215,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3195,7 +3238,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3212,7 +3255,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3229,7 +3272,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3252,7 +3295,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -3275,7 +3318,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3292,7 +3335,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -3309,7 +3352,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -3326,7 +3369,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -3343,7 +3386,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>410</v>
       </c>
@@ -3360,7 +3403,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>664</v>
       </c>
@@ -3377,7 +3420,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>665</v>
       </c>
@@ -3394,7 +3437,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>280</v>
       </c>
@@ -3411,7 +3454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>281</v>
       </c>
@@ -3428,7 +3471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>282</v>
       </c>
@@ -3445,7 +3488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>283</v>
       </c>
@@ -3462,7 +3505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>284</v>
       </c>
@@ -3479,7 +3522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>446</v>
       </c>
@@ -3496,7 +3539,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>447</v>
       </c>
@@ -3513,7 +3556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>448</v>
       </c>
@@ -3530,7 +3573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>449</v>
       </c>
@@ -3547,7 +3590,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>450</v>
       </c>
@@ -3564,7 +3607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>451</v>
       </c>
@@ -3581,7 +3624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>452</v>
       </c>
@@ -3598,7 +3641,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>453</v>
       </c>
@@ -3615,7 +3658,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>454</v>
       </c>
@@ -3632,7 +3675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>455</v>
       </c>
@@ -3649,7 +3692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -3666,7 +3709,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -3683,7 +3726,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -3700,7 +3743,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -3717,7 +3760,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -3734,7 +3777,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -3751,7 +3794,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -3768,7 +3811,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -3785,7 +3828,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -3802,7 +3845,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -3819,7 +3862,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
@@ -3836,7 +3879,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
@@ -3853,7 +3896,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -3870,7 +3913,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
@@ -3887,7 +3930,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
@@ -3904,7 +3947,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>412</v>
       </c>
@@ -3921,7 +3964,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>413</v>
       </c>
@@ -3938,7 +3981,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>414</v>
       </c>
@@ -3955,7 +3998,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -3972,7 +4015,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -3989,7 +4032,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -4006,7 +4049,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -4023,7 +4066,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -4040,7 +4083,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -4060,7 +4103,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
@@ -4080,7 +4123,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
@@ -4100,7 +4143,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>399</v>
       </c>
@@ -4120,7 +4163,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>400</v>
       </c>
@@ -4140,7 +4183,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>406</v>
       </c>
@@ -4160,7 +4203,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>404</v>
       </c>
@@ -4177,7 +4220,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -4194,7 +4237,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
@@ -4211,7 +4254,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -4228,7 +4271,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -4245,7 +4288,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -4262,7 +4305,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
@@ -4285,7 +4328,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -4308,7 +4351,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -4331,7 +4374,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -4354,7 +4397,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
@@ -4377,7 +4420,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>393</v>
       </c>
@@ -4394,7 +4437,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -4411,7 +4454,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -4428,7 +4471,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -4445,7 +4488,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -4462,7 +4505,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>310</v>
       </c>
@@ -4479,7 +4522,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>311</v>
       </c>
@@ -4496,7 +4539,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>312</v>
       </c>
@@ -4513,7 +4556,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>313</v>
       </c>
@@ -4530,7 +4573,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>314</v>
       </c>
@@ -4547,7 +4590,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -4564,7 +4607,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -4581,7 +4624,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -4598,7 +4641,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -4615,7 +4658,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -4632,7 +4675,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>420</v>
       </c>
@@ -4649,7 +4692,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>661</v>
       </c>
@@ -4666,7 +4709,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -4680,7 +4723,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>473</v>
       </c>
@@ -4697,7 +4740,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>676</v>
       </c>
@@ -4714,7 +4757,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>408</v>
       </c>
@@ -4731,7 +4774,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>381</v>
       </c>
@@ -4745,7 +4788,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>383</v>
       </c>
@@ -4759,3039 +4802,3056 @@
         <v>293</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="F102" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B103" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F103" s="1">
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B104" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E103" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F104" s="1">
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B105" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F105" s="1">
         <v>303</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B106" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E105" s="1" t="s">
+      <c r="C106" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F106" s="1">
         <v>304</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B107" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E106" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F107" s="1">
         <v>305</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B108" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E107" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F108" s="1">
         <v>306</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B109" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E108" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F109" s="1">
         <v>307</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B110" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E109" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F110" s="1">
         <v>308</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E110" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F111" s="1">
         <v>309</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E111" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F112" s="1">
         <v>310</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F113" s="1">
         <v>311</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F114" s="1">
         <v>312</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="F114" s="1">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>427</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F115" s="1">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>444</v>
+        <v>390</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>445</v>
+        <v>392</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>427</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="F116" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F117" s="1">
         <v>315</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="B118" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E117" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F118" s="1">
         <v>401</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B119" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E118" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F119" s="1">
         <v>402</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B120" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E119" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F120" s="1">
         <v>403</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B121" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E120" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F121" s="1">
         <v>404</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B122" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E121" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F122" s="1">
         <v>405</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B123" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E122" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F123" s="1">
         <v>406</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B124" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E123" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F124" s="1">
         <v>407</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B125" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E124" s="1" t="s">
+      <c r="C125" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F125" s="1">
         <v>408</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B126" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E125" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F126" s="1">
         <v>409</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B127" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F127" s="1">
         <v>410</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B128" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E127" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F128" s="1">
         <v>411</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="B129" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E128" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F129" s="1">
         <v>412</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B130" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E129" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F130" s="1">
         <v>413</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="B131" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E130" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F131" s="1">
         <v>414</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B132" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E131" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F132" s="1">
         <v>415</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="B133" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E132" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F133" s="1">
         <v>416</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="B134" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E133" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F134" s="1">
         <v>417</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B134" s="5" t="s">
+      <c r="B135" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E134" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F135" s="1">
         <v>418</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B135" s="5" t="s">
+      <c r="B136" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E135" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F136" s="1">
         <v>419</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B136" s="5" t="s">
+      <c r="B137" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E136" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F137" s="1">
         <v>420</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B138" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F138" s="1">
         <v>421</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C139" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F139" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B139" s="6" t="s">
+      <c r="B140" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E139" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F140" s="1">
         <v>431</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B141" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F141" s="1">
         <v>432</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="B142" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E141" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F142" s="1">
         <v>433</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B142" s="6" t="s">
+      <c r="B143" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E142" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F143" s="1">
         <v>434</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B144" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E143" s="1" t="s">
+      <c r="C144" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F144" s="1">
         <v>435</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B144" s="6" t="s">
+      <c r="B145" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E144" s="1" t="s">
+      <c r="C145" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E145" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F145" s="1">
         <v>436</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B145" s="6" t="s">
+      <c r="B146" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E145" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F146" s="1">
         <v>437</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B147" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E146" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F147" s="1">
         <v>438</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B148" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E147" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F148" s="1">
         <v>439</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B149" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E148" s="1" t="s">
+      <c r="C149" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F149" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B149" s="6" t="s">
+      <c r="B150" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E149" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F150" s="1">
         <v>441</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A151" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B150" s="6" t="s">
+      <c r="B151" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E150" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F151" s="1">
         <v>442</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A152" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B151" s="6" t="s">
+      <c r="B152" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E151" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F152" s="1">
         <v>443</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A153" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B153" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E152" s="1" t="s">
+      <c r="C153" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F153" s="1">
         <v>444</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A154" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B154" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E153" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F154" s="1">
         <v>445</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="1" t="s">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A155" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B154" s="6" t="s">
+      <c r="B155" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E154" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F155" s="1">
         <v>446</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="1" t="s">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="B156" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E155" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F156" s="1">
         <v>447</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A157" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B156" s="6" t="s">
+      <c r="B157" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E156" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F157" s="1">
         <v>448</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="1" t="s">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="B158" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E157" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F158" s="1">
         <v>449</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A159" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="B159" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E158" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F159" s="1">
         <v>450</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A160" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B160" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E159" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F160" s="1">
         <v>451</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A161" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B161" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E160" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F161" s="1">
         <v>452</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A162" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B161" s="6" t="s">
+      <c r="B162" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E161" s="1" t="s">
+      <c r="C162" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F162" s="1">
         <v>453</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A163" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="B163" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E162" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F163" s="1">
         <v>454</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A164" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B163" s="6" t="s">
+      <c r="B164" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E163" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F164" s="1">
         <v>455</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B164" s="6" t="s">
+      <c r="B165" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E164" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F165" s="1">
         <v>456</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B165" s="6" t="s">
+      <c r="B166" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E165" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F166" s="1">
         <v>457</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A167" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B166" s="6" t="s">
+      <c r="B167" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E166" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F167" s="1">
         <v>458</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="1" t="s">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A168" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="B168" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E167" s="1" t="s">
+      <c r="C168" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F168" s="1">
         <v>459</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A169" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B168" s="6" t="s">
+      <c r="B169" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E168" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F169" s="1">
         <v>460</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A170" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B169" s="6" t="s">
+      <c r="B170" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E169" s="1" t="s">
+      <c r="C170" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F170" s="1">
         <v>461</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A171" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B170" s="6" t="s">
+      <c r="B171" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F171" s="1">
         <v>462</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A172" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B171" s="6" t="s">
+      <c r="B172" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E171" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F172" s="1">
         <v>463</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A173" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B173" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E172" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F173" s="1">
         <v>464</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A174" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B174" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E173" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F174" s="1">
         <v>465</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="1" t="s">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A175" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B174" s="6" t="s">
+      <c r="B175" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E174" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F175" s="1">
         <v>466</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="1" t="s">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A176" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B176" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E175" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F176" s="1">
         <v>467</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="1" t="s">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A177" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B176" s="6" t="s">
+      <c r="B177" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E176" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F177" s="1">
         <v>468</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A178" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B177" s="6" t="s">
+      <c r="B178" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E177" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F178" s="1">
         <v>469</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A179" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B178" s="6" t="s">
+      <c r="B179" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E179" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F179" s="1">
         <v>470</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A180" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B179" s="6" t="s">
+      <c r="B180" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E179" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F180" s="1">
         <v>471</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="1" t="s">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A181" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B180" s="6" t="s">
+      <c r="B181" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E180" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="F180" s="1">
+      <c r="F181" s="1">
         <v>472</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A182" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B181" s="6" t="s">
+      <c r="B182" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E181" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F182" s="1">
         <v>473</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A183" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B182" s="6" t="s">
+      <c r="B183" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F183" s="1">
         <v>474</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="1" t="s">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A184" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B183" s="6" t="s">
+      <c r="B184" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F184" s="1">
         <v>475</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A185" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B184" s="6" t="s">
+      <c r="B185" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E184" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F185" s="1">
         <v>476</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A186" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B185" s="6" t="s">
+      <c r="B186" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E185" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F186" s="1">
         <v>477</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="1" t="s">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A187" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B186" s="6" t="s">
+      <c r="B187" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E186" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F187" s="1">
         <v>478</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A188" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B187" s="6" t="s">
+      <c r="B188" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E187" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F188" s="1">
         <v>479</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A189" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B188" s="6" t="s">
+      <c r="B189" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E188" s="1" t="s">
+      <c r="C189" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F189" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A190" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B189" s="6" t="s">
+      <c r="B190" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E189" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F190" s="1">
         <v>481</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="1" t="s">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A191" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B190" s="6" t="s">
+      <c r="B191" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E190" s="1" t="s">
+      <c r="C191" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F191" s="1">
         <v>482</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="1" t="s">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A192" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B191" s="6" t="s">
+      <c r="B192" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E191" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F192" s="1">
         <v>483</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="1" t="s">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A193" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B192" s="6" t="s">
+      <c r="B193" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C192" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E192" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F193" s="1">
         <v>484</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="1" t="s">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A194" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B193" s="6" t="s">
+      <c r="B194" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E193" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F194" s="1">
         <v>485</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="1" t="s">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A195" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B194" s="6" t="s">
+      <c r="B195" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E194" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F195" s="1">
         <v>486</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" s="1" t="s">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A196" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B195" s="6" t="s">
+      <c r="B196" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E195" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F196" s="1">
         <v>487</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="1" t="s">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A197" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B196" s="6" t="s">
+      <c r="B197" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E196" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F197" s="1">
         <v>488</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="1" t="s">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A198" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B197" s="6" t="s">
+      <c r="B198" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E197" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F198" s="1">
         <v>489</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="1" t="s">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A199" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B198" s="6" t="s">
+      <c r="B199" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E198" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F199" s="1">
         <v>490</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="1" t="s">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A200" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B199" s="6" t="s">
+      <c r="B200" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E199" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F200" s="1">
         <v>491</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A201" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B200" s="6" t="s">
+      <c r="B201" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E200" s="1" t="s">
+      <c r="C201" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F201" s="1">
         <v>492</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="1" t="s">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A202" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B201" s="6" t="s">
+      <c r="B202" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E201" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="F201" s="1">
+      <c r="F202" s="1">
         <v>493</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="1" t="s">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A203" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B202" s="6" t="s">
+      <c r="B203" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E202" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E203" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F203" s="1">
         <v>494</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="1" t="s">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A204" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B203" s="6" t="s">
+      <c r="B204" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E203" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="F203" s="1">
+      <c r="F204" s="1">
         <v>495</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A205" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B204" s="6" t="s">
+      <c r="B205" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E204" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F205" s="1">
         <v>496</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="1" t="s">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A206" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B205" s="6" t="s">
+      <c r="B206" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E205" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F206" s="1">
         <v>497</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A207" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B206" s="6" t="s">
+      <c r="B207" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E206" s="1" t="s">
+      <c r="C207" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F207" s="1">
         <v>498</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="1" t="s">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A208" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B207" s="6" t="s">
+      <c r="B208" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E207" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F208" s="1">
         <v>499</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A209" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B208" s="6" t="s">
+      <c r="B209" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E208" s="1" t="s">
+      <c r="C209" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F209" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A210" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B209" s="6" t="s">
+      <c r="B210" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E209" s="1" t="s">
+      <c r="C210" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E210" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F210" s="1">
         <v>501</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A211" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B210" s="6" t="s">
+      <c r="B211" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E210" s="1" t="s">
+      <c r="C211" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E211" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F211" s="1">
         <v>502</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A212" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="B212" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F211" s="1">
+      <c r="C212" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F212" s="1">
         <v>801</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A213" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="B213" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F212" s="1">
+      <c r="C213" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F213" s="1">
         <v>802</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A214" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="B214" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F213" s="1">
+      <c r="C214" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F214" s="1">
         <v>803</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
+    <row r="215" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A215" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B215" s="7" t="s">
         <v>683</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F214" s="1">
+      <c r="C215" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F215" s="1">
         <v>821</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A216" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="B216" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F215" s="1">
+      <c r="C216" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F216" s="1">
         <v>822</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A217" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="B217" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F216" s="1">
+      <c r="C217" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F217" s="1">
         <v>823</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" s="1" t="s">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A218" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="B218" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C217" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F217" s="1">
+      <c r="C218" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F218" s="1">
         <v>824</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
+    <row r="219" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A219" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="B218" s="7" t="s">
+      <c r="B219" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F218" s="1">
+      <c r="C219" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F219" s="1">
         <v>825</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A220" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="B220" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F219" s="1">
+      <c r="C220" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F220" s="1">
         <v>826</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A221" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="B221" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F220" s="1">
+      <c r="C221" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F221" s="1">
         <v>827</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A222" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="B222" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C221" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F221" s="1">
+      <c r="C222" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F222" s="1">
         <v>828</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
+    <row r="223" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A223" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B223" s="7" t="s">
         <v>687</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F222" s="1">
+      <c r="C223" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F223" s="1">
         <v>829</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="B224" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F223" s="1">
+      <c r="C224" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F224" s="1">
         <v>830</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A225" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B224" s="1" t="s">
+      <c r="B225" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F224" s="1">
+      <c r="C225" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F225" s="1">
         <v>831</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A226" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="B226" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F225" s="1">
+      <c r="C226" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F226" s="1">
         <v>832</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A227" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B226" s="1" t="s">
+      <c r="B227" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C226" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F226" s="1">
+      <c r="C227" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F227" s="1">
         <v>833</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A228" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B227" s="1" t="s">
+      <c r="B228" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C227" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F227" s="1">
+      <c r="C228" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F228" s="1">
         <v>834</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A229" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B228" s="1" t="s">
+      <c r="B229" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C228" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F228" s="1">
+      <c r="C229" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F229" s="1">
         <v>835</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A230" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B229" s="1" t="s">
+      <c r="B230" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F229" s="1">
+      <c r="C230" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F230" s="1">
         <v>836</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A231" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="B231" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F230" s="1">
+      <c r="C231" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F231" s="1">
         <v>837</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A232" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="B232" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C231" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F231" s="1">
+      <c r="C232" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F232" s="1">
         <v>838</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A233" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="B233" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F232" s="1">
+      <c r="C233" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F233" s="1">
         <v>839</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A234" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="B234" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C233" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F233" s="1">
+      <c r="C234" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F234" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A235" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="B235" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F234" s="1">
+      <c r="C235" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F235" s="1">
         <v>841</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A236" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="B236" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E235" s="1" t="s">
+      <c r="C236" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E236" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="F235" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="F236" s="1">
         <v>999</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
+    <row r="237" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A237" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="C237" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="F237" s="9">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A238" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="B238" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E237" s="1" t="s">
+      <c r="C238" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E238" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F238" s="9">
         <v>999</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238" s="1" t="s">
+    <row r="239" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A239" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="B238" s="1" t="s">
+      <c r="B239" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="C238" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E238" s="1" t="s">
+      <c r="C239" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E239" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F239" s="9">
         <v>999</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" s="1" t="s">
+    <row r="240" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A240" s="9" t="s">
         <v>691</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="B240" s="9" t="s">
         <v>691</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E239" s="1" t="s">
+      <c r="C240" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E240" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F240" s="9">
         <v>999</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A240" s="1" t="s">
+    <row r="241" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A241" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="B240" s="1" t="s">
+      <c r="B241" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="C240" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E240" s="1" t="s">
+      <c r="C241" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E241" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="F240" s="1">
+      <c r="F241" s="9">
         <v>999</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A241" s="1" t="s">
+    <row r="242" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A242" s="9" t="s">
         <v>729</v>
       </c>
-      <c r="B241" s="1" t="s">
+      <c r="B242" s="9" t="s">
         <v>729</v>
       </c>
-      <c r="C241" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E241" s="1" t="s">
+      <c r="C242" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E242" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F242" s="9">
         <v>999</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A242" s="1" t="s">
+    <row r="243" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A243" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="B243" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="C242" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E242" s="1" t="s">
+      <c r="C243" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E243" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F243" s="9">
         <v>999</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A243" s="1" t="s">
+    <row r="244" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="B244" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="C243" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E243" s="1" t="s">
+      <c r="C244" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E244" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F244" s="9">
         <v>999</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A244" s="1" t="s">
+    <row r="245" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="B244" s="1" t="s">
+      <c r="B245" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="C244" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E244" s="1" t="s">
+      <c r="C245" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E245" s="10" t="s">
         <v>734</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F245" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A245" s="1" t="s">
+    <row r="246" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="10" t="s">
         <v>695</v>
       </c>
-      <c r="B245" s="1" t="s">
+      <c r="B246" s="10" t="s">
         <v>695</v>
       </c>
-      <c r="C245" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E245" s="1" t="s">
+      <c r="C246" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E246" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F246" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A246" s="1" t="s">
+    <row r="247" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="B247" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E246" s="1" t="s">
+      <c r="C247" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E247" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="F246" s="1">
+      <c r="F247" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A247" s="1" t="s">
+    <row r="248" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="B247" s="1" t="s">
+      <c r="B248" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="C247" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E247" s="1" t="s">
+      <c r="C248" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E248" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F248" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A248" s="1" t="s">
+    <row r="249" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A249" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="B249" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E248" s="1" t="s">
+      <c r="C249" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E249" s="10" t="s">
         <v>739</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F249" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A249" s="1" t="s">
+    <row r="250" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A250" s="10" t="s">
         <v>698</v>
       </c>
-      <c r="B249" s="1" t="s">
+      <c r="B250" s="10" t="s">
         <v>698</v>
       </c>
-      <c r="C249" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E249" s="1" t="s">
+      <c r="C250" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E250" s="10" t="s">
         <v>740</v>
       </c>
-      <c r="F249" s="1">
+      <c r="F250" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A250" s="1" t="s">
+    <row r="251" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A251" s="10" t="s">
         <v>741</v>
       </c>
-      <c r="B250" s="1" t="s">
+      <c r="B251" s="10" t="s">
         <v>741</v>
       </c>
-      <c r="C250" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E250" s="1" t="s">
+      <c r="C251" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E251" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="F250" s="1">
+      <c r="F251" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A251" s="1" t="s">
+    <row r="252" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A252" s="10" t="s">
         <v>699</v>
       </c>
-      <c r="B251" s="1" t="s">
+      <c r="B252" s="10" t="s">
         <v>786</v>
       </c>
-      <c r="C251" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E251" s="1" t="s">
+      <c r="C252" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E252" s="10" t="s">
         <v>743</v>
       </c>
-      <c r="F251" s="1">
+      <c r="F252" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A252" s="1" t="s">
+    <row r="253" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A253" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="B253" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="C252" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E252" s="1" t="s">
+      <c r="C253" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E253" s="10" t="s">
         <v>745</v>
       </c>
-      <c r="F252" s="1">
+      <c r="F253" s="10">
         <v>999</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A253" s="1" t="s">
+    <row r="254" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A254" s="11" t="s">
         <v>700</v>
       </c>
-      <c r="B253" s="1" t="s">
+      <c r="B254" s="11" t="s">
         <v>700</v>
       </c>
-      <c r="C253" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E253" s="1" t="s">
+      <c r="C254" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E254" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F254" s="11">
         <v>999</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A254" s="1" t="s">
+    <row r="255" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A255" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="B255" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E254" s="1" t="s">
+      <c r="C255" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E255" s="11" t="s">
         <v>747</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F255" s="11">
         <v>999</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255" s="1" t="s">
+    <row r="256" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="B255" s="1" t="s">
+      <c r="B256" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="C255" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E255" s="1" t="s">
+      <c r="C256" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E256" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="F255" s="1">
+      <c r="F256" s="11">
         <v>999</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" s="1" t="s">
+    <row r="257" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A257" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="B257" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E256" s="1" t="s">
+      <c r="C257" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E257" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="F256" s="1">
+      <c r="F257" s="11">
         <v>999</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257" s="1" t="s">
+    <row r="258" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A258" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="B258" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="C257" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E257" s="1" t="s">
+      <c r="C258" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E258" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F258" s="11">
         <v>999</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A258" s="1" t="s">
+    <row r="259" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A259" s="11" t="s">
         <v>751</v>
       </c>
-      <c r="B258" s="1" t="s">
+      <c r="B259" s="11" t="s">
         <v>751</v>
       </c>
-      <c r="C258" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E258" s="1" t="s">
+      <c r="C259" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E259" s="11" t="s">
         <v>752</v>
       </c>
-      <c r="F258" s="1">
+      <c r="F259" s="11">
         <v>999</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A259" s="1" t="s">
+    <row r="260" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A260" s="11" t="s">
         <v>705</v>
       </c>
-      <c r="B259" s="1" t="s">
+      <c r="B260" s="11" t="s">
         <v>705</v>
       </c>
-      <c r="C259" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E259" s="1" t="s">
+      <c r="C260" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E260" s="11" t="s">
         <v>753</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F260" s="11">
         <v>999</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260" s="1" t="s">
+    <row r="261" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A261" s="11" t="s">
         <v>754</v>
       </c>
-      <c r="B260" s="1" t="s">
+      <c r="B261" s="11" t="s">
         <v>754</v>
       </c>
-      <c r="C260" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E260" s="1" t="s">
+      <c r="C261" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E261" s="11" t="s">
         <v>755</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F261" s="11">
         <v>999</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261" s="1" t="s">
+    <row r="262" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A262" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="B261" s="1" t="s">
+      <c r="B262" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="C261" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E261" s="1" t="s">
+      <c r="C262" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E262" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="F261" s="1">
+      <c r="F262" s="12">
         <v>999</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A262" s="1" t="s">
+    <row r="263" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A263" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="B263" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="C262" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E262" s="1" t="s">
+      <c r="C263" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E263" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F263" s="12">
         <v>999</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A263" s="1" t="s">
+    <row r="264" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A264" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="B263" s="1" t="s">
+      <c r="B264" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="C263" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E263" s="1" t="s">
+      <c r="C264" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E264" s="12" t="s">
         <v>758</v>
       </c>
-      <c r="F263" s="1">
+      <c r="F264" s="12">
         <v>999</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264" s="1" t="s">
+    <row r="265" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="B264" s="1" t="s">
+      <c r="B265" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="C264" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E264" s="1" t="s">
+      <c r="C265" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E265" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F265" s="12">
         <v>999</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265" s="1" t="s">
+    <row r="266" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="B265" s="1" t="s">
+      <c r="B266" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="C265" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E265" s="1" t="s">
+      <c r="C266" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E266" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F266" s="12">
         <v>999</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266" s="1" t="s">
+    <row r="267" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="B266" s="1" t="s">
+      <c r="B267" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="C266" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E266" s="1" t="s">
+      <c r="C267" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E267" s="12" t="s">
         <v>761</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F267" s="12">
         <v>999</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A267" s="1" t="s">
+    <row r="268" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="B267" s="1" t="s">
+      <c r="B268" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="C267" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E267" s="1" t="s">
+      <c r="C268" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E268" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="F267" s="1">
+      <c r="F268" s="12">
         <v>999</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A268" s="1" t="s">
+    <row r="269" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="B269" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E268" s="1" t="s">
+      <c r="C269" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E269" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="F268" s="1">
+      <c r="F269" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269" s="1" t="s">
+    <row r="270" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="B270" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="C269" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E269" s="1" t="s">
+      <c r="C270" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E270" s="6" t="s">
         <v>766</v>
       </c>
-      <c r="F269" s="1">
+      <c r="F270" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270" s="1" t="s">
+    <row r="271" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A271" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="B270" s="1" t="s">
+      <c r="B271" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="C270" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E270" s="1" t="s">
+      <c r="C271" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E271" s="6" t="s">
         <v>767</v>
       </c>
-      <c r="F270" s="1">
+      <c r="F271" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A271" s="1" t="s">
+    <row r="272" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="B272" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E271" s="1" t="s">
+      <c r="C272" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E272" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="F271" s="1">
+      <c r="F272" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A272" s="1" t="s">
+    <row r="273" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="6" t="s">
         <v>715</v>
       </c>
-      <c r="B272" s="1" t="s">
+      <c r="B273" s="6" t="s">
         <v>715</v>
       </c>
-      <c r="C272" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E272" s="1" t="s">
+      <c r="C273" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E273" s="6" t="s">
         <v>769</v>
       </c>
-      <c r="F272" s="1">
+      <c r="F273" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" s="1" t="s">
+    <row r="274" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A274" s="6" t="s">
         <v>716</v>
       </c>
-      <c r="B273" s="1" t="s">
+      <c r="B274" s="6" t="s">
         <v>716</v>
       </c>
-      <c r="C273" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E273" s="1" t="s">
+      <c r="C274" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E274" s="6" t="s">
         <v>770</v>
       </c>
-      <c r="F273" s="1">
+      <c r="F274" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" s="1" t="s">
+    <row r="275" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A275" s="6" t="s">
         <v>771</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="B275" s="6" t="s">
         <v>771</v>
       </c>
-      <c r="C274" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E274" s="1" t="s">
+      <c r="C275" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E275" s="6" t="s">
         <v>772</v>
       </c>
-      <c r="F274" s="1">
+      <c r="F275" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" s="1" t="s">
+    <row r="276" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A276" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="B276" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="C275" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E275" s="1" t="s">
+      <c r="C276" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E276" s="6" t="s">
         <v>774</v>
       </c>
-      <c r="F275" s="1">
+      <c r="F276" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" s="1" t="s">
+    <row r="277" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A277" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="B276" s="1" t="s">
+      <c r="B277" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="C276" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E276" s="1" t="s">
+      <c r="C277" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E277" s="6" t="s">
         <v>775</v>
       </c>
-      <c r="F276" s="1">
+      <c r="F277" s="6">
         <v>999</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277" s="1" t="s">
+    <row r="278" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A278" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B277" s="1" t="s">
+      <c r="B278" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="C277" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E277" s="1" t="s">
+      <c r="C278" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E278" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="F277" s="1">
+      <c r="F278" s="4">
         <v>999</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A278" s="1" t="s">
+    <row r="279" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A279" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="B278" s="1" t="s">
+      <c r="B279" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="C278" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E278" s="1" t="s">
+      <c r="C279" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E279" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="F278" s="1">
+      <c r="F279" s="4">
         <v>999</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279" s="1" t="s">
+    <row r="280" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A280" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="B279" s="1" t="s">
+      <c r="B280" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="C279" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E279" s="1" t="s">
+      <c r="C280" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E280" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="F279" s="1">
+      <c r="F280" s="4">
         <v>999</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A280" s="1" t="s">
+    <row r="281" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A281" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="B281" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="C280" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E280" s="1" t="s">
+      <c r="C281" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E281" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="F280" s="1">
+      <c r="F281" s="4">
         <v>999</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A281" s="1" t="s">
+    <row r="282" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A282" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="B281" s="1" t="s">
+      <c r="B282" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="C281" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E281" s="1" t="s">
+      <c r="C282" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E282" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="F281" s="1">
+      <c r="F282" s="4">
         <v>999</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A282" s="1" t="s">
+    <row r="283" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A283" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="B283" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="C282" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E282" s="1" t="s">
+      <c r="C283" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E283" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="F282" s="1">
+      <c r="F283" s="4">
         <v>999</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A283" s="1" t="s">
+    <row r="284" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A284" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="B284" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="C283" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E283" s="1" t="s">
+      <c r="C284" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E284" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="F283" s="1">
+      <c r="F284" s="4">
         <v>999</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A284" s="1" t="s">
+    <row r="285" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A285" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="B284" s="1" t="s">
+      <c r="B285" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="C284" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E284" s="1" t="s">
+      <c r="C285" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E285" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="F284" s="1">
+      <c r="F285" s="4">
         <v>999</v>
       </c>
     </row>
@@ -7800,25 +7860,25 @@
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B236">
+  <conditionalFormatting sqref="B237">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B237">
+  <conditionalFormatting sqref="B238">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B238">
+  <conditionalFormatting sqref="B239">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B239:B240 B242 B244:B246 B248:B284">
+  <conditionalFormatting sqref="B240:B241 B243 B245:B247 B249:B285">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B241">
+  <conditionalFormatting sqref="B242">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B243">
+  <conditionalFormatting sqref="B244">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B247">
+  <conditionalFormatting sqref="B248">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1801A4-B694-4629-B0FB-BFE93D24CE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0A0962-5BAA-439C-9012-6ADDD4AB1F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="2540" yWindow="2890" windowWidth="28800" windowHeight="15370" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0A0962-5BAA-439C-9012-6ADDD4AB1F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34B7722-3D2D-46DF-A323-09290B207679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2540" yWindow="2890" windowWidth="28800" windowHeight="15370" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="3900" yWindow="450" windowWidth="32160" windowHeight="20430" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="798">
   <si>
     <t>id</t>
   </si>
@@ -2449,6 +2449,18 @@
   </si>
   <si>
     <t>可制作五行符</t>
+  </si>
+  <si>
+    <t>save</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>boolean</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2459,7 +2471,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2471,7 +2483,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2574,7 +2586,7 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -2677,7 +2689,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2993,21 +3005,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:H285"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I285"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3032,8 +3044,11 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="1" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -3058,13 +3073,16 @@
       <c r="H2" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" s="1" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>321</v>
       </c>
@@ -3089,8 +3107,11 @@
       <c r="H4" s="8" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" s="8" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -3107,7 +3128,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>395</v>
       </c>
@@ -3124,7 +3145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>396</v>
       </c>
@@ -3141,7 +3162,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>397</v>
       </c>
@@ -3158,7 +3179,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3175,7 +3196,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3192,7 +3213,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3215,7 +3236,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3238,7 +3259,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3255,7 +3276,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3272,7 +3293,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3295,7 +3316,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -3318,7 +3339,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3335,7 +3356,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -3352,7 +3373,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,7 +3390,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -3386,7 +3407,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>410</v>
       </c>
@@ -3403,7 +3424,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>664</v>
       </c>
@@ -3420,7 +3441,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>665</v>
       </c>
@@ -3437,7 +3458,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>280</v>
       </c>
@@ -3454,7 +3475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>281</v>
       </c>
@@ -3471,7 +3492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>282</v>
       </c>
@@ -3488,7 +3509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>283</v>
       </c>
@@ -3505,7 +3526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>284</v>
       </c>
@@ -3522,7 +3543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>446</v>
       </c>
@@ -3539,7 +3560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>447</v>
       </c>
@@ -3556,7 +3577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>448</v>
       </c>
@@ -3573,7 +3594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>449</v>
       </c>
@@ -3590,7 +3611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>450</v>
       </c>
@@ -3607,7 +3628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>451</v>
       </c>
@@ -3624,7 +3645,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>452</v>
       </c>
@@ -3641,7 +3662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>453</v>
       </c>
@@ -3658,7 +3679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>454</v>
       </c>
@@ -3675,7 +3696,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>455</v>
       </c>
@@ -3692,7 +3713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -3709,7 +3730,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -3726,7 +3747,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,7 +3764,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -3760,7 +3781,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -3777,7 +3798,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -3794,7 +3815,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -3811,7 +3832,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -3828,7 +3849,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -3845,7 +3866,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -3862,7 +3883,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
@@ -3879,7 +3900,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
@@ -3896,7 +3917,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -3913,7 +3934,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
@@ -3930,7 +3951,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
@@ -3947,7 +3968,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>412</v>
       </c>
@@ -3964,7 +3985,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>413</v>
       </c>
@@ -3981,7 +4002,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>414</v>
       </c>
@@ -3998,7 +4019,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -4015,7 +4036,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -4032,7 +4053,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -4049,7 +4070,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -4066,7 +4087,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -4083,7 +4104,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -4103,7 +4124,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
@@ -4123,7 +4144,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
@@ -4143,7 +4164,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>399</v>
       </c>
@@ -4163,7 +4184,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>400</v>
       </c>
@@ -4183,7 +4204,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>406</v>
       </c>
@@ -4203,7 +4224,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>404</v>
       </c>
@@ -4220,7 +4241,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -4237,7 +4258,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
@@ -4254,7 +4275,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -4271,7 +4292,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -4288,7 +4309,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -4305,7 +4326,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
@@ -4328,7 +4349,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -4351,7 +4372,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -4374,7 +4395,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -4397,7 +4418,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
@@ -4420,7 +4441,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>393</v>
       </c>
@@ -4437,7 +4458,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -4454,7 +4475,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -4471,7 +4492,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -4488,7 +4509,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -4505,7 +4526,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>310</v>
       </c>
@@ -4522,7 +4543,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>311</v>
       </c>
@@ -4539,7 +4560,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>312</v>
       </c>
@@ -4556,7 +4577,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>313</v>
       </c>
@@ -4573,7 +4594,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>314</v>
       </c>
@@ -4590,7 +4611,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -4607,7 +4628,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -4624,7 +4645,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -4641,7 +4662,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -4658,7 +4679,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -4675,7 +4696,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>420</v>
       </c>
@@ -4692,7 +4713,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>661</v>
       </c>
@@ -4709,7 +4730,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -4723,7 +4744,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>473</v>
       </c>
@@ -4740,7 +4761,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>676</v>
       </c>
@@ -4757,7 +4778,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>408</v>
       </c>
@@ -4774,7 +4795,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>381</v>
       </c>
@@ -4788,7 +4809,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>383</v>
       </c>
@@ -4802,7 +4823,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>792</v>
       </c>
@@ -4819,7 +4840,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>46</v>
       </c>
@@ -4836,7 +4857,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>47</v>
       </c>
@@ -4853,7 +4874,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>48</v>
       </c>
@@ -4870,7 +4891,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>278</v>
       </c>
@@ -4887,7 +4908,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>294</v>
       </c>
@@ -4904,7 +4925,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>295</v>
       </c>
@@ -4921,7 +4942,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>296</v>
       </c>
@@ -4938,7 +4959,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>297</v>
       </c>
@@ -4955,7 +4976,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>72</v>
       </c>
@@ -4972,7 +4993,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>679</v>
       </c>
@@ -4989,7 +5010,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>670</v>
       </c>
@@ -5006,7 +5027,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>673</v>
       </c>
@@ -5023,7 +5044,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>389</v>
       </c>
@@ -5040,7 +5061,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>390</v>
       </c>
@@ -5057,7 +5078,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>444</v>
       </c>
@@ -5074,7 +5095,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>59</v>
       </c>
@@ -5091,7 +5112,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>60</v>
       </c>
@@ -5108,7 +5129,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>61</v>
       </c>
@@ -5125,7 +5146,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>421</v>
       </c>
@@ -5142,7 +5163,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>422</v>
       </c>
@@ -5159,7 +5180,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>655</v>
       </c>
@@ -5176,7 +5197,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>62</v>
       </c>
@@ -5193,7 +5214,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>63</v>
       </c>
@@ -5210,7 +5231,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>64</v>
       </c>
@@ -5227,7 +5248,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>423</v>
       </c>
@@ -5244,7 +5265,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>424</v>
       </c>
@@ -5261,7 +5282,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>656</v>
       </c>
@@ -5278,7 +5299,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>65</v>
       </c>
@@ -5295,7 +5316,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>66</v>
       </c>
@@ -5312,7 +5333,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>67</v>
       </c>
@@ -5329,7 +5350,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>425</v>
       </c>
@@ -5346,7 +5367,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>426</v>
       </c>
@@ -5363,7 +5384,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>658</v>
       </c>
@@ -5380,7 +5401,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>68</v>
       </c>
@@ -5397,7 +5418,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>69</v>
       </c>
@@ -5414,7 +5435,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>70</v>
       </c>
@@ -5431,7 +5452,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>71</v>
       </c>
@@ -5445,7 +5466,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>79</v>
       </c>
@@ -5462,7 +5483,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>80</v>
       </c>
@@ -5479,7 +5500,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>81</v>
       </c>
@@ -5496,7 +5517,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>82</v>
       </c>
@@ -5513,7 +5534,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>83</v>
       </c>
@@ -5530,7 +5551,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,7 +5568,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>85</v>
       </c>
@@ -5564,7 +5585,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>86</v>
       </c>
@@ -5581,7 +5602,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>87</v>
       </c>
@@ -5598,7 +5619,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>88</v>
       </c>
@@ -5615,7 +5636,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>89</v>
       </c>
@@ -5632,7 +5653,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>90</v>
       </c>
@@ -5649,7 +5670,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>91</v>
       </c>
@@ -5666,7 +5687,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>92</v>
       </c>
@@ -5683,7 +5704,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>93</v>
       </c>
@@ -5700,7 +5721,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>94</v>
       </c>
@@ -5717,7 +5738,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>95</v>
       </c>
@@ -5734,7 +5755,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>96</v>
       </c>
@@ -5751,7 +5772,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>97</v>
       </c>
@@ -5768,7 +5789,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>98</v>
       </c>
@@ -5785,7 +5806,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>99</v>
       </c>
@@ -5802,7 +5823,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>100</v>
       </c>
@@ -5819,7 +5840,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>101</v>
       </c>
@@ -5836,7 +5857,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>102</v>
       </c>
@@ -5853,7 +5874,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>103</v>
       </c>
@@ -5870,7 +5891,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>104</v>
       </c>
@@ -5887,7 +5908,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>105</v>
       </c>
@@ -5904,7 +5925,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>106</v>
       </c>
@@ -5921,7 +5942,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>107</v>
       </c>
@@ -5938,7 +5959,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>108</v>
       </c>
@@ -5955,7 +5976,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>109</v>
       </c>
@@ -5972,7 +5993,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>110</v>
       </c>
@@ -5989,7 +6010,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>111</v>
       </c>
@@ -6006,7 +6027,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>112</v>
       </c>
@@ -6023,7 +6044,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>113</v>
       </c>
@@ -6040,7 +6061,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>114</v>
       </c>
@@ -6057,7 +6078,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>115</v>
       </c>
@@ -6074,7 +6095,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>116</v>
       </c>
@@ -6091,7 +6112,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>117</v>
       </c>
@@ -6108,7 +6129,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>118</v>
       </c>
@@ -6125,7 +6146,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>119</v>
       </c>
@@ -6142,7 +6163,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>120</v>
       </c>
@@ -6159,7 +6180,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>121</v>
       </c>
@@ -6176,7 +6197,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>122</v>
       </c>
@@ -6193,7 +6214,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>123</v>
       </c>
@@ -6210,7 +6231,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>124</v>
       </c>
@@ -6227,7 +6248,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>125</v>
       </c>
@@ -6244,7 +6265,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>126</v>
       </c>
@@ -6261,7 +6282,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>127</v>
       </c>
@@ -6278,7 +6299,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>128</v>
       </c>
@@ -6295,7 +6316,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>129</v>
       </c>
@@ -6312,7 +6333,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>130</v>
       </c>
@@ -6329,7 +6350,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>131</v>
       </c>
@@ -6346,7 +6367,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>132</v>
       </c>
@@ -6363,7 +6384,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>133</v>
       </c>
@@ -6380,7 +6401,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>134</v>
       </c>
@@ -6397,7 +6418,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>135</v>
       </c>
@@ -6414,7 +6435,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>136</v>
       </c>
@@ -6431,7 +6452,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>137</v>
       </c>
@@ -6448,7 +6469,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>138</v>
       </c>
@@ -6465,7 +6486,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>139</v>
       </c>
@@ -6482,7 +6503,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>140</v>
       </c>
@@ -6499,7 +6520,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>141</v>
       </c>
@@ -6516,7 +6537,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>142</v>
       </c>
@@ -6533,7 +6554,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>143</v>
       </c>
@@ -6550,7 +6571,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>144</v>
       </c>
@@ -6567,7 +6588,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>145</v>
       </c>
@@ -6584,7 +6605,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>146</v>
       </c>
@@ -6601,7 +6622,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>147</v>
       </c>
@@ -6618,7 +6639,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>148</v>
       </c>
@@ -6635,7 +6656,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>149</v>
       </c>
@@ -6652,7 +6673,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>150</v>
       </c>
@@ -6669,7 +6690,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>385</v>
       </c>
@@ -6683,7 +6704,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>387</v>
       </c>
@@ -6697,7 +6718,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>428</v>
       </c>
@@ -6710,8 +6731,11 @@
       <c r="F214" s="1">
         <v>803</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="I214" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>682</v>
       </c>
@@ -6725,7 +6749,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>320</v>
       </c>
@@ -6739,7 +6763,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>347</v>
       </c>
@@ -6753,7 +6777,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>349</v>
       </c>
@@ -6767,7 +6791,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>684</v>
       </c>
@@ -6781,7 +6805,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>351</v>
       </c>
@@ -6795,7 +6819,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>352</v>
       </c>
@@ -6809,7 +6833,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>353</v>
       </c>
@@ -6823,7 +6847,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>686</v>
       </c>
@@ -6837,7 +6861,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>357</v>
       </c>
@@ -6851,7 +6875,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>358</v>
       </c>
@@ -6865,7 +6889,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>359</v>
       </c>
@@ -6879,7 +6903,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>363</v>
       </c>
@@ -6893,7 +6917,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>365</v>
       </c>
@@ -6907,7 +6931,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>366</v>
       </c>
@@ -6921,7 +6945,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>369</v>
       </c>
@@ -6935,7 +6959,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>370</v>
       </c>
@@ -6949,7 +6973,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>371</v>
       </c>
@@ -6963,7 +6987,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>372</v>
       </c>
@@ -6977,7 +7001,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>377</v>
       </c>
@@ -6991,7 +7015,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>379</v>
       </c>
@@ -7005,7 +7029,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>466</v>
       </c>
@@ -7022,7 +7046,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="237" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
         <v>688</v>
       </c>
@@ -7039,7 +7063,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="238" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
         <v>689</v>
       </c>
@@ -7056,7 +7080,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="239" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>690</v>
       </c>
@@ -7073,7 +7097,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="240" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
         <v>691</v>
       </c>
@@ -7090,7 +7114,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="241" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
         <v>692</v>
       </c>
@@ -7107,7 +7131,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="242" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
         <v>729</v>
       </c>
@@ -7124,7 +7148,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="243" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
         <v>693</v>
       </c>
@@ -7141,7 +7165,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="244" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
         <v>732</v>
       </c>
@@ -7158,7 +7182,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="245" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
         <v>694</v>
       </c>
@@ -7175,7 +7199,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="246" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
         <v>695</v>
       </c>
@@ -7192,7 +7216,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="247" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
         <v>696</v>
       </c>
@@ -7209,7 +7233,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="248" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
         <v>737</v>
       </c>
@@ -7226,7 +7250,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="249" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
         <v>697</v>
       </c>
@@ -7243,7 +7267,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="250" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
         <v>698</v>
       </c>
@@ -7260,7 +7284,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="251" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
         <v>741</v>
       </c>
@@ -7277,7 +7301,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="252" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
         <v>699</v>
       </c>
@@ -7294,7 +7318,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="253" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
         <v>744</v>
       </c>
@@ -7311,7 +7335,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="254" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
         <v>700</v>
       </c>
@@ -7328,7 +7352,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="255" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>701</v>
       </c>
@@ -7345,7 +7369,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="256" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
         <v>702</v>
       </c>
@@ -7362,7 +7386,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="257" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>703</v>
       </c>
@@ -7379,7 +7403,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="258" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
         <v>704</v>
       </c>
@@ -7396,7 +7420,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="259" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="11" t="s">
         <v>751</v>
       </c>
@@ -7413,7 +7437,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="260" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>705</v>
       </c>
@@ -7430,7 +7454,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="261" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
         <v>754</v>
       </c>
@@ -7447,7 +7471,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="262" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
         <v>706</v>
       </c>
@@ -7464,7 +7488,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="263" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
         <v>707</v>
       </c>
@@ -7481,7 +7505,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="264" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
         <v>708</v>
       </c>
@@ -7498,7 +7522,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="265" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
         <v>709</v>
       </c>
@@ -7515,7 +7539,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="266" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
         <v>710</v>
       </c>
@@ -7532,7 +7556,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="267" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
         <v>711</v>
       </c>
@@ -7549,7 +7573,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="268" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
         <v>762</v>
       </c>
@@ -7566,7 +7590,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="269" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
         <v>712</v>
       </c>
@@ -7583,7 +7607,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="270" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
         <v>764</v>
       </c>
@@ -7600,7 +7624,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="271" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
         <v>713</v>
       </c>
@@ -7617,7 +7641,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="272" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
         <v>714</v>
       </c>
@@ -7634,7 +7658,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="273" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
         <v>715</v>
       </c>
@@ -7651,7 +7675,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="274" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
         <v>716</v>
       </c>
@@ -7668,7 +7692,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="275" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
         <v>771</v>
       </c>
@@ -7685,7 +7709,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="276" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
         <v>717</v>
       </c>
@@ -7702,7 +7726,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="277" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
         <v>773</v>
       </c>
@@ -7719,7 +7743,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="278" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>718</v>
       </c>
@@ -7736,7 +7760,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="279" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
         <v>719</v>
       </c>
@@ -7753,7 +7777,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="280" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>720</v>
       </c>
@@ -7770,7 +7794,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="281" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>721</v>
       </c>
@@ -7787,7 +7811,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="282" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>722</v>
       </c>
@@ -7804,7 +7828,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="283" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
         <v>781</v>
       </c>
@@ -7821,7 +7845,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="284" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
         <v>723</v>
       </c>
@@ -7838,7 +7862,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="285" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>784</v>
       </c>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34B7722-3D2D-46DF-A323-09290B207679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469CEDBB-63A8-490C-B9D4-A1C51C7456B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="450" windowWidth="32160" windowHeight="20430" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="808">
   <si>
     <t>id</t>
   </si>
@@ -2460,6 +2460,46 @@
   </si>
   <si>
     <t>保存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>targetSkill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务于技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillTag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能新增分类</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>holy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>psyco</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>poison</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillTag[]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3005,7 +3045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:I285"/>
+  <dimension ref="A1:K285"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.125" style="1" customWidth="1"/>
@@ -3019,7 +3059,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3047,8 +3087,14 @@
       <c r="I1" s="1" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -3076,13 +3122,19 @@
       <c r="I2" s="1" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>321</v>
       </c>
@@ -3110,8 +3162,14 @@
       <c r="I4" s="8" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -3128,7 +3186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>395</v>
       </c>
@@ -3145,7 +3203,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>396</v>
       </c>
@@ -3162,7 +3220,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>397</v>
       </c>
@@ -3179,7 +3237,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3196,7 +3254,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3213,7 +3271,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3236,7 +3294,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3259,7 +3317,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3276,7 +3334,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3293,7 +3351,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3316,7 +3374,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -4475,7 +4533,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -4492,7 +4550,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -4509,7 +4567,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -4526,7 +4584,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>310</v>
       </c>
@@ -4543,7 +4601,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>311</v>
       </c>
@@ -4560,7 +4618,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>312</v>
       </c>
@@ -4577,7 +4635,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>313</v>
       </c>
@@ -4594,7 +4652,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>314</v>
       </c>
@@ -4611,7 +4669,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -4628,7 +4686,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -4645,7 +4703,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -4662,7 +4720,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -4679,7 +4737,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -4696,7 +4754,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>420</v>
       </c>
@@ -4713,7 +4771,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>661</v>
       </c>
@@ -4730,7 +4788,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -4742,6 +4800,9 @@
       </c>
       <c r="F96" s="1">
         <v>288</v>
+      </c>
+      <c r="I96" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -6875,7 +6936,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>358</v>
       </c>
@@ -6889,7 +6950,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>359</v>
       </c>
@@ -6903,7 +6964,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>363</v>
       </c>
@@ -6917,7 +6978,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>365</v>
       </c>
@@ -6931,7 +6992,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>366</v>
       </c>
@@ -6945,7 +7006,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>369</v>
       </c>
@@ -6959,7 +7020,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>370</v>
       </c>
@@ -6973,7 +7034,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>371</v>
       </c>
@@ -6987,7 +7048,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>372</v>
       </c>
@@ -7001,7 +7062,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>377</v>
       </c>
@@ -7015,7 +7076,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>379</v>
       </c>
@@ -7029,7 +7090,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>466</v>
       </c>
@@ -7046,7 +7107,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="237" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
         <v>688</v>
       </c>
@@ -7062,8 +7123,12 @@
       <c r="F237" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="238" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J237" s="9" t="str">
+        <f>MID(A237,3,4)</f>
+        <v>fblt</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
         <v>689</v>
       </c>
@@ -7079,8 +7144,12 @@
       <c r="F238" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="239" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J238" s="9" t="str">
+        <f t="shared" ref="J238:J285" si="0">MID(A238,3,4)</f>
+        <v>frng</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>690</v>
       </c>
@@ -7096,8 +7165,12 @@
       <c r="F239" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="240" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J239" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>finf</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
         <v>691</v>
       </c>
@@ -7113,8 +7186,12 @@
       <c r="F240" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="241" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J240" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>fbal</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
         <v>692</v>
       </c>
@@ -7130,8 +7207,12 @@
       <c r="F241" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="242" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J241" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>fbls</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
         <v>729</v>
       </c>
@@ -7147,8 +7228,12 @@
       <c r="F242" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="243" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J242" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>fbls</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
         <v>693</v>
       </c>
@@ -7164,8 +7249,12 @@
       <c r="F243" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="244" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J243" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>fwal</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
         <v>732</v>
       </c>
@@ -7181,8 +7270,12 @@
       <c r="F244" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="245" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J244" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>fwal</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
         <v>694</v>
       </c>
@@ -7198,8 +7291,12 @@
       <c r="F245" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="246" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J245" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tchm</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
         <v>695</v>
       </c>
@@ -7215,8 +7312,12 @@
       <c r="F246" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="247" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J246" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tblt</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
         <v>696</v>
       </c>
@@ -7232,8 +7333,12 @@
       <c r="F247" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="248" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J247" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tltn</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
         <v>737</v>
       </c>
@@ -7249,8 +7354,12 @@
       <c r="F248" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="249" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J248" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tltn</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
         <v>697</v>
       </c>
@@ -7266,8 +7375,12 @@
       <c r="F249" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="250" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J249" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tnov</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
         <v>698</v>
       </c>
@@ -7283,8 +7396,12 @@
       <c r="F250" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="251" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J250" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tshd</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
         <v>741</v>
       </c>
@@ -7300,8 +7417,12 @@
       <c r="F251" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="252" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J251" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tshd</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
         <v>699</v>
       </c>
@@ -7317,8 +7438,12 @@
       <c r="F252" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="253" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J252" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tblz</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
         <v>744</v>
       </c>
@@ -7334,8 +7459,12 @@
       <c r="F253" s="10">
         <v>999</v>
       </c>
-    </row>
-    <row r="254" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J253" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tblz</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
         <v>700</v>
       </c>
@@ -7351,8 +7480,12 @@
       <c r="F254" s="11">
         <v>999</v>
       </c>
-    </row>
-    <row r="255" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J254" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bbas</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>701</v>
       </c>
@@ -7368,8 +7501,12 @@
       <c r="F255" s="11">
         <v>999</v>
       </c>
-    </row>
-    <row r="256" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J255" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bcrt</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
         <v>702</v>
       </c>
@@ -7385,8 +7522,12 @@
       <c r="F256" s="11">
         <v>999</v>
       </c>
-    </row>
-    <row r="257" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J256" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bthr</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>703</v>
       </c>
@@ -7402,8 +7543,12 @@
       <c r="F257" s="11">
         <v>999</v>
       </c>
-    </row>
-    <row r="258" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J257" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bclv</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
         <v>704</v>
       </c>
@@ -7419,8 +7564,12 @@
       <c r="F258" s="11">
         <v>999</v>
       </c>
-    </row>
-    <row r="259" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J258" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bcrz</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="11" t="s">
         <v>751</v>
       </c>
@@ -7436,8 +7585,12 @@
       <c r="F259" s="11">
         <v>999</v>
       </c>
-    </row>
-    <row r="260" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J259" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bcrz</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>705</v>
       </c>
@@ -7453,8 +7606,15 @@
       <c r="F260" s="11">
         <v>999</v>
       </c>
-    </row>
-    <row r="261" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J260" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bfbl</v>
+      </c>
+      <c r="K260" s="11" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
         <v>754</v>
       </c>
@@ -7470,8 +7630,15 @@
       <c r="F261" s="11">
         <v>999</v>
       </c>
-    </row>
-    <row r="262" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J261" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bfbl</v>
+      </c>
+      <c r="K261" s="11" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
         <v>706</v>
       </c>
@@ -7487,8 +7654,12 @@
       <c r="F262" s="12">
         <v>999</v>
       </c>
-    </row>
-    <row r="263" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J262" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xdef</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
         <v>707</v>
       </c>
@@ -7504,8 +7675,12 @@
       <c r="F263" s="12">
         <v>999</v>
       </c>
-    </row>
-    <row r="264" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J263" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xdog</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
         <v>708</v>
       </c>
@@ -7521,8 +7696,12 @@
       <c r="F264" s="12">
         <v>999</v>
       </c>
-    </row>
-    <row r="265" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J264" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xcta</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
         <v>709</v>
       </c>
@@ -7538,8 +7717,12 @@
       <c r="F265" s="12">
         <v>999</v>
       </c>
-    </row>
-    <row r="266" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J265" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xwms</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
         <v>710</v>
       </c>
@@ -7555,8 +7738,12 @@
       <c r="F266" s="12">
         <v>999</v>
       </c>
-    </row>
-    <row r="267" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J266" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xchg</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
         <v>711</v>
       </c>
@@ -7572,8 +7759,12 @@
       <c r="F267" s="12">
         <v>999</v>
       </c>
-    </row>
-    <row r="268" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J267" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xtst</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
         <v>762</v>
       </c>
@@ -7589,8 +7780,12 @@
       <c r="F268" s="12">
         <v>999</v>
       </c>
-    </row>
-    <row r="269" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J268" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xtst</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
         <v>712</v>
       </c>
@@ -7606,8 +7801,12 @@
       <c r="F269" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="270" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J269" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hhel</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
         <v>764</v>
       </c>
@@ -7623,8 +7822,12 @@
       <c r="F270" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="271" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J270" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hhel</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
         <v>713</v>
       </c>
@@ -7640,8 +7843,12 @@
       <c r="F271" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="272" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J271" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hgsd</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
         <v>714</v>
       </c>
@@ -7657,8 +7864,12 @@
       <c r="F272" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="273" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J272" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hinv</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
         <v>715</v>
       </c>
@@ -7674,8 +7885,12 @@
       <c r="F273" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="274" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J273" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hhsd</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
         <v>716</v>
       </c>
@@ -7691,8 +7906,12 @@
       <c r="F274" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="275" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J274" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hlok</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
         <v>771</v>
       </c>
@@ -7708,8 +7927,12 @@
       <c r="F275" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="276" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J275" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hlok</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
         <v>717</v>
       </c>
@@ -7725,8 +7948,12 @@
       <c r="F276" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="277" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J276" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hmhl</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
         <v>773</v>
       </c>
@@ -7742,8 +7969,12 @@
       <c r="F277" s="6">
         <v>999</v>
       </c>
-    </row>
-    <row r="278" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J277" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hmhl</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>718</v>
       </c>
@@ -7759,8 +7990,12 @@
       <c r="F278" s="4">
         <v>999</v>
       </c>
-    </row>
-    <row r="279" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J278" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pbas</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
         <v>719</v>
       </c>
@@ -7776,8 +8011,12 @@
       <c r="F279" s="4">
         <v>999</v>
       </c>
-    </row>
-    <row r="280" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J279" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>ppoi</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>720</v>
       </c>
@@ -7793,8 +8032,15 @@
       <c r="F280" s="4">
         <v>999</v>
       </c>
-    </row>
-    <row r="281" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J280" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pskl</v>
+      </c>
+      <c r="K280" s="4" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>721</v>
       </c>
@@ -7810,8 +8056,12 @@
       <c r="F281" s="4">
         <v>999</v>
       </c>
-    </row>
-    <row r="282" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J281" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>prun</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>722</v>
       </c>
@@ -7827,8 +8077,12 @@
       <c r="F282" s="4">
         <v>999</v>
       </c>
-    </row>
-    <row r="283" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J282" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pcbl</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
         <v>781</v>
       </c>
@@ -7844,8 +8098,12 @@
       <c r="F283" s="4">
         <v>999</v>
       </c>
-    </row>
-    <row r="284" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J283" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pcbl</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
         <v>723</v>
       </c>
@@ -7861,8 +8119,15 @@
       <c r="F284" s="4">
         <v>999</v>
       </c>
-    </row>
-    <row r="285" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J284" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>psdm</v>
+      </c>
+      <c r="K284" s="4" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>784</v>
       </c>
@@ -7877,6 +8142,10 @@
       </c>
       <c r="F285" s="4">
         <v>999</v>
+      </c>
+      <c r="J285" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>psdm</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469CEDBB-63A8-490C-B9D4-A1C51C7456B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E3B4DD-BAAB-4968-AC0C-600D4540FEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="450" windowWidth="32160" windowHeight="20430" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="864">
   <si>
     <t>id</t>
   </si>
@@ -2501,6 +2501,174 @@
   <si>
     <t>SkillTag[]</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fblt</t>
+  </si>
+  <si>
+    <t>frng</t>
+  </si>
+  <si>
+    <t>finf</t>
+  </si>
+  <si>
+    <t>fbal</t>
+  </si>
+  <si>
+    <t>fbls</t>
+  </si>
+  <si>
+    <t>fwal</t>
+  </si>
+  <si>
+    <t>tblt</t>
+  </si>
+  <si>
+    <t>tltn</t>
+  </si>
+  <si>
+    <t>tnov</t>
+  </si>
+  <si>
+    <t>tshd</t>
+  </si>
+  <si>
+    <t>tblz</t>
+  </si>
+  <si>
+    <t>bbas</t>
+  </si>
+  <si>
+    <t>bcrt</t>
+  </si>
+  <si>
+    <t>bthr</t>
+  </si>
+  <si>
+    <t>bclv</t>
+  </si>
+  <si>
+    <t>bcrz</t>
+  </si>
+  <si>
+    <t>bfbl</t>
+  </si>
+  <si>
+    <t>xdef</t>
+  </si>
+  <si>
+    <t>xdog</t>
+  </si>
+  <si>
+    <t>xcta</t>
+  </si>
+  <si>
+    <t>xwms</t>
+  </si>
+  <si>
+    <t>xchg</t>
+  </si>
+  <si>
+    <t>xtst</t>
+  </si>
+  <si>
+    <t>hhel</t>
+  </si>
+  <si>
+    <t>hgsd</t>
+  </si>
+  <si>
+    <t>hinv</t>
+  </si>
+  <si>
+    <t>hhsd</t>
+  </si>
+  <si>
+    <t>hlok</t>
+  </si>
+  <si>
+    <t>hmhl</t>
+  </si>
+  <si>
+    <t>pbas</t>
+  </si>
+  <si>
+    <t>ppoi</t>
+  </si>
+  <si>
+    <t>prun</t>
+  </si>
+  <si>
+    <t>pcbl</t>
+  </si>
+  <si>
+    <t>psdm</t>
+  </si>
+  <si>
+    <t>tchm</t>
+  </si>
+  <si>
+    <t>targetTag</t>
+  </si>
+  <si>
+    <t>SkillTag</t>
+  </si>
+  <si>
+    <t>服务于分类</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>thunder</t>
+  </si>
+  <si>
+    <t>targetUnit</t>
+  </si>
+  <si>
+    <t>服务于单位</t>
+  </si>
+  <si>
+    <t>mage</t>
+  </si>
+  <si>
+    <t>battle</t>
+  </si>
+  <si>
+    <t>xskill</t>
+  </si>
+  <si>
+    <t>warr</t>
+  </si>
+  <si>
+    <t>holy</t>
+  </si>
+  <si>
+    <t>psyco</t>
+  </si>
+  <si>
+    <t>wlk</t>
+  </si>
+  <si>
+    <t>UnitId[]</t>
+  </si>
+  <si>
+    <t>mage,warr,wlk</t>
+  </si>
+  <si>
+    <t>summon</t>
+  </si>
+  <si>
+    <t>guardian</t>
+  </si>
+  <si>
+    <t>pskl</t>
+  </si>
+  <si>
+    <t>unitConstraint</t>
+  </si>
+  <si>
+    <t>限制单位</t>
   </si>
 </sst>
 </file>
@@ -2511,7 +2679,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2523,7 +2691,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2626,9 +2794,179 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2729,7 +3067,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3045,21 +3383,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:K285"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N285"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3093,8 +3431,17 @@
       <c r="K1" s="1" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -3128,13 +3475,22 @@
       <c r="K2" s="1" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>321</v>
       </c>
@@ -3168,8 +3524,17 @@
       <c r="K4" s="8" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>394</v>
       </c>
@@ -3186,7 +3551,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>395</v>
       </c>
@@ -3203,7 +3568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>396</v>
       </c>
@@ -3220,7 +3585,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>397</v>
       </c>
@@ -3237,7 +3602,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3254,7 +3619,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3271,7 +3636,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3294,7 +3659,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3317,7 +3682,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3334,7 +3699,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3351,7 +3716,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3374,7 +3739,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -3397,7 +3762,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3414,7 +3779,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -3431,7 +3796,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -3448,7 +3813,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -3465,7 +3830,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>410</v>
       </c>
@@ -3482,7 +3847,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>664</v>
       </c>
@@ -3499,7 +3864,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>665</v>
       </c>
@@ -3516,7 +3881,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>280</v>
       </c>
@@ -3533,7 +3898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>281</v>
       </c>
@@ -3550,7 +3915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>282</v>
       </c>
@@ -3567,7 +3932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>283</v>
       </c>
@@ -3584,7 +3949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>284</v>
       </c>
@@ -3601,7 +3966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>446</v>
       </c>
@@ -3618,7 +3983,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>447</v>
       </c>
@@ -3635,7 +4000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>448</v>
       </c>
@@ -3652,7 +4017,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>449</v>
       </c>
@@ -3669,7 +4034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>450</v>
       </c>
@@ -3686,7 +4051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>451</v>
       </c>
@@ -3703,7 +4068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>452</v>
       </c>
@@ -3720,7 +4085,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>453</v>
       </c>
@@ -3737,7 +4102,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>454</v>
       </c>
@@ -3754,7 +4119,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>455</v>
       </c>
@@ -3771,7 +4136,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -3788,7 +4153,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -3805,7 +4170,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -3822,7 +4187,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -3839,7 +4204,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -3856,7 +4221,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -3873,7 +4238,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -3890,7 +4255,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -3907,7 +4272,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -3924,7 +4289,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -3941,7 +4306,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
@@ -3958,7 +4323,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
@@ -3975,7 +4340,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -3992,7 +4357,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
@@ -4009,7 +4374,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
@@ -4026,7 +4391,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>412</v>
       </c>
@@ -4043,7 +4408,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>413</v>
       </c>
@@ -4060,7 +4425,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>414</v>
       </c>
@@ -4077,7 +4442,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -4094,7 +4459,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -4111,7 +4476,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -4128,7 +4493,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -4145,7 +4510,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -4162,7 +4527,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -4182,7 +4547,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
@@ -4202,7 +4567,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
@@ -4222,7 +4587,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>399</v>
       </c>
@@ -4242,7 +4607,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>400</v>
       </c>
@@ -4262,7 +4627,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>406</v>
       </c>
@@ -4282,7 +4647,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>404</v>
       </c>
@@ -4299,7 +4664,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -4316,7 +4681,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
@@ -4333,7 +4698,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -4350,7 +4715,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -4367,7 +4732,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -4384,7 +4749,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
@@ -4407,7 +4772,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -4430,7 +4795,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -4453,7 +4818,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -4476,7 +4841,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
@@ -4499,7 +4864,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>393</v>
       </c>
@@ -4516,7 +4881,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -4533,7 +4898,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -4550,7 +4915,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -4567,7 +4932,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -4584,7 +4949,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>310</v>
       </c>
@@ -4601,7 +4966,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>311</v>
       </c>
@@ -4618,7 +4983,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>312</v>
       </c>
@@ -4635,7 +5000,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>313</v>
       </c>
@@ -4652,7 +5017,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>314</v>
       </c>
@@ -4669,7 +5034,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -4686,7 +5051,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -4703,7 +5068,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -4720,7 +5085,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -4737,7 +5102,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -4754,7 +5119,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>420</v>
       </c>
@@ -4771,7 +5136,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>661</v>
       </c>
@@ -4788,7 +5153,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -4805,7 +5170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>473</v>
       </c>
@@ -4822,7 +5187,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>676</v>
       </c>
@@ -4839,7 +5204,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>408</v>
       </c>
@@ -4856,7 +5221,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>381</v>
       </c>
@@ -4870,7 +5235,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>383</v>
       </c>
@@ -4884,7 +5249,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>792</v>
       </c>
@@ -4901,7 +5266,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>46</v>
       </c>
@@ -4918,7 +5283,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>47</v>
       </c>
@@ -4935,7 +5300,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>48</v>
       </c>
@@ -4952,7 +5317,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>278</v>
       </c>
@@ -4969,7 +5334,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>294</v>
       </c>
@@ -4986,7 +5351,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>295</v>
       </c>
@@ -5003,7 +5368,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>296</v>
       </c>
@@ -5020,7 +5385,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>297</v>
       </c>
@@ -5037,7 +5402,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>72</v>
       </c>
@@ -5054,7 +5419,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>679</v>
       </c>
@@ -5071,7 +5436,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>670</v>
       </c>
@@ -5088,7 +5453,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>673</v>
       </c>
@@ -5105,7 +5470,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>389</v>
       </c>
@@ -5122,7 +5487,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>390</v>
       </c>
@@ -5139,7 +5504,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>444</v>
       </c>
@@ -5156,7 +5521,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>59</v>
       </c>
@@ -5172,8 +5537,11 @@
       <c r="F118" s="1">
         <v>401</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L118" s="1" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>60</v>
       </c>
@@ -5189,8 +5557,11 @@
       <c r="F119" s="1">
         <v>402</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L119" s="1" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>61</v>
       </c>
@@ -5206,8 +5577,11 @@
       <c r="F120" s="1">
         <v>403</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M120" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>421</v>
       </c>
@@ -5223,8 +5597,14 @@
       <c r="F121" s="1">
         <v>404</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L121" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>422</v>
       </c>
@@ -5240,8 +5620,14 @@
       <c r="F122" s="1">
         <v>405</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L122" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>655</v>
       </c>
@@ -5257,8 +5643,14 @@
       <c r="F123" s="1">
         <v>406</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M123" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>62</v>
       </c>
@@ -5274,8 +5666,11 @@
       <c r="F124" s="1">
         <v>407</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L124" s="1" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>63</v>
       </c>
@@ -5291,8 +5686,11 @@
       <c r="F125" s="1">
         <v>408</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L125" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>64</v>
       </c>
@@ -5308,8 +5706,11 @@
       <c r="F126" s="1">
         <v>409</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M126" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>423</v>
       </c>
@@ -5325,8 +5726,14 @@
       <c r="F127" s="1">
         <v>410</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L127" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="N127" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>424</v>
       </c>
@@ -5342,8 +5749,14 @@
       <c r="F128" s="1">
         <v>411</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L128" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>656</v>
       </c>
@@ -5359,8 +5772,14 @@
       <c r="F129" s="1">
         <v>412</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M129" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>65</v>
       </c>
@@ -5376,8 +5795,11 @@
       <c r="F130" s="1">
         <v>413</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L130" s="1" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5815,11 @@
       <c r="F131" s="1">
         <v>414</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L131" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>67</v>
       </c>
@@ -5410,8 +5835,11 @@
       <c r="F132" s="1">
         <v>415</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M132" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>425</v>
       </c>
@@ -5427,8 +5855,14 @@
       <c r="F133" s="1">
         <v>416</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L133" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="N133" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>426</v>
       </c>
@@ -5444,8 +5878,14 @@
       <c r="F134" s="1">
         <v>417</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L134" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="N134" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>658</v>
       </c>
@@ -5461,8 +5901,14 @@
       <c r="F135" s="1">
         <v>418</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M135" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="N135" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>68</v>
       </c>
@@ -5478,8 +5924,11 @@
       <c r="F136" s="1">
         <v>419</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="M136" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>69</v>
       </c>
@@ -5495,8 +5944,11 @@
       <c r="F137" s="1">
         <v>420</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L137" s="1" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>70</v>
       </c>
@@ -5512,8 +5964,11 @@
       <c r="F138" s="1">
         <v>421</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L138" s="1" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>71</v>
       </c>
@@ -5527,7 +5982,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>79</v>
       </c>
@@ -5543,8 +5998,14 @@
       <c r="F140" s="1">
         <v>431</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J140" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="N140" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>80</v>
       </c>
@@ -5560,8 +6021,14 @@
       <c r="F141" s="1">
         <v>432</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J141" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="N141" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>81</v>
       </c>
@@ -5577,8 +6044,14 @@
       <c r="F142" s="1">
         <v>433</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J142" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>82</v>
       </c>
@@ -5594,8 +6067,14 @@
       <c r="F143" s="1">
         <v>434</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J143" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="N143" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>83</v>
       </c>
@@ -5611,8 +6090,14 @@
       <c r="F144" s="1">
         <v>435</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J144" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="N144" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>84</v>
       </c>
@@ -5628,8 +6113,14 @@
       <c r="F145" s="1">
         <v>436</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J145" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="N145" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>85</v>
       </c>
@@ -5645,8 +6136,11 @@
       <c r="F146" s="1">
         <v>437</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J146" s="1" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>86</v>
       </c>
@@ -5662,8 +6156,11 @@
       <c r="F147" s="1">
         <v>438</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J147" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>87</v>
       </c>
@@ -5679,8 +6176,11 @@
       <c r="F148" s="1">
         <v>439</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J148" s="1" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>88</v>
       </c>
@@ -5696,8 +6196,11 @@
       <c r="F149" s="1">
         <v>440</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J149" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>89</v>
       </c>
@@ -5713,8 +6216,11 @@
       <c r="F150" s="1">
         <v>441</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J150" s="1" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>90</v>
       </c>
@@ -5730,8 +6236,11 @@
       <c r="F151" s="1">
         <v>442</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J151" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>91</v>
       </c>
@@ -5747,8 +6256,14 @@
       <c r="F152" s="1">
         <v>443</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J152" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="N152" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>92</v>
       </c>
@@ -5764,8 +6279,14 @@
       <c r="F153" s="1">
         <v>444</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J153" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="N153" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>93</v>
       </c>
@@ -5781,8 +6302,14 @@
       <c r="F154" s="1">
         <v>445</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J154" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="N154" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>94</v>
       </c>
@@ -5798,8 +6325,14 @@
       <c r="F155" s="1">
         <v>446</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J155" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="N155" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>95</v>
       </c>
@@ -5815,8 +6348,14 @@
       <c r="F156" s="1">
         <v>447</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J156" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="N156" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>96</v>
       </c>
@@ -5832,8 +6371,14 @@
       <c r="F157" s="1">
         <v>448</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J157" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="N157" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>97</v>
       </c>
@@ -5849,8 +6394,11 @@
       <c r="F158" s="1">
         <v>449</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J158" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>98</v>
       </c>
@@ -5866,8 +6414,11 @@
       <c r="F159" s="1">
         <v>450</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J159" s="1" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>99</v>
       </c>
@@ -5883,8 +6434,11 @@
       <c r="F160" s="1">
         <v>451</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J160" s="1" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>100</v>
       </c>
@@ -5900,8 +6454,11 @@
       <c r="F161" s="1">
         <v>452</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J161" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>101</v>
       </c>
@@ -5917,8 +6474,11 @@
       <c r="F162" s="1">
         <v>453</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J162" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>102</v>
       </c>
@@ -5934,8 +6494,11 @@
       <c r="F163" s="1">
         <v>454</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J163" s="1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>103</v>
       </c>
@@ -5951,8 +6514,14 @@
       <c r="F164" s="1">
         <v>455</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J164" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="N164" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>104</v>
       </c>
@@ -5968,8 +6537,14 @@
       <c r="F165" s="1">
         <v>456</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J165" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="N165" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>105</v>
       </c>
@@ -5985,8 +6560,14 @@
       <c r="F166" s="1">
         <v>457</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J166" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="N166" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>106</v>
       </c>
@@ -6002,8 +6583,14 @@
       <c r="F167" s="1">
         <v>458</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J167" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="N167" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>107</v>
       </c>
@@ -6019,8 +6606,14 @@
       <c r="F168" s="1">
         <v>459</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J168" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="N168" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>108</v>
       </c>
@@ -6036,8 +6629,14 @@
       <c r="F169" s="1">
         <v>460</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J169" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="N169" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>109</v>
       </c>
@@ -6053,8 +6652,11 @@
       <c r="F170" s="1">
         <v>461</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J170" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>110</v>
       </c>
@@ -6070,8 +6672,11 @@
       <c r="F171" s="1">
         <v>462</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J171" s="1" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>111</v>
       </c>
@@ -6087,8 +6692,11 @@
       <c r="F172" s="1">
         <v>463</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J172" s="1" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>112</v>
       </c>
@@ -6104,8 +6712,11 @@
       <c r="F173" s="1">
         <v>464</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J173" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>113</v>
       </c>
@@ -6121,8 +6732,11 @@
       <c r="F174" s="1">
         <v>465</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J174" s="1" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>114</v>
       </c>
@@ -6138,8 +6752,11 @@
       <c r="F175" s="1">
         <v>466</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J175" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>115</v>
       </c>
@@ -6155,8 +6772,14 @@
       <c r="F176" s="1">
         <v>467</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J176" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="N176" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>116</v>
       </c>
@@ -6172,8 +6795,14 @@
       <c r="F177" s="1">
         <v>468</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J177" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="N177" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>117</v>
       </c>
@@ -6189,8 +6818,14 @@
       <c r="F178" s="1">
         <v>469</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J178" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="N178" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>118</v>
       </c>
@@ -6206,8 +6841,14 @@
       <c r="F179" s="1">
         <v>470</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J179" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="N179" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>119</v>
       </c>
@@ -6223,8 +6864,14 @@
       <c r="F180" s="1">
         <v>471</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J180" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="N180" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>120</v>
       </c>
@@ -6240,8 +6887,14 @@
       <c r="F181" s="1">
         <v>472</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J181" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="N181" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>121</v>
       </c>
@@ -6257,8 +6910,11 @@
       <c r="F182" s="1">
         <v>473</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J182" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>122</v>
       </c>
@@ -6274,8 +6930,11 @@
       <c r="F183" s="1">
         <v>474</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J183" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>123</v>
       </c>
@@ -6291,8 +6950,11 @@
       <c r="F184" s="1">
         <v>475</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J184" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>124</v>
       </c>
@@ -6308,8 +6970,11 @@
       <c r="F185" s="1">
         <v>476</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J185" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>125</v>
       </c>
@@ -6325,8 +6990,11 @@
       <c r="F186" s="1">
         <v>477</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J186" s="1" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>126</v>
       </c>
@@ -6342,8 +7010,11 @@
       <c r="F187" s="1">
         <v>478</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J187" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>127</v>
       </c>
@@ -6359,8 +7030,14 @@
       <c r="F188" s="1">
         <v>479</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J188" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="N188" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>128</v>
       </c>
@@ -6376,8 +7053,14 @@
       <c r="F189" s="1">
         <v>480</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J189" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="N189" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>129</v>
       </c>
@@ -6393,8 +7076,14 @@
       <c r="F190" s="1">
         <v>481</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J190" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="N190" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>130</v>
       </c>
@@ -6410,8 +7099,14 @@
       <c r="F191" s="1">
         <v>482</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J191" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="N191" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>131</v>
       </c>
@@ -6427,8 +7122,14 @@
       <c r="F192" s="1">
         <v>483</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J192" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="N192" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>132</v>
       </c>
@@ -6444,8 +7145,14 @@
       <c r="F193" s="1">
         <v>484</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J193" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="N193" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>133</v>
       </c>
@@ -6461,8 +7168,11 @@
       <c r="F194" s="1">
         <v>485</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J194" s="1" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>134</v>
       </c>
@@ -6478,8 +7188,11 @@
       <c r="F195" s="1">
         <v>486</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J195" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>135</v>
       </c>
@@ -6495,8 +7208,11 @@
       <c r="F196" s="1">
         <v>487</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J196" s="1" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>136</v>
       </c>
@@ -6512,8 +7228,11 @@
       <c r="F197" s="1">
         <v>488</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J197" s="1" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>137</v>
       </c>
@@ -6529,8 +7248,11 @@
       <c r="F198" s="1">
         <v>489</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J198" s="1" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>138</v>
       </c>
@@ -6546,8 +7268,11 @@
       <c r="F199" s="1">
         <v>490</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J199" s="1" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>139</v>
       </c>
@@ -6563,8 +7288,14 @@
       <c r="F200" s="1">
         <v>491</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J200" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="N200" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>140</v>
       </c>
@@ -6580,8 +7311,14 @@
       <c r="F201" s="1">
         <v>492</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J201" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="N201" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>141</v>
       </c>
@@ -6597,8 +7334,14 @@
       <c r="F202" s="1">
         <v>493</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J202" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="N202" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>142</v>
       </c>
@@ -6614,8 +7357,14 @@
       <c r="F203" s="1">
         <v>494</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J203" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="N203" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>143</v>
       </c>
@@ -6631,8 +7380,14 @@
       <c r="F204" s="1">
         <v>495</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J204" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="N204" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>144</v>
       </c>
@@ -6648,8 +7403,14 @@
       <c r="F205" s="1">
         <v>496</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J205" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="N205" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>145</v>
       </c>
@@ -6665,8 +7426,11 @@
       <c r="F206" s="1">
         <v>497</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J206" s="1" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>146</v>
       </c>
@@ -6682,8 +7446,11 @@
       <c r="F207" s="1">
         <v>498</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J207" s="1" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>147</v>
       </c>
@@ -6699,8 +7466,11 @@
       <c r="F208" s="1">
         <v>499</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J208" s="1" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>148</v>
       </c>
@@ -6716,8 +7486,11 @@
       <c r="F209" s="1">
         <v>500</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J209" s="1" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>149</v>
       </c>
@@ -6733,8 +7506,11 @@
       <c r="F210" s="1">
         <v>501</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J210" s="1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>150</v>
       </c>
@@ -6750,8 +7526,11 @@
       <c r="F211" s="1">
         <v>502</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J211" s="1" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>385</v>
       </c>
@@ -6765,7 +7544,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>387</v>
       </c>
@@ -6779,7 +7558,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>428</v>
       </c>
@@ -6796,7 +7575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" ht="15" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>682</v>
       </c>
@@ -6810,7 +7589,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>320</v>
       </c>
@@ -6824,7 +7603,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>347</v>
       </c>
@@ -6838,7 +7617,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>349</v>
       </c>
@@ -6852,7 +7631,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" ht="15" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>684</v>
       </c>
@@ -6866,7 +7645,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>351</v>
       </c>
@@ -6880,7 +7659,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>352</v>
       </c>
@@ -6894,7 +7673,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>353</v>
       </c>
@@ -6908,7 +7687,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="15" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>686</v>
       </c>
@@ -6922,7 +7701,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>357</v>
       </c>
@@ -6936,7 +7715,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>358</v>
       </c>
@@ -6950,7 +7729,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>359</v>
       </c>
@@ -6964,7 +7743,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>363</v>
       </c>
@@ -6978,7 +7757,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>365</v>
       </c>
@@ -6992,7 +7771,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>366</v>
       </c>
@@ -7006,7 +7785,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>369</v>
       </c>
@@ -7020,7 +7799,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>370</v>
       </c>
@@ -7034,7 +7813,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>371</v>
       </c>
@@ -7048,7 +7827,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>372</v>
       </c>
@@ -7062,7 +7841,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>377</v>
       </c>
@@ -7076,7 +7855,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>379</v>
       </c>
@@ -7090,7 +7869,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>466</v>
       </c>
@@ -7107,7 +7886,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="237" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A237" s="9" t="s">
         <v>688</v>
       </c>
@@ -7128,7 +7907,7 @@
         <v>fblt</v>
       </c>
     </row>
-    <row r="238" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A238" s="9" t="s">
         <v>689</v>
       </c>
@@ -7149,7 +7928,7 @@
         <v>frng</v>
       </c>
     </row>
-    <row r="239" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
         <v>690</v>
       </c>
@@ -7170,7 +7949,7 @@
         <v>finf</v>
       </c>
     </row>
-    <row r="240" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
         <v>691</v>
       </c>
@@ -7191,7 +7970,7 @@
         <v>fbal</v>
       </c>
     </row>
-    <row r="241" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
         <v>692</v>
       </c>
@@ -7212,7 +7991,7 @@
         <v>fbls</v>
       </c>
     </row>
-    <row r="242" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A242" s="9" t="s">
         <v>729</v>
       </c>
@@ -7233,7 +8012,7 @@
         <v>fbls</v>
       </c>
     </row>
-    <row r="243" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
         <v>693</v>
       </c>
@@ -7254,7 +8033,7 @@
         <v>fwal</v>
       </c>
     </row>
-    <row r="244" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
         <v>732</v>
       </c>
@@ -7275,7 +8054,7 @@
         <v>fwal</v>
       </c>
     </row>
-    <row r="245" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A245" s="10" t="s">
         <v>694</v>
       </c>
@@ -7296,7 +8075,7 @@
         <v>tchm</v>
       </c>
     </row>
-    <row r="246" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A246" s="10" t="s">
         <v>695</v>
       </c>
@@ -7317,7 +8096,7 @@
         <v>tblt</v>
       </c>
     </row>
-    <row r="247" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A247" s="10" t="s">
         <v>696</v>
       </c>
@@ -7338,7 +8117,7 @@
         <v>tltn</v>
       </c>
     </row>
-    <row r="248" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A248" s="10" t="s">
         <v>737</v>
       </c>
@@ -7359,7 +8138,7 @@
         <v>tltn</v>
       </c>
     </row>
-    <row r="249" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
         <v>697</v>
       </c>
@@ -7380,7 +8159,7 @@
         <v>tnov</v>
       </c>
     </row>
-    <row r="250" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
         <v>698</v>
       </c>
@@ -7401,7 +8180,7 @@
         <v>tshd</v>
       </c>
     </row>
-    <row r="251" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
         <v>741</v>
       </c>
@@ -7422,7 +8201,7 @@
         <v>tshd</v>
       </c>
     </row>
-    <row r="252" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
         <v>699</v>
       </c>
@@ -7443,7 +8222,7 @@
         <v>tblz</v>
       </c>
     </row>
-    <row r="253" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
         <v>744</v>
       </c>
@@ -7464,7 +8243,7 @@
         <v>tblz</v>
       </c>
     </row>
-    <row r="254" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" s="11" t="s">
         <v>700</v>
       </c>
@@ -7485,7 +8264,7 @@
         <v>bbas</v>
       </c>
     </row>
-    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A255" s="11" t="s">
         <v>701</v>
       </c>
@@ -7506,7 +8285,7 @@
         <v>bcrt</v>
       </c>
     </row>
-    <row r="256" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A256" s="11" t="s">
         <v>702</v>
       </c>
@@ -7527,7 +8306,7 @@
         <v>bthr</v>
       </c>
     </row>
-    <row r="257" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A257" s="11" t="s">
         <v>703</v>
       </c>
@@ -7548,7 +8327,7 @@
         <v>bclv</v>
       </c>
     </row>
-    <row r="258" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A258" s="11" t="s">
         <v>704</v>
       </c>
@@ -7569,7 +8348,7 @@
         <v>bcrz</v>
       </c>
     </row>
-    <row r="259" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="11" t="s">
         <v>751</v>
       </c>
@@ -7590,7 +8369,7 @@
         <v>bcrz</v>
       </c>
     </row>
-    <row r="260" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A260" s="11" t="s">
         <v>705</v>
       </c>
@@ -7614,7 +8393,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="261" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A261" s="11" t="s">
         <v>754</v>
       </c>
@@ -7638,7 +8417,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="262" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A262" s="12" t="s">
         <v>706</v>
       </c>
@@ -7659,7 +8438,7 @@
         <v>xdef</v>
       </c>
     </row>
-    <row r="263" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A263" s="12" t="s">
         <v>707</v>
       </c>
@@ -7680,7 +8459,7 @@
         <v>xdog</v>
       </c>
     </row>
-    <row r="264" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A264" s="12" t="s">
         <v>708</v>
       </c>
@@ -7701,7 +8480,7 @@
         <v>xcta</v>
       </c>
     </row>
-    <row r="265" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A265" s="12" t="s">
         <v>709</v>
       </c>
@@ -7722,7 +8501,7 @@
         <v>xwms</v>
       </c>
     </row>
-    <row r="266" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A266" s="12" t="s">
         <v>710</v>
       </c>
@@ -7743,7 +8522,7 @@
         <v>xchg</v>
       </c>
     </row>
-    <row r="267" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A267" s="12" t="s">
         <v>711</v>
       </c>
@@ -7764,7 +8543,7 @@
         <v>xtst</v>
       </c>
     </row>
-    <row r="268" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="12" t="s">
         <v>762</v>
       </c>
@@ -7785,7 +8564,7 @@
         <v>xtst</v>
       </c>
     </row>
-    <row r="269" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" s="6" t="s">
         <v>712</v>
       </c>
@@ -7806,7 +8585,7 @@
         <v>hhel</v>
       </c>
     </row>
-    <row r="270" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="6" t="s">
         <v>764</v>
       </c>
@@ -7827,7 +8606,7 @@
         <v>hhel</v>
       </c>
     </row>
-    <row r="271" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" s="6" t="s">
         <v>713</v>
       </c>
@@ -7848,7 +8627,7 @@
         <v>hgsd</v>
       </c>
     </row>
-    <row r="272" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A272" s="6" t="s">
         <v>714</v>
       </c>
@@ -7869,7 +8648,7 @@
         <v>hinv</v>
       </c>
     </row>
-    <row r="273" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" s="6" t="s">
         <v>715</v>
       </c>
@@ -7890,7 +8669,7 @@
         <v>hhsd</v>
       </c>
     </row>
-    <row r="274" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A274" s="6" t="s">
         <v>716</v>
       </c>
@@ -7911,7 +8690,7 @@
         <v>hlok</v>
       </c>
     </row>
-    <row r="275" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A275" s="6" t="s">
         <v>771</v>
       </c>
@@ -7932,7 +8711,7 @@
         <v>hlok</v>
       </c>
     </row>
-    <row r="276" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A276" s="6" t="s">
         <v>717</v>
       </c>
@@ -7953,7 +8732,7 @@
         <v>hmhl</v>
       </c>
     </row>
-    <row r="277" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A277" s="6" t="s">
         <v>773</v>
       </c>
@@ -7974,7 +8753,7 @@
         <v>hmhl</v>
       </c>
     </row>
-    <row r="278" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>718</v>
       </c>
@@ -7995,7 +8774,7 @@
         <v>pbas</v>
       </c>
     </row>
-    <row r="279" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>719</v>
       </c>
@@ -8016,7 +8795,7 @@
         <v>ppoi</v>
       </c>
     </row>
-    <row r="280" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>720</v>
       </c>
@@ -8040,7 +8819,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="281" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>721</v>
       </c>
@@ -8061,7 +8840,7 @@
         <v>prun</v>
       </c>
     </row>
-    <row r="282" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>722</v>
       </c>
@@ -8082,7 +8861,7 @@
         <v>pcbl</v>
       </c>
     </row>
-    <row r="283" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>781</v>
       </c>
@@ -8103,7 +8882,7 @@
         <v>pcbl</v>
       </c>
     </row>
-    <row r="284" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>723</v>
       </c>
@@ -8127,7 +8906,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="285" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>784</v>
       </c>
@@ -8151,28 +8930,28 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B240:B241 B243 B245:B247 B249:B285">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B244">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E3B4DD-BAAB-4968-AC0C-600D4540FEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE430C4B-1241-4FB1-AEE2-05BEB92A683C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="884">
   <si>
     <t>id</t>
   </si>
@@ -544,10 +544,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>js:(d:import("../data/ReactStat").default)=&gt;void</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>名称</t>
   </si>
   <si>
@@ -2244,9 +2240,6 @@
     <t>大火球的波及数量+{0}</t>
   </si>
   <si>
-    <t>使目标身上的点燃效果立即造成全额伤害</t>
-  </si>
-  <si>
     <t>skfblsm2</t>
   </si>
   <si>
@@ -2265,9 +2258,6 @@
     <t>诱惑之光可以对精英敌人使用</t>
   </si>
   <si>
-    <t>对目标及其相邻的1个敌人造成{0.2}%的粉碎性打击</t>
-  </si>
-  <si>
     <t>疾光电影的命中提升20%，但是伤害降低{0.2}%，同时，疾光电影不再对一条直线的敌人造成伤害，而是转化为闪电链，最多伤害4个目标</t>
   </si>
   <si>
@@ -2277,21 +2267,9 @@
     <t>疾光电影可以攻击2排目标</t>
   </si>
   <si>
-    <t>受影响的目标降低{0.2}%风雷抗性，最多叠加3层</t>
-  </si>
-  <si>
-    <t>可以吸收你的生命上限{0.2}%的物理伤害</t>
-  </si>
-  <si>
     <t>sktshdm2</t>
   </si>
   <si>
-    <t>持续期间，你的反弹伤害效果提升{0.2}%</t>
-  </si>
-  <si>
-    <t>可直接杀死生命值低于{0.2}%的小怪</t>
-  </si>
-  <si>
     <t>sktblzm2</t>
   </si>
   <si>
@@ -2416,10 +2394,6 @@
   </si>
   <si>
     <t>神兽攻击时有概率战吼，整个队伍的物理伤害提升{0.2}%</t>
-  </si>
-  <si>
-    <t>sktblzm1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>number</t>
@@ -2669,6 +2643,90 @@
   </si>
   <si>
     <t>限制单位</t>
+  </si>
+  <si>
+    <t>js:(d:import("../data/ReactStat").default)=&gt;void</t>
+  </si>
+  <si>
+    <t>isSkillMod</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>是技能Mod</t>
+  </si>
+  <si>
+    <t>t4 weap</t>
+  </si>
+  <si>
+    <t>1海魂</t>
+  </si>
+  <si>
+    <t>7巫异时刻</t>
+  </si>
+  <si>
+    <t>14龙牙</t>
+  </si>
+  <si>
+    <t>1偃月</t>
+  </si>
+  <si>
+    <t>7充能短刃</t>
+  </si>
+  <si>
+    <t>14电能印记</t>
+  </si>
+  <si>
+    <t>14 雷神战刃</t>
+  </si>
+  <si>
+    <t>21火骷髅剑</t>
+  </si>
+  <si>
+    <t>21聋哑</t>
+  </si>
+  <si>
+    <t>28魔杖</t>
+  </si>
+  <si>
+    <t>28纵火者</t>
+  </si>
+  <si>
+    <t>28启示录</t>
+  </si>
+  <si>
+    <t>28血饮</t>
+  </si>
+  <si>
+    <t>35 彩虹魔杖</t>
+  </si>
+  <si>
+    <t>35骨玉权杖</t>
+  </si>
+  <si>
+    <t>35火龙杖</t>
+  </si>
+  <si>
+    <t>35火神仲裁官</t>
+  </si>
+  <si>
+    <t>冰咆哮可直接杀死生命值低于{0.2}%的小怪</t>
+  </si>
+  <si>
+    <t>魔法盾可以吸收你的生命上限{0.2}%的物理伤害</t>
+  </si>
+  <si>
+    <t>魔法盾持续期间，你的反弹伤害效果提升{0.2}%</t>
+  </si>
+  <si>
+    <t>受地狱雷光影响的目标降低{0.2}%风雷抗性，最多叠加3层</t>
+  </si>
+  <si>
+    <t>雷电术对目标及其相邻的1个敌人造成{0.2}%的粉碎性打击</t>
+  </si>
+  <si>
+    <t>爆裂火焰使目标身上的点燃效果立即造成全额伤害</t>
   </si>
 </sst>
 </file>
@@ -2796,247 +2854,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3383,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:N285"/>
+  <dimension ref="A1:O285"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.08984375" style="1" customWidth="1"/>
@@ -3397,7 +3215,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3414,7 +3232,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -3423,25 +3241,28 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+        <v>854</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -3458,196 +3279,202 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>168</v>
+        <v>856</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+        <v>849</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>789</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>797</v>
-      </c>
       <c r="J4" s="8" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>855</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F5" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F6" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F7" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>398</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F8" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F9" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F10" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F11" s="1">
         <v>43</v>
@@ -3656,21 +3483,21 @@
         <v>159</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F12" s="1">
         <v>44</v>
@@ -3679,55 +3506,55 @@
         <v>8</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F13" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F14" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F15" s="1">
         <v>53</v>
@@ -3736,21 +3563,21 @@
         <v>160</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F16" s="1">
         <v>54</v>
@@ -3759,7 +3586,7 @@
         <v>12</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -3767,13 +3594,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F17" s="1">
         <v>61</v>
@@ -3784,13 +3611,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F18" s="1">
         <v>62</v>
@@ -3801,13 +3628,13 @@
         <v>73</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F19" s="1">
         <v>321</v>
@@ -3818,13 +3645,13 @@
         <v>74</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F20" s="1">
         <v>322</v>
@@ -3832,16 +3659,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F21" s="1">
         <v>63</v>
@@ -3849,16 +3676,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F22" s="1">
         <v>331</v>
@@ -3866,16 +3693,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F23" s="1">
         <v>332</v>
@@ -3883,16 +3710,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
@@ -3900,16 +3727,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
@@ -3917,16 +3744,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F26" s="1">
         <v>3</v>
@@ -3934,16 +3761,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F27" s="1">
         <v>4</v>
@@ -3951,16 +3778,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F28" s="1">
         <v>5</v>
@@ -3968,16 +3795,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F29" s="1">
         <v>11</v>
@@ -3985,16 +3812,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F30" s="1">
         <v>12</v>
@@ -4002,16 +3829,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F31" s="1">
         <v>13</v>
@@ -4019,16 +3846,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F32" s="1">
         <v>14</v>
@@ -4036,16 +3863,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F33" s="1">
         <v>15</v>
@@ -4053,16 +3880,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F34" s="1">
         <v>21</v>
@@ -4070,16 +3897,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F35" s="1">
         <v>22</v>
@@ -4087,16 +3914,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F36" s="1">
         <v>23</v>
@@ -4104,16 +3931,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F37" s="1">
         <v>24</v>
@@ -4121,16 +3948,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F38" s="1">
         <v>25</v>
@@ -4141,13 +3968,13 @@
         <v>18</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F39" s="1">
         <v>101</v>
@@ -4158,13 +3985,13 @@
         <v>19</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F40" s="1">
         <v>102</v>
@@ -4175,13 +4002,13 @@
         <v>20</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F41" s="1">
         <v>103</v>
@@ -4192,13 +4019,13 @@
         <v>21</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F42" s="1">
         <v>104</v>
@@ -4209,13 +4036,13 @@
         <v>22</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F43" s="1">
         <v>105</v>
@@ -4226,13 +4053,13 @@
         <v>49</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F44" s="1">
         <v>201</v>
@@ -4243,13 +4070,13 @@
         <v>50</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F45" s="1">
         <v>202</v>
@@ -4260,13 +4087,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F46" s="1">
         <v>203</v>
@@ -4277,13 +4104,13 @@
         <v>52</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F47" s="1">
         <v>204</v>
@@ -4294,13 +4121,13 @@
         <v>53</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F48" s="1">
         <v>205</v>
@@ -4311,13 +4138,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F49" s="1">
         <v>206</v>
@@ -4328,13 +4155,13 @@
         <v>55</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F50" s="1">
         <v>207</v>
@@ -4345,13 +4172,13 @@
         <v>56</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F51" s="1">
         <v>208</v>
@@ -4362,13 +4189,13 @@
         <v>57</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F52" s="1">
         <v>209</v>
@@ -4379,13 +4206,13 @@
         <v>58</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F53" s="1">
         <v>210</v>
@@ -4393,16 +4220,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F54" s="1">
         <v>211</v>
@@ -4410,16 +4237,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F55" s="1">
         <v>212</v>
@@ -4427,16 +4254,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F56" s="1">
         <v>213</v>
@@ -4447,13 +4274,13 @@
         <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F57" s="1">
         <v>221</v>
@@ -4464,13 +4291,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F58" s="1">
         <v>222</v>
@@ -4481,13 +4308,13 @@
         <v>25</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F59" s="1">
         <v>223</v>
@@ -4498,13 +4325,13 @@
         <v>26</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F60" s="1">
         <v>224</v>
@@ -4515,13 +4342,13 @@
         <v>27</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F61" s="1">
         <v>225</v>
@@ -4532,7 +4359,7 @@
         <v>38</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>153</v>
@@ -4541,7 +4368,7 @@
         <v>157</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F62" s="1">
         <v>226</v>
@@ -4552,7 +4379,7 @@
         <v>39</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>153</v>
@@ -4561,7 +4388,7 @@
         <v>157</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F63" s="1">
         <v>227</v>
@@ -4572,7 +4399,7 @@
         <v>40</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>153</v>
@@ -4581,7 +4408,7 @@
         <v>158</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F64" s="1">
         <v>228</v>
@@ -4589,19 +4416,19 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F65" s="1">
         <v>229</v>
@@ -4609,19 +4436,19 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F66" s="1">
         <v>230</v>
@@ -4629,19 +4456,19 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F67" s="1">
         <v>231</v>
@@ -4649,16 +4476,16 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F68" s="1">
         <v>232</v>
@@ -4669,13 +4496,13 @@
         <v>28</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F69" s="1">
         <v>241</v>
@@ -4686,13 +4513,13 @@
         <v>29</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F70" s="1">
         <v>242</v>
@@ -4703,13 +4530,13 @@
         <v>30</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F71" s="1">
         <v>243</v>
@@ -4720,13 +4547,13 @@
         <v>31</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F72" s="1">
         <v>244</v>
@@ -4737,13 +4564,13 @@
         <v>32</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F73" s="1">
         <v>245</v>
@@ -4754,13 +4581,13 @@
         <v>33</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F74" s="1">
         <v>251</v>
@@ -4769,7 +4596,7 @@
         <v>161</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
@@ -4777,13 +4604,13 @@
         <v>34</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F75" s="1">
         <v>252</v>
@@ -4792,7 +4619,7 @@
         <v>162</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
@@ -4800,13 +4627,13 @@
         <v>35</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F76" s="1">
         <v>253</v>
@@ -4815,7 +4642,7 @@
         <v>163</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
@@ -4823,13 +4650,13 @@
         <v>36</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F77" s="1">
         <v>254</v>
@@ -4838,7 +4665,7 @@
         <v>164</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
@@ -4846,13 +4673,13 @@
         <v>37</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F78" s="1">
         <v>255</v>
@@ -4861,21 +4688,21 @@
         <v>165</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F79" s="1">
         <v>261</v>
@@ -4886,13 +4713,13 @@
         <v>75</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F80" s="1">
         <v>262</v>
@@ -4903,13 +4730,13 @@
         <v>76</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F81" s="1">
         <v>263</v>
@@ -4920,13 +4747,13 @@
         <v>77</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F82" s="1">
         <v>264</v>
@@ -4937,13 +4764,13 @@
         <v>78</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F83" s="1">
         <v>265</v>
@@ -4951,16 +4778,16 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F84" s="1">
         <v>271</v>
@@ -4968,16 +4795,16 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F85" s="1">
         <v>272</v>
@@ -4985,16 +4812,16 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F86" s="1">
         <v>273</v>
@@ -5002,16 +4829,16 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F87" s="1">
         <v>274</v>
@@ -5019,16 +4846,16 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F88" s="1">
         <v>275</v>
@@ -5039,13 +4866,13 @@
         <v>41</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F89" s="1">
         <v>281</v>
@@ -5056,13 +4883,13 @@
         <v>42</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F90" s="1">
         <v>282</v>
@@ -5073,13 +4900,13 @@
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F91" s="1">
         <v>283</v>
@@ -5090,13 +4917,13 @@
         <v>44</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F92" s="1">
         <v>284</v>
@@ -5107,13 +4934,13 @@
         <v>45</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F93" s="1">
         <v>285</v>
@@ -5121,16 +4948,16 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F94" s="1">
         <v>286</v>
@@ -5138,16 +4965,16 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C95" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>663</v>
       </c>
       <c r="F95" s="1">
         <v>287</v>
@@ -5158,7 +4985,7 @@
         <v>17</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>153</v>
@@ -5172,16 +4999,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C97" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="F97" s="1">
         <v>289</v>
@@ -5189,16 +5016,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>677</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>678</v>
       </c>
       <c r="F98" s="1">
         <v>290</v>
@@ -5206,16 +5033,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F99" s="1">
         <v>291</v>
@@ -5223,13 +5050,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C100" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F100" s="1">
         <v>292</v>
@@ -5237,13 +5064,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C101" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F101" s="1">
         <v>293</v>
@@ -5251,16 +5078,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="F102" s="1">
         <v>999</v>
@@ -5271,13 +5098,13 @@
         <v>46</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F103" s="1">
         <v>301</v>
@@ -5288,13 +5115,13 @@
         <v>47</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F104" s="1">
         <v>302</v>
@@ -5305,13 +5132,13 @@
         <v>48</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F105" s="1">
         <v>303</v>
@@ -5319,16 +5146,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B106" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B106" s="4" t="s">
-        <v>279</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F106" s="1">
         <v>304</v>
@@ -5336,16 +5163,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F107" s="1">
         <v>305</v>
@@ -5353,16 +5180,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F108" s="1">
         <v>306</v>
@@ -5370,16 +5197,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F109" s="1">
         <v>307</v>
@@ -5387,16 +5214,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F110" s="1">
         <v>308</v>
@@ -5407,13 +5234,13 @@
         <v>72</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F111" s="1">
         <v>309</v>
@@ -5421,16 +5248,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>681</v>
       </c>
       <c r="F112" s="1">
         <v>310</v>
@@ -5438,16 +5265,16 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>671</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>672</v>
       </c>
       <c r="F113" s="1">
         <v>311</v>
@@ -5455,16 +5282,16 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>675</v>
       </c>
       <c r="F114" s="1">
         <v>312</v>
@@ -5472,16 +5299,16 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F115" s="1">
         <v>313</v>
@@ -5489,16 +5316,16 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F116" s="1">
         <v>314</v>
@@ -5506,16 +5333,16 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C117" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F117" s="1">
         <v>315</v>
@@ -5526,19 +5353,19 @@
         <v>59</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F118" s="1">
         <v>401</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
@@ -5546,19 +5373,19 @@
         <v>60</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F119" s="1">
         <v>402</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
@@ -5566,88 +5393,88 @@
         <v>61</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F120" s="1">
         <v>403</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F121" s="1">
         <v>404</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F122" s="1">
         <v>405</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F123" s="1">
         <v>406</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
@@ -5655,19 +5482,19 @@
         <v>62</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F124" s="1">
         <v>407</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
@@ -5675,19 +5502,19 @@
         <v>63</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F125" s="1">
         <v>408</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
@@ -5695,88 +5522,88 @@
         <v>64</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F126" s="1">
         <v>409</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F127" s="1">
         <v>410</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F128" s="1">
         <v>411</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>656</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>657</v>
       </c>
       <c r="F129" s="1">
         <v>412</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
@@ -5784,19 +5611,19 @@
         <v>65</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F130" s="1">
         <v>413</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.35">
@@ -5804,19 +5631,19 @@
         <v>66</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F131" s="1">
         <v>414</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
@@ -5824,88 +5651,88 @@
         <v>67</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F132" s="1">
         <v>415</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F133" s="1">
         <v>416</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F134" s="1">
         <v>417</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>659</v>
       </c>
       <c r="F135" s="1">
         <v>418</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.35">
@@ -5913,19 +5740,19 @@
         <v>68</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F136" s="1">
         <v>419</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.35">
@@ -5933,19 +5760,19 @@
         <v>69</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F137" s="1">
         <v>420</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.35">
@@ -5953,19 +5780,19 @@
         <v>70</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F138" s="1">
         <v>421</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
@@ -5973,7 +5800,7 @@
         <v>71</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>155</v>
@@ -5987,22 +5814,22 @@
         <v>79</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F140" s="1">
         <v>431</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.35">
@@ -6010,22 +5837,22 @@
         <v>80</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F141" s="1">
         <v>432</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.35">
@@ -6033,22 +5860,22 @@
         <v>81</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F142" s="1">
         <v>433</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.35">
@@ -6056,22 +5883,22 @@
         <v>82</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F143" s="1">
         <v>434</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.35">
@@ -6079,22 +5906,22 @@
         <v>83</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F144" s="1">
         <v>435</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.35">
@@ -6102,22 +5929,22 @@
         <v>84</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F145" s="1">
         <v>436</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.35">
@@ -6125,19 +5952,19 @@
         <v>85</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F146" s="1">
         <v>437</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.35">
@@ -6145,19 +5972,19 @@
         <v>86</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F147" s="1">
         <v>438</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.35">
@@ -6165,19 +5992,19 @@
         <v>87</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F148" s="1">
         <v>439</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.35">
@@ -6185,19 +6012,19 @@
         <v>88</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F149" s="1">
         <v>440</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.35">
@@ -6205,19 +6032,19 @@
         <v>89</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F150" s="1">
         <v>441</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.35">
@@ -6225,19 +6052,19 @@
         <v>90</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F151" s="1">
         <v>442</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.35">
@@ -6245,22 +6072,22 @@
         <v>91</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F152" s="1">
         <v>443</v>
       </c>
       <c r="J152" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="N152" s="1" t="s">
         <v>842</v>
-      </c>
-      <c r="N152" s="1" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.35">
@@ -6268,22 +6095,22 @@
         <v>92</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F153" s="1">
         <v>444</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.35">
@@ -6291,22 +6118,22 @@
         <v>93</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F154" s="1">
         <v>445</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.35">
@@ -6314,22 +6141,22 @@
         <v>94</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F155" s="1">
         <v>446</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.35">
@@ -6337,22 +6164,22 @@
         <v>95</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F156" s="1">
         <v>447</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.35">
@@ -6360,22 +6187,22 @@
         <v>96</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F157" s="1">
         <v>448</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.35">
@@ -6383,19 +6210,19 @@
         <v>97</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F158" s="1">
         <v>449</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.35">
@@ -6403,19 +6230,19 @@
         <v>98</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F159" s="1">
         <v>450</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.35">
@@ -6423,19 +6250,19 @@
         <v>99</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F160" s="1">
         <v>451</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.35">
@@ -6443,19 +6270,19 @@
         <v>100</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F161" s="1">
         <v>452</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.35">
@@ -6463,19 +6290,19 @@
         <v>101</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F162" s="1">
         <v>453</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.35">
@@ -6483,19 +6310,19 @@
         <v>102</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F163" s="1">
         <v>454</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.35">
@@ -6503,22 +6330,22 @@
         <v>103</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F164" s="1">
         <v>455</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.35">
@@ -6526,22 +6353,22 @@
         <v>104</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F165" s="1">
         <v>456</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.35">
@@ -6549,22 +6376,22 @@
         <v>105</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F166" s="1">
         <v>457</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.35">
@@ -6572,22 +6399,22 @@
         <v>106</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F167" s="1">
         <v>458</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.35">
@@ -6595,22 +6422,22 @@
         <v>107</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F168" s="1">
         <v>459</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.35">
@@ -6618,22 +6445,22 @@
         <v>108</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F169" s="1">
         <v>460</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.35">
@@ -6641,19 +6468,19 @@
         <v>109</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F170" s="1">
         <v>461</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.35">
@@ -6661,19 +6488,19 @@
         <v>110</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F171" s="1">
         <v>462</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.35">
@@ -6681,19 +6508,19 @@
         <v>111</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F172" s="1">
         <v>463</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.35">
@@ -6701,19 +6528,19 @@
         <v>112</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F173" s="1">
         <v>464</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.35">
@@ -6721,19 +6548,19 @@
         <v>113</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F174" s="1">
         <v>465</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.35">
@@ -6741,19 +6568,19 @@
         <v>114</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F175" s="1">
         <v>466</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.35">
@@ -6761,22 +6588,22 @@
         <v>115</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F176" s="1">
         <v>467</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.35">
@@ -6784,22 +6611,22 @@
         <v>116</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F177" s="1">
         <v>468</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="N177" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.35">
@@ -6807,22 +6634,22 @@
         <v>117</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F178" s="1">
         <v>469</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.35">
@@ -6830,22 +6657,22 @@
         <v>118</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F179" s="1">
         <v>470</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.35">
@@ -6853,22 +6680,22 @@
         <v>119</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F180" s="1">
         <v>471</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.35">
@@ -6876,22 +6703,22 @@
         <v>120</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F181" s="1">
         <v>472</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.35">
@@ -6899,19 +6726,19 @@
         <v>121</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F182" s="1">
         <v>473</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.35">
@@ -6919,19 +6746,19 @@
         <v>122</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F183" s="1">
         <v>474</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.35">
@@ -6939,19 +6766,19 @@
         <v>123</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F184" s="1">
         <v>475</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.35">
@@ -6959,19 +6786,19 @@
         <v>124</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F185" s="1">
         <v>476</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.35">
@@ -6979,19 +6806,19 @@
         <v>125</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F186" s="1">
         <v>477</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.35">
@@ -6999,19 +6826,19 @@
         <v>126</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F187" s="1">
         <v>478</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.35">
@@ -7019,22 +6846,22 @@
         <v>127</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F188" s="1">
         <v>479</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.35">
@@ -7042,22 +6869,22 @@
         <v>128</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F189" s="1">
         <v>480</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.35">
@@ -7065,22 +6892,22 @@
         <v>129</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F190" s="1">
         <v>481</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.35">
@@ -7088,22 +6915,22 @@
         <v>130</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F191" s="1">
         <v>482</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.35">
@@ -7111,22 +6938,22 @@
         <v>131</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F192" s="1">
         <v>483</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.35">
@@ -7134,22 +6961,22 @@
         <v>132</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F193" s="1">
         <v>484</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.35">
@@ -7157,19 +6984,19 @@
         <v>133</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F194" s="1">
         <v>485</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
@@ -7177,19 +7004,19 @@
         <v>134</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F195" s="1">
         <v>486</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
@@ -7197,19 +7024,19 @@
         <v>135</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F196" s="1">
         <v>487</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
@@ -7217,19 +7044,19 @@
         <v>136</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F197" s="1">
         <v>488</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
@@ -7237,19 +7064,19 @@
         <v>137</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F198" s="1">
         <v>489</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
@@ -7257,19 +7084,19 @@
         <v>138</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F199" s="1">
         <v>490</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
@@ -7277,22 +7104,22 @@
         <v>139</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F200" s="1">
         <v>491</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="N200" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.35">
@@ -7300,22 +7127,22 @@
         <v>140</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F201" s="1">
         <v>492</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="N201" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.35">
@@ -7323,22 +7150,22 @@
         <v>141</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F202" s="1">
         <v>493</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="N202" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.35">
@@ -7346,22 +7173,22 @@
         <v>142</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F203" s="1">
         <v>494</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="N203" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.35">
@@ -7369,22 +7196,22 @@
         <v>143</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F204" s="1">
         <v>495</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="N204" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.35">
@@ -7392,22 +7219,22 @@
         <v>144</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F205" s="1">
         <v>496</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="N205" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.35">
@@ -7415,19 +7242,19 @@
         <v>145</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F206" s="1">
         <v>497</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
@@ -7435,19 +7262,19 @@
         <v>146</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F207" s="1">
         <v>498</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
@@ -7455,19 +7282,19 @@
         <v>147</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F208" s="1">
         <v>499</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
@@ -7475,19 +7302,19 @@
         <v>148</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F209" s="1">
         <v>500</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.35">
@@ -7495,19 +7322,19 @@
         <v>149</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F210" s="1">
         <v>501</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
@@ -7515,30 +7342,30 @@
         <v>150</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F211" s="1">
         <v>502</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C212" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F212" s="1">
         <v>801</v>
@@ -7546,13 +7373,13 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="C213" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F213" s="1">
         <v>802</v>
@@ -7560,13 +7387,13 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="C214" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F214" s="1">
         <v>803</v>
@@ -7577,10 +7404,10 @@
     </row>
     <row r="215" spans="1:10" ht="15" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B215" s="7" t="s">
         <v>682</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>683</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>153</v>
@@ -7591,10 +7418,10 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>153</v>
@@ -7605,10 +7432,10 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>153</v>
@@ -7619,10 +7446,10 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>153</v>
@@ -7633,10 +7460,10 @@
     </row>
     <row r="219" spans="1:10" ht="15" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B219" s="7" t="s">
         <v>684</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>685</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>153</v>
@@ -7647,10 +7474,10 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>153</v>
@@ -7661,10 +7488,10 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>153</v>
@@ -7675,10 +7502,10 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>153</v>
@@ -7689,10 +7516,10 @@
     </row>
     <row r="223" spans="1:10" ht="15" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B223" s="7" t="s">
         <v>686</v>
-      </c>
-      <c r="B223" s="7" t="s">
-        <v>687</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>153</v>
@@ -7703,10 +7530,10 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>153</v>
@@ -7715,12 +7542,12 @@
         <v>830</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>153</v>
@@ -7729,12 +7556,12 @@
         <v>831</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>153</v>
@@ -7743,12 +7570,12 @@
         <v>832</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>153</v>
@@ -7757,12 +7584,12 @@
         <v>833</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>153</v>
@@ -7771,12 +7598,12 @@
         <v>834</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>153</v>
@@ -7785,12 +7612,12 @@
         <v>835</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>153</v>
@@ -7799,12 +7626,12 @@
         <v>836</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>153</v>
@@ -7813,12 +7640,12 @@
         <v>837</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>153</v>
@@ -7827,12 +7654,12 @@
         <v>838</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>153</v>
@@ -7841,12 +7668,12 @@
         <v>839</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>153</v>
@@ -7855,12 +7682,12 @@
         <v>840</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>153</v>
@@ -7869,35 +7696,35 @@
         <v>841</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="C236" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E236" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="F236" s="1">
         <v>999</v>
       </c>
     </row>
-    <row r="237" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A237" s="9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>688</v>
+        <v>861</v>
       </c>
       <c r="C237" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E237" s="9" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F237" s="9">
         <v>999</v>
@@ -7906,19 +7733,22 @@
         <f>MID(A237,3,4)</f>
         <v>fblt</v>
       </c>
-    </row>
-    <row r="238" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O237" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A238" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>689</v>
+        <v>862</v>
       </c>
       <c r="C238" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E238" s="9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F238" s="9">
         <v>999</v>
@@ -7927,19 +7757,22 @@
         <f t="shared" ref="J238:J285" si="0">MID(A238,3,4)</f>
         <v>frng</v>
       </c>
-    </row>
-    <row r="239" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O238" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>690</v>
+        <v>863</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E239" s="9" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F239" s="9">
         <v>999</v>
@@ -7948,19 +7781,22 @@
         <f t="shared" si="0"/>
         <v>finf</v>
       </c>
-    </row>
-    <row r="240" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O239" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>691</v>
+        <v>868</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F240" s="9">
         <v>999</v>
@@ -7969,19 +7805,22 @@
         <f t="shared" si="0"/>
         <v>fbal</v>
       </c>
-    </row>
-    <row r="241" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O240" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>692</v>
+        <v>870</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>728</v>
+        <v>883</v>
       </c>
       <c r="F241" s="9">
         <v>999</v>
@@ -7990,19 +7829,22 @@
         <f t="shared" si="0"/>
         <v>fbls</v>
       </c>
-    </row>
-    <row r="242" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O241" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A242" s="9" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>729</v>
+        <v>871</v>
       </c>
       <c r="C242" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F242" s="9">
         <v>999</v>
@@ -8011,19 +7853,22 @@
         <f t="shared" si="0"/>
         <v>fbls</v>
       </c>
-    </row>
-    <row r="243" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O242" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>693</v>
+        <v>876</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="F243" s="9">
         <v>999</v>
@@ -8032,19 +7877,22 @@
         <f t="shared" si="0"/>
         <v>fwal</v>
       </c>
-    </row>
-    <row r="244" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O243" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>732</v>
+        <v>877</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E244" s="9" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="F244" s="9">
         <v>999</v>
@@ -8053,19 +7901,22 @@
         <f t="shared" si="0"/>
         <v>fwal</v>
       </c>
-    </row>
-    <row r="245" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O244" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A245" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>694</v>
+        <v>864</v>
       </c>
       <c r="C245" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="F245" s="10">
         <v>999</v>
@@ -8074,19 +7925,22 @@
         <f t="shared" si="0"/>
         <v>tchm</v>
       </c>
-    </row>
-    <row r="246" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O245" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A246" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>695</v>
+        <v>865</v>
       </c>
       <c r="C246" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>735</v>
+        <v>882</v>
       </c>
       <c r="F246" s="10">
         <v>999</v>
@@ -8095,19 +7949,22 @@
         <f t="shared" si="0"/>
         <v>tblt</v>
       </c>
-    </row>
-    <row r="247" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O246" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A247" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>696</v>
+        <v>866</v>
       </c>
       <c r="C247" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F247" s="10">
         <v>999</v>
@@ -8116,19 +7973,22 @@
         <f t="shared" si="0"/>
         <v>tltn</v>
       </c>
-    </row>
-    <row r="248" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O247" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A248" s="10" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>737</v>
+        <v>867</v>
       </c>
       <c r="C248" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E248" s="10" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="F248" s="10">
         <v>999</v>
@@ -8137,19 +7997,22 @@
         <f t="shared" si="0"/>
         <v>tltn</v>
       </c>
-    </row>
-    <row r="249" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O248" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>697</v>
+        <v>869</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>739</v>
+        <v>881</v>
       </c>
       <c r="F249" s="10">
         <v>999</v>
@@ -8158,19 +8021,22 @@
         <f t="shared" si="0"/>
         <v>tnov</v>
       </c>
-    </row>
-    <row r="250" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O249" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>698</v>
+        <v>872</v>
       </c>
       <c r="C250" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>740</v>
+        <v>879</v>
       </c>
       <c r="F250" s="10">
         <v>999</v>
@@ -8179,19 +8045,22 @@
         <f t="shared" si="0"/>
         <v>tshd</v>
       </c>
-    </row>
-    <row r="251" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O250" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>741</v>
+        <v>873</v>
       </c>
       <c r="C251" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>742</v>
+        <v>880</v>
       </c>
       <c r="F251" s="10">
         <v>999</v>
@@ -8200,19 +8069,22 @@
         <f t="shared" si="0"/>
         <v>tshd</v>
       </c>
-    </row>
-    <row r="252" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O251" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>786</v>
+        <v>874</v>
       </c>
       <c r="C252" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>743</v>
+        <v>878</v>
       </c>
       <c r="F252" s="10">
         <v>999</v>
@@ -8221,19 +8093,22 @@
         <f t="shared" si="0"/>
         <v>tblz</v>
       </c>
-    </row>
-    <row r="253" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O252" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>744</v>
+        <v>875</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="F253" s="10">
         <v>999</v>
@@ -8242,19 +8117,22 @@
         <f t="shared" si="0"/>
         <v>tblz</v>
       </c>
-    </row>
-    <row r="254" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O253" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B254" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C254" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E254" s="11" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="F254" s="11">
         <v>999</v>
@@ -8263,19 +8141,22 @@
         <f t="shared" si="0"/>
         <v>bbas</v>
       </c>
-    </row>
-    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O254" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A255" s="11" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C255" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E255" s="11" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="F255" s="11">
         <v>999</v>
@@ -8284,19 +8165,22 @@
         <f t="shared" si="0"/>
         <v>bcrt</v>
       </c>
-    </row>
-    <row r="256" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O255" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A256" s="11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C256" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="F256" s="11">
         <v>999</v>
@@ -8305,19 +8189,22 @@
         <f t="shared" si="0"/>
         <v>bthr</v>
       </c>
-    </row>
-    <row r="257" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O256" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A257" s="11" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E257" s="11" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="F257" s="11">
         <v>999</v>
@@ -8326,19 +8213,22 @@
         <f t="shared" si="0"/>
         <v>bclv</v>
       </c>
-    </row>
-    <row r="258" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O257" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A258" s="11" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E258" s="11" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="F258" s="11">
         <v>999</v>
@@ -8347,19 +8237,22 @@
         <f t="shared" si="0"/>
         <v>bcrz</v>
       </c>
-    </row>
-    <row r="259" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O258" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="11" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E259" s="11" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="F259" s="11">
         <v>999</v>
@@ -8368,19 +8261,22 @@
         <f t="shared" si="0"/>
         <v>bcrz</v>
       </c>
-    </row>
-    <row r="260" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O259" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A260" s="11" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>705</v>
+        <v>860</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="F260" s="11">
         <v>999</v>
@@ -8390,21 +8286,24 @@
         <v>bfbl</v>
       </c>
       <c r="K260" s="11" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.35">
+        <v>795</v>
+      </c>
+      <c r="O260" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A261" s="11" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E261" s="11" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="F261" s="11">
         <v>999</v>
@@ -8414,21 +8313,24 @@
         <v>bfbl</v>
       </c>
       <c r="K261" s="11" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="262" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+        <v>796</v>
+      </c>
+      <c r="O261" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A262" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B262" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C262" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E262" s="12" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="F262" s="12">
         <v>999</v>
@@ -8437,19 +8339,22 @@
         <f t="shared" si="0"/>
         <v>xdef</v>
       </c>
-    </row>
-    <row r="263" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O262" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A263" s="12" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B263" s="12" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C263" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E263" s="12" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="F263" s="12">
         <v>999</v>
@@ -8458,19 +8363,22 @@
         <f t="shared" si="0"/>
         <v>xdog</v>
       </c>
-    </row>
-    <row r="264" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O263" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A264" s="12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B264" s="12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C264" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E264" s="12" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="F264" s="12">
         <v>999</v>
@@ -8479,19 +8387,22 @@
         <f t="shared" si="0"/>
         <v>xcta</v>
       </c>
-    </row>
-    <row r="265" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O264" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A265" s="12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B265" s="12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C265" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E265" s="12" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="F265" s="12">
         <v>999</v>
@@ -8500,19 +8411,22 @@
         <f t="shared" si="0"/>
         <v>xwms</v>
       </c>
-    </row>
-    <row r="266" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O265" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A266" s="12" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B266" s="12" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C266" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E266" s="12" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="F266" s="12">
         <v>999</v>
@@ -8521,19 +8435,22 @@
         <f t="shared" si="0"/>
         <v>xchg</v>
       </c>
-    </row>
-    <row r="267" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O266" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A267" s="12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C267" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E267" s="12" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="F267" s="12">
         <v>999</v>
@@ -8542,19 +8459,22 @@
         <f t="shared" si="0"/>
         <v>xtst</v>
       </c>
-    </row>
-    <row r="268" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O267" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="12" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="B268" s="12" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="C268" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E268" s="12" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="F268" s="12">
         <v>999</v>
@@ -8563,19 +8483,22 @@
         <f t="shared" si="0"/>
         <v>xtst</v>
       </c>
-    </row>
-    <row r="269" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O268" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C269" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E269" s="6" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F269" s="6">
         <v>999</v>
@@ -8584,19 +8507,22 @@
         <f t="shared" si="0"/>
         <v>hhel</v>
       </c>
-    </row>
-    <row r="270" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O269" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="6" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="C270" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="F270" s="6">
         <v>999</v>
@@ -8605,19 +8531,22 @@
         <f t="shared" si="0"/>
         <v>hhel</v>
       </c>
-    </row>
-    <row r="271" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O270" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C271" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="F271" s="6">
         <v>999</v>
@@ -8626,19 +8555,22 @@
         <f t="shared" si="0"/>
         <v>hgsd</v>
       </c>
-    </row>
-    <row r="272" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O271" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A272" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C272" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="F272" s="6">
         <v>999</v>
@@ -8647,19 +8579,22 @@
         <f t="shared" si="0"/>
         <v>hinv</v>
       </c>
-    </row>
-    <row r="273" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O272" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C273" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="F273" s="6">
         <v>999</v>
@@ -8668,19 +8603,22 @@
         <f t="shared" si="0"/>
         <v>hhsd</v>
       </c>
-    </row>
-    <row r="274" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O273" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A274" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C274" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="F274" s="6">
         <v>999</v>
@@ -8689,19 +8627,22 @@
         <f t="shared" si="0"/>
         <v>hlok</v>
       </c>
-    </row>
-    <row r="275" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O274" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A275" s="6" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="C275" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="F275" s="6">
         <v>999</v>
@@ -8710,19 +8651,22 @@
         <f t="shared" si="0"/>
         <v>hlok</v>
       </c>
-    </row>
-    <row r="276" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O275" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A276" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C276" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="F276" s="6">
         <v>999</v>
@@ -8731,19 +8675,22 @@
         <f t="shared" si="0"/>
         <v>hmhl</v>
       </c>
-    </row>
-    <row r="277" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O276" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A277" s="6" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="C277" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="F277" s="6">
         <v>999</v>
@@ -8752,19 +8699,22 @@
         <f t="shared" si="0"/>
         <v>hmhl</v>
       </c>
-    </row>
-    <row r="278" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O277" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E278" s="4" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="F278" s="4">
         <v>999</v>
@@ -8773,19 +8723,22 @@
         <f t="shared" si="0"/>
         <v>pbas</v>
       </c>
-    </row>
-    <row r="279" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O278" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E279" s="4" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="F279" s="4">
         <v>999</v>
@@ -8794,19 +8747,22 @@
         <f t="shared" si="0"/>
         <v>ppoi</v>
       </c>
-    </row>
-    <row r="280" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O279" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="F280" s="4">
         <v>999</v>
@@ -8816,21 +8772,24 @@
         <v>pskl</v>
       </c>
       <c r="K280" s="4" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="281" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>797</v>
+      </c>
+      <c r="O280" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C281" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E281" s="4" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="F281" s="4">
         <v>999</v>
@@ -8839,19 +8798,22 @@
         <f t="shared" si="0"/>
         <v>prun</v>
       </c>
-    </row>
-    <row r="282" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O281" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E282" s="4" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="F282" s="4">
         <v>999</v>
@@ -8860,19 +8822,22 @@
         <f t="shared" si="0"/>
         <v>pcbl</v>
       </c>
-    </row>
-    <row r="283" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O282" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E283" s="4" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="F283" s="4">
         <v>999</v>
@@ -8881,19 +8846,22 @@
         <f t="shared" si="0"/>
         <v>pcbl</v>
       </c>
-    </row>
-    <row r="284" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O283" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E284" s="4" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="F284" s="4">
         <v>999</v>
@@ -8903,21 +8871,24 @@
         <v>psdm</v>
       </c>
       <c r="K284" s="4" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="285" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>798</v>
+      </c>
+      <c r="O284" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E285" s="4" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="F285" s="4">
         <v>999</v>
@@ -8926,32 +8897,14 @@
         <f t="shared" si="0"/>
         <v>psdm</v>
       </c>
+      <c r="O285" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B238">
-    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="21" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B240:B241 B243 B245:B247 B249:B285">
-    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B244">
-    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B248">
-    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE430C4B-1241-4FB1-AEE2-05BEB92A683C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92728DF6-8796-4381-8804-3BCD468362E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="885">
   <si>
     <t>id</t>
   </si>
@@ -2684,9 +2684,6 @@
     <t>21火骷髅剑</t>
   </si>
   <si>
-    <t>21聋哑</t>
-  </si>
-  <si>
     <t>28魔杖</t>
   </si>
   <si>
@@ -2727,6 +2724,12 @@
   </si>
   <si>
     <t>爆裂火焰使目标身上的点燃效果立即造成全额伤害</t>
+  </si>
+  <si>
+    <t>21渡劫刻印</t>
+  </si>
+  <si>
+    <t>1浮屠</t>
   </si>
 </sst>
 </file>
@@ -3202,20 +3205,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
   <dimension ref="A1:O285"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="51.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3262,7 +3266,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -3309,12 +3313,12 @@
         <v>858</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>320</v>
       </c>
@@ -3361,7 +3365,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>393</v>
       </c>
@@ -3378,7 +3382,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>394</v>
       </c>
@@ -3395,7 +3399,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>395</v>
       </c>
@@ -3412,7 +3416,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>396</v>
       </c>
@@ -3429,7 +3433,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3446,7 +3450,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3463,7 +3467,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3486,7 +3490,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3509,7 +3513,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3526,7 +3530,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3543,7 +3547,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3566,7 +3570,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -3589,7 +3593,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3606,7 +3610,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -3623,7 +3627,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -3640,7 +3644,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -3657,7 +3661,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>409</v>
       </c>
@@ -3674,7 +3678,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>663</v>
       </c>
@@ -3691,7 +3695,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>664</v>
       </c>
@@ -3708,7 +3712,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>279</v>
       </c>
@@ -3725,7 +3729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>280</v>
       </c>
@@ -3742,7 +3746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>281</v>
       </c>
@@ -3759,7 +3763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>282</v>
       </c>
@@ -3776,7 +3780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>283</v>
       </c>
@@ -3793,7 +3797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>445</v>
       </c>
@@ -3810,7 +3814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>446</v>
       </c>
@@ -3827,7 +3831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>447</v>
       </c>
@@ -3844,7 +3848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>448</v>
       </c>
@@ -3861,7 +3865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>449</v>
       </c>
@@ -3878,7 +3882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>450</v>
       </c>
@@ -3895,7 +3899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>451</v>
       </c>
@@ -3912,7 +3916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>452</v>
       </c>
@@ -3929,7 +3933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>453</v>
       </c>
@@ -3946,7 +3950,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>454</v>
       </c>
@@ -3963,7 +3967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -3980,7 +3984,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -3997,7 +4001,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -4014,7 +4018,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -4031,7 +4035,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -4048,7 +4052,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -4065,7 +4069,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -4082,7 +4086,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -4099,7 +4103,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -4116,7 +4120,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -4133,7 +4137,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
@@ -4150,7 +4154,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
@@ -4167,7 +4171,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -4184,7 +4188,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
@@ -4201,7 +4205,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
@@ -4218,7 +4222,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>411</v>
       </c>
@@ -4235,7 +4239,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>412</v>
       </c>
@@ -4252,7 +4256,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>413</v>
       </c>
@@ -4269,7 +4273,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -4286,7 +4290,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -4303,7 +4307,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -4320,7 +4324,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -4337,7 +4341,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -4354,7 +4358,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -4374,7 +4378,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
@@ -4394,7 +4398,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
@@ -4414,7 +4418,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>398</v>
       </c>
@@ -4434,7 +4438,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>399</v>
       </c>
@@ -4454,7 +4458,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>405</v>
       </c>
@@ -4474,7 +4478,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>403</v>
       </c>
@@ -4491,7 +4495,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -4508,7 +4512,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
@@ -4525,7 +4529,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -4542,7 +4546,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -4559,7 +4563,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -4576,7 +4580,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
@@ -4599,7 +4603,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -4622,7 +4626,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -4645,7 +4649,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -4668,7 +4672,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
@@ -4691,7 +4695,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>392</v>
       </c>
@@ -4708,7 +4712,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -4725,7 +4729,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -4742,7 +4746,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -4759,7 +4763,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -4776,7 +4780,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>309</v>
       </c>
@@ -4793,7 +4797,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>310</v>
       </c>
@@ -4810,7 +4814,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>311</v>
       </c>
@@ -4827,7 +4831,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>312</v>
       </c>
@@ -4844,7 +4848,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>313</v>
       </c>
@@ -4861,7 +4865,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -4878,7 +4882,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -4895,7 +4899,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -4912,7 +4916,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -4929,7 +4933,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -4946,7 +4950,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>419</v>
       </c>
@@ -4963,7 +4967,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>660</v>
       </c>
@@ -4980,7 +4984,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -4997,7 +5001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>472</v>
       </c>
@@ -5014,7 +5018,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>675</v>
       </c>
@@ -5031,7 +5035,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>407</v>
       </c>
@@ -5048,7 +5052,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>380</v>
       </c>
@@ -5062,7 +5066,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>382</v>
       </c>
@@ -5076,7 +5080,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>784</v>
       </c>
@@ -5093,7 +5097,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>46</v>
       </c>
@@ -5110,7 +5114,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>47</v>
       </c>
@@ -5127,7 +5131,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>48</v>
       </c>
@@ -5144,7 +5148,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>277</v>
       </c>
@@ -5161,7 +5165,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>293</v>
       </c>
@@ -5178,7 +5182,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>294</v>
       </c>
@@ -5195,7 +5199,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>295</v>
       </c>
@@ -5212,7 +5216,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>296</v>
       </c>
@@ -5229,7 +5233,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>72</v>
       </c>
@@ -5246,7 +5250,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>678</v>
       </c>
@@ -5263,7 +5267,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>669</v>
       </c>
@@ -5280,7 +5284,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>672</v>
       </c>
@@ -5297,7 +5301,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>388</v>
       </c>
@@ -5314,7 +5318,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>389</v>
       </c>
@@ -5331,7 +5335,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>443</v>
       </c>
@@ -5348,7 +5352,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>59</v>
       </c>
@@ -5368,7 +5372,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>60</v>
       </c>
@@ -5388,7 +5392,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>61</v>
       </c>
@@ -5408,7 +5412,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>420</v>
       </c>
@@ -5431,7 +5435,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>421</v>
       </c>
@@ -5454,7 +5458,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>654</v>
       </c>
@@ -5477,7 +5481,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>62</v>
       </c>
@@ -5497,7 +5501,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>63</v>
       </c>
@@ -5517,7 +5521,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>64</v>
       </c>
@@ -5537,7 +5541,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>422</v>
       </c>
@@ -5560,7 +5564,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>423</v>
       </c>
@@ -5583,7 +5587,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>655</v>
       </c>
@@ -5606,7 +5610,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>65</v>
       </c>
@@ -5626,7 +5630,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>66</v>
       </c>
@@ -5646,7 +5650,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>67</v>
       </c>
@@ -5666,7 +5670,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>424</v>
       </c>
@@ -5689,7 +5693,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>425</v>
       </c>
@@ -5712,7 +5716,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>657</v>
       </c>
@@ -5735,7 +5739,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>68</v>
       </c>
@@ -5755,7 +5759,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>69</v>
       </c>
@@ -5775,7 +5779,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>70</v>
       </c>
@@ -5795,7 +5799,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,7 +5813,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>79</v>
       </c>
@@ -5832,7 +5836,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>80</v>
       </c>
@@ -5855,7 +5859,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>81</v>
       </c>
@@ -5878,7 +5882,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>82</v>
       </c>
@@ -5901,7 +5905,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>83</v>
       </c>
@@ -5924,7 +5928,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>84</v>
       </c>
@@ -5947,7 +5951,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>85</v>
       </c>
@@ -5967,7 +5971,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>86</v>
       </c>
@@ -5987,7 +5991,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>87</v>
       </c>
@@ -6007,7 +6011,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>88</v>
       </c>
@@ -6027,7 +6031,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>89</v>
       </c>
@@ -6047,7 +6051,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>90</v>
       </c>
@@ -6067,7 +6071,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>91</v>
       </c>
@@ -6090,7 +6094,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>92</v>
       </c>
@@ -6113,7 +6117,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>93</v>
       </c>
@@ -6136,7 +6140,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>94</v>
       </c>
@@ -6159,7 +6163,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>95</v>
       </c>
@@ -6182,7 +6186,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>96</v>
       </c>
@@ -6205,7 +6209,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>97</v>
       </c>
@@ -6225,7 +6229,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>98</v>
       </c>
@@ -6245,7 +6249,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>99</v>
       </c>
@@ -6265,7 +6269,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>100</v>
       </c>
@@ -6285,7 +6289,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>101</v>
       </c>
@@ -6305,7 +6309,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>102</v>
       </c>
@@ -6325,7 +6329,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>103</v>
       </c>
@@ -6348,7 +6352,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>104</v>
       </c>
@@ -6371,7 +6375,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>105</v>
       </c>
@@ -6394,7 +6398,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>106</v>
       </c>
@@ -6417,7 +6421,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>107</v>
       </c>
@@ -6440,7 +6444,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>108</v>
       </c>
@@ -6463,7 +6467,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>109</v>
       </c>
@@ -6483,7 +6487,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>110</v>
       </c>
@@ -6503,7 +6507,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>111</v>
       </c>
@@ -6523,7 +6527,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>112</v>
       </c>
@@ -6543,7 +6547,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>113</v>
       </c>
@@ -6563,7 +6567,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>114</v>
       </c>
@@ -6583,7 +6587,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>115</v>
       </c>
@@ -6606,7 +6610,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>116</v>
       </c>
@@ -6629,7 +6633,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>117</v>
       </c>
@@ -6652,7 +6656,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>118</v>
       </c>
@@ -6675,7 +6679,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>119</v>
       </c>
@@ -6698,7 +6702,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>120</v>
       </c>
@@ -6721,7 +6725,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>121</v>
       </c>
@@ -6741,7 +6745,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>122</v>
       </c>
@@ -6761,7 +6765,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>123</v>
       </c>
@@ -6781,7 +6785,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>124</v>
       </c>
@@ -6801,7 +6805,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>125</v>
       </c>
@@ -6821,7 +6825,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>126</v>
       </c>
@@ -6841,7 +6845,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>127</v>
       </c>
@@ -6864,7 +6868,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>128</v>
       </c>
@@ -6887,7 +6891,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>129</v>
       </c>
@@ -6910,7 +6914,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>130</v>
       </c>
@@ -6933,7 +6937,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>131</v>
       </c>
@@ -6956,7 +6960,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>132</v>
       </c>
@@ -6979,7 +6983,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>133</v>
       </c>
@@ -6999,7 +7003,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>134</v>
       </c>
@@ -7019,7 +7023,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>135</v>
       </c>
@@ -7039,7 +7043,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>136</v>
       </c>
@@ -7059,7 +7063,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>137</v>
       </c>
@@ -7079,7 +7083,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>138</v>
       </c>
@@ -7099,7 +7103,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>139</v>
       </c>
@@ -7122,7 +7126,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>140</v>
       </c>
@@ -7145,7 +7149,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>141</v>
       </c>
@@ -7168,7 +7172,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>142</v>
       </c>
@@ -7191,7 +7195,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>143</v>
       </c>
@@ -7214,7 +7218,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>144</v>
       </c>
@@ -7237,7 +7241,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>145</v>
       </c>
@@ -7257,7 +7261,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>146</v>
       </c>
@@ -7277,7 +7281,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>147</v>
       </c>
@@ -7297,7 +7301,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>148</v>
       </c>
@@ -7317,7 +7321,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>149</v>
       </c>
@@ -7337,7 +7341,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>150</v>
       </c>
@@ -7357,7 +7361,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>384</v>
       </c>
@@ -7371,7 +7375,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>386</v>
       </c>
@@ -7385,7 +7389,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>427</v>
       </c>
@@ -7402,7 +7406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>681</v>
       </c>
@@ -7416,7 +7420,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>319</v>
       </c>
@@ -7430,7 +7434,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>346</v>
       </c>
@@ -7444,7 +7448,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>348</v>
       </c>
@@ -7458,7 +7462,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>683</v>
       </c>
@@ -7472,7 +7476,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>350</v>
       </c>
@@ -7486,7 +7490,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>351</v>
       </c>
@@ -7500,7 +7504,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>352</v>
       </c>
@@ -7514,7 +7518,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>685</v>
       </c>
@@ -7528,7 +7532,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>356</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>357</v>
       </c>
@@ -7556,7 +7560,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>358</v>
       </c>
@@ -7570,7 +7574,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>362</v>
       </c>
@@ -7584,7 +7588,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>364</v>
       </c>
@@ -7598,7 +7602,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>365</v>
       </c>
@@ -7612,7 +7616,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>368</v>
       </c>
@@ -7626,7 +7630,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>369</v>
       </c>
@@ -7640,7 +7644,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>370</v>
       </c>
@@ -7654,7 +7658,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>371</v>
       </c>
@@ -7668,7 +7672,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>376</v>
       </c>
@@ -7682,7 +7686,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>378</v>
       </c>
@@ -7696,7 +7700,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>465</v>
       </c>
@@ -7713,7 +7717,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="237" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
         <v>687</v>
       </c>
@@ -7737,7 +7741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
         <v>688</v>
       </c>
@@ -7761,7 +7765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>689</v>
       </c>
@@ -7785,7 +7789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
         <v>690</v>
       </c>
@@ -7809,18 +7813,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
         <v>691</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F241" s="9">
         <v>999</v>
@@ -7833,12 +7837,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
         <v>727</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C242" s="9" t="s">
         <v>153</v>
@@ -7857,12 +7861,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
         <v>692</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>153</v>
@@ -7881,12 +7885,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
         <v>730</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>153</v>
@@ -7905,7 +7909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
         <v>693</v>
       </c>
@@ -7929,7 +7933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
         <v>694</v>
       </c>
@@ -7940,7 +7944,7 @@
         <v>153</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F246" s="10">
         <v>999</v>
@@ -7953,7 +7957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
         <v>695</v>
       </c>
@@ -7977,7 +7981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
         <v>734</v>
       </c>
@@ -8001,18 +8005,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
         <v>696</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>869</v>
+        <v>883</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F249" s="10">
         <v>999</v>
@@ -8025,18 +8029,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
         <v>697</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C250" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F250" s="10">
         <v>999</v>
@@ -8049,18 +8053,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
         <v>736</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C251" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F251" s="10">
         <v>999</v>
@@ -8073,18 +8077,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
         <v>698</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C252" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F252" s="10">
         <v>999</v>
@@ -8097,12 +8101,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
         <v>737</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>153</v>
@@ -8121,12 +8125,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
         <v>699</v>
       </c>
       <c r="B254" s="11" t="s">
-        <v>699</v>
+        <v>884</v>
       </c>
       <c r="C254" s="11" t="s">
         <v>153</v>
@@ -8145,7 +8149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>700</v>
       </c>
@@ -8169,7 +8173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
         <v>701</v>
       </c>
@@ -8193,7 +8197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>702</v>
       </c>
@@ -8217,7 +8221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
         <v>703</v>
       </c>
@@ -8241,7 +8245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="11" t="s">
         <v>744</v>
       </c>
@@ -8265,7 +8269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>704</v>
       </c>
@@ -8292,7 +8296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
         <v>747</v>
       </c>
@@ -8319,7 +8323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
         <v>705</v>
       </c>
@@ -8343,7 +8347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
         <v>706</v>
       </c>
@@ -8367,7 +8371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
         <v>707</v>
       </c>
@@ -8391,7 +8395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
         <v>708</v>
       </c>
@@ -8415,7 +8419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
         <v>709</v>
       </c>
@@ -8439,7 +8443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
         <v>710</v>
       </c>
@@ -8463,7 +8467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
         <v>755</v>
       </c>
@@ -8487,7 +8491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
         <v>711</v>
       </c>
@@ -8511,7 +8515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
         <v>757</v>
       </c>
@@ -8535,7 +8539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
         <v>712</v>
       </c>
@@ -8559,7 +8563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
         <v>713</v>
       </c>
@@ -8583,7 +8587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
         <v>714</v>
       </c>
@@ -8607,7 +8611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
         <v>715</v>
       </c>
@@ -8631,7 +8635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
         <v>764</v>
       </c>
@@ -8655,7 +8659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
         <v>716</v>
       </c>
@@ -8679,7 +8683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
         <v>766</v>
       </c>
@@ -8703,7 +8707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>717</v>
       </c>
@@ -8727,7 +8731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
         <v>718</v>
       </c>
@@ -8751,7 +8755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>719</v>
       </c>
@@ -8778,7 +8782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>720</v>
       </c>
@@ -8802,7 +8806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>721</v>
       </c>
@@ -8826,7 +8830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
         <v>774</v>
       </c>
@@ -8850,7 +8854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
         <v>722</v>
       </c>
@@ -8877,7 +8881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>777</v>
       </c>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92728DF6-8796-4381-8804-3BCD468362E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3B1E7B-B5FD-4BC0-83F3-658DD70B9EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="887">
   <si>
     <t>id</t>
   </si>
@@ -2457,10 +2457,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>holy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>psyco</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2730,6 +2726,15 @@
   </si>
   <si>
     <t>1浮屠</t>
+  </si>
+  <si>
+    <t>7八荒</t>
+  </si>
+  <si>
+    <t>14凌风</t>
+  </si>
+  <si>
+    <t>holy,hdmg</t>
   </si>
 </sst>
 </file>
@@ -3254,16 +3259,16 @@
         <v>793</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -3289,7 +3294,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>788</v>
@@ -3298,19 +3303,19 @@
         <v>791</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -3353,16 +3358,16 @@
         <v>794</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -5369,7 +5374,7 @@
         <v>401</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
@@ -5389,7 +5394,7 @@
         <v>402</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
@@ -5409,7 +5414,7 @@
         <v>403</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
@@ -5429,10 +5434,10 @@
         <v>404</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
@@ -5452,10 +5457,10 @@
         <v>405</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
@@ -5475,10 +5480,10 @@
         <v>406</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
@@ -5498,7 +5503,7 @@
         <v>407</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
@@ -5518,7 +5523,7 @@
         <v>408</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
@@ -5538,7 +5543,7 @@
         <v>409</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
@@ -5558,10 +5563,10 @@
         <v>410</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
@@ -5581,10 +5586,10 @@
         <v>411</v>
       </c>
       <c r="L128" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="N128" s="1" t="s">
         <v>844</v>
-      </c>
-      <c r="N128" s="1" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
@@ -5604,10 +5609,10 @@
         <v>412</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
@@ -5627,7 +5632,7 @@
         <v>413</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
@@ -5647,7 +5652,7 @@
         <v>414</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -5667,7 +5672,7 @@
         <v>415</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
@@ -5687,10 +5692,10 @@
         <v>416</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
@@ -5710,10 +5715,10 @@
         <v>417</v>
       </c>
       <c r="L134" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="N134" s="1" t="s">
         <v>847</v>
-      </c>
-      <c r="N134" s="1" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
@@ -5733,10 +5738,10 @@
         <v>418</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
@@ -5756,7 +5761,7 @@
         <v>419</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
@@ -5776,7 +5781,7 @@
         <v>420</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
@@ -5796,7 +5801,7 @@
         <v>421</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
@@ -5830,10 +5835,10 @@
         <v>431</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
@@ -5853,10 +5858,10 @@
         <v>432</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
@@ -5876,10 +5881,10 @@
         <v>433</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
@@ -5899,10 +5904,10 @@
         <v>434</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
@@ -5922,10 +5927,10 @@
         <v>435</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
@@ -5945,10 +5950,10 @@
         <v>436</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
@@ -5968,7 +5973,7 @@
         <v>437</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
@@ -5988,7 +5993,7 @@
         <v>438</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
@@ -6008,7 +6013,7 @@
         <v>439</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
@@ -6028,7 +6033,7 @@
         <v>440</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
@@ -6048,7 +6053,7 @@
         <v>441</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
@@ -6068,7 +6073,7 @@
         <v>442</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
@@ -6088,10 +6093,10 @@
         <v>443</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
@@ -6111,10 +6116,10 @@
         <v>444</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
@@ -6134,10 +6139,10 @@
         <v>445</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
@@ -6157,10 +6162,10 @@
         <v>446</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
@@ -6180,10 +6185,10 @@
         <v>447</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
@@ -6203,10 +6208,10 @@
         <v>448</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
@@ -6226,7 +6231,7 @@
         <v>449</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
@@ -6246,7 +6251,7 @@
         <v>450</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
@@ -6266,7 +6271,7 @@
         <v>451</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
@@ -6286,7 +6291,7 @@
         <v>452</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
@@ -6306,7 +6311,7 @@
         <v>453</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
@@ -6326,7 +6331,7 @@
         <v>454</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
@@ -6346,10 +6351,10 @@
         <v>455</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
@@ -6369,10 +6374,10 @@
         <v>456</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
@@ -6392,10 +6397,10 @@
         <v>457</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
@@ -6415,10 +6420,10 @@
         <v>458</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
@@ -6438,10 +6443,10 @@
         <v>459</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
@@ -6461,10 +6466,10 @@
         <v>460</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
@@ -6484,7 +6489,7 @@
         <v>461</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
@@ -6504,7 +6509,7 @@
         <v>462</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
@@ -6524,7 +6529,7 @@
         <v>463</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
@@ -6544,7 +6549,7 @@
         <v>464</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
@@ -6564,7 +6569,7 @@
         <v>465</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
@@ -6584,7 +6589,7 @@
         <v>466</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
@@ -6604,10 +6609,10 @@
         <v>467</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
@@ -6627,10 +6632,10 @@
         <v>468</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="N177" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
@@ -6650,10 +6655,10 @@
         <v>469</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
@@ -6673,10 +6678,10 @@
         <v>470</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
@@ -6696,10 +6701,10 @@
         <v>471</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
@@ -6719,10 +6724,10 @@
         <v>472</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
@@ -6742,7 +6747,7 @@
         <v>473</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
@@ -6762,7 +6767,7 @@
         <v>474</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
@@ -6782,7 +6787,7 @@
         <v>475</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
@@ -6802,7 +6807,7 @@
         <v>476</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
@@ -6822,7 +6827,7 @@
         <v>477</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
@@ -6842,7 +6847,7 @@
         <v>478</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
@@ -6862,10 +6867,10 @@
         <v>479</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
@@ -6885,10 +6890,10 @@
         <v>480</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
@@ -6908,10 +6913,10 @@
         <v>481</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
@@ -6931,10 +6936,10 @@
         <v>482</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
@@ -6954,10 +6959,10 @@
         <v>483</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
@@ -6977,10 +6982,10 @@
         <v>484</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
@@ -7000,7 +7005,7 @@
         <v>485</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
@@ -7020,7 +7025,7 @@
         <v>486</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -7040,7 +7045,7 @@
         <v>487</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
@@ -7060,7 +7065,7 @@
         <v>488</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
@@ -7080,7 +7085,7 @@
         <v>489</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
@@ -7100,7 +7105,7 @@
         <v>490</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
@@ -7120,10 +7125,10 @@
         <v>491</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="N200" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
@@ -7143,10 +7148,10 @@
         <v>492</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N201" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
@@ -7166,10 +7171,10 @@
         <v>493</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="N202" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
@@ -7189,10 +7194,10 @@
         <v>494</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N203" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
@@ -7212,10 +7217,10 @@
         <v>495</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="N204" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
@@ -7235,10 +7240,10 @@
         <v>496</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="N205" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
@@ -7258,7 +7263,7 @@
         <v>497</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
@@ -7278,7 +7283,7 @@
         <v>498</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
@@ -7298,7 +7303,7 @@
         <v>499</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -7318,7 +7323,7 @@
         <v>500</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -7338,7 +7343,7 @@
         <v>501</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -7358,7 +7363,7 @@
         <v>502</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -7722,7 +7727,7 @@
         <v>687</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C237" s="9" t="s">
         <v>153</v>
@@ -7746,7 +7751,7 @@
         <v>688</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C238" s="9" t="s">
         <v>153</v>
@@ -7770,7 +7775,7 @@
         <v>689</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>153</v>
@@ -7794,7 +7799,7 @@
         <v>690</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>153</v>
@@ -7818,13 +7823,13 @@
         <v>691</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F241" s="9">
         <v>999</v>
@@ -7842,7 +7847,7 @@
         <v>727</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C242" s="9" t="s">
         <v>153</v>
@@ -7866,7 +7871,7 @@
         <v>692</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>153</v>
@@ -7890,7 +7895,7 @@
         <v>730</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>153</v>
@@ -7914,7 +7919,7 @@
         <v>693</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C245" s="10" t="s">
         <v>153</v>
@@ -7938,13 +7943,13 @@
         <v>694</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C246" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F246" s="10">
         <v>999</v>
@@ -7962,7 +7967,7 @@
         <v>695</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C247" s="10" t="s">
         <v>153</v>
@@ -7986,7 +7991,7 @@
         <v>734</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C248" s="10" t="s">
         <v>153</v>
@@ -8010,13 +8015,13 @@
         <v>696</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F249" s="10">
         <v>999</v>
@@ -8034,13 +8039,13 @@
         <v>697</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C250" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F250" s="10">
         <v>999</v>
@@ -8058,13 +8063,13 @@
         <v>736</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C251" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F251" s="10">
         <v>999</v>
@@ -8082,13 +8087,13 @@
         <v>698</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C252" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F252" s="10">
         <v>999</v>
@@ -8106,7 +8111,7 @@
         <v>737</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>153</v>
@@ -8130,7 +8135,7 @@
         <v>699</v>
       </c>
       <c r="B254" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C254" s="11" t="s">
         <v>153</v>
@@ -8154,7 +8159,7 @@
         <v>700</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>700</v>
+        <v>884</v>
       </c>
       <c r="C255" s="11" t="s">
         <v>153</v>
@@ -8274,7 +8279,7 @@
         <v>704</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>153</v>
@@ -8290,7 +8295,7 @@
         <v>bfbl</v>
       </c>
       <c r="K260" s="11" t="s">
-        <v>795</v>
+        <v>886</v>
       </c>
       <c r="O260" s="11" t="b">
         <v>1</v>
@@ -8317,7 +8322,7 @@
         <v>bfbl</v>
       </c>
       <c r="K261" s="11" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O261" s="11" t="b">
         <v>1</v>
@@ -8376,7 +8381,7 @@
         <v>707</v>
       </c>
       <c r="B264" s="12" t="s">
-        <v>707</v>
+        <v>885</v>
       </c>
       <c r="C264" s="12" t="s">
         <v>153</v>
@@ -8776,7 +8781,7 @@
         <v>pskl</v>
       </c>
       <c r="K280" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O280" s="4" t="b">
         <v>1</v>
@@ -8875,7 +8880,7 @@
         <v>psdm</v>
       </c>
       <c r="K284" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="O284" s="4" t="b">
         <v>1</v>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3B1E7B-B5FD-4BC0-83F3-658DD70B9EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F50A8E-A55A-4D91-9651-67A7DC0BFA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="17970" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="915">
   <si>
     <t>id</t>
   </si>
@@ -2168,9 +2168,6 @@
     <t>skbclvm1</t>
   </si>
   <si>
-    <t>skbcrzm1</t>
-  </si>
-  <si>
     <t>skbfblm1</t>
   </si>
   <si>
@@ -2183,9 +2180,6 @@
     <t>skxctam1</t>
   </si>
   <si>
-    <t>skxwmsm1</t>
-  </si>
-  <si>
     <t>skxchgm1</t>
   </si>
   <si>
@@ -2276,54 +2270,15 @@
     <t>每命中一个目标，冰咆哮的伤害提升{0.2}%</t>
   </si>
   <si>
-    <t>使用斧类武器时，提升{0.2}%的暴击几率</t>
-  </si>
-  <si>
-    <t>你的非物理伤害也能造成暴击</t>
-  </si>
-  <si>
-    <t>受影响的目标将受到额外{0.2}%的刺杀剑术伤害</t>
-  </si>
-  <si>
-    <t>受影响的目标遭受流血效果，每回合受到{0.2}%的物理伤害</t>
-  </si>
-  <si>
-    <t>施放十字斩后，你的刺杀剑术或者半月弯刀的冷却时间-1回合</t>
-  </si>
-  <si>
-    <t>skbcrzm2</t>
-  </si>
-  <si>
-    <t>你的十字斩攻击范围+1</t>
-  </si>
-  <si>
     <t>烈火剑法附带等额的神圣伤害，烈火剑法现在也是神圣系技能</t>
   </si>
   <si>
     <t>skbfblm2</t>
   </si>
   <si>
-    <t>汲取火焰伤害的{0.2}%的生命值，烈火剑法现在也是道术系技能</t>
-  </si>
-  <si>
-    <t>被击中后恢复物理减伤{0.2}%的生命值</t>
-  </si>
-  <si>
-    <t>提升等额的魔法闪避</t>
-  </si>
-  <si>
-    <t>开启后，提升{0.2}%的最大生命值</t>
-  </si>
-  <si>
-    <t>提升等额的火焰反弹</t>
-  </si>
-  <si>
     <t>施展野蛮冲撞后，你立即普通攻击一次</t>
   </si>
   <si>
-    <t>受影响的目标的物理抗性降低{0.2}%</t>
-  </si>
-  <si>
     <t>skxtstm2</t>
   </si>
   <si>
@@ -2385,9 +2340,6 @@
   </si>
   <si>
     <t>对被灵魂火符命中的不死生物的伤害提升{0.2}%</t>
-  </si>
-  <si>
-    <t>神兽现在攻击扇形范围内的敌人，伤害类型变为毒素系，召唤神兽现在也是毒素系技能</t>
   </si>
   <si>
     <t>skpsdmm2</t>
@@ -2581,9 +2533,6 @@
     <t>targetTag</t>
   </si>
   <si>
-    <t>SkillTag</t>
-  </si>
-  <si>
     <t>服务于分类</t>
   </si>
   <si>
@@ -2593,12 +2542,6 @@
     <t>thunder</t>
   </si>
   <si>
-    <t>targetUnit</t>
-  </si>
-  <si>
-    <t>服务于单位</t>
-  </si>
-  <si>
     <t>mage</t>
   </si>
   <si>
@@ -2623,9 +2566,6 @@
     <t>UnitId[]</t>
   </si>
   <si>
-    <t>mage,warr,wlk</t>
-  </si>
-  <si>
     <t>summon</t>
   </si>
   <si>
@@ -2653,9 +2593,6 @@
     <t>是技能Mod</t>
   </si>
   <si>
-    <t>t4 weap</t>
-  </si>
-  <si>
     <t>1海魂</t>
   </si>
   <si>
@@ -2735,6 +2672,153 @@
   </si>
   <si>
     <t>holy,hdmg</t>
+  </si>
+  <si>
+    <t>skbbasm2</t>
+  </si>
+  <si>
+    <t>skbbasm3</t>
+  </si>
+  <si>
+    <t>skbbasm4</t>
+  </si>
+  <si>
+    <t>skbbasm5</t>
+  </si>
+  <si>
+    <t>skbbasm6</t>
+  </si>
+  <si>
+    <t>bele</t>
+  </si>
+  <si>
+    <t>刺杀剑术对第二目标的伤害提高{0.2}%</t>
+  </si>
+  <si>
+    <t>使用斧类武器时，基础剑术每级额外提升{0.2}%的暴击伤害</t>
+  </si>
+  <si>
+    <t>使用剑类武器时，基础剑术每级额外提升{0.2}%的闪避几率</t>
+  </si>
+  <si>
+    <t>使用锤类武器时，基础剑术每级额外提升{0.2}%的暴击率</t>
+  </si>
+  <si>
+    <t>使用匕首类武器时，基础剑术每级额外提升{0.2}%的命中率</t>
+  </si>
+  <si>
+    <t>使用刀类武器时，基础剑术每级额外提升{0.2}%的攻击吸血</t>
+  </si>
+  <si>
+    <t>使用长柄类武器时，基础剑术每级额外提升{0}点士气</t>
+  </si>
+  <si>
+    <t>元素剑术使你的非物理伤害也能造成暴击</t>
+  </si>
+  <si>
+    <t>被半月弯刀击中的目标遭受流血效果，每回合受到{0.2}%的物理伤害</t>
+  </si>
+  <si>
+    <t>烈火剑法造成火焰伤害{0.2}%的吸血效果，烈火剑法现在也是道术系技能</t>
+  </si>
+  <si>
+    <t>铁布衫每级使你被击中后恢复物理减伤{0.2}%的生命值</t>
+  </si>
+  <si>
+    <t>猎犬步伐现在提升等额的魔法闪避</t>
+  </si>
+  <si>
+    <t>开启战斗指挥后，提升{0.2}%的最大生命值</t>
+  </si>
+  <si>
+    <t>霜冻踏地命中的目标的物理抗性降低{0.2}%</t>
+  </si>
+  <si>
+    <t>skxposm1</t>
+  </si>
+  <si>
+    <t>镇魂拳法现在可以命中目标及其十字范围内的所有目标</t>
+  </si>
+  <si>
+    <t>1祖父</t>
+  </si>
+  <si>
+    <t>1冰铁锤</t>
+  </si>
+  <si>
+    <t>1黄金残光</t>
+  </si>
+  <si>
+    <t>1尸山血海</t>
+  </si>
+  <si>
+    <t>1祭奠长矛</t>
+  </si>
+  <si>
+    <t>14破魂</t>
+  </si>
+  <si>
+    <t>28井中月</t>
+  </si>
+  <si>
+    <t>35圣战斩杀者</t>
+  </si>
+  <si>
+    <t>35裁决</t>
+  </si>
+  <si>
+    <t>1斩马刀</t>
+  </si>
+  <si>
+    <t>修罗</t>
+  </si>
+  <si>
+    <t>凝霜</t>
+  </si>
+  <si>
+    <t>屠龙</t>
+  </si>
+  <si>
+    <t>怒斩</t>
+  </si>
+  <si>
+    <t>卧龙</t>
+  </si>
+  <si>
+    <t>神兽现在攻击扇形范围内的敌人，伤害类型变为毒素系，召唤神兽现在是毒素系技能</t>
+  </si>
+  <si>
+    <t>rmSkillTag</t>
+  </si>
+  <si>
+    <t>删除新增分类</t>
+  </si>
+  <si>
+    <t>zlvl</t>
+  </si>
+  <si>
+    <t>毒素系技能等级</t>
+  </si>
+  <si>
+    <t>毒素系技能等级+{0}</t>
+  </si>
+  <si>
+    <t>poison</t>
+  </si>
+  <si>
+    <t>skmage</t>
+  </si>
+  <si>
+    <t>skwarr</t>
+  </si>
+  <si>
+    <t>skwlok</t>
+  </si>
+  <si>
+    <t>skmage,skwarr,skwlok</t>
+  </si>
+  <si>
+    <t>SkillTag[]</t>
   </si>
 </sst>
 </file>
@@ -2862,7 +2946,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3209,22 +3303,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:O285"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O289"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="51.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="51.453125" style="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.54296875" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3241,7 +3335,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -3250,28 +3344,28 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>834</v>
+        <v>904</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>853</v>
+        <v>833</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>166</v>
       </c>
@@ -3288,42 +3382,42 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>855</v>
+        <v>835</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>835</v>
+        <v>782</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>848</v>
+        <v>914</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>848</v>
+        <v>829</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>320</v>
       </c>
@@ -3340,37 +3434,37 @@
         <v>171</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>836</v>
+        <v>905</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>854</v>
+        <v>834</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>393</v>
       </c>
@@ -3387,7 +3481,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>394</v>
       </c>
@@ -3404,7 +3498,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>395</v>
       </c>
@@ -3421,7 +3515,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>396</v>
       </c>
@@ -3438,7 +3532,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3455,7 +3549,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3472,7 +3566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3495,7 +3589,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3518,7 +3612,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3535,7 +3629,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3552,7 +3646,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3575,7 +3669,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -3598,7 +3692,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3615,7 +3709,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -3632,7 +3726,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -3649,7 +3743,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -3666,7 +3760,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>409</v>
       </c>
@@ -3683,7 +3777,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>663</v>
       </c>
@@ -3700,7 +3794,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>664</v>
       </c>
@@ -3717,7 +3811,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>279</v>
       </c>
@@ -3734,7 +3828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>280</v>
       </c>
@@ -3751,7 +3845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>281</v>
       </c>
@@ -3768,7 +3862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>282</v>
       </c>
@@ -3785,7 +3879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>283</v>
       </c>
@@ -3802,7 +3896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>445</v>
       </c>
@@ -3819,7 +3913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>446</v>
       </c>
@@ -3836,7 +3930,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>447</v>
       </c>
@@ -3853,7 +3947,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>448</v>
       </c>
@@ -3870,7 +3964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>449</v>
       </c>
@@ -3887,7 +3981,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>450</v>
       </c>
@@ -3904,7 +3998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>451</v>
       </c>
@@ -3921,7 +4015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>452</v>
       </c>
@@ -3938,7 +4032,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>453</v>
       </c>
@@ -3955,7 +4049,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>454</v>
       </c>
@@ -3972,7 +4066,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -3989,7 +4083,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -4006,7 +4100,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -4023,7 +4117,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -4040,7 +4134,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -4057,7 +4151,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -4074,7 +4168,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -4091,7 +4185,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -4108,7 +4202,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -4125,7 +4219,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -4142,7 +4236,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
@@ -4159,7 +4253,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
@@ -4176,7 +4270,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -4193,7 +4287,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
@@ -4210,7 +4304,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
@@ -4227,7 +4321,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>411</v>
       </c>
@@ -4244,7 +4338,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>412</v>
       </c>
@@ -4261,7 +4355,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>413</v>
       </c>
@@ -4278,7 +4372,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -4295,7 +4389,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -4312,7 +4406,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -4329,7 +4423,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -4346,7 +4440,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -4363,7 +4457,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -4383,7 +4477,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
@@ -4403,7 +4497,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
@@ -4423,7 +4517,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>398</v>
       </c>
@@ -4443,7 +4537,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>399</v>
       </c>
@@ -4463,7 +4557,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>405</v>
       </c>
@@ -4483,7 +4577,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>403</v>
       </c>
@@ -4500,7 +4594,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -4517,7 +4611,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
@@ -4534,7 +4628,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -4551,7 +4645,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -4568,7 +4662,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -4585,7 +4679,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
@@ -4608,7 +4702,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -4631,7 +4725,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -4654,7 +4748,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -4677,7 +4771,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
@@ -4700,7 +4794,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>392</v>
       </c>
@@ -4717,7 +4811,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -4734,7 +4828,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -4751,7 +4845,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -4768,7 +4862,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -4785,7 +4879,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>309</v>
       </c>
@@ -4802,7 +4896,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>310</v>
       </c>
@@ -4819,7 +4913,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>311</v>
       </c>
@@ -4836,7 +4930,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>312</v>
       </c>
@@ -4853,7 +4947,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>313</v>
       </c>
@@ -4870,7 +4964,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -4887,7 +4981,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -4904,7 +4998,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -4921,7 +5015,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,7 +5032,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -4955,7 +5049,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>419</v>
       </c>
@@ -4972,7 +5066,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>660</v>
       </c>
@@ -4989,7 +5083,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -5006,7 +5100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>472</v>
       </c>
@@ -5023,7 +5117,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>675</v>
       </c>
@@ -5040,7 +5134,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>407</v>
       </c>
@@ -5057,7 +5151,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>380</v>
       </c>
@@ -5071,7 +5165,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>382</v>
       </c>
@@ -5085,24 +5179,24 @@
         <v>293</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>394</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="F102" s="1">
         <v>999</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>46</v>
       </c>
@@ -5119,7 +5213,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>47</v>
       </c>
@@ -5136,7 +5230,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>48</v>
       </c>
@@ -5153,7 +5247,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>277</v>
       </c>
@@ -5170,7 +5264,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>293</v>
       </c>
@@ -5187,7 +5281,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>294</v>
       </c>
@@ -5204,7 +5298,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>295</v>
       </c>
@@ -5221,7 +5315,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>296</v>
       </c>
@@ -5238,7 +5332,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>72</v>
       </c>
@@ -5255,7 +5349,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>678</v>
       </c>
@@ -5272,7 +5366,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>669</v>
       </c>
@@ -5289,7 +5383,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>672</v>
       </c>
@@ -5306,7 +5400,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>388</v>
       </c>
@@ -5323,7 +5417,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>389</v>
       </c>
@@ -5340,7 +5434,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>443</v>
       </c>
@@ -5357,7 +5451,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>59</v>
       </c>
@@ -5373,11 +5467,11 @@
       <c r="F118" s="1">
         <v>401</v>
       </c>
-      <c r="L118" s="1" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M118" s="1" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>60</v>
       </c>
@@ -5393,11 +5487,11 @@
       <c r="F119" s="1">
         <v>402</v>
       </c>
-      <c r="L119" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M119" s="1" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>61</v>
       </c>
@@ -5414,10 +5508,10 @@
         <v>403</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>420</v>
       </c>
@@ -5433,14 +5527,14 @@
       <c r="F121" s="1">
         <v>404</v>
       </c>
-      <c r="L121" s="1" t="s">
-        <v>837</v>
+      <c r="M121" s="1" t="s">
+        <v>820</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>421</v>
       </c>
@@ -5456,14 +5550,14 @@
       <c r="F122" s="1">
         <v>405</v>
       </c>
-      <c r="L122" s="1" t="s">
-        <v>838</v>
+      <c r="M122" s="1" t="s">
+        <v>821</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>654</v>
       </c>
@@ -5480,13 +5574,13 @@
         <v>406</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>841</v>
+        <v>910</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>62</v>
       </c>
@@ -5502,11 +5596,11 @@
       <c r="F124" s="1">
         <v>407</v>
       </c>
-      <c r="L124" s="1" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M124" s="1" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>63</v>
       </c>
@@ -5522,11 +5616,11 @@
       <c r="F125" s="1">
         <v>408</v>
       </c>
-      <c r="L125" s="1" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M125" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>64</v>
       </c>
@@ -5543,10 +5637,10 @@
         <v>409</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>422</v>
       </c>
@@ -5562,14 +5656,14 @@
       <c r="F127" s="1">
         <v>410</v>
       </c>
-      <c r="L127" s="1" t="s">
-        <v>842</v>
+      <c r="M127" s="1" t="s">
+        <v>823</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>423</v>
       </c>
@@ -5585,14 +5679,14 @@
       <c r="F128" s="1">
         <v>411</v>
       </c>
-      <c r="L128" s="1" t="s">
-        <v>843</v>
+      <c r="M128" s="1" t="s">
+        <v>824</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>655</v>
       </c>
@@ -5609,13 +5703,13 @@
         <v>412</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>844</v>
+        <v>911</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>65</v>
       </c>
@@ -5631,11 +5725,11 @@
       <c r="F130" s="1">
         <v>413</v>
       </c>
-      <c r="L130" s="1" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M130" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>66</v>
       </c>
@@ -5651,11 +5745,11 @@
       <c r="F131" s="1">
         <v>414</v>
       </c>
-      <c r="L131" s="1" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M131" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>67</v>
       </c>
@@ -5672,10 +5766,10 @@
         <v>415</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>424</v>
       </c>
@@ -5691,14 +5785,14 @@
       <c r="F133" s="1">
         <v>416</v>
       </c>
-      <c r="L133" s="1" t="s">
-        <v>845</v>
+      <c r="M133" s="1" t="s">
+        <v>826</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>425</v>
       </c>
@@ -5714,14 +5808,14 @@
       <c r="F134" s="1">
         <v>417</v>
       </c>
-      <c r="L134" s="1" t="s">
-        <v>846</v>
+      <c r="M134" s="1" t="s">
+        <v>827</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>657</v>
       </c>
@@ -5738,13 +5832,13 @@
         <v>418</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>847</v>
+        <v>912</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>68</v>
       </c>
@@ -5761,10 +5855,10 @@
         <v>419</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>69</v>
       </c>
@@ -5780,11 +5874,11 @@
       <c r="F137" s="1">
         <v>420</v>
       </c>
-      <c r="L137" s="1" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M137" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>70</v>
       </c>
@@ -5800,2060 +5894,2056 @@
       <c r="F138" s="1">
         <v>421</v>
       </c>
-      <c r="L138" s="1" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M138" s="1" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="F139" s="1">
+        <v>422</v>
+      </c>
+      <c r="M139" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C140" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F140" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B141" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F141" s="1">
         <v>431</v>
       </c>
-      <c r="J140" s="1" t="s">
+      <c r="J141" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="N141" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F142" s="1">
+        <v>432</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="F143" s="1">
+        <v>433</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="N143" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A144" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="F144" s="1">
+        <v>434</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="N144" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F145" s="1">
+        <v>435</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="N145" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="F146" s="1">
+        <v>436</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="N146" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A147" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="F147" s="1">
+        <v>437</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="F148" s="1">
+        <v>438</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A149" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="F149" s="1">
+        <v>439</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="F150" s="1">
+        <v>440</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A151" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F151" s="1">
+        <v>441</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A152" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="F152" s="1">
+        <v>442</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A153" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="F153" s="1">
+        <v>443</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="N153" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A154" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="F154" s="1">
+        <v>444</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="N154" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A155" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="F155" s="1">
+        <v>445</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="N155" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="F156" s="1">
+        <v>446</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="N156" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A157" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="F157" s="1">
+        <v>447</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="N157" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="F158" s="1">
+        <v>448</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="N158" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A159" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="F159" s="1">
+        <v>449</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A160" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="F160" s="1">
+        <v>450</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A161" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="F161" s="1">
+        <v>451</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A162" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="F162" s="1">
+        <v>452</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A163" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="F163" s="1">
+        <v>453</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A164" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="F164" s="1">
+        <v>454</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="F165" s="1">
+        <v>455</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="N165" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="F166" s="1">
+        <v>456</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="N166" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A167" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="F167" s="1">
+        <v>457</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="N167" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A168" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="F168" s="1">
+        <v>458</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="N168" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A169" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F169" s="1">
+        <v>459</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="N169" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A170" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="F170" s="1">
+        <v>460</v>
+      </c>
+      <c r="J170" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="N140" s="1" t="s">
+      <c r="N170" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A171" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="F171" s="1">
+        <v>461</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A172" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F172" s="1">
+        <v>462</v>
+      </c>
+      <c r="J172" s="1" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A173" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="F173" s="1">
+        <v>463</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A174" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="F174" s="1">
+        <v>464</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A175" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="F175" s="1">
+        <v>465</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A176" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="F176" s="1">
+        <v>466</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A177" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="F177" s="1">
+        <v>467</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="N177" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A178" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F178" s="1">
+        <v>468</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="N178" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A179" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="F179" s="1">
+        <v>469</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="N179" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A180" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="F180" s="1">
+        <v>470</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="N180" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A181" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="F181" s="1">
+        <v>471</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="N181" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A182" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="F182" s="1">
+        <v>472</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="N182" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A183" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="F183" s="1">
+        <v>473</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A184" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="F184" s="1">
+        <v>474</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A185" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="F185" s="1">
+        <v>475</v>
+      </c>
+      <c r="J185" s="1" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A186" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="F186" s="1">
+        <v>476</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A187" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="F187" s="1">
+        <v>477</v>
+      </c>
+      <c r="J187" s="1" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A188" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F188" s="1">
+        <v>478</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A189" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="F189" s="1">
+        <v>479</v>
+      </c>
+      <c r="J189" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="N189" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A190" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="F190" s="1">
+        <v>480</v>
+      </c>
+      <c r="J190" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="N190" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A191" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="F191" s="1">
+        <v>481</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="N191" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A192" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F192" s="1">
+        <v>482</v>
+      </c>
+      <c r="J192" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="N192" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A193" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F193" s="1">
+        <v>483</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="N193" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A194" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="F194" s="1">
+        <v>484</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="N194" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A195" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="F195" s="1">
+        <v>485</v>
+      </c>
+      <c r="J195" s="1" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A196" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="F196" s="1">
+        <v>486</v>
+      </c>
+      <c r="J196" s="1" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A197" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="F197" s="1">
+        <v>487</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A198" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="F198" s="1">
+        <v>488</v>
+      </c>
+      <c r="J198" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A199" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="F199" s="1">
+        <v>489</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A200" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="F200" s="1">
+        <v>490</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A201" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="F201" s="1">
+        <v>491</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="N201" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A202" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="F202" s="1">
+        <v>492</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="N202" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A203" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="F203" s="1">
+        <v>493</v>
+      </c>
+      <c r="J203" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="N203" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A204" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F204" s="1">
+        <v>494</v>
+      </c>
+      <c r="J204" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="N204" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A205" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="F205" s="1">
+        <v>495</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="N205" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A206" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="F206" s="1">
+        <v>496</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="N206" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A207" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="F207" s="1">
+        <v>497</v>
+      </c>
+      <c r="J207" s="1" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A208" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="F208" s="1">
+        <v>498</v>
+      </c>
+      <c r="J208" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A209" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="F209" s="1">
+        <v>499</v>
+      </c>
+      <c r="J209" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A210" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="F210" s="1">
+        <v>500</v>
+      </c>
+      <c r="J210" s="1" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A211" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="F211" s="1">
+        <v>501</v>
+      </c>
+      <c r="J211" s="1" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A212" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="F212" s="1">
+        <v>502</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A213" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F213" s="1">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A214" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F214" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A215" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F215" s="1">
+        <v>803</v>
+      </c>
+      <c r="I215" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="A216" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F216" s="1">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A217" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F217" s="1">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A218" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F218" s="1">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A219" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F219" s="1">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="A220" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F220" s="1">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A221" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F221" s="1">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A222" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F222" s="1">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A223" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F223" s="1">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F224" s="1">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A225" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F225" s="1">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A226" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F226" s="1">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A227" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F227" s="1">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A228" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F228" s="1">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A229" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F229" s="1">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A230" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F230" s="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A231" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F231" s="1">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A232" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F232" s="1">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A233" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F233" s="1">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A234" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F234" s="1">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A235" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F235" s="1">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A236" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F236" s="1">
         <v>841</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="F141" s="1">
-        <v>432</v>
-      </c>
-      <c r="J141" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="N141" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="F142" s="1">
-        <v>433</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="N142" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="F143" s="1">
-        <v>434</v>
-      </c>
-      <c r="J143" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="N143" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F144" s="1">
-        <v>435</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="N144" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="F145" s="1">
-        <v>436</v>
-      </c>
-      <c r="J145" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="N145" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="F146" s="1">
-        <v>437</v>
-      </c>
-      <c r="J146" s="1" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="F147" s="1">
-        <v>438</v>
-      </c>
-      <c r="J147" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="F148" s="1">
-        <v>439</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="F149" s="1">
-        <v>440</v>
-      </c>
-      <c r="J149" s="1" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="F150" s="1">
-        <v>441</v>
-      </c>
-      <c r="J150" s="1" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="F151" s="1">
-        <v>442</v>
-      </c>
-      <c r="J151" s="1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="F152" s="1">
-        <v>443</v>
-      </c>
-      <c r="J152" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="N152" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="F153" s="1">
-        <v>444</v>
-      </c>
-      <c r="J153" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="N153" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A154" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="F154" s="1">
-        <v>445</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="N154" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A155" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="F155" s="1">
-        <v>446</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="N155" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="F156" s="1">
-        <v>447</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="N156" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A157" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F157" s="1">
-        <v>448</v>
-      </c>
-      <c r="J157" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="N157" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="F158" s="1">
-        <v>449</v>
-      </c>
-      <c r="J158" s="1" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="F159" s="1">
-        <v>450</v>
-      </c>
-      <c r="J159" s="1" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="F160" s="1">
-        <v>451</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="F161" s="1">
-        <v>452</v>
-      </c>
-      <c r="J161" s="1" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="F162" s="1">
-        <v>453</v>
-      </c>
-      <c r="J162" s="1" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="F163" s="1">
-        <v>454</v>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="F164" s="1">
-        <v>455</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="N164" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="F165" s="1">
-        <v>456</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="N165" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="F166" s="1">
-        <v>457</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="N166" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A167" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="F167" s="1">
-        <v>458</v>
-      </c>
-      <c r="J167" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="N167" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="F168" s="1">
-        <v>459</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="N168" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="F169" s="1">
-        <v>460</v>
-      </c>
-      <c r="J169" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="N169" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="F170" s="1">
-        <v>461</v>
-      </c>
-      <c r="J170" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="F171" s="1">
-        <v>462</v>
-      </c>
-      <c r="J171" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="F172" s="1">
-        <v>463</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="F173" s="1">
-        <v>464</v>
-      </c>
-      <c r="J173" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A174" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="F174" s="1">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A237" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="J174" s="1" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A175" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="F175" s="1">
+      <c r="B237" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="J175" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A176" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="F176" s="1">
+      <c r="C237" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E237" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="J176" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="N176" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="F177" s="1">
-        <v>468</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="N177" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="F178" s="1">
-        <v>469</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="N178" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="F179" s="1">
-        <v>470</v>
-      </c>
-      <c r="J179" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="N179" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A180" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="F180" s="1">
-        <v>471</v>
-      </c>
-      <c r="J180" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="N180" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="F181" s="1">
-        <v>472</v>
-      </c>
-      <c r="J181" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="N181" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="F182" s="1">
-        <v>473</v>
-      </c>
-      <c r="J182" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A183" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="F183" s="1">
-        <v>474</v>
-      </c>
-      <c r="J183" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="F184" s="1">
-        <v>475</v>
-      </c>
-      <c r="J184" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="F185" s="1">
-        <v>476</v>
-      </c>
-      <c r="J185" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A186" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="F186" s="1">
-        <v>477</v>
-      </c>
-      <c r="J186" s="1" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F187" s="1">
-        <v>478</v>
-      </c>
-      <c r="J187" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="F188" s="1">
-        <v>479</v>
-      </c>
-      <c r="J188" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="N188" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="F189" s="1">
-        <v>480</v>
-      </c>
-      <c r="J189" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="N189" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A190" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="F190" s="1">
-        <v>481</v>
-      </c>
-      <c r="J190" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="N190" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A191" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="F191" s="1">
-        <v>482</v>
-      </c>
-      <c r="J191" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="N191" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A192" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="F192" s="1">
-        <v>483</v>
-      </c>
-      <c r="J192" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="N192" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A193" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="F193" s="1">
-        <v>484</v>
-      </c>
-      <c r="J193" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="N193" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="F194" s="1">
-        <v>485</v>
-      </c>
-      <c r="J194" s="1" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="F195" s="1">
-        <v>486</v>
-      </c>
-      <c r="J195" s="1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A196" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="F196" s="1">
-        <v>487</v>
-      </c>
-      <c r="J196" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="F197" s="1">
-        <v>488</v>
-      </c>
-      <c r="J197" s="1" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B198" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="F198" s="1">
-        <v>489</v>
-      </c>
-      <c r="J198" s="1" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="F199" s="1">
-        <v>490</v>
-      </c>
-      <c r="J199" s="1" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B200" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="F200" s="1">
-        <v>491</v>
-      </c>
-      <c r="J200" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="N200" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A201" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="F201" s="1">
-        <v>492</v>
-      </c>
-      <c r="J201" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="N201" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="F202" s="1">
-        <v>493</v>
-      </c>
-      <c r="J202" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="N202" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="F203" s="1">
-        <v>494</v>
-      </c>
-      <c r="J203" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="N203" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="F204" s="1">
-        <v>495</v>
-      </c>
-      <c r="J204" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="N204" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="F205" s="1">
-        <v>496</v>
-      </c>
-      <c r="J205" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="N205" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="F206" s="1">
-        <v>497</v>
-      </c>
-      <c r="J206" s="1" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="F207" s="1">
-        <v>498</v>
-      </c>
-      <c r="J207" s="1" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="F208" s="1">
-        <v>499</v>
-      </c>
-      <c r="J208" s="1" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="F209" s="1">
-        <v>500</v>
-      </c>
-      <c r="J209" s="1" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="F210" s="1">
-        <v>501</v>
-      </c>
-      <c r="J210" s="1" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="F211" s="1">
-        <v>502</v>
-      </c>
-      <c r="J211" s="1" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F212" s="1">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F213" s="1">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F214" s="1">
-        <v>803</v>
-      </c>
-      <c r="I214" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>682</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F215" s="1">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F216" s="1">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F217" s="1">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F218" s="1">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>684</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F219" s="1">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F220" s="1">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F221" s="1">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F222" s="1">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="B223" s="7" t="s">
-        <v>686</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F223" s="1">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F224" s="1">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F225" s="1">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F226" s="1">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F227" s="1">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F228" s="1">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C229" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F229" s="1">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F230" s="1">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F231" s="1">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F232" s="1">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F233" s="1">
+      <c r="F237" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A238" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B238" s="9" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F234" s="1">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F235" s="1">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="F236" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="237" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>860</v>
-      </c>
-      <c r="C237" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E237" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="F237" s="9">
-        <v>999</v>
-      </c>
-      <c r="J237" s="9" t="str">
-        <f>MID(A237,3,4)</f>
-        <v>fblt</v>
-      </c>
-      <c r="O237" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="B238" s="9" t="s">
-        <v>861</v>
-      </c>
       <c r="C238" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E238" s="9" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F238" s="9">
         <v>999</v>
       </c>
       <c r="J238" s="9" t="str">
-        <f t="shared" ref="J238:J285" si="0">MID(A238,3,4)</f>
-        <v>frng</v>
+        <f>MID(A238,3,4)</f>
+        <v>fblt</v>
       </c>
       <c r="O238" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>862</v>
+        <v>840</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E239" s="9" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F239" s="9">
         <v>999</v>
       </c>
       <c r="J239" s="9" t="str">
+        <f t="shared" ref="J239:J289" si="0">MID(A239,3,4)</f>
+        <v>frng</v>
+      </c>
+      <c r="O239" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A240" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="C240" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="F240" s="9">
+        <v>999</v>
+      </c>
+      <c r="J240" s="9" t="str">
         <f t="shared" si="0"/>
         <v>finf</v>
       </c>
-      <c r="O239" s="9" t="b">
+      <c r="O240" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="9" t="s">
+    <row r="241" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A241" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="B240" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="C240" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E240" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="F240" s="9">
+      <c r="B241" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="F241" s="9">
         <v>999</v>
       </c>
-      <c r="J240" s="9" t="str">
+      <c r="J241" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fbal</v>
       </c>
-      <c r="O240" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>868</v>
-      </c>
-      <c r="C241" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E241" s="9" t="s">
-        <v>881</v>
-      </c>
-      <c r="F241" s="9">
-        <v>999</v>
-      </c>
-      <c r="J241" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>fbls</v>
-      </c>
       <c r="O241" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A242" s="9" t="s">
-        <v>727</v>
+        <v>691</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>869</v>
+        <v>847</v>
       </c>
       <c r="C242" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>728</v>
+        <v>860</v>
       </c>
       <c r="F242" s="9">
         <v>999</v>
@@ -7866,42 +7956,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>692</v>
+        <v>725</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F243" s="9">
         <v>999</v>
       </c>
       <c r="J243" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>fwal</v>
+        <v>fbls</v>
       </c>
       <c r="O243" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
-        <v>730</v>
+        <v>692</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>875</v>
+        <v>853</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E244" s="9" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F244" s="9">
         <v>999</v>
@@ -7914,90 +8004,90 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="10" t="s">
+    <row r="245" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="F245" s="9">
+        <v>999</v>
+      </c>
+      <c r="J245" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>fwal</v>
+      </c>
+      <c r="O245" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="B245" s="10" t="s">
-        <v>863</v>
-      </c>
-      <c r="C245" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E245" s="10" t="s">
-        <v>732</v>
-      </c>
-      <c r="F245" s="10">
+      <c r="B246" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="C246" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E246" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="F246" s="10">
         <v>999</v>
       </c>
-      <c r="J245" s="10" t="str">
+      <c r="J246" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tchm</v>
       </c>
-      <c r="O245" s="10" t="b">
+      <c r="O246" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="10" t="s">
+    <row r="247" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="B246" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="C246" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E246" s="10" t="s">
-        <v>880</v>
-      </c>
-      <c r="F246" s="10">
+      <c r="B247" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="C247" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E247" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="F247" s="10">
         <v>999</v>
       </c>
-      <c r="J246" s="10" t="str">
+      <c r="J247" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tblt</v>
       </c>
-      <c r="O246" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="247" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="B247" s="10" t="s">
-        <v>865</v>
-      </c>
-      <c r="C247" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E247" s="10" t="s">
-        <v>733</v>
-      </c>
-      <c r="F247" s="10">
-        <v>999</v>
-      </c>
-      <c r="J247" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>tltn</v>
-      </c>
       <c r="O247" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A248" s="10" t="s">
-        <v>734</v>
+        <v>695</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>866</v>
+        <v>844</v>
       </c>
       <c r="C248" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E248" s="10" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="F248" s="10">
         <v>999</v>
@@ -8010,66 +8100,66 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
-        <v>696</v>
+        <v>732</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>882</v>
+        <v>845</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>879</v>
+        <v>733</v>
       </c>
       <c r="F249" s="10">
         <v>999</v>
       </c>
       <c r="J249" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>tnov</v>
+        <v>tltn</v>
       </c>
       <c r="O249" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="C250" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c r="F250" s="10">
         <v>999</v>
       </c>
       <c r="J250" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>tshd</v>
+        <v>tnov</v>
       </c>
       <c r="O250" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
-        <v>736</v>
+        <v>697</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>871</v>
+        <v>849</v>
       </c>
       <c r="C251" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>878</v>
+        <v>856</v>
       </c>
       <c r="F251" s="10">
         <v>999</v>
@@ -8082,42 +8172,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
-        <v>698</v>
+        <v>734</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>872</v>
+        <v>850</v>
       </c>
       <c r="C252" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>876</v>
+        <v>857</v>
       </c>
       <c r="F252" s="10">
         <v>999</v>
       </c>
       <c r="J252" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>tblz</v>
+        <v>tshd</v>
       </c>
       <c r="O252" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
-        <v>737</v>
+        <v>698</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>873</v>
+        <v>851</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>738</v>
+        <v>855</v>
       </c>
       <c r="F253" s="10">
         <v>999</v>
@@ -8130,790 +8220,888 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="11" t="s">
+    <row r="254" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A254" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="F254" s="10">
+        <v>999</v>
+      </c>
+      <c r="J254" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tblz</v>
+      </c>
+      <c r="O254" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A255" s="11" t="s">
         <v>699</v>
       </c>
-      <c r="B254" s="11" t="s">
-        <v>883</v>
-      </c>
-      <c r="C254" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E254" s="11" t="s">
-        <v>739</v>
-      </c>
-      <c r="F254" s="11">
+      <c r="B255" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E255" s="11" t="s">
+        <v>873</v>
+      </c>
+      <c r="F255" s="11">
         <v>999</v>
       </c>
-      <c r="J254" s="11" t="str">
+      <c r="J255" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bbas</v>
       </c>
-      <c r="O254" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="11" t="s">
-        <v>700</v>
-      </c>
-      <c r="B255" s="11" t="s">
-        <v>884</v>
-      </c>
-      <c r="C255" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E255" s="11" t="s">
-        <v>740</v>
-      </c>
-      <c r="F255" s="11">
-        <v>999</v>
-      </c>
-      <c r="J255" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>bcrt</v>
-      </c>
       <c r="O255" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A256" s="11" t="s">
-        <v>701</v>
+        <v>866</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>701</v>
+        <v>888</v>
       </c>
       <c r="C256" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>741</v>
+        <v>874</v>
       </c>
       <c r="F256" s="11">
         <v>999</v>
       </c>
       <c r="J256" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>bthr</v>
+        <v>bbas</v>
       </c>
       <c r="O256" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A257" s="11" t="s">
-        <v>702</v>
+        <v>867</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>702</v>
+        <v>889</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E257" s="11" t="s">
-        <v>742</v>
+        <v>875</v>
       </c>
       <c r="F257" s="11">
         <v>999</v>
       </c>
       <c r="J257" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>bclv</v>
+        <v>bbas</v>
       </c>
       <c r="O257" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A258" s="11" t="s">
-        <v>703</v>
+        <v>868</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>703</v>
+        <v>890</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E258" s="11" t="s">
-        <v>743</v>
+        <v>876</v>
       </c>
       <c r="F258" s="11">
         <v>999</v>
       </c>
       <c r="J258" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>bcrz</v>
+        <v>bbas</v>
       </c>
       <c r="O258" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="11" t="s">
-        <v>744</v>
+        <v>869</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>744</v>
+        <v>891</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E259" s="11" t="s">
-        <v>745</v>
+        <v>877</v>
       </c>
       <c r="F259" s="11">
         <v>999</v>
       </c>
       <c r="J259" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>bcrz</v>
+        <v>bbas</v>
       </c>
       <c r="O259" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A260" s="11" t="s">
-        <v>704</v>
+        <v>870</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>859</v>
+        <v>892</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>746</v>
+        <v>878</v>
       </c>
       <c r="F260" s="11">
         <v>999</v>
       </c>
       <c r="J260" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>bfbl</v>
-      </c>
-      <c r="K260" s="11" t="s">
-        <v>886</v>
+        <v>bbas</v>
       </c>
       <c r="O260" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A261" s="11" t="s">
-        <v>747</v>
+        <v>700</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>747</v>
+        <v>863</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E261" s="11" t="s">
-        <v>748</v>
+        <v>879</v>
       </c>
       <c r="F261" s="11">
         <v>999</v>
       </c>
-      <c r="J261" s="11" t="str">
+      <c r="J261" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="O261" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A262" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="B262" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="C262" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E262" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="F262" s="11">
+        <v>999</v>
+      </c>
+      <c r="J262" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bthr</v>
+      </c>
+      <c r="O262" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A263" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="B263" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="C263" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E263" s="11" t="s">
+        <v>880</v>
+      </c>
+      <c r="F263" s="11">
+        <v>999</v>
+      </c>
+      <c r="J263" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bclv</v>
+      </c>
+      <c r="O263" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A264" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="B264" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="C264" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E264" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="F264" s="11">
+        <v>999</v>
+      </c>
+      <c r="J264" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bfbl</v>
       </c>
-      <c r="K261" s="11" t="s">
-        <v>795</v>
-      </c>
-      <c r="O261" s="11" t="b">
+      <c r="K264" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="O264" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="12" t="s">
-        <v>705</v>
-      </c>
-      <c r="B262" s="12" t="s">
-        <v>705</v>
-      </c>
-      <c r="C262" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E262" s="12" t="s">
-        <v>749</v>
-      </c>
-      <c r="F262" s="12">
+    <row r="265" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="11" t="s">
+        <v>738</v>
+      </c>
+      <c r="B265" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="C265" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E265" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="F265" s="11">
         <v>999</v>
       </c>
-      <c r="J262" s="12" t="str">
+      <c r="J265" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bfbl</v>
+      </c>
+      <c r="K265" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="O265" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="B266" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E266" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="F266" s="12">
+        <v>999</v>
+      </c>
+      <c r="J266" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xdef</v>
       </c>
-      <c r="O262" s="12" t="b">
+      <c r="O266" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="12" t="s">
-        <v>706</v>
-      </c>
-      <c r="B263" s="12" t="s">
-        <v>706</v>
-      </c>
-      <c r="C263" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E263" s="12" t="s">
-        <v>750</v>
-      </c>
-      <c r="F263" s="12">
+    <row r="267" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="C267" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E267" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="F267" s="12">
         <v>999</v>
       </c>
-      <c r="J263" s="12" t="str">
+      <c r="J267" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xdog</v>
       </c>
-      <c r="O263" s="12" t="b">
+      <c r="O267" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="12" t="s">
-        <v>707</v>
-      </c>
-      <c r="B264" s="12" t="s">
-        <v>885</v>
-      </c>
-      <c r="C264" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E264" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="F264" s="12">
+    <row r="268" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="B268" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="C268" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E268" s="12" t="s">
+        <v>887</v>
+      </c>
+      <c r="F268" s="12">
         <v>999</v>
       </c>
-      <c r="J264" s="12" t="str">
+      <c r="J268" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xpos</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="C269" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E269" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="F269" s="12">
+        <v>999</v>
+      </c>
+      <c r="J269" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xcta</v>
       </c>
-      <c r="O264" s="12" t="b">
+      <c r="O269" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="12" t="s">
-        <v>708</v>
-      </c>
-      <c r="B265" s="12" t="s">
-        <v>708</v>
-      </c>
-      <c r="C265" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E265" s="12" t="s">
-        <v>752</v>
-      </c>
-      <c r="F265" s="12">
+    <row r="270" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="12" t="s">
+        <v>707</v>
+      </c>
+      <c r="B270" s="12" t="s">
+        <v>900</v>
+      </c>
+      <c r="C270" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E270" s="12" t="s">
+        <v>739</v>
+      </c>
+      <c r="F270" s="12">
         <v>999</v>
       </c>
-      <c r="J265" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>xwms</v>
-      </c>
-      <c r="O265" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="12" t="s">
-        <v>709</v>
-      </c>
-      <c r="B266" s="12" t="s">
-        <v>709</v>
-      </c>
-      <c r="C266" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E266" s="12" t="s">
-        <v>753</v>
-      </c>
-      <c r="F266" s="12">
-        <v>999</v>
-      </c>
-      <c r="J266" s="12" t="str">
+      <c r="J270" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xchg</v>
       </c>
-      <c r="O266" s="12" t="b">
+      <c r="O270" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="12" t="s">
-        <v>710</v>
-      </c>
-      <c r="B267" s="12" t="s">
-        <v>710</v>
-      </c>
-      <c r="C267" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E267" s="12" t="s">
-        <v>754</v>
-      </c>
-      <c r="F267" s="12">
+    <row r="271" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A271" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>901</v>
+      </c>
+      <c r="C271" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E271" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="F271" s="12">
         <v>999</v>
       </c>
-      <c r="J267" s="12" t="str">
+      <c r="J271" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xtst</v>
       </c>
-      <c r="O267" s="12" t="b">
+      <c r="O271" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="12" t="s">
-        <v>755</v>
-      </c>
-      <c r="B268" s="12" t="s">
-        <v>755</v>
-      </c>
-      <c r="C268" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E268" s="12" t="s">
-        <v>756</v>
-      </c>
-      <c r="F268" s="12">
+    <row r="272" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="C272" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E272" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="F272" s="12">
         <v>999</v>
       </c>
-      <c r="J268" s="12" t="str">
+      <c r="J272" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xtst</v>
       </c>
-      <c r="O268" s="12" t="b">
+      <c r="O272" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="6" t="s">
-        <v>711</v>
-      </c>
-      <c r="B269" s="6" t="s">
-        <v>711</v>
-      </c>
-      <c r="C269" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E269" s="6" t="s">
-        <v>758</v>
-      </c>
-      <c r="F269" s="6">
+    <row r="273" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E273" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="F273" s="6">
         <v>999</v>
       </c>
-      <c r="J269" s="6" t="str">
+      <c r="J273" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhel</v>
       </c>
-      <c r="O269" s="6" t="b">
+      <c r="O273" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="B270" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="C270" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E270" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="F270" s="6">
+    <row r="274" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A274" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="F274" s="6">
         <v>999</v>
       </c>
-      <c r="J270" s="6" t="str">
+      <c r="J274" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhel</v>
       </c>
-      <c r="O270" s="6" t="b">
+      <c r="O274" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="6" t="s">
-        <v>712</v>
-      </c>
-      <c r="B271" s="6" t="s">
-        <v>712</v>
-      </c>
-      <c r="C271" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E271" s="6" t="s">
-        <v>760</v>
-      </c>
-      <c r="F271" s="6">
+    <row r="275" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A275" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E275" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="F275" s="6">
         <v>999</v>
       </c>
-      <c r="J271" s="6" t="str">
+      <c r="J275" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hgsd</v>
       </c>
-      <c r="O271" s="6" t="b">
+      <c r="O275" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="B272" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="C272" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E272" s="6" t="s">
-        <v>761</v>
-      </c>
-      <c r="F272" s="6">
+    <row r="276" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A276" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="F276" s="6">
         <v>999</v>
       </c>
-      <c r="J272" s="6" t="str">
+      <c r="J276" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hinv</v>
       </c>
-      <c r="O272" s="6" t="b">
+      <c r="O276" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="B273" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="C273" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E273" s="6" t="s">
-        <v>762</v>
-      </c>
-      <c r="F273" s="6">
+    <row r="277" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A277" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E277" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="F277" s="6">
         <v>999</v>
       </c>
-      <c r="J273" s="6" t="str">
+      <c r="J277" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhsd</v>
       </c>
-      <c r="O273" s="6" t="b">
+      <c r="O277" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="6" t="s">
-        <v>715</v>
-      </c>
-      <c r="B274" s="6" t="s">
-        <v>715</v>
-      </c>
-      <c r="C274" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E274" s="6" t="s">
-        <v>763</v>
-      </c>
-      <c r="F274" s="6">
+    <row r="278" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A278" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E278" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="F278" s="6">
         <v>999</v>
       </c>
-      <c r="J274" s="6" t="str">
+      <c r="J278" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hlok</v>
       </c>
-      <c r="O274" s="6" t="b">
+      <c r="O278" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A275" s="6" t="s">
-        <v>764</v>
-      </c>
-      <c r="B275" s="6" t="s">
-        <v>764</v>
-      </c>
-      <c r="C275" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E275" s="6" t="s">
-        <v>765</v>
-      </c>
-      <c r="F275" s="6">
+    <row r="279" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A279" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E279" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="F279" s="6">
         <v>999</v>
       </c>
-      <c r="J275" s="6" t="str">
+      <c r="J279" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hlok</v>
       </c>
-      <c r="O275" s="6" t="b">
+      <c r="O279" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="6" t="s">
-        <v>716</v>
-      </c>
-      <c r="B276" s="6" t="s">
-        <v>716</v>
-      </c>
-      <c r="C276" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E276" s="6" t="s">
-        <v>767</v>
-      </c>
-      <c r="F276" s="6">
+    <row r="280" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A280" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="F280" s="6">
         <v>999</v>
       </c>
-      <c r="J276" s="6" t="str">
+      <c r="J280" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hmhl</v>
       </c>
-      <c r="O276" s="6" t="b">
+      <c r="O280" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="6" t="s">
-        <v>766</v>
-      </c>
-      <c r="B277" s="6" t="s">
-        <v>766</v>
-      </c>
-      <c r="C277" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E277" s="6" t="s">
-        <v>768</v>
-      </c>
-      <c r="F277" s="6">
+    <row r="281" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A281" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E281" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="F281" s="6">
         <v>999</v>
       </c>
-      <c r="J277" s="6" t="str">
+      <c r="J281" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hmhl</v>
       </c>
-      <c r="O277" s="6" t="b">
+      <c r="O281" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="B278" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E278" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="F278" s="4">
+    <row r="282" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A282" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E282" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="F282" s="4">
         <v>999</v>
       </c>
-      <c r="J278" s="4" t="str">
+      <c r="J282" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pbas</v>
       </c>
-      <c r="O278" s="4" t="b">
+      <c r="O282" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A279" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="B279" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="C279" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E279" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="F279" s="4">
+    <row r="283" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A283" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E283" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="F283" s="4">
         <v>999</v>
       </c>
-      <c r="J279" s="4" t="str">
+      <c r="J283" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ppoi</v>
       </c>
-      <c r="O279" s="4" t="b">
+      <c r="O283" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="B280" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E280" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="F280" s="4">
+    <row r="284" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A284" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E284" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="F284" s="4">
         <v>999</v>
       </c>
-      <c r="J280" s="4" t="str">
+      <c r="J284" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pskl</v>
       </c>
-      <c r="K280" s="4" t="s">
-        <v>796</v>
-      </c>
-      <c r="O280" s="4" t="b">
+      <c r="K284" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="O284" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="B281" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="C281" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E281" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="F281" s="4">
+    <row r="285" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A285" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E285" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="F285" s="4">
         <v>999</v>
       </c>
-      <c r="J281" s="4" t="str">
+      <c r="J285" s="4" t="str">
         <f t="shared" si="0"/>
         <v>prun</v>
       </c>
-      <c r="O281" s="4" t="b">
+      <c r="O285" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="B282" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E282" s="4" t="s">
-        <v>773</v>
-      </c>
-      <c r="F282" s="4">
+    <row r="286" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A286" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E286" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="F286" s="4">
         <v>999</v>
       </c>
-      <c r="J282" s="4" t="str">
+      <c r="J286" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pcbl</v>
       </c>
-      <c r="O282" s="4" t="b">
+      <c r="O286" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="B283" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E283" s="4" t="s">
-        <v>775</v>
-      </c>
-      <c r="F283" s="4">
+    <row r="287" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A287" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E287" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="F287" s="4">
         <v>999</v>
       </c>
-      <c r="J283" s="4" t="str">
+      <c r="J287" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pcbl</v>
       </c>
-      <c r="O283" s="4" t="b">
+      <c r="O287" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A284" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="B284" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E284" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="F284" s="4">
+    <row r="288" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A288" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E288" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="F288" s="4">
         <v>999</v>
       </c>
-      <c r="J284" s="4" t="str">
+      <c r="J288" s="4" t="str">
         <f t="shared" si="0"/>
         <v>psdm</v>
       </c>
-      <c r="K284" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="O284" s="4" t="b">
+      <c r="K288" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="L288" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="O288" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="4" t="s">
-        <v>777</v>
-      </c>
-      <c r="B285" s="4" t="s">
-        <v>777</v>
-      </c>
-      <c r="C285" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E285" s="4" t="s">
-        <v>778</v>
-      </c>
-      <c r="F285" s="4">
+    <row r="289" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A289" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E289" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="F289" s="4">
         <v>999</v>
       </c>
-      <c r="J285" s="4" t="str">
+      <c r="J289" s="4" t="str">
         <f t="shared" si="0"/>
         <v>psdm</v>
       </c>
-      <c r="O285" s="4" t="b">
+      <c r="O289" s="4" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B268">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F50A8E-A55A-4D91-9651-67A7DC0BFA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B678E1-11D3-4BF7-917F-DD76CF30AF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="17970" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="932">
   <si>
     <t>id</t>
   </si>
@@ -2294,24 +2294,15 @@
     <t>治愈术现在会治疗你的整个队伍</t>
   </si>
   <si>
-    <t>可以吸收你的生命上限{0.2}%的非物理伤害</t>
-  </si>
-  <si>
     <t>隐身状态的攻击造成{0.2}%的额外伤害</t>
   </si>
   <si>
     <t>神圣战甲同时提供等额的非物理减伤</t>
   </si>
   <si>
-    <t>受影响的目标将被定义为妖魔</t>
-  </si>
-  <si>
     <t>skhlokm2</t>
   </si>
   <si>
-    <t>可对精英敌人和首领敌人施展，持续时间减半</t>
-  </si>
-  <si>
     <t>skhmhlm2</t>
   </si>
   <si>
@@ -2330,22 +2321,10 @@
     <t>骷髅的生命值-90%，骷髅死亡时爆炸，造成火焰伤害，召唤骷髅现在也是火焰系技能</t>
   </si>
   <si>
-    <t>对不死生物的伤害提升{0.2}%</t>
-  </si>
-  <si>
-    <t>击杀妖魔以后，造成的所有伤害提升{0.2}%</t>
-  </si>
-  <si>
     <t>skpcblm2</t>
   </si>
   <si>
-    <t>对被灵魂火符命中的不死生物的伤害提升{0.2}%</t>
-  </si>
-  <si>
     <t>skpsdmm2</t>
-  </si>
-  <si>
-    <t>神兽攻击时有概率战吼，整个队伍的物理伤害提升{0.2}%</t>
   </si>
   <si>
     <t>number</t>
@@ -2819,6 +2798,78 @@
   </si>
   <si>
     <t>SkillTag[]</t>
+  </si>
+  <si>
+    <t>妖道法衣</t>
+  </si>
+  <si>
+    <t>半月</t>
+  </si>
+  <si>
+    <t>无量之杖</t>
+  </si>
+  <si>
+    <t>幽灵盾可以吸收你的生命上限{0.2}%的非物理伤害</t>
+  </si>
+  <si>
+    <t>困魔咒的目标将被定义为妖魔</t>
+  </si>
+  <si>
+    <t>困魔咒可对精英敌人和首领敌人施展，持续时间减半</t>
+  </si>
+  <si>
+    <t>虚空道袍</t>
+  </si>
+  <si>
+    <t>银蛇</t>
+  </si>
+  <si>
+    <t>逍遥扇</t>
+  </si>
+  <si>
+    <t>判官剑</t>
+  </si>
+  <si>
+    <t>锁妖剑</t>
+  </si>
+  <si>
+    <t>无极棍</t>
+  </si>
+  <si>
+    <t>神兽攻击时有概率龙吼，整个队伍的物理伤害提升{0.2}%</t>
+  </si>
+  <si>
+    <t>龙纹剑</t>
+  </si>
+  <si>
+    <t>天师辟邪剑</t>
+  </si>
+  <si>
+    <t>乾坤送灵袋</t>
+  </si>
+  <si>
+    <t>降魔剑术生效时击杀妖魔以后，造成的所有伤害提升{0.2}%</t>
+  </si>
+  <si>
+    <t>降魔剑术生效时，攻击妖魔有{0.2}%的概率使其下一回合无法攻击，对精英和Boss概率减半。</t>
+  </si>
+  <si>
+    <t>死符</t>
+  </si>
+  <si>
+    <t>降魔</t>
+  </si>
+  <si>
+    <t>朱砂腿骨</t>
+  </si>
+  <si>
+    <t>速效毒囊</t>
+  </si>
+  <si>
+    <t>灵魂火符对不死生物的伤害提升{0.2}%</t>
+  </si>
+  <si>
+    <t>斩妖除魔剑</t>
   </si>
 </sst>
 </file>
@@ -3335,7 +3386,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -3344,25 +3395,25 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
@@ -3382,34 +3433,34 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>782</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
@@ -3434,34 +3485,34 @@
         <v>171</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
@@ -5181,16 +5232,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>394</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="F102" s="1">
         <v>999</v>
@@ -5468,7 +5519,7 @@
         <v>401</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
@@ -5488,7 +5539,7 @@
         <v>402</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
@@ -5508,7 +5559,7 @@
         <v>403</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
@@ -5528,10 +5579,10 @@
         <v>404</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
@@ -5551,10 +5602,10 @@
         <v>405</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
@@ -5574,10 +5625,10 @@
         <v>406</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
@@ -5597,7 +5648,7 @@
         <v>407</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
@@ -5617,7 +5668,7 @@
         <v>408</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
@@ -5637,7 +5688,7 @@
         <v>409</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
@@ -5657,10 +5708,10 @@
         <v>410</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
@@ -5680,10 +5731,10 @@
         <v>411</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.35">
@@ -5703,10 +5754,10 @@
         <v>412</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
@@ -5726,7 +5777,7 @@
         <v>413</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.35">
@@ -5746,7 +5797,7 @@
         <v>414</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
@@ -5766,7 +5817,7 @@
         <v>415</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.35">
@@ -5786,10 +5837,10 @@
         <v>416</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.35">
@@ -5809,10 +5860,10 @@
         <v>417</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.35">
@@ -5832,10 +5883,10 @@
         <v>418</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.35">
@@ -5855,7 +5906,7 @@
         <v>419</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.35">
@@ -5875,7 +5926,7 @@
         <v>420</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.35">
@@ -5895,27 +5946,27 @@
         <v>421</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>394</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="F139" s="1">
         <v>422</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.35">
@@ -5949,10 +6000,10 @@
         <v>431</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.35">
@@ -5972,10 +6023,10 @@
         <v>432</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.35">
@@ -5995,10 +6046,10 @@
         <v>433</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.35">
@@ -6018,10 +6069,10 @@
         <v>434</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.35">
@@ -6041,10 +6092,10 @@
         <v>435</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.35">
@@ -6064,10 +6115,10 @@
         <v>436</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.35">
@@ -6087,7 +6138,7 @@
         <v>437</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.35">
@@ -6107,7 +6158,7 @@
         <v>438</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.35">
@@ -6127,7 +6178,7 @@
         <v>439</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.35">
@@ -6147,7 +6198,7 @@
         <v>440</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.35">
@@ -6167,7 +6218,7 @@
         <v>441</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.35">
@@ -6187,7 +6238,7 @@
         <v>442</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.35">
@@ -6207,10 +6258,10 @@
         <v>443</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.35">
@@ -6230,10 +6281,10 @@
         <v>444</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.35">
@@ -6253,10 +6304,10 @@
         <v>445</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.35">
@@ -6276,10 +6327,10 @@
         <v>446</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.35">
@@ -6299,10 +6350,10 @@
         <v>447</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.35">
@@ -6322,10 +6373,10 @@
         <v>448</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.35">
@@ -6345,7 +6396,7 @@
         <v>449</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.35">
@@ -6365,7 +6416,7 @@
         <v>450</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.35">
@@ -6385,7 +6436,7 @@
         <v>451</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.35">
@@ -6405,7 +6456,7 @@
         <v>452</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.35">
@@ -6425,7 +6476,7 @@
         <v>453</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.35">
@@ -6445,7 +6496,7 @@
         <v>454</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.35">
@@ -6465,10 +6516,10 @@
         <v>455</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.35">
@@ -6488,10 +6539,10 @@
         <v>456</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.35">
@@ -6511,10 +6562,10 @@
         <v>457</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.35">
@@ -6534,10 +6585,10 @@
         <v>458</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.35">
@@ -6557,10 +6608,10 @@
         <v>459</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.35">
@@ -6580,10 +6631,10 @@
         <v>460</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="N170" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.35">
@@ -6603,7 +6654,7 @@
         <v>461</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.35">
@@ -6623,7 +6674,7 @@
         <v>462</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.35">
@@ -6643,7 +6694,7 @@
         <v>463</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.35">
@@ -6663,7 +6714,7 @@
         <v>464</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.35">
@@ -6683,7 +6734,7 @@
         <v>465</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.35">
@@ -6703,7 +6754,7 @@
         <v>466</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.35">
@@ -6723,10 +6774,10 @@
         <v>467</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="N177" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.35">
@@ -6746,10 +6797,10 @@
         <v>468</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.35">
@@ -6769,10 +6820,10 @@
         <v>469</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.35">
@@ -6792,10 +6843,10 @@
         <v>470</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.35">
@@ -6815,10 +6866,10 @@
         <v>471</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.35">
@@ -6838,10 +6889,10 @@
         <v>472</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="N182" s="1" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.35">
@@ -6861,7 +6912,7 @@
         <v>473</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.35">
@@ -6881,7 +6932,7 @@
         <v>474</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.35">
@@ -6901,7 +6952,7 @@
         <v>475</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.35">
@@ -6921,7 +6972,7 @@
         <v>476</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.35">
@@ -6941,7 +6992,7 @@
         <v>477</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.35">
@@ -6961,7 +7012,7 @@
         <v>478</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.35">
@@ -6981,10 +7032,10 @@
         <v>479</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.35">
@@ -7004,10 +7055,10 @@
         <v>480</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.35">
@@ -7027,10 +7078,10 @@
         <v>481</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.35">
@@ -7050,10 +7101,10 @@
         <v>482</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.35">
@@ -7073,10 +7124,10 @@
         <v>483</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.35">
@@ -7096,10 +7147,10 @@
         <v>484</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="N194" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
@@ -7119,7 +7170,7 @@
         <v>485</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
@@ -7139,7 +7190,7 @@
         <v>486</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
@@ -7159,7 +7210,7 @@
         <v>487</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
@@ -7179,7 +7230,7 @@
         <v>488</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
@@ -7199,7 +7250,7 @@
         <v>489</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
@@ -7219,7 +7270,7 @@
         <v>490</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.35">
@@ -7239,10 +7290,10 @@
         <v>491</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="N201" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.35">
@@ -7262,10 +7313,10 @@
         <v>492</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="N202" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.35">
@@ -7285,10 +7336,10 @@
         <v>493</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="N203" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.35">
@@ -7308,10 +7359,10 @@
         <v>494</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="N204" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.35">
@@ -7331,10 +7382,10 @@
         <v>495</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="N205" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.35">
@@ -7354,10 +7405,10 @@
         <v>496</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="N206" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
@@ -7377,7 +7428,7 @@
         <v>497</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
@@ -7397,7 +7448,7 @@
         <v>498</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
@@ -7417,7 +7468,7 @@
         <v>499</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.35">
@@ -7437,7 +7488,7 @@
         <v>500</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
@@ -7457,7 +7508,7 @@
         <v>501</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.35">
@@ -7477,7 +7528,7 @@
         <v>502</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
@@ -7841,7 +7892,7 @@
         <v>687</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="C238" s="9" t="s">
         <v>153</v>
@@ -7865,7 +7916,7 @@
         <v>688</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>153</v>
@@ -7889,7 +7940,7 @@
         <v>689</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>153</v>
@@ -7913,7 +7964,7 @@
         <v>690</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>153</v>
@@ -7937,13 +7988,13 @@
         <v>691</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="C242" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="F242" s="9">
         <v>999</v>
@@ -7961,7 +8012,7 @@
         <v>725</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>153</v>
@@ -7985,7 +8036,7 @@
         <v>692</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>153</v>
@@ -8009,7 +8060,7 @@
         <v>728</v>
       </c>
       <c r="B245" s="9" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="C245" s="9" t="s">
         <v>153</v>
@@ -8033,7 +8084,7 @@
         <v>693</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="C246" s="10" t="s">
         <v>153</v>
@@ -8057,13 +8108,13 @@
         <v>694</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="C247" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="F247" s="10">
         <v>999</v>
@@ -8081,7 +8132,7 @@
         <v>695</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="C248" s="10" t="s">
         <v>153</v>
@@ -8105,7 +8156,7 @@
         <v>732</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>153</v>
@@ -8129,13 +8180,13 @@
         <v>696</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="C250" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="F250" s="10">
         <v>999</v>
@@ -8153,13 +8204,13 @@
         <v>697</v>
       </c>
       <c r="B251" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="C251" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E251" s="10" t="s">
         <v>849</v>
-      </c>
-      <c r="C251" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E251" s="10" t="s">
-        <v>856</v>
       </c>
       <c r="F251" s="10">
         <v>999</v>
@@ -8177,13 +8228,13 @@
         <v>734</v>
       </c>
       <c r="B252" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E252" s="10" t="s">
         <v>850</v>
-      </c>
-      <c r="C252" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E252" s="10" t="s">
-        <v>857</v>
       </c>
       <c r="F252" s="10">
         <v>999</v>
@@ -8201,13 +8252,13 @@
         <v>698</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="F253" s="10">
         <v>999</v>
@@ -8225,7 +8276,7 @@
         <v>735</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="C254" s="10" t="s">
         <v>153</v>
@@ -8249,13 +8300,13 @@
         <v>699</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="C255" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E255" s="11" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="F255" s="11">
         <v>999</v>
@@ -8270,16 +8321,16 @@
     </row>
     <row r="256" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A256" s="11" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="C256" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="F256" s="11">
         <v>999</v>
@@ -8294,16 +8345,16 @@
     </row>
     <row r="257" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A257" s="11" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E257" s="11" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="F257" s="11">
         <v>999</v>
@@ -8318,16 +8369,16 @@
     </row>
     <row r="258" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A258" s="11" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E258" s="11" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="F258" s="11">
         <v>999</v>
@@ -8342,16 +8393,16 @@
     </row>
     <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="11" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E259" s="11" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="F259" s="11">
         <v>999</v>
@@ -8366,16 +8417,16 @@
     </row>
     <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A260" s="11" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="F260" s="11">
         <v>999</v>
@@ -8393,19 +8444,19 @@
         <v>700</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E261" s="11" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="F261" s="11">
         <v>999</v>
       </c>
       <c r="J261" s="11" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="O261" s="11" t="b">
         <v>1</v>
@@ -8416,13 +8467,13 @@
         <v>701</v>
       </c>
       <c r="B262" s="11" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="C262" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="F262" s="11">
         <v>999</v>
@@ -8440,13 +8491,13 @@
         <v>702</v>
       </c>
       <c r="B263" s="11" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="C263" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E263" s="11" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="F263" s="11">
         <v>999</v>
@@ -8464,7 +8515,7 @@
         <v>703</v>
       </c>
       <c r="B264" s="11" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="C264" s="11" t="s">
         <v>153</v>
@@ -8480,7 +8531,7 @@
         <v>bfbl</v>
       </c>
       <c r="K264" s="11" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="O264" s="11" t="b">
         <v>1</v>
@@ -8491,13 +8542,13 @@
         <v>738</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="C265" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E265" s="11" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="F265" s="11">
         <v>999</v>
@@ -8507,7 +8558,7 @@
         <v>bfbl</v>
       </c>
       <c r="K265" s="11" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="O265" s="11" t="b">
         <v>1</v>
@@ -8518,13 +8569,13 @@
         <v>704</v>
       </c>
       <c r="B266" s="12" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="C266" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E266" s="12" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="F266" s="12">
         <v>999</v>
@@ -8542,13 +8593,13 @@
         <v>705</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="C267" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E267" s="12" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="F267" s="12">
         <v>999</v>
@@ -8563,16 +8614,16 @@
     </row>
     <row r="268" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="12" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="B268" s="12" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="C268" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E268" s="12" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="F268" s="12">
         <v>999</v>
@@ -8587,13 +8638,13 @@
         <v>706</v>
       </c>
       <c r="B269" s="12" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="C269" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E269" s="12" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="F269" s="12">
         <v>999</v>
@@ -8611,7 +8662,7 @@
         <v>707</v>
       </c>
       <c r="B270" s="12" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="C270" s="12" t="s">
         <v>153</v>
@@ -8635,13 +8686,13 @@
         <v>708</v>
       </c>
       <c r="B271" s="12" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="C271" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E271" s="12" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="F271" s="12">
         <v>999</v>
@@ -8659,7 +8710,7 @@
         <v>740</v>
       </c>
       <c r="B272" s="12" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C272" s="12" t="s">
         <v>153</v>
@@ -8683,7 +8734,7 @@
         <v>709</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>709</v>
+        <v>909</v>
       </c>
       <c r="C273" s="6" t="s">
         <v>153</v>
@@ -8707,7 +8758,7 @@
         <v>742</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>742</v>
+        <v>910</v>
       </c>
       <c r="C274" s="6" t="s">
         <v>153</v>
@@ -8731,13 +8782,13 @@
         <v>710</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>710</v>
+        <v>914</v>
       </c>
       <c r="C275" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>745</v>
+        <v>911</v>
       </c>
       <c r="F275" s="6">
         <v>999</v>
@@ -8755,13 +8806,13 @@
         <v>711</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>711</v>
+        <v>915</v>
       </c>
       <c r="C276" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F276" s="6">
         <v>999</v>
@@ -8779,13 +8830,13 @@
         <v>712</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>712</v>
+        <v>916</v>
       </c>
       <c r="C277" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F277" s="6">
         <v>999</v>
@@ -8803,13 +8854,13 @@
         <v>713</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>713</v>
+        <v>917</v>
       </c>
       <c r="C278" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>748</v>
+        <v>912</v>
       </c>
       <c r="F278" s="6">
         <v>999</v>
@@ -8824,16 +8875,16 @@
     </row>
     <row r="279" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A279" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>749</v>
+        <v>918</v>
       </c>
       <c r="C279" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E279" s="6" t="s">
-        <v>750</v>
+        <v>913</v>
       </c>
       <c r="F279" s="6">
         <v>999</v>
@@ -8851,13 +8902,13 @@
         <v>714</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>714</v>
+        <v>919</v>
       </c>
       <c r="C280" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F280" s="6">
         <v>999</v>
@@ -8872,16 +8923,16 @@
     </row>
     <row r="281" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A281" s="6" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>751</v>
+        <v>922</v>
       </c>
       <c r="C281" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="F281" s="6">
         <v>999</v>
@@ -8899,13 +8950,13 @@
         <v>715</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>715</v>
+        <v>927</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E282" s="4" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="F282" s="4">
         <v>999</v>
@@ -8923,13 +8974,13 @@
         <v>716</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>716</v>
+        <v>929</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E283" s="4" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F283" s="4">
         <v>999</v>
@@ -8947,13 +8998,13 @@
         <v>717</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>717</v>
+        <v>928</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E284" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F284" s="4">
         <v>999</v>
@@ -8963,7 +9014,7 @@
         <v>pskl</v>
       </c>
       <c r="K284" s="4" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="O284" s="4" t="b">
         <v>1</v>
@@ -8974,13 +9025,13 @@
         <v>718</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>718</v>
+        <v>926</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E285" s="4" t="s">
-        <v>757</v>
+        <v>930</v>
       </c>
       <c r="F285" s="4">
         <v>999</v>
@@ -8998,13 +9049,13 @@
         <v>719</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>719</v>
+        <v>931</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E286" s="4" t="s">
-        <v>758</v>
+        <v>924</v>
       </c>
       <c r="F286" s="4">
         <v>999</v>
@@ -9019,16 +9070,16 @@
     </row>
     <row r="287" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>759</v>
+        <v>923</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E287" s="4" t="s">
-        <v>760</v>
+        <v>925</v>
       </c>
       <c r="F287" s="4">
         <v>999</v>
@@ -9046,13 +9097,13 @@
         <v>720</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>720</v>
+        <v>908</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E288" s="4" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="F288" s="4">
         <v>999</v>
@@ -9062,10 +9113,10 @@
         <v>psdm</v>
       </c>
       <c r="K288" s="4" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="O288" s="4" t="b">
         <v>1</v>
@@ -9073,16 +9124,16 @@
     </row>
     <row r="289" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>761</v>
+        <v>921</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E289" s="4" t="s">
-        <v>762</v>
+        <v>920</v>
       </c>
       <c r="F289" s="4">
         <v>999</v>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B678E1-11D3-4BF7-917F-DD76CF30AF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA03E31B-611D-406F-AC2C-18CF874A9E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$290</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="936">
   <si>
     <t>id</t>
   </si>
@@ -2870,6 +2873,18 @@
   </si>
   <si>
     <t>斩妖除魔剑</t>
+  </si>
+  <si>
+    <t>skhwoh</t>
+  </si>
+  <si>
+    <t>圣言术</t>
+  </si>
+  <si>
+    <t>圣言术+{0}</t>
+  </si>
+  <si>
+    <t>hwoh</t>
   </si>
 </sst>
 </file>
@@ -2905,7 +2920,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2966,6 +2981,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2979,7 +3000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2993,6 +3014,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3354,7 +3376,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:O289"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:O290"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" style="1" customWidth="1"/>
@@ -3515,7 +3538,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>393</v>
       </c>
@@ -3532,7 +3555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>394</v>
       </c>
@@ -3549,7 +3572,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>395</v>
       </c>
@@ -3566,7 +3589,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>396</v>
       </c>
@@ -3583,7 +3606,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3600,7 +3623,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3617,7 +3640,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3640,7 +3663,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3663,7 +3686,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3680,7 +3703,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3697,7 +3720,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3720,7 +3743,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
@@ -3743,7 +3766,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3760,7 +3783,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -3777,7 +3800,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -3794,7 +3817,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -3811,7 +3834,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>409</v>
       </c>
@@ -3828,7 +3851,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>663</v>
       </c>
@@ -3845,7 +3868,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>664</v>
       </c>
@@ -3862,7 +3885,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>279</v>
       </c>
@@ -3879,7 +3902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>280</v>
       </c>
@@ -3896,7 +3919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>281</v>
       </c>
@@ -3913,7 +3936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>282</v>
       </c>
@@ -3930,7 +3953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>283</v>
       </c>
@@ -3947,7 +3970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>445</v>
       </c>
@@ -3964,7 +3987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>446</v>
       </c>
@@ -3981,7 +4004,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>447</v>
       </c>
@@ -3998,7 +4021,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>448</v>
       </c>
@@ -4015,7 +4038,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>449</v>
       </c>
@@ -4032,7 +4055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>450</v>
       </c>
@@ -4049,7 +4072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>451</v>
       </c>
@@ -4066,7 +4089,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>452</v>
       </c>
@@ -4083,7 +4106,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>453</v>
       </c>
@@ -4100,7 +4123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>454</v>
       </c>
@@ -4117,7 +4140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -4134,7 +4157,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -4151,7 +4174,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -4168,7 +4191,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -4185,7 +4208,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -4202,7 +4225,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -4219,7 +4242,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -4236,7 +4259,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -4253,7 +4276,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -4270,7 +4293,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -4287,7 +4310,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
@@ -4304,7 +4327,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
@@ -4321,7 +4344,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -4338,7 +4361,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
@@ -4355,7 +4378,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
@@ -4372,7 +4395,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>411</v>
       </c>
@@ -4389,7 +4412,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>412</v>
       </c>
@@ -4406,7 +4429,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>413</v>
       </c>
@@ -4423,7 +4446,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -4440,7 +4463,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -4457,7 +4480,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
@@ -4474,7 +4497,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -4491,7 +4514,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -4508,7 +4531,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -4528,7 +4551,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
@@ -4548,7 +4571,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
@@ -4568,7 +4591,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>398</v>
       </c>
@@ -4588,7 +4611,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>399</v>
       </c>
@@ -4608,7 +4631,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>405</v>
       </c>
@@ -4628,7 +4651,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>403</v>
       </c>
@@ -4645,7 +4668,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -4662,7 +4685,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
@@ -4679,7 +4702,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -4696,7 +4719,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -4713,7 +4736,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
@@ -4730,7 +4753,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
@@ -4753,7 +4776,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -4776,7 +4799,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
@@ -4799,7 +4822,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -4822,7 +4845,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
@@ -4845,7 +4868,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>392</v>
       </c>
@@ -4862,7 +4885,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -4879,7 +4902,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
@@ -4896,7 +4919,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
@@ -4913,7 +4936,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
@@ -4930,7 +4953,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>309</v>
       </c>
@@ -4947,7 +4970,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>310</v>
       </c>
@@ -4964,7 +4987,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>311</v>
       </c>
@@ -4981,7 +5004,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>312</v>
       </c>
@@ -4998,7 +5021,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>313</v>
       </c>
@@ -5015,7 +5038,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -5032,7 +5055,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
@@ -5049,7 +5072,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
@@ -5066,7 +5089,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,7 +5106,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -5100,7 +5123,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>419</v>
       </c>
@@ -5117,7 +5140,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>660</v>
       </c>
@@ -5134,7 +5157,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -5151,7 +5174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>472</v>
       </c>
@@ -5168,7 +5191,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>675</v>
       </c>
@@ -5185,7 +5208,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>407</v>
       </c>
@@ -5202,7 +5225,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>380</v>
       </c>
@@ -5216,7 +5239,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>382</v>
       </c>
@@ -5230,7 +5253,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>761</v>
       </c>
@@ -5247,7 +5270,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>46</v>
       </c>
@@ -5264,7 +5287,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>47</v>
       </c>
@@ -5281,7 +5304,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,7 +5321,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>277</v>
       </c>
@@ -5315,7 +5338,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>293</v>
       </c>
@@ -5332,7 +5355,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>294</v>
       </c>
@@ -5349,7 +5372,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>295</v>
       </c>
@@ -5366,7 +5389,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>296</v>
       </c>
@@ -5383,7 +5406,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>72</v>
       </c>
@@ -5400,7 +5423,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>678</v>
       </c>
@@ -5417,7 +5440,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>669</v>
       </c>
@@ -5434,7 +5457,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>672</v>
       </c>
@@ -5451,7 +5474,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>388</v>
       </c>
@@ -5468,7 +5491,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>389</v>
       </c>
@@ -5485,7 +5508,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>443</v>
       </c>
@@ -5502,7 +5525,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>59</v>
       </c>
@@ -5522,7 +5545,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>60</v>
       </c>
@@ -5542,7 +5565,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>61</v>
       </c>
@@ -5562,7 +5585,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>420</v>
       </c>
@@ -5585,7 +5608,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>421</v>
       </c>
@@ -5608,7 +5631,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>654</v>
       </c>
@@ -5631,7 +5654,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>62</v>
       </c>
@@ -5651,7 +5674,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>63</v>
       </c>
@@ -5671,7 +5694,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>64</v>
       </c>
@@ -5691,7 +5714,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>422</v>
       </c>
@@ -5714,7 +5737,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>423</v>
       </c>
@@ -5737,7 +5760,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>655</v>
       </c>
@@ -5760,7 +5783,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>65</v>
       </c>
@@ -5780,7 +5803,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>66</v>
       </c>
@@ -5800,7 +5823,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>67</v>
       </c>
@@ -5820,7 +5843,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>424</v>
       </c>
@@ -5843,7 +5866,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>425</v>
       </c>
@@ -5866,7 +5889,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>657</v>
       </c>
@@ -5889,7 +5912,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>68</v>
       </c>
@@ -5909,7 +5932,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>69</v>
       </c>
@@ -5929,7 +5952,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>70</v>
       </c>
@@ -5949,7 +5972,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>899</v>
       </c>
@@ -5969,7 +5992,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>71</v>
       </c>
@@ -5983,7 +6006,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>79</v>
       </c>
@@ -6006,7 +6029,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>80</v>
       </c>
@@ -6029,7 +6052,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>81</v>
       </c>
@@ -6052,7 +6075,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>82</v>
       </c>
@@ -6075,7 +6098,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>83</v>
       </c>
@@ -6098,7 +6121,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>84</v>
       </c>
@@ -6241,7 +6264,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>91</v>
       </c>
@@ -6264,7 +6287,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>92</v>
       </c>
@@ -6287,7 +6310,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>93</v>
       </c>
@@ -6310,7 +6333,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>94</v>
       </c>
@@ -6333,7 +6356,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>95</v>
       </c>
@@ -6356,7 +6379,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>96</v>
       </c>
@@ -6499,7 +6522,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>103</v>
       </c>
@@ -6522,7 +6545,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>104</v>
       </c>
@@ -6545,7 +6568,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>105</v>
       </c>
@@ -6568,7 +6591,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>106</v>
       </c>
@@ -6591,7 +6614,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>107</v>
       </c>
@@ -6614,7 +6637,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>108</v>
       </c>
@@ -6757,7 +6780,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>115</v>
       </c>
@@ -6780,7 +6803,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>116</v>
       </c>
@@ -6803,7 +6826,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>117</v>
       </c>
@@ -6826,7 +6849,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>118</v>
       </c>
@@ -6849,7 +6872,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>119</v>
       </c>
@@ -6872,7 +6895,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>120</v>
       </c>
@@ -7015,7 +7038,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>127</v>
       </c>
@@ -7038,7 +7061,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>128</v>
       </c>
@@ -7061,7 +7084,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>129</v>
       </c>
@@ -7084,7 +7107,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>130</v>
       </c>
@@ -7107,7 +7130,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>131</v>
       </c>
@@ -7130,7 +7153,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>132</v>
       </c>
@@ -7273,7 +7296,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>139</v>
       </c>
@@ -7296,7 +7319,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>140</v>
       </c>
@@ -7319,7 +7342,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>141</v>
       </c>
@@ -7342,7 +7365,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>142</v>
       </c>
@@ -7365,7 +7388,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>143</v>
       </c>
@@ -7388,7 +7411,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>144</v>
       </c>
@@ -7533,492 +7556,488 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B213" s="13" t="s">
+        <v>933</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="F213" s="1">
+        <v>503</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A214" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="B214" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F213" s="1">
+      <c r="C214" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F214" s="1">
         <v>801</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A214" s="1" t="s">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A215" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="B215" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F214" s="1">
+      <c r="C215" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F215" s="1">
         <v>802</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A215" s="1" t="s">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A216" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="B216" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F215" s="1">
+      <c r="C216" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F216" s="1">
         <v>803</v>
       </c>
-      <c r="I215" s="1" t="b">
+      <c r="I216" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="15" x14ac:dyDescent="0.35">
-      <c r="A216" s="1" t="s">
+    <row r="217" spans="1:10" ht="15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B216" s="7" t="s">
+      <c r="B217" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F216" s="1">
+      <c r="C217" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F217" s="1">
         <v>821</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A217" s="1" t="s">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A218" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="B218" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C217" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F217" s="1">
+      <c r="C218" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F218" s="1">
         <v>822</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A218" s="1" t="s">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A219" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="B219" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F218" s="1">
+      <c r="C219" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F219" s="1">
         <v>823</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A219" s="1" t="s">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A220" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="B220" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F219" s="1">
+      <c r="C220" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F220" s="1">
         <v>824</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="15" x14ac:dyDescent="0.35">
-      <c r="A220" s="1" t="s">
+    <row r="221" spans="1:10" ht="15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A221" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B221" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F220" s="1">
+      <c r="C221" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F221" s="1">
         <v>825</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A221" s="1" t="s">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A222" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="B222" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C221" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F221" s="1">
+      <c r="C222" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F222" s="1">
         <v>826</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A222" s="1" t="s">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A223" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="B223" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F222" s="1">
+      <c r="C223" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F223" s="1">
         <v>827</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A223" s="1" t="s">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="B224" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F223" s="1">
+      <c r="C224" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F224" s="1">
         <v>828</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="15" x14ac:dyDescent="0.35">
-      <c r="A224" s="1" t="s">
+    <row r="225" spans="1:15" ht="15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A225" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B225" s="7" t="s">
         <v>686</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F224" s="1">
+      <c r="C225" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F225" s="1">
         <v>829</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A225" s="1" t="s">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A226" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="B226" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F225" s="1">
+      <c r="C226" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F226" s="1">
         <v>830</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A226" s="1" t="s">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A227" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B226" s="1" t="s">
+      <c r="B227" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C226" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F226" s="1">
+      <c r="C227" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F227" s="1">
         <v>831</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A227" s="1" t="s">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A228" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B227" s="1" t="s">
+      <c r="B228" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C227" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F227" s="1">
+      <c r="C228" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F228" s="1">
         <v>832</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A228" s="1" t="s">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B228" s="1" t="s">
+      <c r="B229" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C228" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F228" s="1">
+      <c r="C229" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F229" s="1">
         <v>833</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A229" s="1" t="s">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A230" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B229" s="1" t="s">
+      <c r="B230" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F229" s="1">
+      <c r="C230" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F230" s="1">
         <v>834</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A230" s="1" t="s">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A231" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="B231" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F230" s="1">
+      <c r="C231" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F231" s="1">
         <v>835</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A231" s="1" t="s">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A232" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="B232" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C231" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F231" s="1">
+      <c r="C232" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F232" s="1">
         <v>836</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A232" s="1" t="s">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A233" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="B233" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F232" s="1">
+      <c r="C233" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F233" s="1">
         <v>837</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A233" s="1" t="s">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A234" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="B234" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C233" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F233" s="1">
+      <c r="C234" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F234" s="1">
         <v>838</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A234" s="1" t="s">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A235" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="B235" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F234" s="1">
+      <c r="C235" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F235" s="1">
         <v>839</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A235" s="1" t="s">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A236" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="B236" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F235" s="1">
+      <c r="C236" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F236" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A236" s="1" t="s">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A237" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="B237" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C236" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F236" s="1">
+      <c r="C237" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F237" s="1">
         <v>841</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A237" s="1" t="s">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A238" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="B238" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E237" s="1" t="s">
+      <c r="C238" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E238" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="F237" s="1">
+      <c r="F238" s="1">
         <v>999</v>
       </c>
     </row>
-    <row r="238" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="9" t="s">
+    <row r="239" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A239" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="B238" s="9" t="s">
+      <c r="B239" s="9" t="s">
         <v>832</v>
       </c>
-      <c r="C238" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E238" s="9" t="s">
+      <c r="C239" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E239" s="9" t="s">
         <v>721</v>
-      </c>
-      <c r="F238" s="9">
-        <v>999</v>
-      </c>
-      <c r="J238" s="9" t="str">
-        <f>MID(A238,3,4)</f>
-        <v>fblt</v>
-      </c>
-      <c r="O238" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="B239" s="9" t="s">
-        <v>833</v>
-      </c>
-      <c r="C239" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E239" s="9" t="s">
-        <v>722</v>
       </c>
       <c r="F239" s="9">
         <v>999</v>
       </c>
       <c r="J239" s="9" t="str">
-        <f t="shared" ref="J239:J289" si="0">MID(A239,3,4)</f>
-        <v>frng</v>
+        <f>MID(A239,3,4)</f>
+        <v>fblt</v>
       </c>
       <c r="O239" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F240" s="9">
         <v>999</v>
       </c>
       <c r="J240" s="9" t="str">
+        <f t="shared" ref="J240:J290" si="0">MID(A240,3,4)</f>
+        <v>frng</v>
+      </c>
+      <c r="O240" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A241" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="F241" s="9">
+        <v>999</v>
+      </c>
+      <c r="J241" s="9" t="str">
         <f t="shared" si="0"/>
         <v>finf</v>
       </c>
-      <c r="O240" s="9" t="b">
+      <c r="O241" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="9" t="s">
+    <row r="242" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A242" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="B241" s="9" t="s">
+      <c r="B242" s="9" t="s">
         <v>839</v>
       </c>
-      <c r="C241" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E241" s="9" t="s">
+      <c r="C242" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E242" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="F241" s="9">
+      <c r="F242" s="9">
         <v>999</v>
       </c>
-      <c r="J241" s="9" t="str">
+      <c r="J242" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fbal</v>
       </c>
-      <c r="O241" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="B242" s="9" t="s">
-        <v>840</v>
-      </c>
-      <c r="C242" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E242" s="9" t="s">
-        <v>853</v>
-      </c>
-      <c r="F242" s="9">
-        <v>999</v>
-      </c>
-      <c r="J242" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>fbls</v>
-      </c>
       <c r="O242" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
-        <v>725</v>
+        <v>691</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>726</v>
+        <v>853</v>
       </c>
       <c r="F243" s="9">
         <v>999</v>
@@ -8031,42 +8050,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
-        <v>692</v>
+        <v>725</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E244" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F244" s="9">
         <v>999</v>
       </c>
       <c r="J244" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>fwal</v>
+        <v>fbls</v>
       </c>
       <c r="O244" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="9" t="s">
-        <v>728</v>
+        <v>692</v>
       </c>
       <c r="B245" s="9" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C245" s="9" t="s">
         <v>153</v>
       </c>
       <c r="E245" s="9" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F245" s="9">
         <v>999</v>
@@ -8079,90 +8098,90 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="10" t="s">
+    <row r="246" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E246" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="F246" s="9">
+        <v>999</v>
+      </c>
+      <c r="J246" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>fwal</v>
+      </c>
+      <c r="O246" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="B246" s="10" t="s">
+      <c r="B247" s="10" t="s">
         <v>835</v>
       </c>
-      <c r="C246" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E246" s="10" t="s">
+      <c r="C247" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E247" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="F246" s="10">
+      <c r="F247" s="10">
         <v>999</v>
       </c>
-      <c r="J246" s="10" t="str">
+      <c r="J247" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tchm</v>
       </c>
-      <c r="O246" s="10" t="b">
+      <c r="O247" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="10" t="s">
+    <row r="248" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="B247" s="10" t="s">
+      <c r="B248" s="10" t="s">
         <v>836</v>
       </c>
-      <c r="C247" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E247" s="10" t="s">
+      <c r="C248" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E248" s="10" t="s">
         <v>852</v>
       </c>
-      <c r="F247" s="10">
+      <c r="F248" s="10">
         <v>999</v>
       </c>
-      <c r="J247" s="10" t="str">
+      <c r="J248" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tblt</v>
       </c>
-      <c r="O247" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="B248" s="10" t="s">
-        <v>837</v>
-      </c>
-      <c r="C248" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E248" s="10" t="s">
-        <v>731</v>
-      </c>
-      <c r="F248" s="10">
-        <v>999</v>
-      </c>
-      <c r="J248" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>tltn</v>
-      </c>
       <c r="O248" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
-        <v>732</v>
+        <v>695</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="F249" s="10">
         <v>999</v>
@@ -8175,66 +8194,66 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
-        <v>696</v>
+        <v>732</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="C250" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E250" s="10" t="s">
-        <v>851</v>
+        <v>733</v>
       </c>
       <c r="F250" s="10">
         <v>999</v>
       </c>
       <c r="J250" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>tnov</v>
+        <v>tltn</v>
       </c>
       <c r="O250" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C251" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="F251" s="10">
         <v>999</v>
       </c>
       <c r="J251" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>tshd</v>
+        <v>tnov</v>
       </c>
       <c r="O251" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
-        <v>734</v>
+        <v>697</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C252" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E252" s="10" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F252" s="10">
         <v>999</v>
@@ -8247,42 +8266,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
-        <v>698</v>
+        <v>734</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F253" s="10">
         <v>999</v>
       </c>
       <c r="J253" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>tblz</v>
+        <v>tshd</v>
       </c>
       <c r="O253" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="10" t="s">
-        <v>735</v>
+        <v>698</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C254" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E254" s="10" t="s">
-        <v>736</v>
+        <v>848</v>
       </c>
       <c r="F254" s="10">
         <v>999</v>
@@ -8295,42 +8314,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="11" t="s">
+    <row r="255" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A255" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B255" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="C255" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E255" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="F255" s="10">
+        <v>999</v>
+      </c>
+      <c r="J255" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>tblz</v>
+      </c>
+      <c r="O255" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="11" t="s">
         <v>699</v>
       </c>
-      <c r="B255" s="11" t="s">
+      <c r="B256" s="11" t="s">
         <v>855</v>
       </c>
-      <c r="C255" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E255" s="11" t="s">
+      <c r="C256" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E256" s="11" t="s">
         <v>866</v>
-      </c>
-      <c r="F255" s="11">
-        <v>999</v>
-      </c>
-      <c r="J255" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>bbas</v>
-      </c>
-      <c r="O255" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="11" t="s">
-        <v>859</v>
-      </c>
-      <c r="B256" s="11" t="s">
-        <v>881</v>
-      </c>
-      <c r="C256" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E256" s="11" t="s">
-        <v>867</v>
       </c>
       <c r="F256" s="11">
         <v>999</v>
@@ -8343,18 +8362,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E257" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F257" s="11">
         <v>999</v>
@@ -8367,18 +8386,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="11" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E258" s="11" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F258" s="11">
         <v>999</v>
@@ -8391,18 +8410,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="11" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E259" s="11" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F259" s="11">
         <v>999</v>
@@ -8415,18 +8434,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F260" s="11">
         <v>999</v>
@@ -8439,116 +8458,113 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="11" t="s">
-        <v>700</v>
+        <v>863</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>856</v>
+        <v>885</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E261" s="11" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F261" s="11">
         <v>999</v>
       </c>
-      <c r="J261" s="11" t="s">
-        <v>864</v>
+      <c r="J261" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bbas</v>
       </c>
       <c r="O261" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="11" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B262" s="11" t="s">
-        <v>886</v>
+        <v>856</v>
       </c>
       <c r="C262" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="F262" s="11">
         <v>999</v>
       </c>
-      <c r="J262" s="11" t="str">
+      <c r="J262" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="O262" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A263" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="B263" s="11" t="s">
+        <v>886</v>
+      </c>
+      <c r="C263" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E263" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="F263" s="11">
+        <v>999</v>
+      </c>
+      <c r="J263" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bthr</v>
       </c>
-      <c r="O262" s="11" t="b">
+      <c r="O263" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A263" s="11" t="s">
+    <row r="264" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A264" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="B263" s="11" t="s">
+      <c r="B264" s="11" t="s">
         <v>887</v>
       </c>
-      <c r="C263" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E263" s="11" t="s">
+      <c r="C264" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E264" s="11" t="s">
         <v>873</v>
       </c>
-      <c r="F263" s="11">
+      <c r="F264" s="11">
         <v>999</v>
       </c>
-      <c r="J263" s="11" t="str">
+      <c r="J264" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bclv</v>
       </c>
-      <c r="O263" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A264" s="11" t="s">
-        <v>703</v>
-      </c>
-      <c r="B264" s="11" t="s">
-        <v>888</v>
-      </c>
-      <c r="C264" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E264" s="11" t="s">
-        <v>737</v>
-      </c>
-      <c r="F264" s="11">
-        <v>999</v>
-      </c>
-      <c r="J264" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>bfbl</v>
-      </c>
-      <c r="K264" s="11" t="s">
-        <v>858</v>
-      </c>
       <c r="O264" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="11" t="s">
-        <v>738</v>
+        <v>703</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C265" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E265" s="11" t="s">
-        <v>874</v>
+        <v>737</v>
       </c>
       <c r="F265" s="11">
         <v>999</v>
@@ -8558,165 +8574,171 @@
         <v>bfbl</v>
       </c>
       <c r="K265" s="11" t="s">
-        <v>772</v>
+        <v>858</v>
       </c>
       <c r="O265" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="12" t="s">
+    <row r="266" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="11" t="s">
+        <v>738</v>
+      </c>
+      <c r="B266" s="11" t="s">
+        <v>889</v>
+      </c>
+      <c r="C266" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E266" s="11" t="s">
+        <v>874</v>
+      </c>
+      <c r="F266" s="11">
+        <v>999</v>
+      </c>
+      <c r="J266" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bfbl</v>
+      </c>
+      <c r="K266" s="11" t="s">
+        <v>772</v>
+      </c>
+      <c r="O266" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="B266" s="12" t="s">
+      <c r="B267" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="C266" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E266" s="12" t="s">
+      <c r="C267" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E267" s="12" t="s">
         <v>875</v>
       </c>
-      <c r="F266" s="12">
+      <c r="F267" s="12">
         <v>999</v>
       </c>
-      <c r="J266" s="12" t="str">
+      <c r="J267" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xdef</v>
       </c>
-      <c r="O266" s="12" t="b">
+      <c r="O267" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="12" t="s">
+    <row r="268" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="B267" s="12" t="s">
+      <c r="B268" s="12" t="s">
         <v>891</v>
       </c>
-      <c r="C267" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E267" s="12" t="s">
+      <c r="C268" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E268" s="12" t="s">
         <v>876</v>
       </c>
-      <c r="F267" s="12">
+      <c r="F268" s="12">
         <v>999</v>
       </c>
-      <c r="J267" s="12" t="str">
+      <c r="J268" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xdog</v>
       </c>
-      <c r="O267" s="12" t="b">
+      <c r="O268" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="12" t="s">
+    <row r="269" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="12" t="s">
         <v>879</v>
       </c>
-      <c r="B268" s="12" t="s">
+      <c r="B269" s="12" t="s">
         <v>892</v>
       </c>
-      <c r="C268" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E268" s="12" t="s">
+      <c r="C269" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E269" s="12" t="s">
         <v>880</v>
       </c>
-      <c r="F268" s="12">
+      <c r="F269" s="12">
         <v>999</v>
       </c>
-      <c r="J268" s="12" t="str">
+      <c r="J269" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xpos</v>
       </c>
-    </row>
-    <row r="269" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="12" t="s">
+      <c r="O269" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="B269" s="12" t="s">
+      <c r="B270" s="12" t="s">
         <v>857</v>
       </c>
-      <c r="C269" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E269" s="12" t="s">
+      <c r="C270" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E270" s="12" t="s">
         <v>877</v>
       </c>
-      <c r="F269" s="12">
+      <c r="F270" s="12">
         <v>999</v>
       </c>
-      <c r="J269" s="12" t="str">
+      <c r="J270" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xcta</v>
       </c>
-      <c r="O269" s="12" t="b">
+      <c r="O270" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A270" s="12" t="s">
+    <row r="271" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A271" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="B270" s="12" t="s">
+      <c r="B271" s="12" t="s">
         <v>893</v>
       </c>
-      <c r="C270" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E270" s="12" t="s">
+      <c r="C271" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E271" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="F270" s="12">
+      <c r="F271" s="12">
         <v>999</v>
       </c>
-      <c r="J270" s="12" t="str">
+      <c r="J271" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xchg</v>
       </c>
-      <c r="O270" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="271" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A271" s="12" t="s">
-        <v>708</v>
-      </c>
-      <c r="B271" s="12" t="s">
-        <v>894</v>
-      </c>
-      <c r="C271" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E271" s="12" t="s">
-        <v>878</v>
-      </c>
-      <c r="F271" s="12">
-        <v>999</v>
-      </c>
-      <c r="J271" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>xtst</v>
-      </c>
       <c r="O271" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="12" t="s">
-        <v>740</v>
+        <v>708</v>
       </c>
       <c r="B272" s="12" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C272" s="12" t="s">
         <v>153</v>
       </c>
       <c r="E272" s="12" t="s">
-        <v>741</v>
+        <v>878</v>
       </c>
       <c r="F272" s="12">
         <v>999</v>
@@ -8729,42 +8751,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="6" t="s">
+    <row r="273" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="B273" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="C273" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E273" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="F273" s="12">
+        <v>999</v>
+      </c>
+      <c r="J273" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>xtst</v>
+      </c>
+      <c r="O273" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A274" s="6" t="s">
         <v>709</v>
       </c>
-      <c r="B273" s="6" t="s">
+      <c r="B274" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="C273" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E273" s="6" t="s">
+      <c r="C274" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E274" s="6" t="s">
         <v>743</v>
-      </c>
-      <c r="F273" s="6">
-        <v>999</v>
-      </c>
-      <c r="J273" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>hhel</v>
-      </c>
-      <c r="O273" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A274" s="6" t="s">
-        <v>742</v>
-      </c>
-      <c r="B274" s="6" t="s">
-        <v>910</v>
-      </c>
-      <c r="C274" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E274" s="6" t="s">
-        <v>744</v>
       </c>
       <c r="F274" s="6">
         <v>999</v>
@@ -8777,114 +8799,114 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="6" t="s">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C275" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>911</v>
+        <v>744</v>
       </c>
       <c r="F275" s="6">
         <v>999</v>
       </c>
       <c r="J275" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>hgsd</v>
+        <v>hhel</v>
       </c>
       <c r="O275" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C276" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>745</v>
+        <v>911</v>
       </c>
       <c r="F276" s="6">
         <v>999</v>
       </c>
       <c r="J276" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>hinv</v>
+        <v>hgsd</v>
       </c>
       <c r="O276" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C277" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F277" s="6">
         <v>999</v>
       </c>
       <c r="J277" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>hhsd</v>
+        <v>hinv</v>
       </c>
       <c r="O277" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C278" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>912</v>
+        <v>746</v>
       </c>
       <c r="F278" s="6">
         <v>999</v>
       </c>
       <c r="J278" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>hlok</v>
+        <v>hhsd</v>
       </c>
       <c r="O278" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="6" t="s">
-        <v>747</v>
+        <v>713</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C279" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E279" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F279" s="6">
         <v>999</v>
@@ -8897,42 +8919,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="6" t="s">
-        <v>714</v>
+        <v>747</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C280" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>749</v>
+        <v>913</v>
       </c>
       <c r="F280" s="6">
         <v>999</v>
       </c>
       <c r="J280" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>hmhl</v>
+        <v>hlok</v>
       </c>
       <c r="O280" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="6" t="s">
-        <v>748</v>
+        <v>714</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C281" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F281" s="6">
         <v>999</v>
@@ -8945,141 +8967,141 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="4" t="s">
+    <row r="282" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A282" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="F282" s="6">
+        <v>999</v>
+      </c>
+      <c r="J282" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>hmhl</v>
+      </c>
+      <c r="O282" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A283" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="B282" s="4" t="s">
+      <c r="B283" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="C282" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E282" s="4" t="s">
+      <c r="C283" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E283" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="F282" s="4">
+      <c r="F283" s="4">
         <v>999</v>
       </c>
-      <c r="J282" s="4" t="str">
+      <c r="J283" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pbas</v>
       </c>
-      <c r="O282" s="4" t="b">
+      <c r="O283" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A283" s="4" t="s">
+    <row r="284" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A284" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="B283" s="4" t="s">
+      <c r="B284" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="C283" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E283" s="4" t="s">
+      <c r="C284" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E284" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="F283" s="4">
+      <c r="F284" s="4">
         <v>999</v>
       </c>
-      <c r="J283" s="4" t="str">
+      <c r="J284" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ppoi</v>
       </c>
-      <c r="O283" s="4" t="b">
+      <c r="O284" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A284" s="4" t="s">
+    <row r="285" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A285" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="B284" s="4" t="s">
+      <c r="B285" s="4" t="s">
         <v>928</v>
       </c>
-      <c r="C284" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E284" s="4" t="s">
+      <c r="C285" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E285" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="F284" s="4">
+      <c r="F285" s="4">
         <v>999</v>
       </c>
-      <c r="J284" s="4" t="str">
+      <c r="J285" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pskl</v>
       </c>
-      <c r="K284" s="4" t="s">
+      <c r="K285" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="O284" s="4" t="b">
+      <c r="O285" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A285" s="4" t="s">
+    <row r="286" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A286" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B285" s="4" t="s">
+      <c r="B286" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="C285" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E285" s="4" t="s">
+      <c r="C286" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E286" s="4" t="s">
         <v>930</v>
       </c>
-      <c r="F285" s="4">
+      <c r="F286" s="4">
         <v>999</v>
       </c>
-      <c r="J285" s="4" t="str">
+      <c r="J286" s="4" t="str">
         <f t="shared" si="0"/>
         <v>prun</v>
       </c>
-      <c r="O285" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A286" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="B286" s="4" t="s">
-        <v>931</v>
-      </c>
-      <c r="C286" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E286" s="4" t="s">
-        <v>924</v>
-      </c>
-      <c r="F286" s="4">
-        <v>999</v>
-      </c>
-      <c r="J286" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pcbl</v>
-      </c>
       <c r="O286" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
-        <v>754</v>
+        <v>719</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E287" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F287" s="4">
         <v>999</v>
@@ -9092,48 +9114,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
-        <v>720</v>
+        <v>754</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E288" s="4" t="s">
-        <v>896</v>
+        <v>925</v>
       </c>
       <c r="F288" s="4">
         <v>999</v>
       </c>
       <c r="J288" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>psdm</v>
-      </c>
-      <c r="K288" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="L288" s="4" t="s">
-        <v>813</v>
+        <v>pcbl</v>
       </c>
       <c r="O288" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
-        <v>755</v>
+        <v>720</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>153</v>
       </c>
       <c r="E289" s="4" t="s">
-        <v>920</v>
+        <v>896</v>
       </c>
       <c r="F289" s="4">
         <v>999</v>
@@ -9142,16 +9158,59 @@
         <f t="shared" si="0"/>
         <v>psdm</v>
       </c>
+      <c r="K289" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="L289" s="4" t="s">
+        <v>813</v>
+      </c>
       <c r="O289" s="4" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="290" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A290" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E290" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="F290" s="4">
+        <v>999</v>
+      </c>
+      <c r="J290" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>psdm</v>
+      </c>
+      <c r="O290" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:O290" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
+    <filterColumn colId="9">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="13">
+      <filters blank="1"/>
+    </filterColumn>
+    <filterColumn colId="14">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B268">
+  <conditionalFormatting sqref="B269">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA03E31B-611D-406F-AC2C-18CF874A9E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7830C8DD-2752-43B4-831F-14DA46EF2BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="7880" yWindow="3340" windowWidth="28800" windowHeight="15370" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$293</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="954">
   <si>
     <t>id</t>
   </si>
@@ -516,9 +516,6 @@
   </si>
   <si>
     <t>elite</t>
-  </si>
-  <si>
-    <t>maxhp,mhex</t>
   </si>
   <si>
     <t>maxmp,mpex</t>
@@ -1346,9 +1343,6 @@
     <t>(d) =&gt; (d.setStat("rthp", {value:Math.min(d.getStat("rtmaxhp").value, d.getStat("rthp").value)}))</t>
   </si>
   <si>
-    <t>(d) =&gt; (d.setStat("rtmaxhp", {value:Math.floor(d.getStat("maxhp").value * (1 + d.getStat("mhex").value / 100))}))</t>
-  </si>
-  <si>
     <t>(d) =&gt; (d.setStat("rtmp", {value:Math.min(d.getStat("rtmaxmp").value, d.getStat("rtmp").value)}))</t>
   </si>
   <si>
@@ -2885,6 +2879,66 @@
   </si>
   <si>
     <t>hwoh</t>
+  </si>
+  <si>
+    <t>expmax</t>
+  </si>
+  <si>
+    <t>最大经验值</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>atpts</t>
+  </si>
+  <si>
+    <t>(d) =&gt; (d.setStat("rtmaxhp", {value:Math.floor(d.getStat("maxhp").value * (1 + d.getStat("mhex").value / 100)+d.getStat("vit").value*10)}))</t>
+  </si>
+  <si>
+    <t>maxhp,mhex,vit</t>
+  </si>
+  <si>
+    <t>未分配属性点数</t>
+  </si>
+  <si>
+    <t>未分配属性点数：{0}</t>
+  </si>
+  <si>
+    <t>重型套装：{0}</t>
+  </si>
+  <si>
+    <t>战神套装：{0}</t>
+  </si>
+  <si>
+    <t>天魔套装：{0}</t>
+  </si>
+  <si>
+    <t>圣战套装：{0}</t>
+  </si>
+  <si>
+    <t>灵魂套装：{0}</t>
+  </si>
+  <si>
+    <t>幽灵套装：{0}</t>
+  </si>
+  <si>
+    <t>天尊套装：{0}</t>
+  </si>
+  <si>
+    <t>天师套装：{0}</t>
+  </si>
+  <si>
+    <t>魔法套装：{0}</t>
+  </si>
+  <si>
+    <t>恶魔套装：{0}</t>
+  </si>
+  <si>
+    <t>法神套装：{0}</t>
   </si>
 </sst>
 </file>
@@ -3376,8 +3430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O290"/>
+  <dimension ref="A1:O293"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" style="1" customWidth="1"/>
@@ -3409,7 +3462,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -3418,30 +3471,30 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -3456,225 +3509,225 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>771</v>
-      </c>
       <c r="L4" s="8" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F5" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F6" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F7" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>397</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F8" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F9" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F10" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F11" s="1">
         <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>159</v>
+        <v>940</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F12" s="1">
         <v>44</v>
@@ -3683,78 +3736,78 @@
         <v>8</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F13" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F14" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F15" s="1">
         <v>53</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F16" s="1">
         <v>54</v>
@@ -3763,780 +3816,780 @@
         <v>12</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F17" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F18" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F19" s="1">
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F20" s="1">
         <v>322</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F21" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>667</v>
       </c>
       <c r="F22" s="1">
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>668</v>
       </c>
       <c r="F23" s="1">
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F26" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F27" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F28" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F29" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F30" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F31" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F32" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F33" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F34" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F35" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F36" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F37" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F38" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F39" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F40" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F41" s="1">
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F42" s="1">
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F43" s="1">
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F44" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F45" s="1">
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F46" s="1">
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F47" s="1">
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F48" s="1">
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F49" s="1">
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F50" s="1">
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F51" s="1">
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F52" s="1">
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F53" s="1">
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F54" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F55" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F56" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F57" s="1">
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F58" s="1">
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F59" s="1">
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F60" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F61" s="1">
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>153</v>
@@ -4545,18 +4598,18 @@
         <v>157</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F62" s="1">
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>153</v>
@@ -4565,18 +4618,18 @@
         <v>157</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F63" s="1">
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>153</v>
@@ -4585,694 +4638,694 @@
         <v>158</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F64" s="1">
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F65" s="1">
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F66" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F67" s="1">
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F68" s="1">
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F69" s="1">
         <v>241</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F70" s="1">
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F71" s="1">
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F72" s="1">
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F73" s="1">
         <v>245</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F74" s="1">
         <v>251</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F75" s="1">
         <v>252</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F76" s="1">
         <v>253</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F77" s="1">
         <v>254</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F78" s="1">
         <v>255</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F79" s="1">
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F80" s="1">
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F81" s="1">
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F82" s="1">
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F83" s="1">
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F84" s="1">
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F85" s="1">
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F86" s="1">
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F87" s="1">
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F88" s="1">
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F89" s="1">
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F90" s="1">
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F91" s="1">
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F92" s="1">
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F93" s="1">
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F94" s="1">
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>662</v>
       </c>
       <c r="F95" s="1">
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>17</v>
+        <v>470</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>180</v>
+        <v>471</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E96" s="1" t="s">
+        <v>472</v>
+      </c>
       <c r="F96" s="1">
-        <v>288</v>
-      </c>
-      <c r="I96" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>473</v>
+        <v>673</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>674</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>474</v>
+        <v>675</v>
       </c>
       <c r="F97" s="1">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>675</v>
+        <v>406</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>676</v>
+        <v>407</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>677</v>
+        <v>562</v>
       </c>
       <c r="F98" s="1">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>407</v>
+        <v>379</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>564</v>
+        <v>393</v>
       </c>
       <c r="F99" s="1">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F100" s="1">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>382</v>
+        <v>759</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>383</v>
+        <v>760</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>761</v>
       </c>
       <c r="F101" s="1">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>762</v>
+        <v>46</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>394</v>
+        <v>153</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>763</v>
+        <v>504</v>
       </c>
       <c r="F102" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>209</v>
@@ -5281,64 +5334,64 @@
         <v>153</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F103" s="1">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="F104" s="1">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>48</v>
+        <v>276</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F105" s="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="F105" s="1">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="F106" s="1">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>293</v>
       </c>
@@ -5349,13 +5402,13 @@
         <v>153</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F107" s="1">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>294</v>
       </c>
@@ -5366,13 +5419,13 @@
         <v>153</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F108" s="1">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>295</v>
       </c>
@@ -5383,98 +5436,98 @@
         <v>153</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F109" s="1">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>292</v>
+        <v>72</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>505</v>
+        <v>561</v>
       </c>
       <c r="F110" s="1">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>72</v>
+        <v>676</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>238</v>
+        <v>677</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>563</v>
+        <v>678</v>
       </c>
       <c r="F111" s="1">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>153</v>
+        <v>393</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="F112" s="1">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>394</v>
+        <v>153</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F113" s="1">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>672</v>
+        <v>387</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>673</v>
+        <v>389</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>153</v>
+        <v>425</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>674</v>
+        <v>648</v>
       </c>
       <c r="F114" s="1">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>388</v>
       </c>
@@ -5482,110 +5535,116 @@
         <v>390</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E115" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="F115" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A116" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="F115" s="1">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="F116" s="1">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>444</v>
+        <v>59</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>652</v>
+        <v>543</v>
       </c>
       <c r="F117" s="1">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>401</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>225</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F118" s="1">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>226</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="F119" s="1">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>61</v>
+        <v>419</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F120" s="1">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>811</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>420</v>
       </c>
@@ -5593,128 +5652,128 @@
         <v>225</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F121" s="1">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M121" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="N121" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="N121" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>421</v>
+        <v>652</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>226</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>556</v>
+        <v>651</v>
       </c>
       <c r="F122" s="1">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>814</v>
+        <v>901</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>654</v>
+        <v>62</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>227</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>653</v>
+        <v>545</v>
       </c>
       <c r="F123" s="1">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="N123" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>228</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F124" s="1">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>229</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="F125" s="1">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>64</v>
+        <v>421</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F126" s="1">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>814</v>
+      </c>
+      <c r="N126" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>422</v>
       </c>
@@ -5722,128 +5781,128 @@
         <v>228</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F127" s="1">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M127" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="N127" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="N127" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>229</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>559</v>
+        <v>654</v>
       </c>
       <c r="F128" s="1">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>817</v>
+        <v>902</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>230</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>656</v>
+        <v>547</v>
       </c>
       <c r="F129" s="1">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="N129" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>231</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F130" s="1">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>232</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F131" s="1">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>67</v>
+        <v>423</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="F132" s="1">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>817</v>
+      </c>
+      <c r="N132" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>424</v>
       </c>
@@ -5851,2577 +5910,2553 @@
         <v>231</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F133" s="1">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M133" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="N133" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="N133" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>425</v>
+        <v>655</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>232</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>562</v>
+        <v>656</v>
       </c>
       <c r="F134" s="1">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>820</v>
+        <v>903</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>657</v>
+        <v>68</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>233</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>658</v>
+        <v>550</v>
       </c>
       <c r="F135" s="1">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="N135" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>234</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F136" s="1">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>235</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F137" s="1">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>70</v>
+        <v>897</v>
       </c>
       <c r="B138" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="F138" s="1">
+        <v>422</v>
+      </c>
+      <c r="M138" s="1" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A139" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="F138" s="1">
-        <v>421</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>900</v>
-      </c>
       <c r="C139" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>901</v>
+        <v>155</v>
       </c>
       <c r="F139" s="1">
-        <v>422</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>237</v>
+        <v>79</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>155</v>
+        <v>393</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>576</v>
       </c>
       <c r="F140" s="1">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="N140" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F141" s="1">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>322</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F142" s="1">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>323</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F143" s="1">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F144" s="1">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>325</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E145" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="F145" s="1">
+        <v>436</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="N145" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="F145" s="1">
-        <v>435</v>
-      </c>
-      <c r="J145" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="N145" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>583</v>
-      </c>
       <c r="F146" s="1">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="N146" s="1" t="s">
-        <v>815</v>
+        <v>774</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>241</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F147" s="1">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>242</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F148" s="1">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>243</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F149" s="1">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>244</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F150" s="1">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>245</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F151" s="1">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F152" s="1">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>808</v>
+      </c>
+      <c r="N152" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>297</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F153" s="1">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>298</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F154" s="1">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>299</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F155" s="1">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>300</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F156" s="1">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>301</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E157" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="F157" s="1">
+        <v>448</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="N157" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="F157" s="1">
-        <v>447</v>
-      </c>
-      <c r="J157" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="N157" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>595</v>
-      </c>
       <c r="F158" s="1">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="N158" s="1" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>247</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F159" s="1">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>810</v>
+        <v>780</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F160" s="1">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>249</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F161" s="1">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>250</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F162" s="1">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>251</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F163" s="1">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F164" s="1">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+      <c r="N164" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>303</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F165" s="1">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>304</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F166" s="1">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>305</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F167" s="1">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>306</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F168" s="1">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>307</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E169" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="F169" s="1">
+        <v>460</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="N169" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A170" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="F169" s="1">
-        <v>459</v>
-      </c>
-      <c r="J169" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="N169" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="F170" s="1">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="N170" s="1" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>253</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F171" s="1">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>254</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F172" s="1">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>255</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F173" s="1">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>256</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F174" s="1">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>257</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F175" s="1">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>258</v>
+        <v>326</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F176" s="1">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>791</v>
+      </c>
+      <c r="N176" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>327</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F177" s="1">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="N177" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F178" s="1">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>329</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F179" s="1">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>330</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F180" s="1">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>331</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E181" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="F181" s="1">
+        <v>472</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="N181" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A182" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="F181" s="1">
-        <v>471</v>
-      </c>
-      <c r="J181" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="N181" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>619</v>
-      </c>
       <c r="F182" s="1">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="N182" s="1" t="s">
-        <v>818</v>
+        <v>791</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>259</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F183" s="1">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>260</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F184" s="1">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>261</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F185" s="1">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>262</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F186" s="1">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>263</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F187" s="1">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F188" s="1">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>797</v>
+      </c>
+      <c r="N188" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>333</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F189" s="1">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>334</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F190" s="1">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>335</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F191" s="1">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>336</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F192" s="1">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>337</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F193" s="1">
+        <v>484</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="N193" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A194" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="F193" s="1">
-        <v>483</v>
-      </c>
-      <c r="J193" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="N193" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="F194" s="1">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="N194" s="1" t="s">
-        <v>821</v>
+        <v>797</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>265</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F195" s="1">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>266</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F196" s="1">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>267</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F197" s="1">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>268</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F198" s="1">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>269</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F199" s="1">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>270</v>
+        <v>338</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F200" s="1">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>803</v>
+      </c>
+      <c r="N200" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>339</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F201" s="1">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N201" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>340</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F202" s="1">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
       <c r="N202" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>341</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F203" s="1">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="N203" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>342</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F204" s="1">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="N204" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>343</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E205" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F205" s="1">
+        <v>496</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="N205" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A206" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="F205" s="1">
-        <v>495</v>
-      </c>
-      <c r="J205" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="N205" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="F206" s="1">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="N206" s="1" t="s">
-        <v>821</v>
+        <v>803</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>271</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F207" s="1">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>272</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F208" s="1">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>273</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F209" s="1">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>274</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F210" s="1">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>275</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F211" s="1">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>276</v>
+        <v>930</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>931</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>649</v>
+        <v>932</v>
       </c>
       <c r="F212" s="1">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>809</v>
+        <v>933</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="B213" s="13" t="s">
-        <v>933</v>
+        <v>383</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E213" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F213" s="1">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A214" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F214" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A215" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F215" s="1">
+        <v>288</v>
+      </c>
+      <c r="I215" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A216" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="F213" s="1">
-        <v>503</v>
-      </c>
-      <c r="J213" s="1" t="s">
+      <c r="B216" s="2" t="s">
         <v>935</v>
       </c>
-    </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A214" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F214" s="1">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A215" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F215" s="1">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="C216" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F216" s="1">
-        <v>803</v>
+        <v>289</v>
       </c>
       <c r="I216" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F217" s="1">
+        <v>289</v>
+      </c>
+      <c r="I217" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A218" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F218" s="1">
+        <v>803</v>
+      </c>
+      <c r="I218" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A219" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="F219" s="1">
+        <v>804</v>
+      </c>
+      <c r="I219" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="A220" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F220" s="1">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A221" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F221" s="1">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A222" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F222" s="1">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A223" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F223" s="1">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B217" s="7" t="s">
+      <c r="B224" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="C217" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F217" s="1">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F218" s="1">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F219" s="1">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B220" s="1" t="s">
+      <c r="C224" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F224" s="1">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A225" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F220" s="1">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" ht="15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="1" t="s">
+      <c r="B225" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F225" s="1">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A226" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F226" s="1">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A227" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F227" s="1">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A228" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B221" s="7" t="s">
+      <c r="B228" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="C221" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F221" s="1">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F222" s="1">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F223" s="1">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B224" s="1" t="s">
+      <c r="C228" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F228" s="1">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A229" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F224" s="1">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="225" spans="1:15" ht="15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="1" t="s">
+      <c r="B229" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F229" s="1">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A230" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F230" s="1">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A231" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F231" s="1">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A232" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F232" s="1">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A233" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F233" s="1">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A234" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F234" s="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A235" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F235" s="1">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A236" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F236" s="1">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A237" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F237" s="1">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A238" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F238" s="1">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A239" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F239" s="1">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A240" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F240" s="1">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A241" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F241" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A242" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B242" s="9" t="s">
+        <v>830</v>
+      </c>
+      <c r="C242" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E242" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="F242" s="9">
+        <v>999</v>
+      </c>
+      <c r="J242" s="9" t="str">
+        <f>MID(A242,3,4)</f>
+        <v>fblt</v>
+      </c>
+      <c r="O242" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A243" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F225" s="1">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F226" s="1">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F227" s="1">
+      <c r="B243" s="9" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F228" s="1">
+      <c r="C243" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="F243" s="9">
+        <v>999</v>
+      </c>
+      <c r="J243" s="9" t="str">
+        <f t="shared" ref="J243:J293" si="0">MID(A243,3,4)</f>
+        <v>frng</v>
+      </c>
+      <c r="O243" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B244" s="9" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C229" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F229" s="1">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A230" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F230" s="1">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F231" s="1">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F232" s="1">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F233" s="1">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F234" s="1">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A235" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F235" s="1">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F236" s="1">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F237" s="1">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E238" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="F238" s="1">
+      <c r="C244" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E244" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="F244" s="9">
         <v>999</v>
       </c>
-    </row>
-    <row r="239" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="B239" s="9" t="s">
-        <v>832</v>
-      </c>
-      <c r="C239" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E239" s="9" t="s">
-        <v>721</v>
-      </c>
-      <c r="F239" s="9">
-        <v>999</v>
-      </c>
-      <c r="J239" s="9" t="str">
-        <f>MID(A239,3,4)</f>
-        <v>fblt</v>
-      </c>
-      <c r="O239" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="240" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>833</v>
-      </c>
-      <c r="C240" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E240" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="F240" s="9">
-        <v>999</v>
-      </c>
-      <c r="J240" s="9" t="str">
-        <f t="shared" ref="J240:J290" si="0">MID(A240,3,4)</f>
-        <v>frng</v>
-      </c>
-      <c r="O240" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>834</v>
-      </c>
-      <c r="C241" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E241" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="F241" s="9">
-        <v>999</v>
-      </c>
-      <c r="J241" s="9" t="str">
+      <c r="J244" s="9" t="str">
         <f t="shared" si="0"/>
         <v>finf</v>
       </c>
-      <c r="O241" s="9" t="b">
+      <c r="O244" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="B242" s="9" t="s">
-        <v>839</v>
-      </c>
-      <c r="C242" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E242" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="F242" s="9">
+    <row r="245" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="F245" s="9">
         <v>999</v>
       </c>
-      <c r="J242" s="9" t="str">
+      <c r="J245" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fbal</v>
       </c>
-      <c r="O242" s="9" t="b">
+      <c r="O245" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A243" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="B243" s="9" t="s">
-        <v>840</v>
-      </c>
-      <c r="C243" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E243" s="9" t="s">
-        <v>853</v>
-      </c>
-      <c r="F243" s="9">
+    <row r="246" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E246" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="F246" s="9">
         <v>999</v>
       </c>
-      <c r="J243" s="9" t="str">
+      <c r="J246" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fbls</v>
       </c>
-      <c r="O243" s="9" t="b">
+      <c r="O246" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="9" t="s">
-        <v>725</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>841</v>
-      </c>
-      <c r="C244" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E244" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="F244" s="9">
+    <row r="247" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="F247" s="9">
         <v>999</v>
       </c>
-      <c r="J244" s="9" t="str">
+      <c r="J247" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fbls</v>
       </c>
-      <c r="O244" s="9" t="b">
+      <c r="O247" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="B245" s="9" t="s">
-        <v>846</v>
-      </c>
-      <c r="C245" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E245" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="F245" s="9">
+    <row r="248" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B248" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="C248" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E248" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="F248" s="9">
         <v>999</v>
       </c>
-      <c r="J245" s="9" t="str">
+      <c r="J248" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fwal</v>
       </c>
-      <c r="O245" s="9" t="b">
+      <c r="O248" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="B246" s="9" t="s">
-        <v>847</v>
-      </c>
-      <c r="C246" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E246" s="9" t="s">
-        <v>729</v>
-      </c>
-      <c r="F246" s="9">
+    <row r="249" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A249" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E249" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="F249" s="9">
         <v>999</v>
       </c>
-      <c r="J246" s="9" t="str">
+      <c r="J249" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fwal</v>
       </c>
-      <c r="O246" s="9" t="b">
+      <c r="O249" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="10" t="s">
-        <v>693</v>
-      </c>
-      <c r="B247" s="10" t="s">
-        <v>835</v>
-      </c>
-      <c r="C247" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E247" s="10" t="s">
-        <v>730</v>
-      </c>
-      <c r="F247" s="10">
+    <row r="250" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A250" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="C250" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E250" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="F250" s="10">
         <v>999</v>
       </c>
-      <c r="J247" s="10" t="str">
+      <c r="J250" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tchm</v>
       </c>
-      <c r="O247" s="10" t="b">
+      <c r="O250" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="10" t="s">
-        <v>694</v>
-      </c>
-      <c r="B248" s="10" t="s">
-        <v>836</v>
-      </c>
-      <c r="C248" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E248" s="10" t="s">
-        <v>852</v>
-      </c>
-      <c r="F248" s="10">
+    <row r="251" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A251" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="B251" s="10" t="s">
+        <v>834</v>
+      </c>
+      <c r="C251" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E251" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="F251" s="10">
         <v>999</v>
       </c>
-      <c r="J248" s="10" t="str">
+      <c r="J251" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tblt</v>
       </c>
-      <c r="O248" s="10" t="b">
+      <c r="O251" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="B249" s="10" t="s">
-        <v>837</v>
-      </c>
-      <c r="C249" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E249" s="10" t="s">
-        <v>731</v>
-      </c>
-      <c r="F249" s="10">
+    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A252" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E252" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="F252" s="10">
         <v>999</v>
       </c>
-      <c r="J249" s="10" t="str">
+      <c r="J252" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tltn</v>
       </c>
-      <c r="O249" s="10" t="b">
+      <c r="O252" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="10" t="s">
-        <v>732</v>
-      </c>
-      <c r="B250" s="10" t="s">
-        <v>838</v>
-      </c>
-      <c r="C250" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E250" s="10" t="s">
-        <v>733</v>
-      </c>
-      <c r="F250" s="10">
+    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A253" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>836</v>
+      </c>
+      <c r="C253" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E253" s="10" t="s">
+        <v>731</v>
+      </c>
+      <c r="F253" s="10">
         <v>999</v>
       </c>
-      <c r="J250" s="10" t="str">
+      <c r="J253" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tltn</v>
       </c>
-      <c r="O250" s="10" t="b">
+      <c r="O253" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="B251" s="10" t="s">
-        <v>854</v>
-      </c>
-      <c r="C251" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E251" s="10" t="s">
-        <v>851</v>
-      </c>
-      <c r="F251" s="10">
+    <row r="254" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A254" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>849</v>
+      </c>
+      <c r="F254" s="10">
         <v>999</v>
       </c>
-      <c r="J251" s="10" t="str">
+      <c r="J254" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tnov</v>
       </c>
-      <c r="O251" s="10" t="b">
+      <c r="O254" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A252" s="10" t="s">
-        <v>697</v>
-      </c>
-      <c r="B252" s="10" t="s">
-        <v>842</v>
-      </c>
-      <c r="C252" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E252" s="10" t="s">
-        <v>849</v>
-      </c>
-      <c r="F252" s="10">
+    <row r="255" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A255" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="B255" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C255" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E255" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="F255" s="10">
         <v>999</v>
       </c>
-      <c r="J252" s="10" t="str">
+      <c r="J255" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tshd</v>
       </c>
-      <c r="O252" s="10" t="b">
+      <c r="O255" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="10" t="s">
-        <v>734</v>
-      </c>
-      <c r="B253" s="10" t="s">
-        <v>843</v>
-      </c>
-      <c r="C253" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E253" s="10" t="s">
-        <v>850</v>
-      </c>
-      <c r="F253" s="10">
+    <row r="256" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>841</v>
+      </c>
+      <c r="C256" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>848</v>
+      </c>
+      <c r="F256" s="10">
         <v>999</v>
       </c>
-      <c r="J253" s="10" t="str">
+      <c r="J256" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tshd</v>
       </c>
-      <c r="O253" s="10" t="b">
+      <c r="O256" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="10" t="s">
-        <v>698</v>
-      </c>
-      <c r="B254" s="10" t="s">
-        <v>844</v>
-      </c>
-      <c r="C254" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E254" s="10" t="s">
-        <v>848</v>
-      </c>
-      <c r="F254" s="10">
+    <row r="257" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A257" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="B257" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="C257" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E257" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="F257" s="10">
         <v>999</v>
       </c>
-      <c r="J254" s="10" t="str">
+      <c r="J257" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tblz</v>
       </c>
-      <c r="O254" s="10" t="b">
+      <c r="O257" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:15" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="10" t="s">
-        <v>735</v>
-      </c>
-      <c r="B255" s="10" t="s">
-        <v>845</v>
-      </c>
-      <c r="C255" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E255" s="10" t="s">
-        <v>736</v>
-      </c>
-      <c r="F255" s="10">
+    <row r="258" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A258" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="F258" s="10">
         <v>999</v>
       </c>
-      <c r="J255" s="10" t="str">
+      <c r="J258" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tblz</v>
       </c>
-      <c r="O255" s="10" t="b">
+      <c r="O258" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="11" t="s">
-        <v>699</v>
-      </c>
-      <c r="B256" s="11" t="s">
-        <v>855</v>
-      </c>
-      <c r="C256" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E256" s="11" t="s">
-        <v>866</v>
-      </c>
-      <c r="F256" s="11">
-        <v>999</v>
-      </c>
-      <c r="J256" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>bbas</v>
-      </c>
-      <c r="O256" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A257" s="11" t="s">
-        <v>859</v>
-      </c>
-      <c r="B257" s="11" t="s">
-        <v>881</v>
-      </c>
-      <c r="C257" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E257" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="F257" s="11">
-        <v>999</v>
-      </c>
-      <c r="J257" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>bbas</v>
-      </c>
-      <c r="O257" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="11" t="s">
-        <v>860</v>
-      </c>
-      <c r="B258" s="11" t="s">
-        <v>882</v>
-      </c>
-      <c r="C258" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E258" s="11" t="s">
-        <v>868</v>
-      </c>
-      <c r="F258" s="11">
-        <v>999</v>
-      </c>
-      <c r="J258" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>bbas</v>
-      </c>
-      <c r="O258" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="11" t="s">
-        <v>861</v>
+        <v>697</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>883</v>
+        <v>853</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E259" s="11" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="F259" s="11">
         <v>999</v>
@@ -8434,18 +8469,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A260" s="11" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F260" s="11">
         <v>999</v>
@@ -8458,18 +8493,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A261" s="11" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E261" s="11" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="F261" s="11">
         <v>999</v>
@@ -8482,735 +8517,795 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A262" s="11" t="s">
-        <v>700</v>
+        <v>859</v>
       </c>
       <c r="B262" s="11" t="s">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="C262" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="F262" s="11">
         <v>999</v>
       </c>
-      <c r="J262" s="11" t="s">
-        <v>864</v>
+      <c r="J262" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bbas</v>
       </c>
       <c r="O262" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A263" s="11" t="s">
-        <v>701</v>
+        <v>860</v>
       </c>
       <c r="B263" s="11" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C263" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E263" s="11" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="F263" s="11">
         <v>999</v>
       </c>
       <c r="J263" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>bthr</v>
+        <v>bbas</v>
       </c>
       <c r="O263" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A264" s="11" t="s">
-        <v>702</v>
+        <v>861</v>
       </c>
       <c r="B264" s="11" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C264" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E264" s="11" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F264" s="11">
         <v>999</v>
       </c>
       <c r="J264" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>bclv</v>
+        <v>bbas</v>
       </c>
       <c r="O264" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A265" s="11" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>888</v>
+        <v>854</v>
       </c>
       <c r="C265" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E265" s="11" t="s">
-        <v>737</v>
+        <v>870</v>
       </c>
       <c r="F265" s="11">
         <v>999</v>
       </c>
-      <c r="J265" s="11" t="str">
+      <c r="J265" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="O265" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="B266" s="11" t="s">
+        <v>884</v>
+      </c>
+      <c r="C266" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E266" s="11" t="s">
+        <v>863</v>
+      </c>
+      <c r="F266" s="11">
+        <v>999</v>
+      </c>
+      <c r="J266" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bthr</v>
+      </c>
+      <c r="O266" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="11" t="s">
+        <v>700</v>
+      </c>
+      <c r="B267" s="11" t="s">
+        <v>885</v>
+      </c>
+      <c r="C267" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E267" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="F267" s="11">
+        <v>999</v>
+      </c>
+      <c r="J267" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bclv</v>
+      </c>
+      <c r="O267" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="B268" s="11" t="s">
+        <v>886</v>
+      </c>
+      <c r="C268" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E268" s="11" t="s">
+        <v>735</v>
+      </c>
+      <c r="F268" s="11">
+        <v>999</v>
+      </c>
+      <c r="J268" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bfbl</v>
       </c>
-      <c r="K265" s="11" t="s">
-        <v>858</v>
-      </c>
-      <c r="O265" s="11" t="b">
+      <c r="K268" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="O268" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:15" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="11" t="s">
-        <v>738</v>
-      </c>
-      <c r="B266" s="11" t="s">
-        <v>889</v>
-      </c>
-      <c r="C266" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E266" s="11" t="s">
-        <v>874</v>
-      </c>
-      <c r="F266" s="11">
+    <row r="269" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="B269" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="C269" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E269" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="F269" s="11">
         <v>999</v>
       </c>
-      <c r="J266" s="11" t="str">
+      <c r="J269" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bfbl</v>
       </c>
-      <c r="K266" s="11" t="s">
-        <v>772</v>
-      </c>
-      <c r="O266" s="11" t="b">
+      <c r="K269" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="O269" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="12" t="s">
-        <v>704</v>
-      </c>
-      <c r="B267" s="12" t="s">
-        <v>890</v>
-      </c>
-      <c r="C267" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E267" s="12" t="s">
-        <v>875</v>
-      </c>
-      <c r="F267" s="12">
+    <row r="270" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="B270" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="C270" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E270" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="F270" s="12">
         <v>999</v>
       </c>
-      <c r="J267" s="12" t="str">
+      <c r="J270" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xdef</v>
       </c>
-      <c r="O267" s="12" t="b">
+      <c r="O270" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="12" t="s">
-        <v>705</v>
-      </c>
-      <c r="B268" s="12" t="s">
-        <v>891</v>
-      </c>
-      <c r="C268" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E268" s="12" t="s">
-        <v>876</v>
-      </c>
-      <c r="F268" s="12">
+    <row r="271" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A271" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="C271" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E271" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="F271" s="12">
         <v>999</v>
       </c>
-      <c r="J268" s="12" t="str">
+      <c r="J271" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xdog</v>
       </c>
-      <c r="O268" s="12" t="b">
+      <c r="O271" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="12" t="s">
-        <v>879</v>
-      </c>
-      <c r="B269" s="12" t="s">
-        <v>892</v>
-      </c>
-      <c r="C269" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E269" s="12" t="s">
-        <v>880</v>
-      </c>
-      <c r="F269" s="12">
+    <row r="272" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>890</v>
+      </c>
+      <c r="C272" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E272" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="F272" s="12">
         <v>999</v>
       </c>
-      <c r="J269" s="12" t="str">
+      <c r="J272" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xpos</v>
       </c>
-      <c r="O269" s="12" t="b">
+      <c r="O272" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A270" s="12" t="s">
-        <v>706</v>
-      </c>
-      <c r="B270" s="12" t="s">
-        <v>857</v>
-      </c>
-      <c r="C270" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E270" s="12" t="s">
-        <v>877</v>
-      </c>
-      <c r="F270" s="12">
+    <row r="273" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="B273" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="C273" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E273" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="F273" s="12">
         <v>999</v>
       </c>
-      <c r="J270" s="12" t="str">
+      <c r="J273" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xcta</v>
       </c>
-      <c r="O270" s="12" t="b">
+      <c r="O273" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A271" s="12" t="s">
-        <v>707</v>
-      </c>
-      <c r="B271" s="12" t="s">
-        <v>893</v>
-      </c>
-      <c r="C271" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E271" s="12" t="s">
-        <v>739</v>
-      </c>
-      <c r="F271" s="12">
+    <row r="274" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A274" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="B274" s="12" t="s">
+        <v>891</v>
+      </c>
+      <c r="C274" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E274" s="12" t="s">
+        <v>737</v>
+      </c>
+      <c r="F274" s="12">
         <v>999</v>
       </c>
-      <c r="J271" s="12" t="str">
+      <c r="J274" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xchg</v>
       </c>
-      <c r="O271" s="12" t="b">
+      <c r="O274" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="12" t="s">
-        <v>708</v>
-      </c>
-      <c r="B272" s="12" t="s">
-        <v>894</v>
-      </c>
-      <c r="C272" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E272" s="12" t="s">
-        <v>878</v>
-      </c>
-      <c r="F272" s="12">
+    <row r="275" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A275" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="B275" s="12" t="s">
+        <v>892</v>
+      </c>
+      <c r="C275" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E275" s="12" t="s">
+        <v>876</v>
+      </c>
+      <c r="F275" s="12">
         <v>999</v>
       </c>
-      <c r="J272" s="12" t="str">
+      <c r="J275" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xtst</v>
       </c>
-      <c r="O272" s="12" t="b">
+      <c r="O275" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="12" t="s">
-        <v>740</v>
-      </c>
-      <c r="B273" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="C273" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E273" s="12" t="s">
-        <v>741</v>
-      </c>
-      <c r="F273" s="12">
+    <row r="276" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A276" s="12" t="s">
+        <v>738</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="C276" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E276" s="12" t="s">
+        <v>739</v>
+      </c>
+      <c r="F276" s="12">
         <v>999</v>
       </c>
-      <c r="J273" s="12" t="str">
+      <c r="J276" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xtst</v>
       </c>
-      <c r="O273" s="12" t="b">
+      <c r="O276" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A274" s="6" t="s">
-        <v>709</v>
-      </c>
-      <c r="B274" s="6" t="s">
-        <v>909</v>
-      </c>
-      <c r="C274" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E274" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="F274" s="6">
+    <row r="277" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A277" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E277" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="F277" s="6">
         <v>999</v>
       </c>
-      <c r="J274" s="6" t="str">
+      <c r="J277" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhel</v>
       </c>
-      <c r="O274" s="6" t="b">
+      <c r="O277" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A275" s="6" t="s">
+    <row r="278" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A278" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E278" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="B275" s="6" t="s">
-        <v>910</v>
-      </c>
-      <c r="C275" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E275" s="6" t="s">
-        <v>744</v>
-      </c>
-      <c r="F275" s="6">
+      <c r="F278" s="6">
         <v>999</v>
       </c>
-      <c r="J275" s="6" t="str">
+      <c r="J278" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhel</v>
       </c>
-      <c r="O275" s="6" t="b">
+      <c r="O278" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A276" s="6" t="s">
-        <v>710</v>
-      </c>
-      <c r="B276" s="6" t="s">
-        <v>914</v>
-      </c>
-      <c r="C276" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E276" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="F276" s="6">
+    <row r="279" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A279" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E279" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="F279" s="6">
         <v>999</v>
       </c>
-      <c r="J276" s="6" t="str">
+      <c r="J279" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hgsd</v>
       </c>
-      <c r="O276" s="6" t="b">
+      <c r="O279" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="6" t="s">
-        <v>711</v>
-      </c>
-      <c r="B277" s="6" t="s">
-        <v>915</v>
-      </c>
-      <c r="C277" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E277" s="6" t="s">
-        <v>745</v>
-      </c>
-      <c r="F277" s="6">
+    <row r="280" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A280" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="F280" s="6">
         <v>999</v>
       </c>
-      <c r="J277" s="6" t="str">
+      <c r="J280" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hinv</v>
       </c>
-      <c r="O277" s="6" t="b">
+      <c r="O280" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="6" t="s">
-        <v>712</v>
-      </c>
-      <c r="B278" s="6" t="s">
-        <v>916</v>
-      </c>
-      <c r="C278" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E278" s="6" t="s">
-        <v>746</v>
-      </c>
-      <c r="F278" s="6">
+    <row r="281" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A281" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E281" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="F281" s="6">
         <v>999</v>
       </c>
-      <c r="J278" s="6" t="str">
+      <c r="J281" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhsd</v>
       </c>
-      <c r="O278" s="6" t="b">
+      <c r="O281" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A279" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="B279" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="C279" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E279" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="F279" s="6">
+    <row r="282" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A282" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="F282" s="6">
         <v>999</v>
       </c>
-      <c r="J279" s="6" t="str">
+      <c r="J282" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hlok</v>
       </c>
-      <c r="O279" s="6" t="b">
+      <c r="O282" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="6" t="s">
-        <v>747</v>
-      </c>
-      <c r="B280" s="6" t="s">
-        <v>918</v>
-      </c>
-      <c r="C280" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E280" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="F280" s="6">
+    <row r="283" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A283" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="F283" s="6">
         <v>999</v>
       </c>
-      <c r="J280" s="6" t="str">
+      <c r="J283" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hlok</v>
       </c>
-      <c r="O280" s="6" t="b">
+      <c r="O283" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="B281" s="6" t="s">
-        <v>919</v>
-      </c>
-      <c r="C281" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E281" s="6" t="s">
-        <v>749</v>
-      </c>
-      <c r="F281" s="6">
+    <row r="284" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A284" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="F284" s="6">
         <v>999</v>
       </c>
-      <c r="J281" s="6" t="str">
+      <c r="J284" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hmhl</v>
       </c>
-      <c r="O281" s="6" t="b">
+      <c r="O284" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:15" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="6" t="s">
+    <row r="285" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A285" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E285" s="6" t="s">
         <v>748</v>
       </c>
-      <c r="B282" s="6" t="s">
-        <v>922</v>
-      </c>
-      <c r="C282" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E282" s="6" t="s">
-        <v>750</v>
-      </c>
-      <c r="F282" s="6">
+      <c r="F285" s="6">
         <v>999</v>
       </c>
-      <c r="J282" s="6" t="str">
+      <c r="J285" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hmhl</v>
       </c>
-      <c r="O282" s="6" t="b">
+      <c r="O285" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A283" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="B283" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E283" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="F283" s="4">
+    <row r="286" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A286" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E286" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="F286" s="4">
         <v>999</v>
       </c>
-      <c r="J283" s="4" t="str">
+      <c r="J286" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pbas</v>
       </c>
-      <c r="O283" s="4" t="b">
+      <c r="O286" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A284" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="B284" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E284" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="F284" s="4">
+    <row r="287" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A287" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E287" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="F287" s="4">
         <v>999</v>
       </c>
-      <c r="J284" s="4" t="str">
+      <c r="J287" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ppoi</v>
       </c>
-      <c r="O284" s="4" t="b">
+      <c r="O287" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A285" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="B285" s="4" t="s">
-        <v>928</v>
-      </c>
-      <c r="C285" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E285" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="F285" s="4">
+    <row r="288" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A288" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E288" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="F288" s="4">
         <v>999</v>
       </c>
-      <c r="J285" s="4" t="str">
+      <c r="J288" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pskl</v>
       </c>
-      <c r="K285" s="4" t="s">
-        <v>773</v>
-      </c>
-      <c r="O285" s="4" t="b">
+      <c r="K288" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="O288" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A286" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="B286" s="4" t="s">
-        <v>926</v>
-      </c>
-      <c r="C286" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E286" s="4" t="s">
-        <v>930</v>
-      </c>
-      <c r="F286" s="4">
+    <row r="289" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A289" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E289" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="F289" s="4">
         <v>999</v>
       </c>
-      <c r="J286" s="4" t="str">
+      <c r="J289" s="4" t="str">
         <f t="shared" si="0"/>
         <v>prun</v>
       </c>
-      <c r="O286" s="4" t="b">
+      <c r="O289" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A287" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="B287" s="4" t="s">
-        <v>931</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E287" s="4" t="s">
-        <v>924</v>
-      </c>
-      <c r="F287" s="4">
+    <row r="290" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A290" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E290" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="F290" s="4">
         <v>999</v>
       </c>
-      <c r="J287" s="4" t="str">
+      <c r="J290" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pcbl</v>
       </c>
-      <c r="O287" s="4" t="b">
+      <c r="O290" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A288" s="4" t="s">
-        <v>754</v>
-      </c>
-      <c r="B288" s="4" t="s">
+    <row r="291" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A291" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E291" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C288" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E288" s="4" t="s">
-        <v>925</v>
-      </c>
-      <c r="F288" s="4">
+      <c r="F291" s="4">
         <v>999</v>
       </c>
-      <c r="J288" s="4" t="str">
+      <c r="J291" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pcbl</v>
       </c>
-      <c r="O288" s="4" t="b">
+      <c r="O291" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A289" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="B289" s="4" t="s">
-        <v>908</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E289" s="4" t="s">
-        <v>896</v>
-      </c>
-      <c r="F289" s="4">
+    <row r="292" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A292" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E292" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="F292" s="4">
         <v>999</v>
       </c>
-      <c r="J289" s="4" t="str">
+      <c r="J292" s="4" t="str">
         <f t="shared" si="0"/>
         <v>psdm</v>
       </c>
-      <c r="K289" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="L289" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="O289" s="4" t="b">
+      <c r="K292" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="L292" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="O292" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:15" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A290" s="4" t="s">
-        <v>755</v>
-      </c>
-      <c r="B290" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="C290" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E290" s="4" t="s">
-        <v>920</v>
-      </c>
-      <c r="F290" s="4">
+    <row r="293" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A293" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E293" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="F293" s="4">
         <v>999</v>
       </c>
-      <c r="J290" s="4" t="str">
+      <c r="J293" s="4" t="str">
         <f t="shared" si="0"/>
         <v>psdm</v>
       </c>
-      <c r="O290" s="4" t="b">
+      <c r="O293" s="4" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O290" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-    <filterColumn colId="9">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="13">
-      <filters blank="1"/>
-    </filterColumn>
-    <filterColumn colId="14">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:O293" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B269">
+  <conditionalFormatting sqref="B272">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7830C8DD-2752-43B4-831F-14DA46EF2BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4457D0D-00B0-48FD-BAE5-48816B1545B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7880" yWindow="3340" windowWidth="28800" windowHeight="15370" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$295</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="951">
   <si>
     <t>id</t>
   </si>
@@ -2908,37 +2908,28 @@
     <t>未分配属性点数：{0}</t>
   </si>
   <si>
-    <t>重型套装：{0}</t>
-  </si>
-  <si>
-    <t>战神套装：{0}</t>
-  </si>
-  <si>
-    <t>天魔套装：{0}</t>
-  </si>
-  <si>
-    <t>圣战套装：{0}</t>
-  </si>
-  <si>
-    <t>灵魂套装：{0}</t>
-  </si>
-  <si>
-    <t>幽灵套装：{0}</t>
-  </si>
-  <si>
-    <t>天尊套装：{0}</t>
-  </si>
-  <si>
-    <t>天师套装：{0}</t>
-  </si>
-  <si>
-    <t>魔法套装：{0}</t>
-  </si>
-  <si>
-    <t>恶魔套装：{0}</t>
-  </si>
-  <si>
-    <t>法神套装：{0}</t>
+    <t>rthploss</t>
+  </si>
+  <si>
+    <t>缺失生命</t>
+  </si>
+  <si>
+    <t>rtmaxhp,rthp</t>
+  </si>
+  <si>
+    <t>(d) =&gt; (d.getStat("rtmaxhp").value - d.getStat("rthp").value)</t>
+  </si>
+  <si>
+    <t>rtmploss</t>
+  </si>
+  <si>
+    <t>缺失魔法</t>
+  </si>
+  <si>
+    <t>rtmaxmp,rtmp</t>
+  </si>
+  <si>
+    <t>(d) =&gt; (d.getStat("rtmaxmp").value - d.getStat("rtmp").value)</t>
   </si>
 </sst>
 </file>
@@ -3430,22 +3421,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:O293"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O295"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="51.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="51.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.54296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3492,7 +3483,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>165</v>
       </c>
@@ -3539,12 +3530,12 @@
         <v>828</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>319</v>
       </c>
@@ -3591,7 +3582,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>392</v>
       </c>
@@ -3608,7 +3599,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>393</v>
       </c>
@@ -3625,7 +3616,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>394</v>
       </c>
@@ -3642,7 +3633,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>395</v>
       </c>
@@ -3659,7 +3650,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3676,7 +3667,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3693,7 +3684,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3716,7 +3707,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3738,44 +3729,53 @@
       <c r="H12" s="1" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="I12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="F14" s="1">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>175</v>
@@ -3784,24 +3784,18 @@
         <v>153</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>657</v>
+        <v>469</v>
       </c>
       <c r="F15" s="1">
-        <v>53</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>153</v>
@@ -3810,1054 +3804,1057 @@
         <v>657</v>
       </c>
       <c r="F16" s="1">
+        <v>53</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F17" s="1">
         <v>54</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+      <c r="I17" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F18" s="1">
+        <v>54</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F19" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F20" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F21" s="1">
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F22" s="1">
         <v>322</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F23" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F24" s="1">
         <v>331</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F25" s="1">
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="F25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F26" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F27" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="F29" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F30" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F31" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F32" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F33" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F34" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F35" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F36" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F37" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F38" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F39" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F40" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="F39" s="1">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="F40" s="1">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F41" s="1">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F42" s="1">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F43" s="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="F44" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F45" s="1">
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F46" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F47" s="1">
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F48" s="1">
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F49" s="1">
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E48" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F50" s="1">
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F51" s="1">
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F52" s="1">
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F53" s="1">
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F54" s="1">
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E53" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F55" s="1">
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F56" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F57" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F58" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F59" s="1">
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F60" s="1">
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F61" s="1">
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F62" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F63" s="1">
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="C64" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F64" s="1">
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F65" s="1">
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F66" s="1">
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F67" s="1">
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D66" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F68" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F69" s="1">
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F70" s="1">
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F71" s="1">
         <v>241</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F72" s="1">
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E71" s="1" t="s">
+      <c r="C73" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F73" s="1">
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E72" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F74" s="1">
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="1" t="s">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F75" s="1">
         <v>245</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="F74" s="1">
-        <v>251</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A75" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="F75" s="1">
-        <v>252</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A76" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>153</v>
@@ -4866,21 +4863,21 @@
         <v>657</v>
       </c>
       <c r="F76" s="1">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>153</v>
@@ -4889,21 +4886,21 @@
         <v>657</v>
       </c>
       <c r="F77" s="1">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>153</v>
@@ -4912,3599 +4909,3597 @@
         <v>657</v>
       </c>
       <c r="F78" s="1">
+        <v>253</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F79" s="1">
+        <v>254</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F80" s="1">
         <v>255</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F81" s="1">
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E80" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F82" s="1">
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F83" s="1">
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E82" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F84" s="1">
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="1" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E83" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F85" s="1">
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="1" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F86" s="1">
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="1" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E85" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F87" s="1">
         <v>272</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E86" s="1" t="s">
+      <c r="C88" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F88" s="1">
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F89" s="1">
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="C90" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F90" s="1">
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="1" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E89" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F91" s="1">
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="1" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E90" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F92" s="1">
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="1" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E91" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F93" s="1">
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="1" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E92" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F94" s="1">
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="1" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E93" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F95" s="1">
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="1" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B96" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E94" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F96" s="1">
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B97" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E95" s="1" t="s">
+      <c r="C97" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F97" s="1">
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="1" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B98" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E96" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F98" s="1">
         <v>289</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="1" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E97" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F99" s="1">
         <v>290</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="1" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E98" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F100" s="1">
         <v>291</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="1" t="s">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F99" s="1">
+      <c r="C101" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F101" s="1">
         <v>292</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="1" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F100" s="1">
+      <c r="C102" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F102" s="1">
         <v>293</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="1" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E101" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F103" s="1">
         <v>999</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="1" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B104" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F104" s="1">
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="1" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B105" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E103" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F105" s="1">
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="1" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B106" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="C106" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F106" s="1">
         <v>303</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="1" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B107" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E105" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F107" s="1">
         <v>304</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B108" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E106" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F108" s="1">
         <v>305</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="1" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B109" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E107" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F109" s="1">
         <v>306</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="1" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B110" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E108" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F110" s="1">
         <v>307</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="1" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B111" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E109" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F111" s="1">
         <v>308</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E110" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F112" s="1">
         <v>309</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="1" t="s">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E111" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F113" s="1">
         <v>310</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="1" t="s">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F114" s="1">
         <v>311</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A113" s="1" t="s">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="C115" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F115" s="1">
         <v>312</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A114" s="1" t="s">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="F114" s="1">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A115" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="F115" s="1">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A116" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>425</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="F116" s="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="F117" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F118" s="1">
         <v>315</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A117" s="1" t="s">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="B119" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E117" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F119" s="1">
         <v>401</v>
       </c>
-      <c r="M117" s="1" t="s">
+      <c r="M119" s="1" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A118" s="1" t="s">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B120" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E118" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F120" s="1">
         <v>402</v>
       </c>
-      <c r="M118" s="1" t="s">
+      <c r="M120" s="1" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A119" s="1" t="s">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B121" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E119" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F121" s="1">
         <v>403</v>
       </c>
-      <c r="M119" s="1" t="s">
+      <c r="M121" s="1" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A120" s="1" t="s">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B122" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E120" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F122" s="1">
         <v>404</v>
       </c>
-      <c r="M120" s="1" t="s">
+      <c r="M122" s="1" t="s">
         <v>811</v>
-      </c>
-      <c r="N120" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A121" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="F121" s="1">
-        <v>405</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A122" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="F122" s="1">
-        <v>406</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>901</v>
       </c>
       <c r="N122" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="F123" s="1">
+        <v>405</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="F124" s="1">
+        <v>406</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B125" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E123" s="1" t="s">
+      <c r="C125" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F125" s="1">
         <v>407</v>
       </c>
-      <c r="M123" s="1" t="s">
+      <c r="M125" s="1" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A124" s="1" t="s">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B126" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E124" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F126" s="1">
         <v>408</v>
       </c>
-      <c r="M124" s="1" t="s">
+      <c r="M126" s="1" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A125" s="1" t="s">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B127" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E125" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F127" s="1">
         <v>409</v>
       </c>
-      <c r="M125" s="1" t="s">
+      <c r="M127" s="1" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A126" s="1" t="s">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B128" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F128" s="1">
         <v>410</v>
       </c>
-      <c r="M126" s="1" t="s">
+      <c r="M128" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="N126" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A127" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="F127" s="1">
-        <v>411</v>
-      </c>
-      <c r="M127" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="N127" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A128" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="F128" s="1">
-        <v>412</v>
-      </c>
-      <c r="M128" s="1" t="s">
-        <v>902</v>
       </c>
       <c r="N128" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="F129" s="1">
+        <v>411</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="F130" s="1">
+        <v>412</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="N130" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B131" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E129" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F131" s="1">
         <v>413</v>
       </c>
-      <c r="M129" s="1" t="s">
+      <c r="M131" s="1" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A130" s="1" t="s">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="B132" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E130" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F132" s="1">
         <v>414</v>
       </c>
-      <c r="M130" s="1" t="s">
+      <c r="M132" s="1" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A131" s="1" t="s">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B133" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E131" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F133" s="1">
         <v>415</v>
       </c>
-      <c r="M131" s="1" t="s">
+      <c r="M133" s="1" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A132" s="1" t="s">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="B134" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E132" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F134" s="1">
         <v>416</v>
       </c>
-      <c r="M132" s="1" t="s">
+      <c r="M134" s="1" t="s">
         <v>817</v>
-      </c>
-      <c r="N132" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A133" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F133" s="1">
-        <v>417</v>
-      </c>
-      <c r="M133" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="N133" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A134" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="F134" s="1">
-        <v>418</v>
-      </c>
-      <c r="M134" s="1" t="s">
-        <v>903</v>
       </c>
       <c r="N134" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="F135" s="1">
+        <v>417</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="N135" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="F136" s="1">
+        <v>418</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B135" s="5" t="s">
+      <c r="B137" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E135" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F137" s="1">
         <v>419</v>
       </c>
-      <c r="M135" s="1" t="s">
+      <c r="M137" s="1" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A136" s="1" t="s">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B136" s="5" t="s">
+      <c r="B138" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E136" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F138" s="1">
         <v>420</v>
       </c>
-      <c r="M136" s="1" t="s">
+      <c r="M138" s="1" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A137" s="1" t="s">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B139" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F139" s="1">
         <v>421</v>
       </c>
-      <c r="M137" s="1" t="s">
+      <c r="M139" s="1" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A138" s="1" t="s">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="B140" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E138" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F140" s="1">
         <v>422</v>
       </c>
-      <c r="M138" s="1" t="s">
+      <c r="M140" s="1" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A139" s="1" t="s">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C141" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F141" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A140" s="1" t="s">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B142" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F142" s="1">
         <v>431</v>
       </c>
-      <c r="J140" s="1" t="s">
+      <c r="J142" s="1" t="s">
         <v>774</v>
-      </c>
-      <c r="N140" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A141" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="F141" s="1">
-        <v>432</v>
-      </c>
-      <c r="J141" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="N141" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A142" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="F142" s="1">
-        <v>433</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>776</v>
       </c>
       <c r="N142" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F143" s="1">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="N143" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F144" s="1">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="N144" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F145" s="1">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="N145" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="F146" s="1">
+        <v>435</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="N146" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="F147" s="1">
+        <v>436</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="N147" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B148" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E146" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F148" s="1">
         <v>437</v>
       </c>
-      <c r="J146" s="1" t="s">
+      <c r="J148" s="1" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A147" s="1" t="s">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B149" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E147" s="1" t="s">
+      <c r="C149" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F149" s="1">
         <v>438</v>
       </c>
-      <c r="J147" s="1" t="s">
+      <c r="J149" s="1" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A148" s="1" t="s">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B150" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E148" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F150" s="1">
         <v>439</v>
       </c>
-      <c r="J148" s="1" t="s">
+      <c r="J150" s="1" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A149" s="1" t="s">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B149" s="6" t="s">
+      <c r="B151" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E149" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F151" s="1">
         <v>440</v>
       </c>
-      <c r="J149" s="1" t="s">
+      <c r="J151" s="1" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A150" s="1" t="s">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B150" s="6" t="s">
+      <c r="B152" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E150" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F152" s="1">
         <v>441</v>
       </c>
-      <c r="J150" s="1" t="s">
+      <c r="J152" s="1" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A151" s="1" t="s">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B151" s="6" t="s">
+      <c r="B153" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E151" s="1" t="s">
+      <c r="C153" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F153" s="1">
         <v>442</v>
       </c>
-      <c r="J151" s="1" t="s">
+      <c r="J153" s="1" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A152" s="1" t="s">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B154" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E152" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F154" s="1">
         <v>443</v>
       </c>
-      <c r="J152" s="1" t="s">
+      <c r="J154" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="N152" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A153" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="F153" s="1">
-        <v>444</v>
-      </c>
-      <c r="J153" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="N153" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A154" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="F154" s="1">
-        <v>445</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>781</v>
       </c>
       <c r="N154" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F155" s="1">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="N155" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F156" s="1">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="N156" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F157" s="1">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="N157" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="F158" s="1">
+        <v>447</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="N158" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="F159" s="1">
+        <v>448</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="N159" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="B160" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E158" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F160" s="1">
         <v>449</v>
       </c>
-      <c r="J158" s="1" t="s">
+      <c r="J160" s="1" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A159" s="1" t="s">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B161" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E159" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F161" s="1">
         <v>450</v>
       </c>
-      <c r="J159" s="1" t="s">
+      <c r="J161" s="1" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A160" s="1" t="s">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B162" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E160" s="1" t="s">
+      <c r="C162" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F162" s="1">
         <v>451</v>
       </c>
-      <c r="J160" s="1" t="s">
+      <c r="J162" s="1" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A161" s="1" t="s">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B161" s="6" t="s">
+      <c r="B163" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E161" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F163" s="1">
         <v>452</v>
       </c>
-      <c r="J161" s="1" t="s">
+      <c r="J163" s="1" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A162" s="1" t="s">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="B164" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E162" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F164" s="1">
         <v>453</v>
       </c>
-      <c r="J162" s="1" t="s">
+      <c r="J164" s="1" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A163" s="1" t="s">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B163" s="6" t="s">
+      <c r="B165" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E163" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F165" s="1">
         <v>454</v>
       </c>
-      <c r="J163" s="1" t="s">
+      <c r="J165" s="1" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A164" s="1" t="s">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B164" s="6" t="s">
+      <c r="B166" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E164" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F166" s="1">
         <v>455</v>
       </c>
-      <c r="J164" s="1" t="s">
+      <c r="J166" s="1" t="s">
         <v>785</v>
-      </c>
-      <c r="N164" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A165" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="F165" s="1">
-        <v>456</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="N165" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A166" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="F166" s="1">
-        <v>457</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>787</v>
       </c>
       <c r="N166" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F167" s="1">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="N167" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F168" s="1">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="N168" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F169" s="1">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="N169" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="F170" s="1">
+        <v>459</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="N170" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="F171" s="1">
+        <v>460</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="N171" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B170" s="6" t="s">
+      <c r="B172" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F172" s="1">
         <v>461</v>
       </c>
-      <c r="J170" s="1" t="s">
+      <c r="J172" s="1" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A171" s="1" t="s">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B171" s="6" t="s">
+      <c r="B173" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E171" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F173" s="1">
         <v>462</v>
       </c>
-      <c r="J171" s="1" t="s">
+      <c r="J173" s="1" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A172" s="1" t="s">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B174" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E172" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F174" s="1">
         <v>463</v>
       </c>
-      <c r="J172" s="1" t="s">
+      <c r="J174" s="1" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A173" s="1" t="s">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B175" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E173" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F175" s="1">
         <v>464</v>
       </c>
-      <c r="J173" s="1" t="s">
+      <c r="J175" s="1" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A174" s="1" t="s">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B174" s="6" t="s">
+      <c r="B176" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E174" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F176" s="1">
         <v>465</v>
       </c>
-      <c r="J174" s="1" t="s">
+      <c r="J176" s="1" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A175" s="1" t="s">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B177" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E175" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F177" s="1">
         <v>466</v>
       </c>
-      <c r="J175" s="1" t="s">
+      <c r="J177" s="1" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A176" s="1" t="s">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B176" s="6" t="s">
+      <c r="B178" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E176" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F178" s="1">
         <v>467</v>
       </c>
-      <c r="J176" s="1" t="s">
+      <c r="J178" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="N176" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A177" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="F177" s="1">
-        <v>468</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="N177" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A178" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="F178" s="1">
-        <v>469</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>793</v>
       </c>
       <c r="N178" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F179" s="1">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="N179" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F180" s="1">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="N180" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F181" s="1">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="N181" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="F182" s="1">
+        <v>471</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="N182" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="F183" s="1">
+        <v>472</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="N183" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B182" s="6" t="s">
+      <c r="B184" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F184" s="1">
         <v>473</v>
       </c>
-      <c r="J182" s="1" t="s">
+      <c r="J184" s="1" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A183" s="1" t="s">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B183" s="6" t="s">
+      <c r="B185" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F185" s="1">
         <v>474</v>
       </c>
-      <c r="J183" s="1" t="s">
+      <c r="J185" s="1" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A184" s="1" t="s">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B184" s="6" t="s">
+      <c r="B186" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E184" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F186" s="1">
         <v>475</v>
       </c>
-      <c r="J184" s="1" t="s">
+      <c r="J186" s="1" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A185" s="1" t="s">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B185" s="6" t="s">
+      <c r="B187" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E185" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F187" s="1">
         <v>476</v>
       </c>
-      <c r="J185" s="1" t="s">
+      <c r="J187" s="1" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A186" s="1" t="s">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B186" s="6" t="s">
+      <c r="B188" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E186" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F188" s="1">
         <v>477</v>
       </c>
-      <c r="J186" s="1" t="s">
+      <c r="J188" s="1" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A187" s="1" t="s">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B187" s="6" t="s">
+      <c r="B189" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E187" s="1" t="s">
+      <c r="C189" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F189" s="1">
         <v>478</v>
       </c>
-      <c r="J187" s="1" t="s">
+      <c r="J189" s="1" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A188" s="1" t="s">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B188" s="6" t="s">
+      <c r="B190" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E188" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F190" s="1">
         <v>479</v>
       </c>
-      <c r="J188" s="1" t="s">
+      <c r="J190" s="1" t="s">
         <v>797</v>
-      </c>
-      <c r="N188" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A189" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F189" s="1">
-        <v>480</v>
-      </c>
-      <c r="J189" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="N189" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A190" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="F190" s="1">
-        <v>481</v>
-      </c>
-      <c r="J190" s="1" t="s">
-        <v>799</v>
       </c>
       <c r="N190" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F191" s="1">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="N191" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F192" s="1">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="N192" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F193" s="1">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="N193" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="F194" s="1">
+        <v>483</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="N194" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F195" s="1">
+        <v>484</v>
+      </c>
+      <c r="J195" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="N195" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B194" s="6" t="s">
+      <c r="B196" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E194" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F196" s="1">
         <v>485</v>
       </c>
-      <c r="J194" s="1" t="s">
+      <c r="J196" s="1" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A195" s="1" t="s">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B195" s="6" t="s">
+      <c r="B197" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E195" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F197" s="1">
         <v>486</v>
       </c>
-      <c r="J195" s="1" t="s">
+      <c r="J197" s="1" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A196" s="1" t="s">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B196" s="6" t="s">
+      <c r="B198" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E196" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F198" s="1">
         <v>487</v>
       </c>
-      <c r="J196" s="1" t="s">
+      <c r="J198" s="1" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A197" s="1" t="s">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B197" s="6" t="s">
+      <c r="B199" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E197" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F199" s="1">
         <v>488</v>
       </c>
-      <c r="J197" s="1" t="s">
+      <c r="J199" s="1" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A198" s="1" t="s">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B198" s="6" t="s">
+      <c r="B200" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E198" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F200" s="1">
         <v>489</v>
       </c>
-      <c r="J198" s="1" t="s">
+      <c r="J200" s="1" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A199" s="1" t="s">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B199" s="6" t="s">
+      <c r="B201" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E199" s="1" t="s">
+      <c r="C201" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F201" s="1">
         <v>490</v>
       </c>
-      <c r="J199" s="1" t="s">
+      <c r="J201" s="1" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A200" s="1" t="s">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B200" s="6" t="s">
+      <c r="B202" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E200" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F202" s="1">
         <v>491</v>
       </c>
-      <c r="J200" s="1" t="s">
+      <c r="J202" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="N200" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A201" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="F201" s="1">
-        <v>492</v>
-      </c>
-      <c r="J201" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="N201" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A202" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="F202" s="1">
-        <v>493</v>
-      </c>
-      <c r="J202" s="1" t="s">
-        <v>823</v>
       </c>
       <c r="N202" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F203" s="1">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N203" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F204" s="1">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
       <c r="N204" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F205" s="1">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="N205" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="F206" s="1">
+        <v>495</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="N206" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F207" s="1">
+        <v>496</v>
+      </c>
+      <c r="J207" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="N207" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B206" s="6" t="s">
+      <c r="B208" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E206" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F208" s="1">
         <v>497</v>
       </c>
-      <c r="J206" s="1" t="s">
+      <c r="J208" s="1" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A207" s="1" t="s">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B207" s="6" t="s">
+      <c r="B209" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E207" s="1" t="s">
+      <c r="C209" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F209" s="1">
         <v>498</v>
       </c>
-      <c r="J207" s="1" t="s">
+      <c r="J209" s="1" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A208" s="1" t="s">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B208" s="6" t="s">
+      <c r="B210" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E208" s="1" t="s">
+      <c r="C210" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E210" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F210" s="1">
         <v>499</v>
       </c>
-      <c r="J208" s="1" t="s">
+      <c r="J210" s="1" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A209" s="1" t="s">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B209" s="6" t="s">
+      <c r="B211" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E209" s="1" t="s">
+      <c r="C211" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E211" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F211" s="1">
         <v>500</v>
       </c>
-      <c r="J209" s="1" t="s">
+      <c r="J211" s="1" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A210" s="1" t="s">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B210" s="6" t="s">
+      <c r="B212" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E210" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F212" s="1">
         <v>501</v>
       </c>
-      <c r="J210" s="1" t="s">
+      <c r="J212" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A211" s="1" t="s">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B211" s="6" t="s">
+      <c r="B213" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E211" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E213" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F213" s="1">
         <v>502</v>
       </c>
-      <c r="J211" s="1" t="s">
+      <c r="J213" s="1" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A212" s="1" t="s">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="B212" s="13" t="s">
+      <c r="B214" s="13" t="s">
         <v>931</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E212" s="1" t="s">
+      <c r="C214" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E214" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="F212" s="1">
+      <c r="F214" s="1">
         <v>503</v>
       </c>
-      <c r="J212" s="1" t="s">
+      <c r="J214" s="1" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A213" s="1" t="s">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="B215" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F213" s="1">
+      <c r="C215" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F215" s="1">
         <v>801</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A214" s="1" t="s">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="B216" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F214" s="1">
+      <c r="C216" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F216" s="1">
         <v>802</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A215" s="1" t="s">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B215" s="2" t="s">
+      <c r="B217" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F215" s="1">
+      <c r="C217" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F217" s="1">
         <v>288</v>
-      </c>
-      <c r="I215" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A216" s="1" t="s">
-        <v>934</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F216" s="1">
-        <v>289</v>
-      </c>
-      <c r="I216" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A217" s="1" t="s">
-        <v>936</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F217" s="1">
-        <v>289</v>
       </c>
       <c r="I217" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>427</v>
+        <v>934</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>935</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>393</v>
       </c>
       <c r="F218" s="1">
-        <v>803</v>
+        <v>289</v>
       </c>
       <c r="I218" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E219" s="2" t="s">
-        <v>942</v>
-      </c>
       <c r="F219" s="1">
-        <v>804</v>
+        <v>289</v>
       </c>
       <c r="I219" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F220" s="1">
+        <v>803</v>
+      </c>
+      <c r="I220" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="F221" s="1">
+        <v>804</v>
+      </c>
+      <c r="I221" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B222" s="7" t="s">
         <v>680</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F220" s="1">
+      <c r="C222" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F222" s="1">
         <v>821</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A221" s="1" t="s">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="B223" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C221" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F221" s="1">
+      <c r="C223" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F223" s="1">
         <v>822</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A222" s="1" t="s">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="B224" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F222" s="1">
+      <c r="C224" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F224" s="1">
         <v>823</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A223" s="1" t="s">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="B225" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F223" s="1">
+      <c r="C225" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F225" s="1">
         <v>824</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="15" x14ac:dyDescent="0.35">
-      <c r="A224" s="1" t="s">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B226" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F224" s="1">
+      <c r="C226" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F226" s="1">
         <v>825</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A225" s="1" t="s">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="B227" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F225" s="1">
+      <c r="C227" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F227" s="1">
         <v>826</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A226" s="1" t="s">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B226" s="1" t="s">
+      <c r="B228" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C226" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F226" s="1">
+      <c r="C228" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F228" s="1">
         <v>827</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A227" s="1" t="s">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B227" s="1" t="s">
+      <c r="B229" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C227" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F227" s="1">
+      <c r="C229" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F229" s="1">
         <v>828</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A228" s="1" t="s">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B230" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="C228" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F228" s="1">
+      <c r="C230" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F230" s="1">
         <v>829</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A229" s="1" t="s">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B229" s="1" t="s">
+      <c r="B231" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F229" s="1">
+      <c r="C231" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F231" s="1">
         <v>830</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A230" s="1" t="s">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="B232" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F230" s="1">
+      <c r="C232" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F232" s="1">
         <v>831</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A231" s="1" t="s">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="B233" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C231" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F231" s="1">
+      <c r="C233" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F233" s="1">
         <v>832</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A232" s="1" t="s">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B232" s="1" t="s">
+      <c r="B234" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F232" s="1">
+      <c r="C234" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F234" s="1">
         <v>833</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A233" s="1" t="s">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="B235" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C233" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F233" s="1">
+      <c r="C235" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F235" s="1">
         <v>834</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A234" s="1" t="s">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="B236" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F234" s="1">
+      <c r="C236" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F236" s="1">
         <v>835</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A235" s="1" t="s">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="B237" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F235" s="1">
+      <c r="C237" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F237" s="1">
         <v>836</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A236" s="1" t="s">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="B238" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C236" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F236" s="1">
+      <c r="C238" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F238" s="1">
         <v>837</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A237" s="1" t="s">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="B239" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F237" s="1">
+      <c r="C239" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F239" s="1">
         <v>838</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A238" s="1" t="s">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B238" s="1" t="s">
+      <c r="B240" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C238" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F238" s="1">
+      <c r="C240" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F240" s="1">
         <v>839</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A239" s="1" t="s">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="B241" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F239" s="1">
+      <c r="C241" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F241" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A240" s="1" t="s">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B240" s="1" t="s">
+      <c r="B242" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C240" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F240" s="1">
+      <c r="C242" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F242" s="1">
         <v>841</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A241" s="1" t="s">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B241" s="1" t="s">
+      <c r="B243" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C241" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E241" s="1" t="s">
+      <c r="C243" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E243" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F243" s="1">
         <v>999</v>
       </c>
     </row>
-    <row r="242" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="9" t="s">
+    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="B242" s="9" t="s">
+      <c r="B244" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="C242" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E242" s="9" t="s">
+      <c r="C244" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E244" s="9" t="s">
         <v>719</v>
-      </c>
-      <c r="F242" s="9">
-        <v>999</v>
-      </c>
-      <c r="J242" s="9" t="str">
-        <f>MID(A242,3,4)</f>
-        <v>fblt</v>
-      </c>
-      <c r="O242" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A243" s="9" t="s">
-        <v>686</v>
-      </c>
-      <c r="B243" s="9" t="s">
-        <v>831</v>
-      </c>
-      <c r="C243" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E243" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="F243" s="9">
-        <v>999</v>
-      </c>
-      <c r="J243" s="9" t="str">
-        <f t="shared" ref="J243:J293" si="0">MID(A243,3,4)</f>
-        <v>frng</v>
-      </c>
-      <c r="O243" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>832</v>
-      </c>
-      <c r="C244" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E244" s="9" t="s">
-        <v>721</v>
       </c>
       <c r="F244" s="9">
         <v>999</v>
       </c>
       <c r="J244" s="9" t="str">
+        <f>MID(A244,3,4)</f>
+        <v>fblt</v>
+      </c>
+      <c r="O244" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="F245" s="9">
+        <v>999</v>
+      </c>
+      <c r="J245" s="9" t="str">
+        <f t="shared" ref="J245:J295" si="0">MID(A245,3,4)</f>
+        <v>frng</v>
+      </c>
+      <c r="O245" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E246" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="F246" s="9">
+        <v>999</v>
+      </c>
+      <c r="J246" s="9" t="str">
         <f t="shared" si="0"/>
         <v>finf</v>
       </c>
-      <c r="O244" s="9" t="b">
+      <c r="O246" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="9" t="s">
+    <row r="247" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="B245" s="9" t="s">
+      <c r="B247" s="9" t="s">
         <v>837</v>
       </c>
-      <c r="C245" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E245" s="9" t="s">
+      <c r="C247" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E247" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="F245" s="9">
+      <c r="F247" s="9">
         <v>999</v>
       </c>
-      <c r="J245" s="9" t="str">
+      <c r="J247" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fbal</v>
       </c>
-      <c r="O245" s="9" t="b">
+      <c r="O247" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="9" t="s">
+    <row r="248" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="B246" s="9" t="s">
+      <c r="B248" s="9" t="s">
         <v>838</v>
       </c>
-      <c r="C246" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E246" s="9" t="s">
+      <c r="C248" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E248" s="9" t="s">
         <v>851</v>
       </c>
-      <c r="F246" s="9">
+      <c r="F248" s="9">
         <v>999</v>
       </c>
-      <c r="J246" s="9" t="str">
+      <c r="J248" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fbls</v>
       </c>
-      <c r="O246" s="9" t="b">
+      <c r="O248" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="9" t="s">
+    <row r="249" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="B247" s="9" t="s">
+      <c r="B249" s="9" t="s">
         <v>839</v>
       </c>
-      <c r="C247" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E247" s="9" t="s">
+      <c r="C249" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E249" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="F247" s="9">
+      <c r="F249" s="9">
         <v>999</v>
       </c>
-      <c r="J247" s="9" t="str">
+      <c r="J249" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fbls</v>
       </c>
-      <c r="O247" s="9" t="b">
+      <c r="O249" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="9" t="s">
+    <row r="250" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="B248" s="9" t="s">
+      <c r="B250" s="9" t="s">
         <v>844</v>
       </c>
-      <c r="C248" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E248" s="9" t="s">
+      <c r="C250" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E250" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="F248" s="9">
+      <c r="F250" s="9">
         <v>999</v>
       </c>
-      <c r="J248" s="9" t="str">
+      <c r="J250" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fwal</v>
       </c>
-      <c r="O248" s="9" t="b">
+      <c r="O250" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="9" t="s">
+    <row r="251" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="B249" s="9" t="s">
+      <c r="B251" s="9" t="s">
         <v>845</v>
       </c>
-      <c r="C249" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E249" s="9" t="s">
+      <c r="C251" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E251" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="F249" s="9">
+      <c r="F251" s="9">
         <v>999</v>
       </c>
-      <c r="J249" s="9" t="str">
+      <c r="J251" s="9" t="str">
         <f t="shared" si="0"/>
         <v>fwal</v>
       </c>
-      <c r="O249" s="9" t="b">
+      <c r="O251" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="10" t="s">
+    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="B250" s="10" t="s">
+      <c r="B252" s="10" t="s">
         <v>833</v>
       </c>
-      <c r="C250" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E250" s="10" t="s">
+      <c r="C252" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E252" s="10" t="s">
         <v>728</v>
       </c>
-      <c r="F250" s="10">
+      <c r="F252" s="10">
         <v>999</v>
       </c>
-      <c r="J250" s="10" t="str">
+      <c r="J252" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tchm</v>
       </c>
-      <c r="O250" s="10" t="b">
+      <c r="O252" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="10" t="s">
+    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="10" t="s">
         <v>692</v>
       </c>
-      <c r="B251" s="10" t="s">
+      <c r="B253" s="10" t="s">
         <v>834</v>
       </c>
-      <c r="C251" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E251" s="10" t="s">
+      <c r="C253" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E253" s="10" t="s">
         <v>850</v>
       </c>
-      <c r="F251" s="10">
+      <c r="F253" s="10">
         <v>999</v>
       </c>
-      <c r="J251" s="10" t="str">
+      <c r="J253" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tblt</v>
       </c>
-      <c r="O251" s="10" t="b">
+      <c r="O253" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A252" s="10" t="s">
+    <row r="254" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="B252" s="10" t="s">
+      <c r="B254" s="10" t="s">
         <v>835</v>
       </c>
-      <c r="C252" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E252" s="10" t="s">
+      <c r="C254" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E254" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="F252" s="10">
+      <c r="F254" s="10">
         <v>999</v>
       </c>
-      <c r="J252" s="10" t="str">
+      <c r="J254" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tltn</v>
       </c>
-      <c r="O252" s="10" t="b">
+      <c r="O254" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="10" t="s">
+    <row r="255" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="B253" s="10" t="s">
+      <c r="B255" s="10" t="s">
         <v>836</v>
       </c>
-      <c r="C253" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E253" s="10" t="s">
+      <c r="C255" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E255" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="F253" s="10">
+      <c r="F255" s="10">
         <v>999</v>
       </c>
-      <c r="J253" s="10" t="str">
+      <c r="J255" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tltn</v>
       </c>
-      <c r="O253" s="10" t="b">
+      <c r="O255" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="10" t="s">
+    <row r="256" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="B254" s="10" t="s">
+      <c r="B256" s="10" t="s">
         <v>852</v>
       </c>
-      <c r="C254" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E254" s="10" t="s">
+      <c r="C256" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E256" s="10" t="s">
         <v>849</v>
       </c>
-      <c r="F254" s="10">
+      <c r="F256" s="10">
         <v>999</v>
       </c>
-      <c r="J254" s="10" t="str">
+      <c r="J256" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tnov</v>
       </c>
-      <c r="O254" s="10" t="b">
+      <c r="O256" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="10" t="s">
+    <row r="257" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="10" t="s">
         <v>695</v>
       </c>
-      <c r="B255" s="10" t="s">
+      <c r="B257" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="C255" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E255" s="10" t="s">
+      <c r="C257" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E257" s="10" t="s">
         <v>847</v>
       </c>
-      <c r="F255" s="10">
+      <c r="F257" s="10">
         <v>999</v>
       </c>
-      <c r="J255" s="10" t="str">
+      <c r="J257" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tshd</v>
       </c>
-      <c r="O255" s="10" t="b">
+      <c r="O257" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="10" t="s">
+    <row r="258" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="10" t="s">
         <v>732</v>
       </c>
-      <c r="B256" s="10" t="s">
+      <c r="B258" s="10" t="s">
         <v>841</v>
       </c>
-      <c r="C256" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E256" s="10" t="s">
+      <c r="C258" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E258" s="10" t="s">
         <v>848</v>
       </c>
-      <c r="F256" s="10">
+      <c r="F258" s="10">
         <v>999</v>
       </c>
-      <c r="J256" s="10" t="str">
+      <c r="J258" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tshd</v>
       </c>
-      <c r="O256" s="10" t="b">
+      <c r="O258" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A257" s="10" t="s">
+    <row r="259" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="B257" s="10" t="s">
+      <c r="B259" s="10" t="s">
         <v>842</v>
       </c>
-      <c r="C257" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E257" s="10" t="s">
+      <c r="C259" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E259" s="10" t="s">
         <v>846</v>
       </c>
-      <c r="F257" s="10">
+      <c r="F259" s="10">
         <v>999</v>
       </c>
-      <c r="J257" s="10" t="str">
+      <c r="J259" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tblz</v>
       </c>
-      <c r="O257" s="10" t="b">
+      <c r="O259" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="10" t="s">
+    <row r="260" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="B258" s="10" t="s">
+      <c r="B260" s="10" t="s">
         <v>843</v>
       </c>
-      <c r="C258" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E258" s="10" t="s">
+      <c r="C260" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E260" s="10" t="s">
         <v>734</v>
       </c>
-      <c r="F258" s="10">
+      <c r="F260" s="10">
         <v>999</v>
       </c>
-      <c r="J258" s="10" t="str">
+      <c r="J260" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tblz</v>
       </c>
-      <c r="O258" s="10" t="b">
+      <c r="O260" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="11" t="s">
+    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="B259" s="11" t="s">
+      <c r="B261" s="11" t="s">
         <v>853</v>
       </c>
-      <c r="C259" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E259" s="11" t="s">
+      <c r="C261" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E261" s="11" t="s">
         <v>864</v>
-      </c>
-      <c r="F259" s="11">
-        <v>999</v>
-      </c>
-      <c r="J259" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>bbas</v>
-      </c>
-      <c r="O259" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A260" s="11" t="s">
-        <v>857</v>
-      </c>
-      <c r="B260" s="11" t="s">
-        <v>879</v>
-      </c>
-      <c r="C260" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E260" s="11" t="s">
-        <v>865</v>
-      </c>
-      <c r="F260" s="11">
-        <v>999</v>
-      </c>
-      <c r="J260" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>bbas</v>
-      </c>
-      <c r="O260" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A261" s="11" t="s">
-        <v>858</v>
-      </c>
-      <c r="B261" s="11" t="s">
-        <v>880</v>
-      </c>
-      <c r="C261" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E261" s="11" t="s">
-        <v>866</v>
       </c>
       <c r="F261" s="11">
         <v>999</v>
@@ -8517,18 +8512,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B262" s="11" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C262" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="F262" s="11">
         <v>999</v>
@@ -8541,18 +8536,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="11" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B263" s="11" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C263" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E263" s="11" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F263" s="11">
         <v>999</v>
@@ -8565,18 +8560,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B264" s="11" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C264" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E264" s="11" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F264" s="11">
         <v>999</v>
@@ -8589,723 +8584,771 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="11" t="s">
-        <v>698</v>
+        <v>860</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>854</v>
+        <v>882</v>
       </c>
       <c r="C265" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E265" s="11" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="F265" s="11">
         <v>999</v>
       </c>
-      <c r="J265" s="11" t="s">
-        <v>862</v>
+      <c r="J265" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bbas</v>
       </c>
       <c r="O265" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
-        <v>699</v>
+        <v>861</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C266" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E266" s="11" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="F266" s="11">
         <v>999</v>
       </c>
       <c r="J266" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>bthr</v>
+        <v>bbas</v>
       </c>
       <c r="O266" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>885</v>
+        <v>854</v>
       </c>
       <c r="C267" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E267" s="11" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F267" s="11">
         <v>999</v>
       </c>
-      <c r="J267" s="11" t="str">
+      <c r="J267" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="O267" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="B268" s="11" t="s">
+        <v>884</v>
+      </c>
+      <c r="C268" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E268" s="11" t="s">
+        <v>863</v>
+      </c>
+      <c r="F268" s="11">
+        <v>999</v>
+      </c>
+      <c r="J268" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>bthr</v>
+      </c>
+      <c r="O268" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="11" t="s">
+        <v>700</v>
+      </c>
+      <c r="B269" s="11" t="s">
+        <v>885</v>
+      </c>
+      <c r="C269" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E269" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="F269" s="11">
+        <v>999</v>
+      </c>
+      <c r="J269" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bclv</v>
       </c>
-      <c r="O267" s="11" t="b">
+      <c r="O269" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="11" t="s">
+    <row r="270" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="B268" s="11" t="s">
+      <c r="B270" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="C268" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E268" s="11" t="s">
+      <c r="C270" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E270" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="F268" s="11">
+      <c r="F270" s="11">
         <v>999</v>
       </c>
-      <c r="J268" s="11" t="str">
+      <c r="J270" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bfbl</v>
       </c>
-      <c r="K268" s="11" t="s">
+      <c r="K270" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="O268" s="11" t="b">
+      <c r="O270" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="11" t="s">
+    <row r="271" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="11" t="s">
         <v>736</v>
       </c>
-      <c r="B269" s="11" t="s">
+      <c r="B271" s="11" t="s">
         <v>887</v>
       </c>
-      <c r="C269" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E269" s="11" t="s">
+      <c r="C271" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E271" s="11" t="s">
         <v>872</v>
       </c>
-      <c r="F269" s="11">
+      <c r="F271" s="11">
         <v>999</v>
       </c>
-      <c r="J269" s="11" t="str">
+      <c r="J271" s="11" t="str">
         <f t="shared" si="0"/>
         <v>bfbl</v>
       </c>
-      <c r="K269" s="11" t="s">
+      <c r="K271" s="11" t="s">
         <v>770</v>
       </c>
-      <c r="O269" s="11" t="b">
+      <c r="O271" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A270" s="12" t="s">
+    <row r="272" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="B270" s="12" t="s">
+      <c r="B272" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="C270" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E270" s="12" t="s">
+      <c r="C272" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E272" s="12" t="s">
         <v>873</v>
       </c>
-      <c r="F270" s="12">
+      <c r="F272" s="12">
         <v>999</v>
       </c>
-      <c r="J270" s="12" t="str">
+      <c r="J272" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xdef</v>
       </c>
-      <c r="O270" s="12" t="b">
+      <c r="O272" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A271" s="12" t="s">
+    <row r="273" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="B271" s="12" t="s">
+      <c r="B273" s="12" t="s">
         <v>889</v>
       </c>
-      <c r="C271" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E271" s="12" t="s">
+      <c r="C273" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E273" s="12" t="s">
         <v>874</v>
       </c>
-      <c r="F271" s="12">
+      <c r="F273" s="12">
         <v>999</v>
       </c>
-      <c r="J271" s="12" t="str">
+      <c r="J273" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xdog</v>
       </c>
-      <c r="O271" s="12" t="b">
+      <c r="O273" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="12" t="s">
+    <row r="274" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="12" t="s">
         <v>877</v>
       </c>
-      <c r="B272" s="12" t="s">
+      <c r="B274" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="C272" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E272" s="12" t="s">
+      <c r="C274" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E274" s="12" t="s">
         <v>878</v>
       </c>
-      <c r="F272" s="12">
+      <c r="F274" s="12">
         <v>999</v>
       </c>
-      <c r="J272" s="12" t="str">
+      <c r="J274" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xpos</v>
       </c>
-      <c r="O272" s="12" t="b">
+      <c r="O274" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="12" t="s">
+    <row r="275" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="B273" s="12" t="s">
+      <c r="B275" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="C273" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E273" s="12" t="s">
+      <c r="C275" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E275" s="12" t="s">
         <v>875</v>
       </c>
-      <c r="F273" s="12">
+      <c r="F275" s="12">
         <v>999</v>
       </c>
-      <c r="J273" s="12" t="str">
+      <c r="J275" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xcta</v>
       </c>
-      <c r="O273" s="12" t="b">
+      <c r="O275" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A274" s="12" t="s">
+    <row r="276" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="B274" s="12" t="s">
+      <c r="B276" s="12" t="s">
         <v>891</v>
       </c>
-      <c r="C274" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E274" s="12" t="s">
+      <c r="C276" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E276" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="F274" s="12">
+      <c r="F276" s="12">
         <v>999</v>
       </c>
-      <c r="J274" s="12" t="str">
+      <c r="J276" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xchg</v>
       </c>
-      <c r="O274" s="12" t="b">
+      <c r="O276" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A275" s="12" t="s">
+    <row r="277" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="B275" s="12" t="s">
+      <c r="B277" s="12" t="s">
         <v>892</v>
       </c>
-      <c r="C275" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E275" s="12" t="s">
+      <c r="C277" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E277" s="12" t="s">
         <v>876</v>
       </c>
-      <c r="F275" s="12">
+      <c r="F277" s="12">
         <v>999</v>
       </c>
-      <c r="J275" s="12" t="str">
+      <c r="J277" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xtst</v>
       </c>
-      <c r="O275" s="12" t="b">
+      <c r="O277" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A276" s="12" t="s">
+    <row r="278" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="B276" s="12" t="s">
+      <c r="B278" s="12" t="s">
         <v>893</v>
       </c>
-      <c r="C276" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E276" s="12" t="s">
+      <c r="C278" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E278" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="F276" s="12">
+      <c r="F278" s="12">
         <v>999</v>
       </c>
-      <c r="J276" s="12" t="str">
+      <c r="J278" s="12" t="str">
         <f t="shared" si="0"/>
         <v>xtst</v>
       </c>
-      <c r="O276" s="12" t="b">
+      <c r="O278" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="6" t="s">
+    <row r="279" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="B277" s="6" t="s">
+      <c r="B279" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="C277" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E277" s="6" t="s">
+      <c r="C279" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E279" s="6" t="s">
         <v>741</v>
       </c>
-      <c r="F277" s="6">
+      <c r="F279" s="6">
         <v>999</v>
       </c>
-      <c r="J277" s="6" t="str">
+      <c r="J279" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhel</v>
       </c>
-      <c r="O277" s="6" t="b">
+      <c r="O279" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="6" t="s">
+    <row r="280" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="B278" s="6" t="s">
+      <c r="B280" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="C278" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E278" s="6" t="s">
+      <c r="C280" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E280" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="F278" s="6">
+      <c r="F280" s="6">
         <v>999</v>
       </c>
-      <c r="J278" s="6" t="str">
+      <c r="J280" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhel</v>
       </c>
-      <c r="O278" s="6" t="b">
+      <c r="O280" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A279" s="6" t="s">
+    <row r="281" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A281" s="6" t="s">
         <v>708</v>
       </c>
-      <c r="B279" s="6" t="s">
+      <c r="B281" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="C279" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E279" s="6" t="s">
+      <c r="C281" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E281" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="F279" s="6">
+      <c r="F281" s="6">
         <v>999</v>
       </c>
-      <c r="J279" s="6" t="str">
+      <c r="J281" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hgsd</v>
       </c>
-      <c r="O279" s="6" t="b">
+      <c r="O281" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="6" t="s">
+    <row r="282" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="6" t="s">
         <v>709</v>
       </c>
-      <c r="B280" s="6" t="s">
+      <c r="B282" s="6" t="s">
         <v>913</v>
       </c>
-      <c r="C280" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E280" s="6" t="s">
+      <c r="C282" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E282" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="F280" s="6">
+      <c r="F282" s="6">
         <v>999</v>
       </c>
-      <c r="J280" s="6" t="str">
+      <c r="J282" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hinv</v>
       </c>
-      <c r="O280" s="6" t="b">
+      <c r="O282" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="6" t="s">
+    <row r="283" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="6" t="s">
         <v>710</v>
       </c>
-      <c r="B281" s="6" t="s">
+      <c r="B283" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="C281" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E281" s="6" t="s">
+      <c r="C283" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E283" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="F281" s="6">
+      <c r="F283" s="6">
         <v>999</v>
       </c>
-      <c r="J281" s="6" t="str">
+      <c r="J283" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hhsd</v>
       </c>
-      <c r="O281" s="6" t="b">
+      <c r="O283" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="6" t="s">
+    <row r="284" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="B282" s="6" t="s">
+      <c r="B284" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="C282" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E282" s="6" t="s">
+      <c r="C284" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E284" s="6" t="s">
         <v>910</v>
       </c>
-      <c r="F282" s="6">
+      <c r="F284" s="6">
         <v>999</v>
       </c>
-      <c r="J282" s="6" t="str">
+      <c r="J284" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hlok</v>
       </c>
-      <c r="O282" s="6" t="b">
+      <c r="O284" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A283" s="6" t="s">
+    <row r="285" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="6" t="s">
         <v>745</v>
       </c>
-      <c r="B283" s="6" t="s">
+      <c r="B285" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="C283" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E283" s="6" t="s">
+      <c r="C285" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E285" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="F283" s="6">
+      <c r="F285" s="6">
         <v>999</v>
       </c>
-      <c r="J283" s="6" t="str">
+      <c r="J285" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hlok</v>
       </c>
-      <c r="O283" s="6" t="b">
+      <c r="O285" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A284" s="6" t="s">
+    <row r="286" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="B284" s="6" t="s">
+      <c r="B286" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="C284" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E284" s="6" t="s">
+      <c r="C286" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E286" s="6" t="s">
         <v>747</v>
       </c>
-      <c r="F284" s="6">
+      <c r="F286" s="6">
         <v>999</v>
       </c>
-      <c r="J284" s="6" t="str">
+      <c r="J286" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hmhl</v>
       </c>
-      <c r="O284" s="6" t="b">
+      <c r="O286" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A285" s="6" t="s">
+    <row r="287" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A287" s="6" t="s">
         <v>746</v>
       </c>
-      <c r="B285" s="6" t="s">
+      <c r="B287" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="C285" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E285" s="6" t="s">
+      <c r="C287" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E287" s="6" t="s">
         <v>748</v>
       </c>
-      <c r="F285" s="6">
+      <c r="F287" s="6">
         <v>999</v>
       </c>
-      <c r="J285" s="6" t="str">
+      <c r="J287" s="6" t="str">
         <f t="shared" si="0"/>
         <v>hmhl</v>
       </c>
-      <c r="O285" s="6" t="b">
+      <c r="O287" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A286" s="4" t="s">
+    <row r="288" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="B286" s="4" t="s">
+      <c r="B288" s="4" t="s">
         <v>925</v>
       </c>
-      <c r="C286" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E286" s="4" t="s">
+      <c r="C288" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E288" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="F286" s="4">
+      <c r="F288" s="4">
         <v>999</v>
       </c>
-      <c r="J286" s="4" t="str">
+      <c r="J288" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pbas</v>
       </c>
-      <c r="O286" s="4" t="b">
+      <c r="O288" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A287" s="4" t="s">
+    <row r="289" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="B287" s="4" t="s">
+      <c r="B289" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="C287" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E287" s="4" t="s">
+      <c r="C289" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E289" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="F287" s="4">
+      <c r="F289" s="4">
         <v>999</v>
       </c>
-      <c r="J287" s="4" t="str">
+      <c r="J289" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ppoi</v>
       </c>
-      <c r="O287" s="4" t="b">
+      <c r="O289" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A288" s="4" t="s">
+    <row r="290" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="B288" s="4" t="s">
+      <c r="B290" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="C288" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E288" s="4" t="s">
+      <c r="C290" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E290" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="F288" s="4">
+      <c r="F290" s="4">
         <v>999</v>
       </c>
-      <c r="J288" s="4" t="str">
+      <c r="J290" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pskl</v>
       </c>
-      <c r="K288" s="4" t="s">
+      <c r="K290" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="O288" s="4" t="b">
+      <c r="O290" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A289" s="4" t="s">
+    <row r="291" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A291" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="B289" s="4" t="s">
+      <c r="B291" s="4" t="s">
         <v>924</v>
       </c>
-      <c r="C289" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E289" s="4" t="s">
+      <c r="C291" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E291" s="4" t="s">
         <v>928</v>
       </c>
-      <c r="F289" s="4">
+      <c r="F291" s="4">
         <v>999</v>
       </c>
-      <c r="J289" s="4" t="str">
+      <c r="J291" s="4" t="str">
         <f t="shared" si="0"/>
         <v>prun</v>
       </c>
-      <c r="O289" s="4" t="b">
+      <c r="O291" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A290" s="4" t="s">
+    <row r="292" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="B290" s="4" t="s">
+      <c r="B292" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="C290" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E290" s="4" t="s">
+      <c r="C292" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E292" s="4" t="s">
         <v>922</v>
       </c>
-      <c r="F290" s="4">
+      <c r="F292" s="4">
         <v>999</v>
       </c>
-      <c r="J290" s="4" t="str">
+      <c r="J292" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pcbl</v>
       </c>
-      <c r="O290" s="4" t="b">
+      <c r="O292" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A291" s="4" t="s">
+    <row r="293" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A293" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="B291" s="4" t="s">
+      <c r="B293" s="4" t="s">
         <v>921</v>
       </c>
-      <c r="C291" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E291" s="4" t="s">
+      <c r="C293" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E293" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="F291" s="4">
+      <c r="F293" s="4">
         <v>999</v>
       </c>
-      <c r="J291" s="4" t="str">
+      <c r="J293" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pcbl</v>
       </c>
-      <c r="O291" s="4" t="b">
+      <c r="O293" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A292" s="4" t="s">
+    <row r="294" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B292" s="4" t="s">
+      <c r="B294" s="4" t="s">
         <v>906</v>
       </c>
-      <c r="C292" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E292" s="4" t="s">
+      <c r="C294" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E294" s="4" t="s">
         <v>894</v>
       </c>
-      <c r="F292" s="4">
+      <c r="F294" s="4">
         <v>999</v>
       </c>
-      <c r="J292" s="4" t="str">
+      <c r="J294" s="4" t="str">
         <f t="shared" si="0"/>
         <v>psdm</v>
       </c>
-      <c r="K292" s="4" t="s">
+      <c r="K294" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="L292" s="4" t="s">
+      <c r="L294" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="O292" s="4" t="b">
+      <c r="O294" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A293" s="4" t="s">
+    <row r="295" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="B293" s="4" t="s">
+      <c r="B295" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="C293" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E293" s="4" t="s">
+      <c r="C295" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E295" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="F293" s="4">
+      <c r="F295" s="4">
         <v>999</v>
       </c>
-      <c r="J293" s="4" t="str">
+      <c r="J295" s="4" t="str">
         <f t="shared" si="0"/>
         <v>psdm</v>
       </c>
-      <c r="O293" s="4" t="b">
+      <c r="O295" s="4" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O293" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
+  <autoFilter ref="A4:O295" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B272">
+  <conditionalFormatting sqref="B274">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4457D0D-00B0-48FD-BAE5-48816B1545B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C96D30-F6EA-4D11-A017-E450D7B97BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="951">
   <si>
     <t>id</t>
   </si>
@@ -2896,9 +2896,6 @@
     <t>atpts</t>
   </si>
   <si>
-    <t>(d) =&gt; (d.setStat("rtmaxhp", {value:Math.floor(d.getStat("maxhp").value * (1 + d.getStat("mhex").value / 100)+d.getStat("vit").value*10)}))</t>
-  </si>
-  <si>
     <t>maxhp,mhex,vit</t>
   </si>
   <si>
@@ -2930,6 +2927,9 @@
   </si>
   <si>
     <t>(d) =&gt; (d.getStat("rtmaxmp").value - d.getStat("rtmp").value)</t>
+  </si>
+  <si>
+    <t>(d) =&gt; (d.setStat("rtmaxhp", {value:Math.floor(d.getStat("maxhp").value * (1 + d.getStat("mhex").value / 100)+d.getStat("vit").value*2)}))</t>
   </si>
 </sst>
 </file>
@@ -3701,10 +3701,10 @@
         <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -3735,10 +3735,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>943</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>944</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>153</v>
@@ -3750,10 +3750,10 @@
         <v>44</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -3841,10 +3841,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>947</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>948</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>153</v>
@@ -3856,10 +3856,10 @@
         <v>54</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -7754,13 +7754,13 @@
         <v>938</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E221" s="2" t="s">
         <v>941</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>942</v>
       </c>
       <c r="F221" s="1">
         <v>804</v>

--- a/configs/Stat.xlsx
+++ b/configs/Stat.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C96D30-F6EA-4D11-A017-E450D7B97BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCFA5E6-27BF-4ACF-B56D-A78ED490C816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$P$295</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="964">
   <si>
     <t>id</t>
   </si>
@@ -2930,6 +2930,45 @@
   </si>
   <si>
     <t>(d) =&gt; (d.setStat("rtmaxhp", {value:Math.floor(d.getStat("maxhp").value * (1 + d.getStat("mhex").value / 100)+d.getStat("vit").value*2)}))</t>
+  </si>
+  <si>
+    <t>statType</t>
+  </si>
+  <si>
+    <t>Enum:StatType</t>
+  </si>
+  <si>
+    <t>属性分类</t>
+  </si>
+  <si>
+    <t>primary</t>
+  </si>
+  <si>
+    <t>utility</t>
+  </si>
+  <si>
+    <t>dmg</t>
+  </si>
+  <si>
+    <t>offensive</t>
+  </si>
+  <si>
+    <t>defensive</t>
+  </si>
+  <si>
+    <t>socket</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>legendary</t>
   </si>
 </sst>
 </file>
@@ -3421,22 +3460,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:O295"/>
+  <dimension ref="A1:P295"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="51.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5703125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3450,40 +3490,43 @@
         <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>165</v>
       </c>
@@ -3497,45 +3540,48 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>773</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>773</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>319</v>
       </c>
@@ -3549,40 +3595,43 @@
         <v>169</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>392</v>
       </c>
@@ -3593,13 +3642,16 @@
         <v>393</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>393</v>
       </c>
@@ -3610,13 +3662,16 @@
         <v>393</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>394</v>
       </c>
@@ -3627,13 +3682,16 @@
         <v>393</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>395</v>
       </c>
@@ -3644,13 +3702,16 @@
         <v>393</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -3661,13 +3722,16 @@
         <v>153</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3678,13 +3742,16 @@
         <v>153</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3695,19 +3762,22 @@
         <v>153</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>43</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -3718,22 +3788,25 @@
         <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>44</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="I12" s="1" t="b">
+      <c r="J12" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>942</v>
       </c>
@@ -3744,19 +3817,22 @@
         <v>153</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>44</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -3767,13 +3843,16 @@
         <v>153</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -3784,13 +3863,16 @@
         <v>153</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -3801,19 +3883,22 @@
         <v>153</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>53</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -3824,22 +3909,25 @@
         <v>153</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>54</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="I17" s="1" t="b">
+      <c r="J17" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>946</v>
       </c>
@@ -3850,19 +3938,22 @@
         <v>153</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>54</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
@@ -3873,13 +3964,16 @@
         <v>153</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
@@ -3890,13 +3984,16 @@
         <v>153</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
@@ -3907,13 +4004,16 @@
         <v>153</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>321</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>74</v>
       </c>
@@ -3924,13 +4024,16 @@
         <v>153</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>322</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>408</v>
       </c>
@@ -3941,13 +4044,16 @@
         <v>153</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>661</v>
       </c>
@@ -3958,13 +4064,16 @@
         <v>153</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>331</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>662</v>
       </c>
@@ -3975,13 +4084,16 @@
         <v>153</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>278</v>
       </c>
@@ -3992,13 +4104,16 @@
         <v>154</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>279</v>
       </c>
@@ -4009,13 +4124,16 @@
         <v>154</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>280</v>
       </c>
@@ -4026,13 +4144,16 @@
         <v>154</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>281</v>
       </c>
@@ -4043,13 +4164,16 @@
         <v>154</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>282</v>
       </c>
@@ -4060,13 +4184,16 @@
         <v>154</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>443</v>
       </c>
@@ -4077,13 +4204,16 @@
         <v>153</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="F31" s="1">
+      <c r="G31" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>444</v>
       </c>
@@ -4094,13 +4224,16 @@
         <v>153</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="F32" s="1">
+      <c r="G32" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>445</v>
       </c>
@@ -4111,13 +4244,16 @@
         <v>153</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="F33" s="1">
+      <c r="G33" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>446</v>
       </c>
@@ -4128,13 +4264,16 @@
         <v>153</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>447</v>
       </c>
@@ -4145,13 +4284,16 @@
         <v>153</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="F35" s="1">
+      <c r="G35" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>448</v>
       </c>
@@ -4162,13 +4304,16 @@
         <v>153</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G36" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>449</v>
       </c>
@@ -4179,13 +4324,16 @@
         <v>153</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="F37" s="1">
+      <c r="G37" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>450</v>
       </c>
@@ -4196,13 +4344,16 @@
         <v>153</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F38" s="1">
+      <c r="G38" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>451</v>
       </c>
@@ -4213,13 +4364,16 @@
         <v>153</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G39" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>452</v>
       </c>
@@ -4230,13 +4384,16 @@
         <v>153</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="F40" s="1">
+      <c r="G40" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>18</v>
       </c>
@@ -4247,13 +4404,16 @@
         <v>154</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="F41" s="1">
+      <c r="G41" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -4264,13 +4424,16 @@
         <v>154</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="F42" s="1">
+      <c r="G42" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
@@ -4281,13 +4444,16 @@
         <v>154</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="F43" s="1">
+      <c r="G43" s="1">
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -4298,13 +4464,16 @@
         <v>154</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="F44" s="1">
+      <c r="G44" s="1">
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
@@ -4315,13 +4484,16 @@
         <v>154</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="F45" s="1">
+      <c r="G45" s="1">
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
@@ -4332,13 +4504,16 @@
         <v>153</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="F46" s="1">
+      <c r="G46" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
@@ -4349,13 +4524,16 @@
         <v>153</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="F47" s="1">
+      <c r="G47" s="1">
         <v>202</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
@@ -4366,13 +4544,16 @@
         <v>153</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F48" s="1">
+      <c r="G48" s="1">
         <v>203</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
@@ -4383,13 +4564,16 @@
         <v>153</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="F49" s="1">
+      <c r="G49" s="1">
         <v>204</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
@@ -4400,13 +4584,16 @@
         <v>153</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="F50" s="1">
+      <c r="G50" s="1">
         <v>205</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>54</v>
       </c>
@@ -4417,13 +4604,16 @@
         <v>153</v>
       </c>
       <c r="E51" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="F51" s="1">
+      <c r="G51" s="1">
         <v>206</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>55</v>
       </c>
@@ -4434,13 +4624,16 @@
         <v>153</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="F52" s="1">
+      <c r="G52" s="1">
         <v>207</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -4451,13 +4644,16 @@
         <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="F53" s="1">
+      <c r="G53" s="1">
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -4468,13 +4664,16 @@
         <v>153</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="F54" s="1">
+      <c r="G54" s="1">
         <v>209</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -4485,13 +4684,16 @@
         <v>153</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="F55" s="1">
+      <c r="G55" s="1">
         <v>210</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>410</v>
       </c>
@@ -4502,13 +4704,16 @@
         <v>153</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F56" s="1">
+      <c r="G56" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>411</v>
       </c>
@@ -4519,13 +4724,16 @@
         <v>153</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F57" s="1">
+      <c r="G57" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>412</v>
       </c>
@@ -4536,13 +4744,16 @@
         <v>153</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="F58" s="1">
+      <c r="G58" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>23</v>
       </c>
@@ -4553,13 +4764,16 @@
         <v>153</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="F59" s="1">
+      <c r="G59" s="1">
         <v>221</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>24</v>
       </c>
@@ -4570,13 +4784,16 @@
         <v>153</v>
       </c>
       <c r="E60" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="F60" s="1">
+      <c r="G60" s="1">
         <v>222</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>25</v>
       </c>
@@ -4587,13 +4804,16 @@
         <v>153</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="F61" s="1">
+      <c r="G61" s="1">
         <v>223</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>26</v>
       </c>
@@ -4604,13 +4824,16 @@
         <v>153</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="F62" s="1">
+      <c r="G62" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>27</v>
       </c>
@@ -4621,13 +4844,16 @@
         <v>153</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="F63" s="1">
+      <c r="G63" s="1">
         <v>225</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>38</v>
       </c>
@@ -4641,13 +4867,16 @@
         <v>157</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="F64" s="1">
+      <c r="G64" s="1">
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>39</v>
       </c>
@@ -4661,13 +4890,16 @@
         <v>157</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F65" s="1">
+      <c r="G65" s="1">
         <v>227</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>40</v>
       </c>
@@ -4681,13 +4913,16 @@
         <v>158</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F66" s="1">
+      <c r="G66" s="1">
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>397</v>
       </c>
@@ -4701,13 +4936,16 @@
         <v>401</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="F67" s="1">
+      <c r="G67" s="1">
         <v>229</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>398</v>
       </c>
@@ -4721,13 +4959,16 @@
         <v>401</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="F68" s="1">
+      <c r="G68" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>404</v>
       </c>
@@ -4741,13 +4982,16 @@
         <v>405</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F69" s="1">
+      <c r="G69" s="1">
         <v>231</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>402</v>
       </c>
@@ -4758,13 +5002,16 @@
         <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="F70" s="1">
+      <c r="G70" s="1">
         <v>232</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>28</v>
       </c>
@@ -4775,13 +5022,16 @@
         <v>153</v>
       </c>
       <c r="E71" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F71" s="1">
+      <c r="G71" s="1">
         <v>241</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>29</v>
       </c>
@@ -4792,13 +5042,16 @@
         <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F72" s="1">
+      <c r="G72" s="1">
         <v>242</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>30</v>
       </c>
@@ -4809,13 +5062,16 @@
         <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="F73" s="1">
+      <c r="G73" s="1">
         <v>243</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>31</v>
       </c>
@@ -4826,13 +5082,16 @@
         <v>153</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="F74" s="1">
+      <c r="G74" s="1">
         <v>244</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>32</v>
       </c>
@@ -4843,13 +5102,16 @@
         <v>153</v>
       </c>
       <c r="E75" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="F75" s="1">
+      <c r="G75" s="1">
         <v>245</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>33</v>
       </c>
@@ -4860,19 +5122,22 @@
         <v>153</v>
       </c>
       <c r="E76" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F76" s="1">
+      <c r="G76" s="1">
         <v>251</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="I76" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>34</v>
       </c>
@@ -4883,19 +5148,22 @@
         <v>153</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F77" s="1">
+      <c r="G77" s="1">
         <v>252</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="I77" s="1" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>35</v>
       </c>
@@ -4906,19 +5174,22 @@
         <v>153</v>
       </c>
       <c r="E78" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F78" s="1">
+      <c r="G78" s="1">
         <v>253</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>36</v>
       </c>
@@ -4929,19 +5200,22 @@
         <v>153</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F79" s="1">
+      <c r="G79" s="1">
         <v>254</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H79" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>37</v>
       </c>
@@ -4952,19 +5226,22 @@
         <v>153</v>
       </c>
       <c r="E80" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F80" s="1">
+      <c r="G80" s="1">
         <v>255</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="I80" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>391</v>
       </c>
@@ -4975,13 +5252,16 @@
         <v>153</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="F81" s="1">
+      <c r="G81" s="1">
         <v>261</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>75</v>
       </c>
@@ -4992,13 +5272,16 @@
         <v>153</v>
       </c>
       <c r="E82" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="F82" s="1">
+      <c r="G82" s="1">
         <v>262</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>76</v>
       </c>
@@ -5009,13 +5292,16 @@
         <v>153</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="F83" s="1">
+      <c r="G83" s="1">
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>77</v>
       </c>
@@ -5026,13 +5312,16 @@
         <v>153</v>
       </c>
       <c r="E84" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="F84" s="1">
+      <c r="G84" s="1">
         <v>264</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>78</v>
       </c>
@@ -5043,13 +5332,16 @@
         <v>153</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="F85" s="1">
+      <c r="G85" s="1">
         <v>265</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>308</v>
       </c>
@@ -5060,13 +5352,16 @@
         <v>153</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F86" s="1">
+      <c r="G86" s="1">
         <v>271</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>309</v>
       </c>
@@ -5077,13 +5372,16 @@
         <v>153</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="F87" s="1">
+      <c r="G87" s="1">
         <v>272</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>310</v>
       </c>
@@ -5094,13 +5392,16 @@
         <v>153</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="F88" s="1">
+      <c r="G88" s="1">
         <v>273</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>311</v>
       </c>
@@ -5111,13 +5412,16 @@
         <v>153</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="F89" s="1">
+      <c r="G89" s="1">
         <v>274</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>312</v>
       </c>
@@ -5128,13 +5432,16 @@
         <v>153</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="F90" s="1">
+      <c r="G90" s="1">
         <v>275</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>41</v>
       </c>
@@ -5145,13 +5452,16 @@
         <v>153</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F91" s="1">
+      <c r="G91" s="1">
         <v>281</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>42</v>
       </c>
@@ -5162,13 +5472,16 @@
         <v>153</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F92" s="1">
+      <c r="G92" s="1">
         <v>282</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,13 +5492,16 @@
         <v>153</v>
       </c>
       <c r="E93" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="F93" s="1">
+      <c r="G93" s="1">
         <v>283</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>44</v>
       </c>
@@ -5196,13 +5512,16 @@
         <v>153</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="F94" s="1">
+      <c r="G94" s="1">
         <v>284</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>45</v>
       </c>
@@ -5213,13 +5532,16 @@
         <v>393</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="F95" s="1">
+      <c r="G95" s="1">
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>418</v>
       </c>
@@ -5230,13 +5552,16 @@
         <v>153</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F96" s="1">
+      <c r="G96" s="1">
         <v>286</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>658</v>
       </c>
@@ -5247,13 +5572,16 @@
         <v>153</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F97" s="1">
+      <c r="G97" s="1">
         <v>287</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>470</v>
       </c>
@@ -5264,13 +5592,16 @@
         <v>153</v>
       </c>
       <c r="E98" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="F98" s="1">
+      <c r="G98" s="1">
         <v>289</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>673</v>
       </c>
@@ -5281,13 +5612,16 @@
         <v>153</v>
       </c>
       <c r="E99" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="F99" s="1">
+      <c r="G99" s="1">
         <v>290</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>406</v>
       </c>
@@ -5298,13 +5632,16 @@
         <v>153</v>
       </c>
       <c r="E100" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="F100" s="1">
+      <c r="G100" s="1">
         <v>291</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>379</v>
       </c>
@@ -5314,11 +5651,14 @@
       <c r="C101" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="F101" s="1">
+      <c r="E101" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="G101" s="1">
         <v>292</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>381</v>
       </c>
@@ -5328,11 +5668,14 @@
       <c r="C102" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="F102" s="1">
+      <c r="E102" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="G102" s="1">
         <v>293</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>759</v>
       </c>
@@ -5343,13 +5686,16 @@
         <v>393</v>
       </c>
       <c r="E103" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="F103" s="1">
+      <c r="G103" s="1">
         <v>999</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>46</v>
       </c>
@@ -5360,13 +5706,16 @@
         <v>153</v>
       </c>
       <c r="E104" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F104" s="1">
+      <c r="G104" s="1">
         <v>301</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>47</v>
       </c>
@@ -5377,13 +5726,16 @@
         <v>153</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="F105" s="1">
+      <c r="G105" s="1">
         <v>302</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>48</v>
       </c>
@@ -5394,13 +5746,16 @@
         <v>153</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F106" s="1">
+      <c r="G106" s="1">
         <v>303</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>276</v>
       </c>
@@ -5411,13 +5766,16 @@
         <v>153</v>
       </c>
       <c r="E107" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="F107" s="1">
+      <c r="G107" s="1">
         <v>304</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>292</v>
       </c>
@@ -5428,13 +5786,16 @@
         <v>153</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="F108" s="1">
+      <c r="G108" s="1">
         <v>305</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>293</v>
       </c>
@@ -5445,13 +5806,16 @@
         <v>153</v>
       </c>
       <c r="E109" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="F109" s="1">
+      <c r="G109" s="1">
         <v>306</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>294</v>
       </c>
@@ -5462,13 +5826,16 @@
         <v>153</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="F110" s="1">
+      <c r="G110" s="1">
         <v>307</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>295</v>
       </c>
@@ -5479,13 +5846,16 @@
         <v>153</v>
       </c>
       <c r="E111" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="F111" s="1">
+      <c r="G111" s="1">
         <v>308</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>72</v>
       </c>
@@ -5496,13 +5866,16 @@
         <v>153</v>
       </c>
       <c r="E112" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="F112" s="1">
+      <c r="G112" s="1">
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>676</v>
       </c>
@@ -5513,13 +5886,16 @@
         <v>153</v>
       </c>
       <c r="E113" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="F113" s="1">
+      <c r="G113" s="1">
         <v>310</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>667</v>
       </c>
@@ -5530,13 +5906,16 @@
         <v>393</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="F114" s="1">
+      <c r="G114" s="1">
         <v>311</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>670</v>
       </c>
@@ -5547,13 +5926,16 @@
         <v>153</v>
       </c>
       <c r="E115" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="F115" s="1">
+      <c r="G115" s="1">
         <v>312</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>387</v>
       </c>
@@ -5564,13 +5946,16 @@
         <v>425</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="F116" s="1">
+      <c r="G116" s="1">
         <v>313</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>388</v>
       </c>
@@ -5581,13 +5966,16 @@
         <v>425</v>
       </c>
       <c r="E117" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="F117" s="1">
+      <c r="G117" s="1">
         <v>314</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>441</v>
       </c>
@@ -5598,13 +5986,16 @@
         <v>425</v>
       </c>
       <c r="E118" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="F118" s="1">
+      <c r="G118" s="1">
         <v>315</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>59</v>
       </c>
@@ -5615,16 +6006,19 @@
         <v>393</v>
       </c>
       <c r="E119" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="F119" s="1">
+      <c r="G119" s="1">
         <v>401</v>
       </c>
-      <c r="M119" s="1" t="s">
+      <c r="N119" s="1" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>60</v>
       </c>
@@ -5635,16 +6029,19 @@
         <v>393</v>
       </c>
       <c r="E120" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="F120" s="1">
+      <c r="G120" s="1">
         <v>402</v>
       </c>
-      <c r="M120" s="1" t="s">
+      <c r="N120" s="1" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>61</v>
       </c>
@@ -5655,16 +6052,19 @@
         <v>393</v>
       </c>
       <c r="E121" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F121" s="1">
+      <c r="G121" s="1">
         <v>403</v>
       </c>
-      <c r="M121" s="1" t="s">
+      <c r="N121" s="1" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>419</v>
       </c>
@@ -5675,19 +6075,22 @@
         <v>393</v>
       </c>
       <c r="E122" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="F122" s="1">
+      <c r="G122" s="1">
         <v>404</v>
       </c>
-      <c r="M122" s="1" t="s">
+      <c r="N122" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="N122" s="1" t="s">
+      <c r="O122" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>420</v>
       </c>
@@ -5698,19 +6101,22 @@
         <v>393</v>
       </c>
       <c r="E123" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="F123" s="1">
+      <c r="G123" s="1">
         <v>405</v>
       </c>
-      <c r="M123" s="1" t="s">
+      <c r="N123" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="N123" s="1" t="s">
+      <c r="O123" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>652</v>
       </c>
@@ -5721,19 +6127,22 @@
         <v>393</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="F124" s="1">
+      <c r="G124" s="1">
         <v>406</v>
       </c>
-      <c r="M124" s="1" t="s">
+      <c r="N124" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="N124" s="1" t="s">
+      <c r="O124" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>62</v>
       </c>
@@ -5744,16 +6153,19 @@
         <v>393</v>
       </c>
       <c r="E125" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F125" s="1">
+      <c r="G125" s="1">
         <v>407</v>
       </c>
-      <c r="M125" s="1" t="s">
+      <c r="N125" s="1" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>63</v>
       </c>
@@ -5764,16 +6176,19 @@
         <v>393</v>
       </c>
       <c r="E126" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="F126" s="1">
+      <c r="G126" s="1">
         <v>408</v>
       </c>
-      <c r="M126" s="1" t="s">
+      <c r="N126" s="1" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>64</v>
       </c>
@@ -5784,16 +6199,19 @@
         <v>393</v>
       </c>
       <c r="E127" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="F127" s="1">
+      <c r="G127" s="1">
         <v>409</v>
       </c>
-      <c r="M127" s="1" t="s">
+      <c r="N127" s="1" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>421</v>
       </c>
@@ -5804,19 +6222,22 @@
         <v>393</v>
       </c>
       <c r="E128" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="F128" s="1">
+      <c r="G128" s="1">
         <v>410</v>
       </c>
-      <c r="M128" s="1" t="s">
+      <c r="N128" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="N128" s="1" t="s">
+      <c r="O128" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>422</v>
       </c>
@@ -5827,19 +6248,22 @@
         <v>393</v>
       </c>
       <c r="E129" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="F129" s="1">
+      <c r="G129" s="1">
         <v>411</v>
       </c>
-      <c r="M129" s="1" t="s">
+      <c r="N129" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="N129" s="1" t="s">
+      <c r="O129" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>653</v>
       </c>
@@ -5850,19 +6274,22 @@
         <v>393</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="F130" s="1">
+      <c r="G130" s="1">
         <v>412</v>
       </c>
-      <c r="M130" s="1" t="s">
+      <c r="N130" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="N130" s="1" t="s">
+      <c r="O130" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>65</v>
       </c>
@@ -5873,16 +6300,19 @@
         <v>393</v>
       </c>
       <c r="E131" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="F131" s="1">
+      <c r="G131" s="1">
         <v>413</v>
       </c>
-      <c r="M131" s="1" t="s">
+      <c r="N131" s="1" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>66</v>
       </c>
@@ -5893,16 +6323,19 @@
         <v>393</v>
       </c>
       <c r="E132" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F132" s="1">
+      <c r="G132" s="1">
         <v>414</v>
       </c>
-      <c r="M132" s="1" t="s">
+      <c r="N132" s="1" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>67</v>
       </c>
@@ -5913,16 +6346,19 @@
         <v>393</v>
       </c>
       <c r="E133" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="F133" s="1">
+      <c r="G133" s="1">
         <v>415</v>
       </c>
-      <c r="M133" s="1" t="s">
+      <c r="N133" s="1" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>423</v>
       </c>
@@ -5933,19 +6369,22 @@
         <v>393</v>
       </c>
       <c r="E134" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F134" s="1">
+      <c r="G134" s="1">
         <v>416</v>
       </c>
-      <c r="M134" s="1" t="s">
+      <c r="N134" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="N134" s="1" t="s">
+      <c r="O134" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>424</v>
       </c>
@@ -5956,19 +6395,22 @@
         <v>393</v>
       </c>
       <c r="E135" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="F135" s="1">
+      <c r="G135" s="1">
         <v>417</v>
       </c>
-      <c r="M135" s="1" t="s">
+      <c r="N135" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="N135" s="1" t="s">
+      <c r="O135" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>655</v>
       </c>
@@ -5979,19 +6421,22 @@
         <v>393</v>
       </c>
       <c r="E136" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="F136" s="1">
+      <c r="G136" s="1">
         <v>418</v>
       </c>
-      <c r="M136" s="1" t="s">
+      <c r="N136" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="N136" s="1" t="s">
+      <c r="O136" s="1" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>68</v>
       </c>
@@ -6002,16 +6447,19 @@
         <v>393</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="F137" s="1">
+      <c r="G137" s="1">
         <v>419</v>
       </c>
-      <c r="M137" s="1" t="s">
+      <c r="N137" s="1" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>69</v>
       </c>
@@ -6022,16 +6470,19 @@
         <v>393</v>
       </c>
       <c r="E138" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="F138" s="1">
+      <c r="G138" s="1">
         <v>420</v>
       </c>
-      <c r="M138" s="1" t="s">
+      <c r="N138" s="1" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>70</v>
       </c>
@@ -6042,16 +6493,19 @@
         <v>393</v>
       </c>
       <c r="E139" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F139" s="1">
+      <c r="G139" s="1">
         <v>421</v>
       </c>
-      <c r="M139" s="1" t="s">
+      <c r="N139" s="1" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>897</v>
       </c>
@@ -6062,16 +6516,19 @@
         <v>393</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="F140" s="1">
+      <c r="G140" s="1">
         <v>422</v>
       </c>
-      <c r="M140" s="1" t="s">
+      <c r="N140" s="1" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>71</v>
       </c>
@@ -6081,11 +6538,14 @@
       <c r="C141" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F141" s="1">
+      <c r="E141" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="G141" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>79</v>
       </c>
@@ -6096,19 +6556,22 @@
         <v>393</v>
       </c>
       <c r="E142" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="F142" s="1">
+      <c r="G142" s="1">
         <v>431</v>
       </c>
-      <c r="J142" s="1" t="s">
+      <c r="K142" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="N142" s="1" t="s">
+      <c r="O142" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>80</v>
       </c>
@@ -6119,19 +6582,22 @@
         <v>393</v>
       </c>
       <c r="E143" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="F143" s="1">
+      <c r="G143" s="1">
         <v>432</v>
       </c>
-      <c r="J143" s="1" t="s">
+      <c r="K143" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="N143" s="1" t="s">
+      <c r="O143" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>81</v>
       </c>
@@ -6142,19 +6608,22 @@
         <v>393</v>
       </c>
       <c r="E144" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="F144" s="1">
+      <c r="G144" s="1">
         <v>433</v>
       </c>
-      <c r="J144" s="1" t="s">
+      <c r="K144" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="N144" s="1" t="s">
+      <c r="O144" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>82</v>
       </c>
@@ -6165,19 +6634,22 @@
         <v>393</v>
       </c>
       <c r="E145" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="F145" s="1">
+      <c r="G145" s="1">
         <v>434</v>
       </c>
-      <c r="J145" s="1" t="s">
+      <c r="K145" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="N145" s="1" t="s">
+      <c r="O145" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>83</v>
       </c>
@@ -6188,19 +6660,22 @@
         <v>393</v>
       </c>
       <c r="E146" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F146" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="F146" s="1">
+      <c r="G146" s="1">
         <v>435</v>
       </c>
-      <c r="J146" s="1" t="s">
+      <c r="K146" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="N146" s="1" t="s">
+      <c r="O146" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>84</v>
       </c>
@@ -6211,19 +6686,22 @@
         <v>393</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F147" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="F147" s="1">
+      <c r="G147" s="1">
         <v>436</v>
       </c>
-      <c r="J147" s="1" t="s">
+      <c r="K147" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="N147" s="1" t="s">
+      <c r="O147" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>85</v>
       </c>
@@ -6234,16 +6712,19 @@
         <v>393</v>
       </c>
       <c r="E148" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="F148" s="1">
+      <c r="G148" s="1">
         <v>437</v>
       </c>
-      <c r="J148" s="1" t="s">
+      <c r="K148" s="1" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>86</v>
       </c>
@@ -6254,16 +6735,19 @@
         <v>393</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F149" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="F149" s="1">
+      <c r="G149" s="1">
         <v>438</v>
       </c>
-      <c r="J149" s="1" t="s">
+      <c r="K149" s="1" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>87</v>
       </c>
@@ -6274,16 +6758,19 @@
         <v>393</v>
       </c>
       <c r="E150" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F150" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="F150" s="1">
+      <c r="G150" s="1">
         <v>439</v>
       </c>
-      <c r="J150" s="1" t="s">
+      <c r="K150" s="1" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>88</v>
       </c>
@@ -6294,16 +6781,19 @@
         <v>393</v>
       </c>
       <c r="E151" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="F151" s="1">
+      <c r="G151" s="1">
         <v>440</v>
       </c>
-      <c r="J151" s="1" t="s">
+      <c r="K151" s="1" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>89</v>
       </c>
@@ -6314,16 +6804,19 @@
         <v>393</v>
       </c>
       <c r="E152" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="F152" s="1">
+      <c r="G152" s="1">
         <v>441</v>
       </c>
-      <c r="J152" s="1" t="s">
+      <c r="K152" s="1" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>90</v>
       </c>
@@ -6334,16 +6827,19 @@
         <v>393</v>
       </c>
       <c r="E153" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="F153" s="1">
+      <c r="G153" s="1">
         <v>442</v>
       </c>
-      <c r="J153" s="1" t="s">
+      <c r="K153" s="1" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>91</v>
       </c>
@@ -6354,19 +6850,22 @@
         <v>393</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="F154" s="1">
+      <c r="G154" s="1">
         <v>443</v>
       </c>
-      <c r="J154" s="1" t="s">
+      <c r="K154" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="N154" s="1" t="s">
+      <c r="O154" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>92</v>
       </c>
@@ -6377,19 +6876,22 @@
         <v>393</v>
       </c>
       <c r="E155" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="F155" s="1">
+      <c r="G155" s="1">
         <v>444</v>
       </c>
-      <c r="J155" s="1" t="s">
+      <c r="K155" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="N155" s="1" t="s">
+      <c r="O155" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>93</v>
       </c>
@@ -6400,19 +6902,22 @@
         <v>393</v>
       </c>
       <c r="E156" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="F156" s="1">
+      <c r="G156" s="1">
         <v>445</v>
       </c>
-      <c r="J156" s="1" t="s">
+      <c r="K156" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="N156" s="1" t="s">
+      <c r="O156" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>94</v>
       </c>
@@ -6423,19 +6928,22 @@
         <v>393</v>
       </c>
       <c r="E157" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F157" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="F157" s="1">
+      <c r="G157" s="1">
         <v>446</v>
       </c>
-      <c r="J157" s="1" t="s">
+      <c r="K157" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="N157" s="1" t="s">
+      <c r="O157" s="1" t="s">
         <v>813</v>
       </c>
    